--- a/mapping_oracle_full.xlsx
+++ b/mapping_oracle_full.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T228"/>
+  <dimension ref="A1:U228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,30 +502,35 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>catalog_distinct_coverage</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>catalog_confidence</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>llm_data_confidence</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>llm_final_confidence</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>reviewer_status</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>correct_client_column</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>reviewer_note</t>
         </is>
@@ -575,15 +580,16 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -623,21 +629,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the expected role of 'Base CBS' and provide no valid mapping evidence.</t>
+          <t>All candidates have semantic header conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -654,7 +661,7 @@
         <v>0.7843</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7746</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.009599999999999999</v>
@@ -677,21 +684,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family for 'Aliquota CBS'.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -737,15 +745,16 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -791,15 +800,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -845,15 +855,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -893,21 +904,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates have semantic header conflicts with the canonical column, indicating incompatible tax roles.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -947,21 +959,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column, indicating incompatible tax-family roles.</t>
+          <t>No suitable candidate due to semantic header conflicts and lack of relevant data evidence.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1001,21 +1014,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates have a semantic header conflict with the expected tax base role.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1055,21 +1069,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family for 'Aliquota IBSM'.</t>
+          <t>All candidates have semantic header conflicts with the IBSM tax type, indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1109,21 +1124,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the IBSM value, indicating they do not represent the same business meaning.</t>
+          <t>All candidates conflict with the tax-family of the target column and provide no valid mapping evidence.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1163,21 +1179,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended meaning of 'Isentas IBSM'.</t>
+          <t>All candidates have a tax-family conflict with the IBSM column, indicating incompatible semantic roles.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1217,21 +1234,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the original column, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have a semantic header conflict with the 'Outras IBSM' column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1271,21 +1289,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the target column, indicating incompatible tax roles.</t>
+          <t>All candidates have a semantic header conflict with the target column, and the data evidence is insufficient.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1325,21 +1344,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type.</t>
+          <t>All candidates have semantic header conflicts with the target column.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1379,21 +1399,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the 'Base IBS' column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1407,10 +1428,10 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>0.7886</v>
+        <v>0.7885</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7842</v>
+        <v>0.7841</v>
       </c>
       <c r="G18" t="n">
         <v>0.0044</v>
@@ -1433,21 +1454,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of the target column, and no strong evidence supports a mapping.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended role of 'Aliquota IBS'.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1487,21 +1509,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the 'Valor IBS' column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the tax family, and the evidence does not support a mapping.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1518,7 +1541,7 @@
         <v>0.8008999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.791</v>
+        <v>0.7911</v>
       </c>
       <c r="G20" t="n">
         <v>0.009900000000000001</v>
@@ -1541,21 +1564,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>All candidates conflict semantically with the tax family of the source column, and no distinctive evidence supports a mapping.</t>
+          <t>All candidates have a semantic header conflict with the tax-family context, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1601,15 +1625,16 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1655,15 +1680,16 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1680,7 +1706,7 @@
         <v>0.8319</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8288</v>
+        <v>0.8287</v>
       </c>
       <c r="G23" t="n">
         <v>0.0032</v>
@@ -1703,21 +1729,22 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate found due to lack of relevant data evidence.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>0.8319</v>
-      </c>
-      <c r="R23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1734,10 +1761,10 @@
         <v>0.8171</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8074</v>
+        <v>0.8073</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0097</v>
+        <v>0.0098</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1757,21 +1784,22 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column 'Base IS' has only zeros, indicating a mismatch in semantic meaning.</t>
+          <t>All candidate columns contain non-zero values, while the source column 'Base IS' has only zeros, indicating no compatible mapping.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1791,7 +1819,7 @@
         <v>0.8058</v>
       </c>
       <c r="G25" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0091</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1811,21 +1839,22 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>All candidates have non-zero values, but none align semantically with 'Aliquota IS', which indicates a tax rate.</t>
+          <t>All candidates have non-zero values, while the model column contains only zeros, indicating a mismatch in data semantics.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1865,21 +1894,22 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>The candidate columns contain non-zero values, while 'Valor IS' has only zeros, indicating a mismatch in semantic meaning.</t>
+          <t>All candidate columns contain non-zero values, while 'Valor IS' has only zeros, indicating a mismatch in semantic roles.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>0.7942</v>
-      </c>
-      <c r="R26" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1896,10 +1926,10 @@
         <v>0.8108</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7993</v>
+        <v>0.7992</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0115</v>
+        <v>0.0116</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1919,21 +1949,22 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the model column is entirely zero.</t>
+          <t>All candidate columns contain non-zero values, while the source column is entirely zero.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1973,21 +2004,22 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column 'Outras IS' has only zeros, indicating no compatible mapping.</t>
+          <t>All candidate columns contain non-zero values, while the source column has only zeros, indicating no compatible mapping.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2004,7 +2036,7 @@
         <v>0.7844</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7778</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0.0067</v>
@@ -2033,15 +2065,16 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2061,7 +2094,7 @@
         <v>0.844</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0529</v>
+        <v>-0.0528</v>
       </c>
       <c r="H30" t="n">
         <v>0.395</v>
@@ -2087,15 +2120,16 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
         <v>0.8</v>
       </c>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>0.8</v>
+      </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2141,15 +2175,16 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>0.7902</v>
-      </c>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
         <v>0.7902</v>
       </c>
-      <c r="R31" t="inlineStr"/>
+      <c r="R31" t="n">
+        <v>0.7902</v>
+      </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2201,15 +2236,16 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0.6669</v>
-      </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>0.8119</v>
+      </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2255,21 +2291,22 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a high name confidence but a significantly lower profile similarity and does not match the expected format of a 9-digit invoice number.</t>
+          <t>The candidate 'NUMERO NF' closely matches the semantic role of 'Nº da Nota Fiscal' with high name confidence and consistent numeric formatting.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="n">
+        <v>0.7833</v>
+      </c>
+      <c r="R33" t="n">
         <v>0.8556</v>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2292,10 +2329,10 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8111</v>
+        <v>0.8112</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1889</v>
+        <v>0.1888</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -2324,6 +2361,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2334,8 +2372,14 @@
           <t>CFOP</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>16</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CFO</t>
+        </is>
+      </c>
       <c r="E35" t="n">
         <v>0.8421</v>
       </c>
@@ -2343,41 +2387,46 @@
         <v>0.8260999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>0.016</v>
+        <v>0.0159</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.8824</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.8542</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>catalog</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>Versioned official cfop codes cover 88.2% of the 17 distinct codes used (66.7% of rows) and uniquely identify this candidate among the available columns.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>cfop</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0.6673</v>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>0.6673</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0.8047</v>
-      </c>
+        <v>0.8824</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2423,21 +2472,22 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>The header 'DESC_PRODUTO' suggests a product description, but the numeric profile indicates mixed content, conflicting with the string nature of 'Descrição'.</t>
+          <t>The header 'DESC_PRODUTO' suggests a product description, but the numeric content indicates it is not compatible with the 'Descrição' column.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="n">
         <v>0.1586</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>0.8823</v>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2451,10 +2501,10 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>0.7706</v>
+        <v>0.7705</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8051</v>
+        <v>0.805</v>
       </c>
       <c r="G37" t="n">
         <v>-0.0345</v>
@@ -2483,15 +2533,16 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="n">
         <v>0.85</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>0.8</v>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2537,15 +2588,16 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
-        <v>0.8175</v>
-      </c>
-      <c r="R38" t="inlineStr"/>
+        <v>0.4187</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.8265</v>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2559,16 +2611,16 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>0.8116</v>
+        <v>0.8288</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8302</v>
+        <v>0.7987</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0187</v>
+        <v>0.0301</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2181</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2585,21 +2637,22 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The header 'NUMERO NF' conflicts semantically with the expected role of 'Nº ID fiscal 1', which is a tax ID, not a document ID.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R39" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2613,16 +2666,16 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>0.7129</v>
+        <v>0.8043</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8043</v>
+        <v>0.7581</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0914</v>
+        <v>0.0462</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4164</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2639,21 +2692,22 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate matches the semantic role of 'Região' based on header names and data evidence.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
-        <v>0.7514</v>
-      </c>
-      <c r="R40" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2673,19 +2727,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.828</v>
+        <v>0.8278</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7922</v>
+        <v>0.7916</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0358</v>
+        <v>0.0362</v>
       </c>
       <c r="H41" t="n">
         <v>0.84</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8316</v>
+        <v>0.8315</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2699,21 +2753,22 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>The header 'TOTAL DO ITEM' aligns with the numeric nature of 'Val.Total NF' and has no semantic conflicts.</t>
+          <t>The 'TOTAL DO ITEM' column has a compatible numeric type and no semantic conflicts, aligning closely with the 'Val.Total NF' values.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="n">
-        <v>0.9368</v>
-      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="n">
-        <v>0.828</v>
-      </c>
-      <c r="R41" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.85</v>
+      </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2768,6 +2823,7 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2822,6 +2878,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2841,19 +2898,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.8065</v>
+        <v>0.8066</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8052</v>
+        <v>0.8045</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0013</v>
+        <v>0.0021</v>
       </c>
       <c r="H44" t="n">
         <v>0.84</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8165</v>
+        <v>0.8166</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2873,15 +2930,16 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
-      <c r="R44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2892,14 +2950,8 @@
           <t>Isentas ICMS</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>21</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>IND TRIB ICMS</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
         <v>0.8794</v>
       </c>
@@ -2910,10 +2962,10 @@
         <v>0.0305</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7498</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8794</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2922,26 +2974,27 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>The header 'IND TRIB ICMS' suggests a tax indicator, but it conflicts with the expected role of 'Isentas ICMS' as a tax exemption amount.</t>
+          <t>The candidate 'IND TRIB IPI' has a semantic header conflict with 'ICMS', indicating a tax-family mismatch.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
-        <v>0.8794</v>
-      </c>
-      <c r="R45" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2952,22 +3005,28 @@
           <t>Outras ICMS</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>21</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
       <c r="E46" t="n">
         <v>0.8968</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8621</v>
+        <v>0.8622</v>
       </c>
       <c r="G46" t="n">
         <v>0.0347</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>0.8968</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2976,26 +3035,27 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a strong name match but lacks relevant data evidence, making it unsuitable.</t>
+          <t>The candidate 'IND TRIB ICMS' has a high name confidence but lacks relevant data evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>0.8968</v>
+      </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3009,13 +3069,13 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7948</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7899</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0049</v>
+        <v>0.005</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -3041,15 +3101,16 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3063,10 +3124,10 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>0.805</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8015</v>
+        <v>0.8014</v>
       </c>
       <c r="G48" t="n">
         <v>0.0035</v>
@@ -3089,21 +3150,22 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the ICEP value, indicating they do not represent the same business meaning.</t>
+          <t>All candidates have semantic header conflicts with the ICEP value, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3126,10 +3188,10 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8939</v>
+        <v>0.8938</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1061</v>
+        <v>0.1062</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -3158,6 +3220,7 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3212,6 +3275,7 @@
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3234,7 +3298,7 @@
         <v>0.8776</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8084</v>
+        <v>0.8085</v>
       </c>
       <c r="G51" t="n">
         <v>0.0692</v>
@@ -3263,15 +3327,16 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>0.8776</v>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3294,10 +3359,10 @@
         <v>0.8832</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8274</v>
+        <v>0.8275</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0558</v>
+        <v>0.0557</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -3317,21 +3382,22 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a high name confidence but lacks supporting data evidence, and the all-zero profile indicates no valid mapping.</t>
+          <t>The candidate 'IND TRIB IPI' has a high name confidence but lacks supporting data evidence, as it conflicts with the IPI tax type.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
         <v>0.8832</v>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3386,6 +3452,7 @@
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3440,6 +3507,7 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3494,6 +3562,7 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3548,6 +3617,7 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3561,7 +3631,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>0.7675</v>
+        <v>0.7674</v>
       </c>
       <c r="F57" t="n">
         <v>0.7665999999999999</v>
@@ -3587,21 +3657,22 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>The 'Frete' column contains only zeros, providing no evidence to support a mapping to any candidate.</t>
+          <t>All candidate columns are unrelated to 'Frete' as they either represent product codes, descriptions, or other identifiers, with no relevant numeric or monetary values.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
         <v>0.7544</v>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3618,7 +3689,7 @@
         <v>0.8061</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7995</v>
+        <v>0.7996</v>
       </c>
       <c r="G58" t="n">
         <v>0.0066</v>
@@ -3641,21 +3712,22 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>All candidate columns contain only zeros or non-numeric values, making them incompatible with the 'Seguros' column.</t>
+          <t>All candidates are incompatible due to distinct content types and all-zero evidence.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
-      <c r="R58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>0.7861</v>
+      </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3695,21 +3767,22 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>The candidate columns do not match the semantic role of 'Observações', which typically contains notes or comments, while the candidates are product descriptions or identifiers.</t>
+          <t>The 'DESC_PRODUTO' column contains product descriptions, which do not match the 'Observações' column's content.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3749,21 +3822,22 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Chave de acesso' as all candidates are unrelated.</t>
+          <t>No client column matches the semantic role or format of the 'Chave de acesso'.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
-        <v>0.7635999999999999</v>
-      </c>
-      <c r="R60" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3809,15 +3883,16 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="n">
-        <v>0.8067</v>
-      </c>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="n">
         <v>0.8067</v>
       </c>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>0.8067</v>
+      </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3863,21 +3938,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>The column 'DATA GL' has a high name confidence and matches the datetime format of 'Data documento'.</t>
+          <t>The header 'DATA GL' closely matches the expected date format and has strong evidence from the sample values.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="n">
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="R62" t="n">
         <v>0.88</v>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3923,15 +3999,16 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="n">
-        <v>0.7271</v>
-      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="n">
         <v>0.7271</v>
       </c>
-      <c r="R63" t="inlineStr"/>
+      <c r="R63" t="n">
+        <v>0.7271</v>
+      </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3951,7 +4028,7 @@
         <v>0.7608</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0005</v>
+        <v>0.0004</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3977,15 +4054,16 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
-      <c r="R64" t="inlineStr"/>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4031,15 +4109,16 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
-      <c r="R65" t="inlineStr"/>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4053,13 +4132,13 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>0.7906</v>
+        <v>0.792</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8129</v>
+        <v>0.8136</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.0223</v>
+        <v>-0.0216</v>
       </c>
       <c r="H66" t="n">
         <v>0.73</v>
@@ -4085,15 +4164,16 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="n">
-        <v>0.73</v>
-      </c>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="n">
-        <v>0.7906</v>
-      </c>
-      <c r="R66" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.8</v>
+      </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4145,15 +4225,16 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="n">
         <v>0.8</v>
       </c>
-      <c r="R67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>0.8</v>
+      </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4167,10 +4248,10 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>0.8289</v>
+        <v>0.829</v>
       </c>
       <c r="F68" t="n">
-        <v>0.8202</v>
+        <v>0.8203</v>
       </c>
       <c r="G68" t="n">
         <v>0.008699999999999999</v>
@@ -4199,15 +4280,16 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
-      <c r="R68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4230,10 +4312,10 @@
         <v>0.8231000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8089</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0142</v>
+        <v>0.0141</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -4253,21 +4335,22 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>The 'NUMERO NF' column has a strong numeric profile and high name confidence, aligning well with the 'Nº FCI' semantic role.</t>
+          <t>The 'NUMERO NF' column has a strong numeric profile and high name confidence, aligning well with the expected invoice number.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="n">
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="R69" t="n">
         <v>0.85</v>
       </c>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4307,21 +4390,22 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No candidate column matches the semantic role of 'Condições pagamento' as they all pertain to product codes or identifiers.</t>
+          <t>No suitable candidate matches the semantic role of 'Condições pagamento' as all candidates are unrelated to payment conditions.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
         <v>0.75</v>
       </c>
-      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4335,7 +4419,7 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>0.8041</v>
+        <v>0.804</v>
       </c>
       <c r="F71" t="n">
         <v>0.7938</v>
@@ -4361,21 +4445,22 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates have semantic header conflicts with the expected role of 'Base ICAP', indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
-      <c r="R71" t="inlineStr"/>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4415,21 +4500,22 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family for 'Aliquota ICAP'.</t>
+          <t>All candidates have semantic header conflicts with the expected tax role of 'Aliquota ICAP', indicating they do not match the intended meaning.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
-      <c r="R72" t="inlineStr"/>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4443,13 +4529,13 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>0.7945</v>
+        <v>0.7937</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8192</v>
+        <v>0.8176</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0247</v>
+        <v>-0.0239</v>
       </c>
       <c r="H73" t="n">
         <v>0.4751</v>
@@ -4475,15 +4561,16 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="n">
-        <v>0.7945</v>
-      </c>
-      <c r="R73" t="inlineStr"/>
+        <v>0.7937</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.7937</v>
+      </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4506,7 +4593,7 @@
         <v>0.8437</v>
       </c>
       <c r="F74" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8101</v>
       </c>
       <c r="G74" t="n">
         <v>0.0337</v>
@@ -4535,15 +4622,16 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="n">
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="R74" t="n">
         <v>0.6718</v>
       </c>
-      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4583,21 +4671,22 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No candidate column aligns semantically or contextually with the 'Mensagem' column.</t>
+          <t>No candidate column matches the semantic role of 'Mensagem' as all candidates are unrelated to message content.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
-      <c r="R75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4611,10 +4700,10 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>0.8247</v>
+        <v>0.8246</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7896</v>
+        <v>0.7895</v>
       </c>
       <c r="G76" t="n">
         <v>0.0351</v>
@@ -4637,21 +4726,22 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of non-empty values in all columns.</t>
+          <t>All candidate columns are empty or lack relevant data to support a mapping.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
-      <c r="R76" t="inlineStr"/>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4665,16 +4755,16 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>0.826</v>
+        <v>0.8259</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="G77" t="n">
         <v>0.0059</v>
       </c>
       <c r="H77" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -4691,21 +4781,22 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate 'COD_FIS_JUR' does not match the expected numeric format of 'Domicílio fiscal', which is a specific identifier.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
+      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="R77" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4719,7 +4810,7 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>0.7917</v>
+        <v>0.7916</v>
       </c>
       <c r="F78" t="n">
         <v>0.858</v>
@@ -4751,15 +4842,16 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="n">
-        <v>0.7917</v>
-      </c>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="n">
-        <v>0.7917</v>
-      </c>
-      <c r="R78" t="inlineStr"/>
+        <v>0.7916</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.7916</v>
+      </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4782,7 +4874,7 @@
         <v>0.8209</v>
       </c>
       <c r="F79" t="n">
-        <v>0.7874</v>
+        <v>0.7875</v>
       </c>
       <c r="G79" t="n">
         <v>0.0335</v>
@@ -4805,21 +4897,22 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>The column 'NUMERO NF' has a strong numeric profile and matches the semantic role of 'Nº de serviço' despite the empty evidence.</t>
+          <t>The header 'NUMERO NF' closely matches the expected 'Nº de serviço' and has substantial numeric evidence.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="n">
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="R79" t="n">
         <v>0.85</v>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4839,10 +4932,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8017</v>
+        <v>0.8016</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7869</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="G80" t="n">
         <v>0.0148</v>
@@ -4851,7 +4944,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8017</v>
+        <v>0.8016</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4865,21 +4958,22 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>The column 'DESC_PRODUTO' has a high name confidence and contains descriptive product information, aligning with the expected content for 'Texto breve serviço'.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="n">
-        <v>0.7664</v>
-      </c>
-      <c r="R80" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.8016</v>
+      </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4896,7 +4990,7 @@
         <v>0.7657</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8135</v>
+        <v>0.8134</v>
       </c>
       <c r="G81" t="n">
         <v>-0.0478</v>
@@ -4925,15 +5019,16 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="n">
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="n">
         <v>0.85</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="R81" t="n">
         <v>0.8</v>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4950,7 +5045,7 @@
         <v>0.7895</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7859</v>
       </c>
       <c r="G82" t="n">
         <v>0.0036</v>
@@ -4979,15 +5074,16 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
-      <c r="R82" t="inlineStr"/>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5007,7 +5103,7 @@
         <v>0.7779</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0151</v>
+        <v>0.0152</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -5033,15 +5129,16 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="n">
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="n">
         <v>0.646</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="R83" t="n">
         <v>0.7931</v>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5055,13 +5152,13 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>0.74</v>
+        <v>0.7402</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7365</v>
+        <v>0.7368</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0035</v>
+        <v>0.0034</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -5081,21 +5178,22 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>All candidate columns have semantic conflicts or do not match the expected numeric type for 'Mont.líquido frete', which should represent a monetary value.</t>
+          <t>All candidate columns have semantic-role conflicts or do not match the expected type for 'Mont.líquido frete', which should represent a monetary value.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
+      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
-      <c r="R84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5109,13 +5207,13 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>0.762</v>
+        <v>0.7622</v>
       </c>
       <c r="F85" t="n">
-        <v>0.7561</v>
+        <v>0.7562</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0059</v>
+        <v>0.006</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -5135,21 +5233,22 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to semantic header conflicts and all-zero evidence.</t>
+          <t>All candidates have semantic conflicts or do not match the expected numeric type for 'Mont.líquido seguro', which is expected to be a monetary value.</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
+      <c r="P85" t="inlineStr"/>
       <c r="Q85" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="R85" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0.7453</v>
+      </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5163,13 +5262,13 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>0.8228</v>
+        <v>0.8227</v>
       </c>
       <c r="F86" t="n">
         <v>0.8223</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0005</v>
+        <v>0.0004</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -5189,21 +5288,22 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>All candidates have conflicting semantic roles or insufficient evidence.</t>
+          <t>All candidates have conflicting semantic roles or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
-      <c r="R86" t="inlineStr"/>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5229,7 +5329,7 @@
         <v>0.862</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0261</v>
+        <v>0.026</v>
       </c>
       <c r="H87" t="n">
         <v>0.7375</v>
@@ -5255,15 +5355,16 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="n">
-        <v>0.8881</v>
-      </c>
+      <c r="P87" t="inlineStr"/>
       <c r="Q87" t="n">
         <v>0.8881</v>
       </c>
-      <c r="R87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>0.8881</v>
+      </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5283,7 +5384,7 @@
         <v>0.8292</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0296</v>
+        <v>0.0295</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -5309,15 +5410,16 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
+      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
-      <c r="R88" t="inlineStr"/>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5357,21 +5459,22 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type for ICAP.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type, indicating they do not match the intended role of 'Tipo de Imposto ICAP'.</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
+      <c r="P89" t="inlineStr"/>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
-      <c r="R89" t="inlineStr"/>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5388,10 +5491,10 @@
         <v>0.7875</v>
       </c>
       <c r="F90" t="n">
-        <v>0.7811</v>
+        <v>0.7812</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0064</v>
+        <v>0.0063</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -5411,21 +5514,22 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the expected tax family, and no distinctive row evidence supports a mapping.</t>
+          <t>All candidates have semantic header conflicts and do not match the expected tax base context.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
+      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
-      <c r="R90" t="inlineStr"/>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5465,21 +5569,22 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the original column, and the evidence does not support a mapping.</t>
+          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
+      <c r="P91" t="inlineStr"/>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
-      <c r="R91" t="inlineStr"/>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5493,13 +5598,13 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>0.7916</v>
+        <v>0.7914</v>
       </c>
       <c r="F92" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.7783</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0129</v>
+        <v>0.0131</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -5519,21 +5624,22 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
+      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
-      <c r="R92" t="inlineStr"/>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5547,7 +5653,7 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>0.7851</v>
+        <v>0.785</v>
       </c>
       <c r="F93" t="n">
         <v>0.7783</v>
@@ -5573,21 +5679,22 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type, and there is no supporting data evidence.</t>
+          <t>All candidates have semantic header conflicts and no relevant data evidence.</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
+      <c r="P93" t="inlineStr"/>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
-      <c r="R93" t="inlineStr"/>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5604,7 +5711,7 @@
         <v>0.8079</v>
       </c>
       <c r="F94" t="n">
-        <v>0.8025</v>
+        <v>0.8024</v>
       </c>
       <c r="G94" t="n">
         <v>0.0054</v>
@@ -5627,21 +5734,22 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
+          <t>All candidates have a semantic header conflict with the ICEP base, indicating they do not represent the same business meaning.</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
+      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
-      <c r="R94" t="inlineStr"/>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5655,10 +5763,10 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>0.7861</v>
+        <v>0.786</v>
       </c>
       <c r="F95" t="n">
-        <v>0.7834</v>
+        <v>0.7833</v>
       </c>
       <c r="G95" t="n">
         <v>0.0027</v>
@@ -5681,21 +5789,22 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP tax type, indicating incompatible mappings.</t>
+          <t>All candidates have a semantic header conflict with the ICEP tax type, indicating they do not match the intended meaning.</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
+      <c r="P95" t="inlineStr"/>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
-      <c r="R95" t="inlineStr"/>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5715,7 +5824,7 @@
         <v>0.786</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -5735,21 +5844,22 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
+      <c r="P96" t="inlineStr"/>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
-      <c r="R96" t="inlineStr"/>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5789,21 +5899,22 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of distinctive row evidence.</t>
+          <t>All candidates have semantic header conflicts or insufficient evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
-      <c r="P97" t="n">
-        <v>0</v>
-      </c>
+      <c r="P97" t="inlineStr"/>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
-      <c r="R97" t="inlineStr"/>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5843,21 +5954,22 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP role, indicating incompatible tax-family contexts.</t>
+          <t>All candidates have a semantic header conflict with the ICEP role, indicating they do not match the intended mapping.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
+      <c r="P98" t="inlineStr"/>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
-      <c r="R98" t="inlineStr"/>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5897,21 +6009,22 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type.</t>
+          <t>All candidates have semantic header conflicts with the model column.</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
+      <c r="P99" t="inlineStr"/>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
-      <c r="R99" t="inlineStr"/>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5957,15 +6070,16 @@
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
+      <c r="P100" t="inlineStr"/>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
-      <c r="R100" t="inlineStr"/>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6005,21 +6119,22 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family, indicating no suitable mapping.</t>
+          <t>All candidates conflict with the tax-family context of ICSP, providing no valid mapping.</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
+      <c r="P101" t="inlineStr"/>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
-      <c r="R101" t="inlineStr"/>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6059,21 +6174,22 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
+      <c r="P102" t="inlineStr"/>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
-      <c r="R102" t="inlineStr"/>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6119,15 +6235,16 @@
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
+      <c r="P103" t="inlineStr"/>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
-      <c r="R103" t="inlineStr"/>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6173,15 +6290,16 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
+      <c r="P104" t="inlineStr"/>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
-      <c r="R104" t="inlineStr"/>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6221,21 +6339,22 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax role, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
+      <c r="P105" t="inlineStr"/>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
-      <c r="R105" t="inlineStr"/>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6252,10 +6371,10 @@
         <v>0.803</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8103</v>
+        <v>0.8102</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.0073</v>
+        <v>-0.0072</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -6281,15 +6400,16 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
-      <c r="P106" t="n">
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="R106" t="inlineStr"/>
+      <c r="R106" t="n">
+        <v>0.803</v>
+      </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6329,21 +6449,22 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>All candidate columns contain zero values, providing no evidence for a mapping.</t>
+          <t>All candidate columns contain zero values, indicating no relevant data to support a mapping.</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
+      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
-      <c r="R107" t="inlineStr"/>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6363,7 +6484,7 @@
         <v>0.784</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0036</v>
+        <v>0.0035</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -6383,21 +6504,22 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>The candidate columns contain non-zero values, while the model column is all zeros, indicating a mismatch in semantic roles.</t>
+          <t>All candidates have non-zero values, while the model column only contains zeros, indicating a mismatch in semantic roles.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
+      <c r="P108" t="inlineStr"/>
       <c r="Q108" t="n">
-        <v>0.7875</v>
-      </c>
-      <c r="R108" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6414,10 +6536,10 @@
         <v>0.7976</v>
       </c>
       <c r="F109" t="n">
-        <v>0.7864</v>
+        <v>0.7865</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0112</v>
+        <v>0.0111</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -6437,21 +6559,22 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>All candidate columns have semantic conflicts or lack relevant data evidence to support a mapping.</t>
+          <t>No suitable candidate matches the semantic role of 'Valor DIF_ALIQ' as all candidates either conflict semantically or provide no relevant data.</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
+      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
         <v>0.7976</v>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6471,7 +6594,7 @@
         <v>0.8058999999999999</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0021</v>
+        <v>0.002</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -6497,15 +6620,16 @@
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
-      <c r="P110" t="n">
-        <v>0</v>
-      </c>
+      <c r="P110" t="inlineStr"/>
       <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
         <v>0.8079</v>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6545,21 +6669,22 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>All candidates have conflicting semantic roles or lack relevant data evidence.</t>
+          <t>No suitable candidate found due to all-zero evidence and lack of semantic alignment.</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
+      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
-      <c r="R111" t="inlineStr"/>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6579,7 +6704,7 @@
         <v>0.7776</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -6605,15 +6730,16 @@
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
+      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
         <v>0.7779</v>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6653,21 +6779,22 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>All candidates have conflicting semantic roles or insufficient evidence to support a mapping.</t>
+          <t>All candidates have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
+      <c r="P113" t="inlineStr"/>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
-      <c r="R113" t="inlineStr"/>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6719,15 +6846,16 @@
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
+      <c r="P114" t="inlineStr"/>
       <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
         <v>0.8551</v>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6741,13 +6869,13 @@
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
-        <v>0.7909</v>
+        <v>0.8587</v>
       </c>
       <c r="F115" t="n">
-        <v>0.8587</v>
+        <v>0.8296</v>
       </c>
       <c r="G115" t="n">
-        <v>-0.0678</v>
+        <v>0.0291</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -6767,21 +6895,22 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate found due to all candidates having conflicting semantic roles or insufficient evidence.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="n">
-        <v>0.7909</v>
-      </c>
+      <c r="P115" t="inlineStr"/>
       <c r="Q115" t="n">
-        <v>0.7909</v>
-      </c>
-      <c r="R115" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6821,21 +6950,22 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or do not match the expected tax role.</t>
+          <t>All candidates have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
+      <c r="P116" t="inlineStr"/>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
-      <c r="R116" t="inlineStr"/>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6846,23 +6976,29 @@
           <t>Outras ICMS_FECP</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
+      <c r="C117" t="n">
+        <v>21</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
       <c r="E117" t="n">
-        <v>0.8084</v>
+        <v>0.8659</v>
       </c>
       <c r="F117" t="n">
+        <v>0.8351</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
         <v>0.8659</v>
       </c>
-      <c r="G117" t="n">
-        <v>-0.0575</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
       <c r="J117" t="inlineStr">
         <is>
           <t>data</t>
@@ -6870,26 +7006,27 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate 'IND TRIB ICMS' has a high name confidence and aligns with the tax context despite its numeric values being non-zero.</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
-      <c r="P117" t="n">
-        <v>0.8084</v>
-      </c>
+      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="n">
-        <v>0.8084</v>
-      </c>
-      <c r="R117" t="inlineStr"/>
+        <v>0.8659</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.8659</v>
+      </c>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6903,13 +7040,13 @@
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
+        <v>0.7784</v>
+      </c>
+      <c r="F118" t="n">
         <v>0.8304</v>
       </c>
-      <c r="F118" t="n">
-        <v>0.803</v>
-      </c>
       <c r="G118" t="n">
-        <v>0.0274</v>
+        <v>-0.052</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -6929,21 +7066,22 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the target column is entirely zero, indicating a mismatch.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
+      <c r="P118" t="inlineStr"/>
       <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="inlineStr"/>
+        <v>0.7784</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.7784</v>
+      </c>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6969,7 +7107,7 @@
         <v>0.792</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0616</v>
+        <v>0.0615</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -6989,21 +7127,22 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a strong name match but lacks supporting data evidence, as it contains non-zero values while the source column is all zeros.</t>
+          <t>The candidate 'IND TRIB IPI' has a strong name match but conflicts with the tax-family context of 'Base Reduzida IPI', and the data evidence is all zeros.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
+      <c r="P119" t="inlineStr"/>
       <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
         <v>0.8535</v>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7043,21 +7182,22 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the tax-family context of COFINS.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context, making them incompatible.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
+      <c r="P120" t="inlineStr"/>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
-      <c r="R120" t="inlineStr"/>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7103,15 +7243,16 @@
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
+      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
-      <c r="R121" t="inlineStr"/>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7157,15 +7298,16 @@
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
+      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
-      <c r="R122" t="inlineStr"/>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7205,21 +7347,22 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the COFINS tax family, making them incompatible.</t>
+          <t>All candidates have semantic header conflicts with the required COFINS base, and no suitable mapping evidence is present.</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
+      <c r="P123" t="inlineStr"/>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
-      <c r="R123" t="inlineStr"/>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7259,21 +7402,22 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no valid row evidence.</t>
+          <t>All candidates have semantic header conflicts with the PIS tax family and provide no valid mapping evidence.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
+      <c r="P124" t="inlineStr"/>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
-      <c r="R124" t="inlineStr"/>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7313,21 +7457,22 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>The candidate columns conflict with the tax-family context of 'Outras PIS' and provide no relevant row evidence.</t>
+          <t>All candidates have semantic conflicts with the PIS tax family and provide no relevant row evidence.</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
+      <c r="P125" t="inlineStr"/>
       <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
         <v>0.5</v>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7367,21 +7512,22 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of relevant data evidence.</t>
+          <t>All candidates have semantic conflicts with the tax family of PIS, making them incompatible.</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
+      <c r="P126" t="inlineStr"/>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
-      <c r="R126" t="inlineStr"/>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7421,21 +7567,22 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the PIS tax base, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the PIS tax base, and the evidence does not support a mapping.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
+      <c r="P127" t="inlineStr"/>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
-      <c r="R127" t="inlineStr"/>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7475,21 +7622,22 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type (ISS) and provide no relevant data evidence.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type (ISS), providing no valid mapping.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
+      <c r="P128" t="inlineStr"/>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
-      <c r="R128" t="inlineStr"/>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7529,21 +7677,22 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of the target column, and the evidence does not support a mapping.</t>
+          <t>All candidates conflict with the tax-family of the target column, and no valid mapping evidence is present.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
+      <c r="P129" t="inlineStr"/>
       <c r="Q129" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R129" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7583,21 +7732,22 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of the target column.</t>
+          <t>All candidates have a semantic header conflict with the tax family, making them incompatible.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
+      <c r="P130" t="inlineStr"/>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
-      <c r="R130" t="inlineStr"/>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7611,7 +7761,7 @@
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="n">
-        <v>0.7899</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="F131" t="n">
         <v>0.7796</v>
@@ -7643,15 +7793,16 @@
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
+      <c r="P131" t="inlineStr"/>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
-      <c r="R131" t="inlineStr"/>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7691,21 +7842,22 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with the source column, indicating incompatible meanings.</t>
+          <t>All candidates conflict with the tax-family context of 'Isentas ISS'.</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
+      <c r="P132" t="inlineStr"/>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
-      <c r="R132" t="inlineStr"/>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7719,10 +7871,10 @@
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
-        <v>0.7975</v>
+        <v>0.7974</v>
       </c>
       <c r="F133" t="n">
-        <v>0.7947</v>
+        <v>0.7946</v>
       </c>
       <c r="G133" t="n">
         <v>0.0028</v>
@@ -7745,21 +7897,22 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family context of ISS, providing no valid mapping.</t>
+          <t>All candidates conflict with the tax-family context of 'Outras ISS'.</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
+      <c r="P133" t="inlineStr"/>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
-      <c r="R133" t="inlineStr"/>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7773,13 +7926,13 @@
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="n">
-        <v>0.7673</v>
+        <v>0.7668</v>
       </c>
       <c r="F134" t="n">
-        <v>0.7599</v>
+        <v>0.7597</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0074</v>
+        <v>0.0071</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -7799,21 +7952,22 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the target column, and the evidence does not support a mapping.</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
+      <c r="P134" t="inlineStr"/>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
-      <c r="R134" t="inlineStr"/>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
       <c r="S134" t="inlineStr"/>
       <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7853,21 +8007,22 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or lack relevant data evidence.</t>
+          <t>All candidates have significant semantic or data conflicts, and the evidence does not support a mapping.</t>
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
+      <c r="P135" t="inlineStr"/>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
-      <c r="R135" t="inlineStr"/>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -7881,7 +8036,7 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
-        <v>0.8146</v>
+        <v>0.8147</v>
       </c>
       <c r="F136" t="n">
         <v>0.802</v>
@@ -7907,21 +8062,22 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to semantic conflicts and lack of relevant data evidence.</t>
+          <t>No suitable candidate due to semantic header conflicts and all-zero evidence.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
+      <c r="P136" t="inlineStr"/>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
-      <c r="R136" t="inlineStr"/>
+      <c r="R136" t="n">
+        <v>0.8147</v>
+      </c>
       <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -7935,13 +8091,13 @@
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
-        <v>0.8077</v>
+        <v>0.8076</v>
       </c>
       <c r="F137" t="n">
         <v>0.8074</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -7961,21 +8117,22 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column has only zeros, indicating no compatible mapping.</t>
+          <t>All candidate columns contain non-distinctive or conflicting data, with no suitable mapping to the tax base for FECP.</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
+      <c r="P137" t="inlineStr"/>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
-      <c r="R137" t="inlineStr"/>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -7989,13 +8146,13 @@
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="n">
-        <v>0.8094</v>
+        <v>0.8093</v>
       </c>
       <c r="F138" t="n">
         <v>0.8042</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0052</v>
+        <v>0.0051</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -8015,21 +8172,22 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>The candidate columns conflict semantically with the tax family of the target column, and there is no supporting data evidence.</t>
+          <t>All candidates have semantic header conflicts or do not match the expected tax situation for 'Isentas FECP_ST'.</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
+      <c r="P138" t="inlineStr"/>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
-      <c r="R138" t="inlineStr"/>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8069,21 +8227,22 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic and numeric discrepancies with the source column.</t>
+          <t>All candidate columns contain conflicting semantic roles or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
+      <c r="P139" t="inlineStr"/>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
-      <c r="R139" t="inlineStr"/>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8097,13 +8256,13 @@
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
-        <v>0.797</v>
+        <v>0.7973</v>
       </c>
       <c r="F140" t="n">
-        <v>0.7823</v>
+        <v>0.7829</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0147</v>
+        <v>0.0144</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -8123,21 +8282,22 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
+          <t>All candidates have semantic conflicts or do not match the expected type for 'Base Reduzida FECP_ST', which is an integer with all zero values.</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
+      <c r="P140" t="inlineStr"/>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
-      <c r="R140" t="inlineStr"/>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8151,10 +8311,10 @@
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
-        <v>0.7837</v>
+        <v>0.7836</v>
       </c>
       <c r="F141" t="n">
-        <v>0.7736</v>
+        <v>0.7735</v>
       </c>
       <c r="G141" t="n">
         <v>0.0101</v>
@@ -8177,21 +8337,22 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>The candidate headers conflict with the required tax qualifier, indicating a mismatch in semantic roles.</t>
+          <t>All candidates have semantic header conflicts with the required tax type, indicating they do not match the intended role.</t>
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
+      <c r="P141" t="inlineStr"/>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
-      <c r="R141" t="inlineStr"/>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8208,7 +8369,7 @@
         <v>0.7915</v>
       </c>
       <c r="F142" t="n">
-        <v>0.7902</v>
+        <v>0.7901</v>
       </c>
       <c r="G142" t="n">
         <v>0.0014</v>
@@ -8231,21 +8392,22 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the expected role of 'Base ICMS_ST' and do not provide relevant evidence.</t>
+          <t>All candidates have semantic conflicts with the expected role of 'Base ICMS_ST'.</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
-      <c r="P142" t="n">
-        <v>0</v>
-      </c>
+      <c r="P142" t="inlineStr"/>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
-      <c r="R142" t="inlineStr"/>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8285,21 +8447,22 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the expected role of 'Aliquota ICMS_ST'.</t>
+          <t>All candidates have semantic conflicts with the required tax role, indicating they do not match the 'Aliquota ICMS_ST' column.</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
+      <c r="P143" t="inlineStr"/>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
-      <c r="R143" t="inlineStr"/>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8313,10 +8476,10 @@
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="n">
-        <v>0.7802</v>
+        <v>0.7801</v>
       </c>
       <c r="F144" t="n">
-        <v>0.78</v>
+        <v>0.7799</v>
       </c>
       <c r="G144" t="n">
         <v>0.0002</v>
@@ -8339,21 +8502,22 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
+          <t>All candidates have semantic header conflicts or do not match the expected tax base for ICMS_ST.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
+      <c r="P144" t="inlineStr"/>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
-      <c r="R144" t="inlineStr"/>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8393,21 +8557,22 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and do not match the expected tax base for ICMS_ST.</t>
+          <t>All candidates have semantic header conflicts and do not align with the tax situation of 'Outras ICMS_ST'.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
-      <c r="P145" t="n">
-        <v>0</v>
-      </c>
+      <c r="P145" t="inlineStr"/>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
-      <c r="R145" t="inlineStr"/>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8447,21 +8612,22 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax situation, indicating they do not match the intended role of 'Base Reduzida ICMS_ST'.</t>
+          <t>All candidates have semantic conflicts with the required tax base role.</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
+      <c r="P146" t="inlineStr"/>
       <c r="Q146" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R146" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
       <c r="S146" t="inlineStr"/>
       <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8507,15 +8673,16 @@
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
-      <c r="P147" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P147" t="inlineStr"/>
       <c r="Q147" t="n">
         <v>0.8</v>
       </c>
-      <c r="R147" t="inlineStr"/>
+      <c r="R147" t="n">
+        <v>0.8</v>
+      </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8555,21 +8722,22 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>All candidate columns lack relevant data evidence to support a mapping.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
-      <c r="P148" t="n">
-        <v>0</v>
-      </c>
+      <c r="P148" t="inlineStr"/>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
-      <c r="R148" t="inlineStr"/>
+      <c r="R148" t="n">
+        <v>0.7684</v>
+      </c>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8586,10 +8754,10 @@
         <v>0.7773</v>
       </c>
       <c r="F149" t="n">
-        <v>0.7519</v>
+        <v>0.752</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0254</v>
+        <v>0.0253</v>
       </c>
       <c r="H149" t="n">
         <v>0.84</v>
@@ -8615,15 +8783,16 @@
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
-      <c r="P149" t="n">
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q149" t="n">
+      <c r="R149" t="n">
         <v>0.7886</v>
       </c>
-      <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8646,7 +8815,7 @@
         <v>0.0033</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1633</v>
+        <v>0</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
@@ -8663,21 +8832,22 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The header 'DATA GL' does not match the time format of 'Criado às:'.</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
-      <c r="P150" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="P150" t="inlineStr"/>
       <c r="Q150" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R150" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -8717,21 +8887,22 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>All candidate columns are empty or lack relevant data to support a mapping.</t>
+          <t>The candidate columns are empty and do not provide any relevant data to support a mapping.</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
-      <c r="P151" t="n">
-        <v>0</v>
-      </c>
+      <c r="P151" t="inlineStr"/>
       <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
         <v>0.8161</v>
       </c>
-      <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8745,13 +8916,13 @@
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="n">
-        <v>0.7749</v>
+        <v>0.7748</v>
       </c>
       <c r="F152" t="n">
         <v>0.7746</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -8771,21 +8942,22 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-numeric or zero-only data, conflicting with the expected numeric nature of 'Redução'.</t>
+          <t>All candidates are incompatible due to distinct content types and zero-only evidence.</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
-      <c r="P152" t="n">
-        <v>0</v>
-      </c>
+      <c r="P152" t="inlineStr"/>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
-      <c r="R152" t="inlineStr"/>
+      <c r="R152" t="n">
+        <v>0.7748</v>
+      </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8831,15 +9003,16 @@
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
-      <c r="P153" t="n">
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q153" t="n">
+      <c r="R153" t="n">
         <v>0.7627</v>
       </c>
-      <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8879,21 +9052,22 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>All candidate columns have empty or non-informative evidence, making a mapping unsupported.</t>
+          <t>All candidate columns have empty or non-informative data, making it impossible to establish a valid mapping.</t>
         </is>
       </c>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
+      <c r="P154" t="inlineStr"/>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
-      <c r="R154" t="inlineStr"/>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8933,21 +9107,22 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>All candidate columns contain no relevant data, making mapping impossible.</t>
+          <t>All candidate columns contain no relevant data or evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
+      <c r="P155" t="inlineStr"/>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
-      <c r="R155" t="inlineStr"/>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8987,21 +9162,22 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>All candidate columns lack non-empty values, making them unsuitable for mapping.</t>
+          <t>No suitable candidate found due to lack of non-empty values in the model column.</t>
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
-      <c r="P156" t="n">
-        <v>0</v>
-      </c>
+      <c r="P156" t="inlineStr"/>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
-      <c r="R156" t="inlineStr"/>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9015,16 +9191,16 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
+        <v>0.7796</v>
+      </c>
+      <c r="F157" t="n">
         <v>0.8222</v>
       </c>
-      <c r="F157" t="n">
-        <v>0.8033</v>
-      </c>
       <c r="G157" t="n">
-        <v>0.0188</v>
+        <v>-0.0425</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -9041,21 +9217,22 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'ID do consumidor final' based on name and data evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
-      <c r="P157" t="n">
-        <v>0</v>
-      </c>
+      <c r="P157" t="inlineStr"/>
       <c r="Q157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0.8</v>
+      </c>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9075,7 +9252,7 @@
         <v>0.7927999999999999</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.0377</v>
+        <v>-0.0376</v>
       </c>
       <c r="H158" t="n">
         <v>0.84</v>
@@ -9101,15 +9278,16 @@
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
-      <c r="P158" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="P158" t="inlineStr"/>
       <c r="Q158" t="n">
         <v>0.85</v>
       </c>
-      <c r="R158" t="inlineStr"/>
+      <c r="R158" t="n">
+        <v>0.85</v>
+      </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9155,21 +9333,22 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a high numeric fraction and matches the semantic role of 'Nº NF-e dos serviços'.</t>
+          <t>The candidate 'NUMERO NF' has a high name confidence and contains numeric values consistent with invoice numbers.</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
-      <c r="P159" t="n">
-        <v>1</v>
-      </c>
+      <c r="P159" t="inlineStr"/>
       <c r="Q159" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R159" t="n">
         <v>0.8556</v>
       </c>
-      <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9209,21 +9388,22 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Código verificação' as all candidates are unrelated to verification codes.</t>
+          <t>No suitable candidate found due to lack of non-empty values in the model column.</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
+      <c r="P160" t="inlineStr"/>
       <c r="Q160" t="n">
-        <v>0.7804</v>
-      </c>
-      <c r="R160" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.7803</v>
+      </c>
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9263,21 +9443,22 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>The candidate 'ORGANIZACAO' has a high name confidence but does not match the expected semantic role of 'Ordem'.</t>
+          <t>The candidate 'ORGANIZACAO' has a high name confidence but no relevant data evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
+      <c r="P161" t="inlineStr"/>
       <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
         <v>0.8438</v>
       </c>
-      <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9291,7 +9472,7 @@
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="n">
-        <v>0.7991</v>
+        <v>0.7992</v>
       </c>
       <c r="F162" t="n">
         <v>0.7887</v>
@@ -9317,21 +9498,22 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>The 'Despesas' column contains only zeros, making it incompatible with any candidate that has meaningful non-zero values.</t>
+          <t>The candidate columns do not match the expected type or content for 'Despesas', which should represent expenses, while the candidates are unrelated to financial data.</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
-      <c r="P162" t="n">
-        <v>0</v>
-      </c>
+      <c r="P162" t="inlineStr"/>
       <c r="Q162" t="n">
-        <v>0.7694</v>
-      </c>
-      <c r="R162" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.7992</v>
+      </c>
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9348,10 +9530,10 @@
         <v>0.8242</v>
       </c>
       <c r="F163" t="n">
-        <v>0.7865</v>
+        <v>0.7866</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0377</v>
+        <v>0.0376</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -9377,15 +9559,16 @@
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
-      <c r="P163" t="n">
-        <v>0</v>
-      </c>
+      <c r="P163" t="inlineStr"/>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
-      <c r="R163" t="inlineStr"/>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9425,21 +9608,22 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>No viable candidates match the semantic role of 'Municipio Fim' as all candidates are unrelated to municipalities.</t>
+          <t>No viable candidates match the semantic role of 'Municipio Fim' as all candidates are unrelated to municipality identification.</t>
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
-      <c r="P164" t="n">
-        <v>0</v>
-      </c>
+      <c r="P164" t="inlineStr"/>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
-      <c r="R164" t="inlineStr"/>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -9479,21 +9663,22 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts or insufficient evidence to support a mapping.</t>
+          <t>No suitable candidate found due to lack of evidence and semantic conflicts.</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
-      <c r="P165" t="n">
-        <v>0</v>
-      </c>
+      <c r="P165" t="inlineStr"/>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
-      <c r="R165" t="inlineStr"/>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -9519,7 +9704,7 @@
         <v>0.8619</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0115</v>
+        <v>0.0116</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -9539,21 +9724,22 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>The column 'COD_PRODUTO' has a high name confidence and contains numeric values that align with item codes.</t>
+          <t>The column 'COD_PRODUTO' has a high name confidence and contains numeric values that align with item codes, despite the empty evidence for the model column.</t>
         </is>
       </c>
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
-      <c r="P166" t="n">
-        <v>0.8734</v>
-      </c>
+      <c r="P166" t="inlineStr"/>
       <c r="Q166" t="n">
         <v>0.8734</v>
       </c>
-      <c r="R166" t="inlineStr"/>
+      <c r="R166" t="n">
+        <v>0.8734</v>
+      </c>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -9576,7 +9762,7 @@
         <v>0.8369</v>
       </c>
       <c r="F167" t="n">
-        <v>0.7693</v>
+        <v>0.7694</v>
       </c>
       <c r="G167" t="n">
         <v>0.0675</v>
@@ -9605,15 +9791,16 @@
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
-      <c r="P167" t="n">
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="n">
         <v>1</v>
       </c>
-      <c r="Q167" t="n">
+      <c r="R167" t="n">
         <v>0.8369</v>
       </c>
-      <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -9627,16 +9814,16 @@
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
-        <v>0.8041</v>
+        <v>0.7264</v>
       </c>
       <c r="F168" t="n">
         <v>0.8082</v>
       </c>
       <c r="G168" t="n">
-        <v>-0.0041</v>
+        <v>-0.0818</v>
       </c>
       <c r="H168" t="n">
-        <v>0.2625</v>
+        <v>0.7937</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -9659,15 +9846,16 @@
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
-      <c r="P168" t="n">
-        <v>0.8041</v>
-      </c>
+      <c r="P168" t="inlineStr"/>
       <c r="Q168" t="n">
-        <v>0.8041</v>
-      </c>
-      <c r="R168" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.85</v>
+      </c>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -9684,7 +9872,7 @@
         <v>0.8421</v>
       </c>
       <c r="F169" t="n">
-        <v>0.8177</v>
+        <v>0.8176</v>
       </c>
       <c r="G169" t="n">
         <v>0.0245</v>
@@ -9707,21 +9895,22 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidate columns contain non-zero values, while the model column has only zeros, indicating a lack of semantic alignment.</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
-      <c r="P169" t="n">
-        <v>0</v>
-      </c>
+      <c r="P169" t="inlineStr"/>
       <c r="Q169" t="n">
-        <v>0.8421</v>
-      </c>
-      <c r="R169" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -9761,21 +9950,22 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended role of 'Base de Cálculo ICOP FECP'.</t>
+          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
-      <c r="P170" t="n">
-        <v>0</v>
-      </c>
+      <c r="P170" t="inlineStr"/>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
-      <c r="R170" t="inlineStr"/>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -9792,7 +9982,7 @@
         <v>0.8003</v>
       </c>
       <c r="F171" t="n">
-        <v>0.7982</v>
+        <v>0.7983</v>
       </c>
       <c r="G171" t="n">
         <v>0.0021</v>
@@ -9821,15 +10011,16 @@
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
-      <c r="P171" t="n">
-        <v>0</v>
-      </c>
+      <c r="P171" t="inlineStr"/>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
-      <c r="R171" t="inlineStr"/>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -9843,13 +10034,13 @@
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
-        <v>0.8203</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="F172" t="n">
-        <v>0.8008</v>
+        <v>0.8204</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0195</v>
+        <v>-0.0195</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -9869,21 +10060,22 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of distinctive row evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
-      <c r="P172" t="n">
-        <v>0</v>
-      </c>
+      <c r="P172" t="inlineStr"/>
       <c r="Q172" t="n">
         <v>0</v>
       </c>
-      <c r="R172" t="inlineStr"/>
+      <c r="R172" t="n">
+        <v>0.8008999999999999</v>
+      </c>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9903,7 +10095,7 @@
         <v>0.7989000000000001</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0015</v>
+        <v>0.0016</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -9923,21 +10115,22 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the source column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
-      <c r="P173" t="n">
-        <v>0</v>
-      </c>
+      <c r="P173" t="inlineStr"/>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
-      <c r="R173" t="inlineStr"/>
+      <c r="R173" t="n">
+        <v>0</v>
+      </c>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -9951,7 +10144,7 @@
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
-        <v>0.8272</v>
+        <v>0.8273</v>
       </c>
       <c r="F174" t="n">
         <v>0.8174</v>
@@ -9977,21 +10170,22 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of distinctive sample evidence.</t>
+          <t>No suitable candidate due to semantic header conflicts and lack of distinctive row evidence.</t>
         </is>
       </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
-      <c r="P174" t="n">
-        <v>0</v>
-      </c>
+      <c r="P174" t="inlineStr"/>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
-      <c r="R174" t="inlineStr"/>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10011,19 +10205,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.831</v>
       </c>
       <c r="F175" t="n">
         <v>0.7859</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0452</v>
+        <v>0.0451</v>
       </c>
       <c r="H175" t="n">
         <v>0.7405</v>
       </c>
       <c r="I175" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.831</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -10037,21 +10231,22 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' closely matches the semantic role of 'Numero do Pedido', but the numeric evidence suggests it may refer to invoice numbers rather than order numbers.</t>
+          <t>The header 'NUMERO NF' suggests a document number, but the sample values do not align with the expected format of an invoice number.</t>
         </is>
       </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
-      <c r="P175" t="n">
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0.8310999999999999</v>
-      </c>
-      <c r="R175" t="inlineStr"/>
+      <c r="R175" t="n">
+        <v>0.831</v>
+      </c>
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10062,22 +10257,28 @@
           <t>Centro de lucro</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
+      <c r="C176" t="n">
+        <v>41</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>PROFIT_CENTER</t>
+        </is>
+      </c>
       <c r="E176" t="n">
-        <v>0.7929</v>
+        <v>0.8643</v>
       </c>
       <c r="F176" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.797</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.0673</v>
       </c>
       <c r="H176" t="n">
-        <v>0.7459</v>
+        <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>0.8643</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -10086,26 +10287,27 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate 'PROFIT_CENTER' has a high name confidence and a similar numeric profile, but lacks distinctive sample overlap.</t>
         </is>
       </c>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
-      <c r="P176" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P176" t="inlineStr"/>
       <c r="Q176" t="n">
         <v>0.8</v>
       </c>
-      <c r="R176" t="inlineStr"/>
+      <c r="R176" t="n">
+        <v>0.8</v>
+      </c>
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -10122,10 +10324,10 @@
         <v>0.8037</v>
       </c>
       <c r="F177" t="n">
-        <v>0.7861</v>
+        <v>0.7862</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0175</v>
+        <v>0.0176</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -10145,21 +10347,22 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not align with the required CBS tax situation.</t>
+          <t>All candidates have semantic header conflicts with the target column, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
-      <c r="P177" t="n">
-        <v>0</v>
-      </c>
+      <c r="P177" t="inlineStr"/>
       <c r="Q177" t="n">
         <v>0</v>
       </c>
-      <c r="R177" t="inlineStr"/>
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -10173,10 +10376,10 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="n">
-        <v>0.7833</v>
+        <v>0.7832</v>
       </c>
       <c r="F178" t="n">
-        <v>0.7749</v>
+        <v>0.7748</v>
       </c>
       <c r="G178" t="n">
         <v>0.008399999999999999</v>
@@ -10199,21 +10402,22 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the required tax classification, and there is no supporting data evidence.</t>
+          <t>All candidates have semantic header conflicts with the tax classification, making them incompatible.</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
-      <c r="P178" t="n">
-        <v>0</v>
-      </c>
+      <c r="P178" t="inlineStr"/>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
-      <c r="R178" t="inlineStr"/>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -10233,19 +10437,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.8388</v>
+        <v>0.8387</v>
       </c>
       <c r="F179" t="n">
         <v>0.8398</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.001</v>
+        <v>-0.0011</v>
       </c>
       <c r="H179" t="n">
         <v>0.5</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8388</v>
+        <v>0.8387</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -10265,15 +10469,16 @@
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
-      <c r="P179" t="n">
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="R179" t="inlineStr"/>
+      <c r="R179" t="n">
+        <v>0.865</v>
+      </c>
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -10287,16 +10492,16 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>0.751</v>
+        <v>0.8449</v>
       </c>
       <c r="F180" t="n">
         <v>0.8505</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0057</v>
       </c>
       <c r="H180" t="n">
-        <v>0.82</v>
+        <v>0.7123</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
@@ -10319,15 +10524,16 @@
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
-      <c r="P180" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="P180" t="inlineStr"/>
       <c r="Q180" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="R180" t="inlineStr"/>
+        <v>0.8449</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0.8449</v>
+      </c>
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -10373,21 +10579,22 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>The 'FORNECEDOR' column contains valid supplier names, aligning with the 'Exportador' role despite the empty evidence for 'Exportador'.</t>
+          <t>The 'FORNECEDOR' column contains valid supplier names, aligning with the 'Exportador' role.</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
-      <c r="P181" t="n">
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q181" t="n">
+      <c r="R181" t="n">
         <v>0.861</v>
       </c>
-      <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -10401,13 +10608,13 @@
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
-        <v>0.7905</v>
+        <v>0.788</v>
       </c>
       <c r="F182" t="n">
-        <v>0.788</v>
+        <v>0.7904</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0024</v>
+        <v>-0.0024</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -10427,21 +10634,22 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>All candidate columns are empty with no distinctive content or evidence to support a mapping.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
-      <c r="P182" t="n">
-        <v>0</v>
-      </c>
+      <c r="P182" t="inlineStr"/>
       <c r="Q182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="inlineStr"/>
+        <v>0.788</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0.788</v>
+      </c>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -10455,7 +10663,7 @@
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
-        <v>0.8126</v>
+        <v>0.8127</v>
       </c>
       <c r="F183" t="n">
         <v>0.8282</v>
@@ -10487,15 +10695,16 @@
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
-      <c r="P183" t="n">
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0.8126</v>
-      </c>
-      <c r="R183" t="inlineStr"/>
+      <c r="R183" t="n">
+        <v>0.8127</v>
+      </c>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -10509,16 +10718,16 @@
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="n">
-        <v>0.7874</v>
+        <v>0.857</v>
       </c>
       <c r="F184" t="n">
-        <v>0.857</v>
+        <v>0.8091</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.0696</v>
+        <v>0.048</v>
       </c>
       <c r="H184" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
@@ -10535,21 +10744,22 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate matches the semantic role of 'Código Fornecedor Início' based on header and data evidence.</t>
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
-      <c r="P184" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="P184" t="inlineStr"/>
       <c r="Q184" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="R184" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -10604,6 +10814,7 @@
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -10617,10 +10828,10 @@
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="n">
-        <v>0.802</v>
+        <v>0.8021</v>
       </c>
       <c r="F186" t="n">
-        <v>0.786</v>
+        <v>0.7861</v>
       </c>
       <c r="G186" t="n">
         <v>0.016</v>
@@ -10643,21 +10854,22 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>The candidate 'DATA GL' has a strong name match and contains datetime values, but the original column is empty, leading to no viable mapping.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
-      <c r="P186" t="n">
-        <v>0</v>
-      </c>
+      <c r="P186" t="inlineStr"/>
       <c r="Q186" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="R186" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0.8021</v>
+      </c>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -10703,15 +10915,16 @@
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
-      <c r="P187" t="n">
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q187" t="n">
+      <c r="R187" t="n">
         <v>0.8016</v>
       </c>
-      <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -10763,15 +10976,16 @@
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
-      <c r="P188" t="n">
-        <v>0</v>
-      </c>
+      <c r="P188" t="inlineStr"/>
       <c r="Q188" t="n">
         <v>0</v>
       </c>
-      <c r="R188" t="inlineStr"/>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -10797,7 +11011,7 @@
         <v>0.8623</v>
       </c>
       <c r="G189" t="n">
-        <v>0.0414</v>
+        <v>0.0413</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -10823,15 +11037,16 @@
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
-      <c r="P189" t="n">
-        <v>0</v>
-      </c>
+      <c r="P189" t="inlineStr"/>
       <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
         <v>0.9036</v>
       </c>
-      <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -10845,7 +11060,7 @@
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="n">
-        <v>0.7822</v>
+        <v>0.7823</v>
       </c>
       <c r="F190" t="n">
         <v>0.7811</v>
@@ -10871,21 +11086,22 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>All candidate columns are empty or lack relevant data evidence.</t>
+          <t>All candidate columns are empty, providing no evidence for mapping.</t>
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
+      <c r="P190" t="inlineStr"/>
       <c r="Q190" t="n">
         <v>0</v>
       </c>
-      <c r="R190" t="inlineStr"/>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -10908,10 +11124,10 @@
         <v>0.98</v>
       </c>
       <c r="F191" t="n">
-        <v>0.8995</v>
+        <v>0.8996</v>
       </c>
       <c r="G191" t="n">
-        <v>0.0805</v>
+        <v>0.0804</v>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
@@ -10940,6 +11156,7 @@
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -10953,10 +11170,10 @@
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
-        <v>0.7775</v>
+        <v>0.7774</v>
       </c>
       <c r="F192" t="n">
-        <v>0.7987</v>
+        <v>0.7988</v>
       </c>
       <c r="G192" t="n">
         <v>-0.0213</v>
@@ -10985,15 +11202,16 @@
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
-      <c r="P192" t="n">
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R192" t="inlineStr"/>
+      <c r="R192" t="n">
+        <v>0.7774</v>
+      </c>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -11016,10 +11234,10 @@
         <v>0.98</v>
       </c>
       <c r="F193" t="n">
-        <v>0.8933</v>
+        <v>0.8932</v>
       </c>
       <c r="G193" t="n">
-        <v>0.0867</v>
+        <v>0.0868</v>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
@@ -11048,6 +11266,7 @@
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -11067,7 +11286,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0.8927</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="F194" t="n">
         <v>0.8123</v>
@@ -11079,7 +11298,7 @@
         <v>0.7375</v>
       </c>
       <c r="I194" t="n">
-        <v>0.8927</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -11093,21 +11312,22 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a high name confidence and aligns with the IPI tax type, despite some numeric discrepancies.</t>
+          <t>The candidate 'IND TRIB IPI' closely matches the tax type 'Tipo de Imposto IPI' with high name confidence and consistent numeric values.</t>
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
-      <c r="P194" t="n">
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q194" t="n">
+      <c r="R194" t="n">
         <v>0.85</v>
       </c>
-      <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -11153,21 +11373,22 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>The header 'NUM_ITEM' suggests an item number, but the numeric values and profile do not align with the expected format for invoice item numbers.</t>
+          <t>The candidate 'NUM_ITEM' has a high name confidence but does not match the expected item ID role.</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
-      <c r="P195" t="n">
-        <v>0</v>
-      </c>
+      <c r="P195" t="inlineStr"/>
       <c r="Q195" t="n">
+        <v>0</v>
+      </c>
+      <c r="R195" t="n">
         <v>0.8752</v>
       </c>
-      <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -11219,15 +11440,16 @@
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
-      <c r="P196" t="n">
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="n">
         <v>0.7981</v>
       </c>
-      <c r="Q196" t="n">
+      <c r="R196" t="n">
         <v>0.8352000000000001</v>
       </c>
-      <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11273,15 +11495,16 @@
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
-      <c r="P197" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="P197" t="inlineStr"/>
       <c r="Q197" t="n">
         <v>0.85</v>
       </c>
-      <c r="R197" t="inlineStr"/>
+      <c r="R197" t="n">
+        <v>0.85</v>
+      </c>
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11327,15 +11550,16 @@
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
-      <c r="P198" t="n">
-        <v>0.8062</v>
-      </c>
+      <c r="P198" t="inlineStr"/>
       <c r="Q198" t="n">
         <v>0.8062</v>
       </c>
-      <c r="R198" t="inlineStr"/>
+      <c r="R198" t="n">
+        <v>0.8062</v>
+      </c>
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -11381,21 +11605,22 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>The header 'COD_MEDIDA' aligns semantically with 'Unidade de medida' and has no conflicting roles.</t>
+          <t>The header 'COD_MEDIDA' aligns semantically with 'Unidade de medida' and has no conflicting evidence.</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
-      <c r="P199" t="n">
-        <v>0.8463000000000001</v>
-      </c>
+      <c r="P199" t="inlineStr"/>
       <c r="Q199" t="n">
         <v>0.8463000000000001</v>
       </c>
-      <c r="R199" t="inlineStr"/>
+      <c r="R199" t="n">
+        <v>0.8463000000000001</v>
+      </c>
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -11450,6 +11675,7 @@
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -11495,15 +11721,16 @@
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
-      <c r="P201" t="n">
-        <v>0</v>
-      </c>
+      <c r="P201" t="inlineStr"/>
       <c r="Q201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
         <v>0.7675999999999999</v>
       </c>
-      <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -11543,21 +11770,22 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>The candidate 'LOCATION' has low name confidence and no relevant data evidence to support a mapping to 'Município do Local de Início'.</t>
+          <t>The candidate 'LOCATION' does not semantically match 'Município do Local de Início' as it lacks relevant municipal data.</t>
         </is>
       </c>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
-      <c r="P202" t="n">
-        <v>0</v>
-      </c>
+      <c r="P202" t="inlineStr"/>
       <c r="Q202" t="n">
         <v>0</v>
       </c>
-      <c r="R202" t="inlineStr"/>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -11574,7 +11802,7 @@
         <v>0.8247</v>
       </c>
       <c r="F203" t="n">
-        <v>0.8124</v>
+        <v>0.8125</v>
       </c>
       <c r="G203" t="n">
         <v>0.0123</v>
@@ -11603,15 +11831,16 @@
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
-      <c r="P203" t="n">
-        <v>0</v>
-      </c>
+      <c r="P203" t="inlineStr"/>
       <c r="Q203" t="n">
         <v>0</v>
       </c>
-      <c r="R203" t="inlineStr"/>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
       <c r="S203" t="inlineStr"/>
       <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -11657,15 +11886,16 @@
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
-      <c r="P204" t="n">
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q204" t="n">
+      <c r="R204" t="n">
         <v>0.8044</v>
       </c>
-      <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr"/>
       <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -11705,21 +11935,22 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' conflicts semantically with 'Nº do NCM', which is a tax classification code.</t>
+          <t>The header 'NUMERO NF' does not match the semantic role of 'Nº do NCM', which is a tax classification code.</t>
         </is>
       </c>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
-      <c r="P205" t="n">
-        <v>0</v>
-      </c>
+      <c r="P205" t="inlineStr"/>
       <c r="Q205" t="n">
         <v>0</v>
       </c>
-      <c r="R205" t="inlineStr"/>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -11771,15 +12002,16 @@
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
-      <c r="P206" t="n">
-        <v>0</v>
-      </c>
+      <c r="P206" t="inlineStr"/>
       <c r="Q206" t="n">
         <v>0</v>
       </c>
-      <c r="R206" t="inlineStr"/>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -11825,21 +12057,22 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>The candidate 'PRECO UNITARIO' has a high name confidence and matches the numeric profile of 'Preço líq.' as a unit price.</t>
+          <t>The candidate 'PRECO UNITARIO' has a high name confidence and a similar numeric profile, indicating it likely represents a unit price.</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
-      <c r="P207" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="P207" t="inlineStr"/>
       <c r="Q207" t="n">
         <v>0.85</v>
       </c>
-      <c r="R207" t="inlineStr"/>
+      <c r="R207" t="n">
+        <v>0.85</v>
+      </c>
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -11885,15 +12118,16 @@
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
-      <c r="P208" t="n">
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q208" t="n">
+      <c r="R208" t="n">
         <v>0.785</v>
       </c>
-      <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -11910,7 +12144,7 @@
         <v>0.8511</v>
       </c>
       <c r="F209" t="n">
-        <v>0.845</v>
+        <v>0.8449</v>
       </c>
       <c r="G209" t="n">
         <v>0.0062</v>
@@ -11939,15 +12173,16 @@
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
+      <c r="P209" t="inlineStr"/>
       <c r="Q209" t="n">
         <v>0</v>
       </c>
-      <c r="R209" t="inlineStr"/>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -11999,15 +12234,16 @@
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
-      <c r="P210" t="n">
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="n">
         <v>1</v>
       </c>
-      <c r="Q210" t="n">
+      <c r="R210" t="n">
         <v>0.8629</v>
       </c>
-      <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -12053,21 +12289,22 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>The name 'TOTAL DO ITEM' closely matches 'Valor Total do Item' with high numeric consistency and no semantic conflicts.</t>
+          <t>The candidate 'TOTAL DO ITEM' closely matches the canonical 'Valor Total do Item' in both name and numeric profile.</t>
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
-      <c r="P211" t="n">
-        <v>0.9388</v>
-      </c>
+      <c r="P211" t="inlineStr"/>
       <c r="Q211" t="n">
         <v>0.9388</v>
       </c>
-      <c r="R211" t="inlineStr"/>
+      <c r="R211" t="n">
+        <v>0.9388</v>
+      </c>
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12081,13 +12318,13 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8308</v>
       </c>
       <c r="F212" t="n">
         <v>0.7799</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0512</v>
+        <v>0.051</v>
       </c>
       <c r="H212" t="n">
         <v>0.4406</v>
@@ -12113,15 +12350,16 @@
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
-      <c r="P212" t="n">
-        <v>0.8310999999999999</v>
-      </c>
+      <c r="P212" t="inlineStr"/>
       <c r="Q212" t="n">
-        <v>0.8310999999999999</v>
-      </c>
-      <c r="R212" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0.8154</v>
+      </c>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12138,7 +12376,7 @@
         <v>0.8137</v>
       </c>
       <c r="F213" t="n">
-        <v>0.8086</v>
+        <v>0.8087</v>
       </c>
       <c r="G213" t="n">
         <v>0.005</v>
@@ -12161,21 +12399,22 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>No viable candidates due to lack of relevant data and evidence.</t>
+          <t>The candidate columns contain numeric product codes, which do not match the expected transportadora code.</t>
         </is>
       </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
+      <c r="P213" t="inlineStr"/>
       <c r="Q213" t="n">
         <v>0</v>
       </c>
-      <c r="R213" t="inlineStr"/>
+      <c r="R213" t="n">
+        <v>0.8137</v>
+      </c>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12230,6 +12469,7 @@
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="inlineStr"/>
+      <c r="U214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12275,15 +12515,16 @@
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
-      <c r="P215" t="n">
-        <v>0.7821</v>
-      </c>
+      <c r="P215" t="inlineStr"/>
       <c r="Q215" t="n">
         <v>0.7821</v>
       </c>
-      <c r="R215" t="inlineStr"/>
+      <c r="R215" t="n">
+        <v>0.7821</v>
+      </c>
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -12294,8 +12535,14 @@
           <t>Texto ICMS</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr"/>
+      <c r="C216" t="n">
+        <v>21</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
       <c r="E216" t="n">
         <v>0.889</v>
       </c>
@@ -12306,10 +12553,10 @@
         <v>0.0259</v>
       </c>
       <c r="H216" t="n">
-        <v>0</v>
+        <v>0.7321</v>
       </c>
       <c r="I216" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -12318,26 +12565,27 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' is an integer type, while 'Texto ICMS' is a string type, indicating a semantic mismatch.</t>
+          <t>The header 'IND TRIB ICMS' suggests a tax indicator for ICMS, but the numeric values and type do not align with the expected text format of 'Texto ICMS'.</t>
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
-      <c r="P216" t="n">
-        <v>0</v>
-      </c>
+      <c r="P216" t="inlineStr"/>
       <c r="Q216" t="n">
         <v>0</v>
       </c>
-      <c r="R216" t="inlineStr"/>
+      <c r="R216" t="n">
+        <v>0.889</v>
+      </c>
       <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -12383,21 +12631,22 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>The header 'IND TRIB IPI' aligns with the IPI tax context, despite the numeric profile indicating integer values.</t>
+          <t>The candidate 'IND TRIB IPI' has a strong name match and aligns with the expected integer type for IPI indicators, despite the numeric values being limited.</t>
         </is>
       </c>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
-      <c r="P217" t="n">
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0.8353</v>
-      </c>
-      <c r="R217" t="inlineStr"/>
+      <c r="R217" t="n">
+        <v>0.8256</v>
+      </c>
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -12443,15 +12692,16 @@
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
-      <c r="P218" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="P218" t="inlineStr"/>
       <c r="Q218" t="n">
         <v>0.8172</v>
       </c>
-      <c r="R218" t="inlineStr"/>
+      <c r="R218" t="n">
+        <v>0.8172</v>
+      </c>
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -12468,10 +12718,10 @@
         <v>0.7873</v>
       </c>
       <c r="F219" t="n">
-        <v>0.7845</v>
+        <v>0.7846</v>
       </c>
       <c r="G219" t="n">
-        <v>0.0028</v>
+        <v>0.0027</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -12491,21 +12741,22 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the PIS tax family, indicating incompatible mappings.</t>
+          <t>All candidates have semantic header conflicts with the PIS tax family, indicating they do not match the intended mapping.</t>
         </is>
       </c>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
-      <c r="P219" t="n">
-        <v>0</v>
-      </c>
+      <c r="P219" t="inlineStr"/>
       <c r="Q219" t="n">
         <v>0</v>
       </c>
-      <c r="R219" t="inlineStr"/>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
       <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -12528,10 +12779,10 @@
         <v>1</v>
       </c>
       <c r="F220" t="n">
-        <v>0.8828</v>
+        <v>0.8827</v>
       </c>
       <c r="G220" t="n">
-        <v>0.1172</v>
+        <v>0.1173</v>
       </c>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
@@ -12561,13 +12812,16 @@
         <v>1</v>
       </c>
       <c r="O220" t="n">
+        <v>1</v>
+      </c>
+      <c r="P220" t="n">
         <v>0.55</v>
       </c>
-      <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr"/>
       <c r="T220" t="inlineStr"/>
+      <c r="U220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -12623,13 +12877,16 @@
         <v>1</v>
       </c>
       <c r="O221" t="n">
+        <v>1</v>
+      </c>
+      <c r="P221" t="n">
         <v>0.55</v>
       </c>
-      <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr"/>
+      <c r="U221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -12685,13 +12942,16 @@
         <v>1</v>
       </c>
       <c r="O222" t="n">
+        <v>1</v>
+      </c>
+      <c r="P222" t="n">
         <v>0.55</v>
       </c>
-      <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr"/>
+      <c r="U222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -12747,13 +13007,16 @@
         <v>1</v>
       </c>
       <c r="O223" t="n">
+        <v>1</v>
+      </c>
+      <c r="P223" t="n">
         <v>0.75</v>
       </c>
-      <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr"/>
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr"/>
+      <c r="U223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -12773,7 +13036,7 @@
         <v>0.7693</v>
       </c>
       <c r="G224" t="n">
-        <v>0.0305</v>
+        <v>0.0304</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -12793,21 +13056,22 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>The client column 'LOCATION' has a high non-empty count but lacks relevant content to match the semantic role of 'Região do local do desembaraço aduaneiro'.</t>
+          <t>No suitable candidate matches the semantic role of the canonical column.</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
-      <c r="P224" t="n">
-        <v>0</v>
-      </c>
+      <c r="P224" t="inlineStr"/>
       <c r="Q224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
         <v>0.7998</v>
       </c>
-      <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr"/>
+      <c r="U224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -12847,21 +13111,22 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of relevant data evidence.</t>
+          <t>No suitable candidate found due to lack of non-empty values in the model column.</t>
         </is>
       </c>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
-      <c r="P225" t="n">
-        <v>0</v>
-      </c>
+      <c r="P225" t="inlineStr"/>
       <c r="Q225" t="n">
         <v>0</v>
       </c>
-      <c r="R225" t="inlineStr"/>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
       <c r="S225" t="inlineStr"/>
       <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -12901,21 +13166,22 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>The candidate 'ORGANIZACAO' does not semantically match 'UF do Local de Início' as it refers to an organization rather than a state code.</t>
+          <t>The candidate 'FORNECEDOR' does not match the expected content of 'UF do Local de Início', which should contain state abbreviations.</t>
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
-      <c r="P226" t="n">
-        <v>0</v>
-      </c>
+      <c r="P226" t="inlineStr"/>
       <c r="Q226" t="n">
         <v>0</v>
       </c>
-      <c r="R226" t="inlineStr"/>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -12961,15 +13227,16 @@
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
-      <c r="P227" t="n">
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="n">
         <v>0.85</v>
       </c>
-      <c r="Q227" t="n">
+      <c r="R227" t="n">
         <v>0.8</v>
       </c>
-      <c r="R227" t="inlineStr"/>
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -13015,15 +13282,16 @@
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
-      <c r="P228" t="n">
-        <v>0</v>
-      </c>
+      <c r="P228" t="inlineStr"/>
       <c r="Q228" t="n">
+        <v>0</v>
+      </c>
+      <c r="R228" t="n">
         <v>0.8005</v>
       </c>
-      <c r="R228" t="inlineStr"/>
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13069,7 +13337,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04T23:45:33.629972+00:00</t>
+          <t>2026-08-25T04:28:48.772469+00:00</t>
         </is>
       </c>
     </row>

--- a/mapping_oracle_full.xlsx
+++ b/mapping_oracle_full.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U228"/>
+  <dimension ref="A1:V228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,25 +512,30 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>arithmetic_proof</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>llm_data_confidence</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>llm_final_confidence</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>reviewer_status</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>correct_client_column</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>reviewer_note</t>
         </is>
@@ -551,10 +556,10 @@
         <v>0.7675</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7667</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008</v>
+        <v>0.0009</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -574,22 +579,23 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type, and the evidence quality is insufficient.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -603,13 +609,13 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0.7955</v>
+        <v>0.7956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7945</v>
+        <v>0.7944</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0011</v>
+        <v>0.0013</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -629,22 +635,23 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or lack relevant data evidence.</t>
+          <t>All candidates have semantic header conflicts or do not match the expected type for 'Base CBS', which is a tax base.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -658,13 +665,13 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.7843</v>
+        <v>0.7842</v>
       </c>
       <c r="F4" t="n">
         <v>0.7747000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0095</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -684,22 +691,23 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family for 'Aliquota CBS'.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -713,7 +721,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>0.7936</v>
+        <v>0.7937</v>
       </c>
       <c r="F5" t="n">
         <v>0.7896</v>
@@ -746,15 +754,16 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -768,13 +777,13 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.7914</v>
+        <v>0.7913</v>
       </c>
       <c r="F6" t="n">
         <v>0.7892</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -794,22 +803,23 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the tax family and provide no valid row evidence.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -823,7 +833,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.8207</v>
+        <v>0.8206</v>
       </c>
       <c r="F7" t="n">
         <v>0.8154</v>
@@ -849,22 +859,23 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of distinctive sample evidence.</t>
+          <t>No suitable candidate due to semantic header conflicts and lack of relevant data evidence.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -904,22 +915,23 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the canonical column, indicating incompatible tax roles.</t>
+          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -936,10 +948,10 @@
         <v>0.7939000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7833</v>
+        <v>0.7832</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0106</v>
+        <v>0.0107</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -959,22 +971,23 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of relevant data evidence.</t>
+          <t>All candidates have semantic header conflicts with the target column, and the evidence quality is insufficient.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1014,22 +1027,23 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the expected tax base role.</t>
+          <t>All candidates have semantic header conflicts with the 'Base IBSM' role.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1043,13 +1057,13 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>0.7866</v>
+        <v>0.7864</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7841</v>
+        <v>0.7842</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0024</v>
+        <v>0.0023</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1069,22 +1083,23 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the IBSM tax type, indicating incompatible mappings.</t>
+          <t>All candidates have a semantic header conflict with the tax-family of the model column.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1124,22 +1139,23 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of the target column and provide no valid mapping evidence.</t>
+          <t>All candidates conflict with the tax-family of the target column, and no valid mapping evidence exists.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1153,13 +1169,13 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.7913</v>
+        <v>0.7912</v>
       </c>
       <c r="F13" t="n">
         <v>0.787</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0043</v>
+        <v>0.0042</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1179,22 +1195,23 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with the IBSM column, indicating incompatible semantic roles.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context of the source column.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1234,22 +1251,23 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the 'Outras IBSM' column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have a semantic header conflict with the tax-family of the model column.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1269,7 +1287,7 @@
         <v>0.7735</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0075</v>
+        <v>0.0074</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1289,22 +1307,23 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the target column, and the data evidence is insufficient.</t>
+          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1344,22 +1363,23 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column.</t>
+          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1376,10 +1396,10 @@
         <v>0.8095</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8084</v>
+        <v>0.8082</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1399,22 +1419,23 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
+          <t>All candidates conflict semantically with the tax base role of 'Base IBS'.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1428,13 +1449,13 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>0.7885</v>
+        <v>0.7884</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7841</v>
+        <v>0.7842</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0044</v>
+        <v>0.0042</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1454,22 +1475,23 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended role of 'Aliquota IBS'.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context, and the evidence does not support a mapping.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1483,10 +1505,10 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8272</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8197</v>
+        <v>0.8198</v>
       </c>
       <c r="G19" t="n">
         <v>0.0074</v>
@@ -1509,22 +1531,23 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax family, and the evidence does not support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1538,13 +1561,13 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8008</v>
       </c>
       <c r="F20" t="n">
         <v>0.7911</v>
       </c>
       <c r="G20" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0098</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1564,22 +1587,23 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the tax-family context, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have a semantic header conflict with the original column, indicating they do not represent the same business meaning.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1596,10 +1620,10 @@
         <v>0.8224</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8074</v>
+        <v>0.8072</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0149</v>
+        <v>0.0151</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1626,15 +1650,16 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1681,15 +1706,16 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1706,7 +1732,7 @@
         <v>0.8319</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8287</v>
+        <v>0.8288</v>
       </c>
       <c r="G23" t="n">
         <v>0.0032</v>
@@ -1729,22 +1755,23 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of relevant data evidence.</t>
+          <t>All candidates have strong semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1761,10 +1788,10 @@
         <v>0.8171</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8073</v>
+        <v>0.8074</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0098</v>
+        <v>0.0097</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1784,22 +1811,23 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column 'Base IS' has only zeros, indicating no compatible mapping.</t>
+          <t>All candidate columns contain non-zero values, while the source column has only zeros, indicating a mismatch in semantic meaning.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1819,7 +1847,7 @@
         <v>0.8058</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0091</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1846,15 +1874,16 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1871,7 +1900,7 @@
         <v>0.7942</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7889</v>
+        <v>0.789</v>
       </c>
       <c r="G26" t="n">
         <v>0.0053</v>
@@ -1894,22 +1923,23 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while 'Valor IS' has only zeros, indicating a mismatch in semantic roles.</t>
+          <t>All candidate columns contain non-zero values, while the source column 'Valor IS' has only zeros, indicating a mismatch in semantic meaning.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1926,10 +1956,10 @@
         <v>0.8108</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7992</v>
+        <v>0.7993</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0116</v>
+        <v>0.0115</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1956,15 +1986,16 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2011,15 +2042,16 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2036,7 +2068,7 @@
         <v>0.7844</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.7778</v>
       </c>
       <c r="G29" t="n">
         <v>0.0067</v>
@@ -2066,15 +2098,16 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2088,16 +2121,16 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>0.7911</v>
+        <v>0.7521</v>
       </c>
       <c r="F30" t="n">
         <v>0.844</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0528</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.395</v>
+        <v>0.84</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2121,15 +2154,16 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S30" t="inlineStr"/>
+        <v>0.85</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.85</v>
+      </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2146,7 +2180,7 @@
         <v>0.7902</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7705</v>
+        <v>0.7704</v>
       </c>
       <c r="G31" t="n">
         <v>0.0198</v>
@@ -2176,15 +2210,16 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
-        <v>0.7902</v>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>0.7902</v>
-      </c>
-      <c r="S31" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.7951</v>
+      </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2230,22 +2265,23 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a high name confidence and matches the numeric format of the document number, despite a lower median length.</t>
+          <t>The candidate 'NUMERO NF' has a similar numeric structure but a lower median length than the expected 7 digits for document numbers.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="n">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="n">
         <v>0.5</v>
       </c>
-      <c r="R32" t="n">
-        <v>0.8119</v>
-      </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>0.6669</v>
+      </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2265,19 +2301,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.8556</v>
+        <v>0.8557</v>
       </c>
       <c r="F33" t="n">
         <v>0.8024</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0532</v>
+        <v>0.0533</v>
       </c>
       <c r="H33" t="n">
         <v>0.7833</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8556</v>
+        <v>0.8557</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2291,22 +2327,23 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' closely matches the semantic role of 'Nº da Nota Fiscal' with high name confidence and consistent numeric formatting.</t>
+          <t>The header 'NUMERO NF' closely matches 'Nº da Nota Fiscal' and has a high name confidence, but the numeric profile indicates a mismatch in expected digit length.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
-        <v>0.7833</v>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>0.8556</v>
-      </c>
-      <c r="S33" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.8557</v>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2329,10 +2366,10 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8112</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1888</v>
+        <v>0.189</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -2362,6 +2399,7 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2381,19 +2419,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.8421</v>
+        <v>0.842</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8238</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0159</v>
+        <v>0.0182</v>
       </c>
       <c r="H35" t="n">
         <v>0.8824</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8542</v>
+        <v>0.8541</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2427,6 +2465,7 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2446,19 +2485,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.8823</v>
+        <v>0.8824</v>
       </c>
       <c r="F36" t="n">
         <v>0.8250999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0572</v>
+        <v>0.0573</v>
       </c>
       <c r="H36" t="n">
         <v>0.1586</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8823</v>
+        <v>0.8824</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2472,22 +2511,23 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>The header 'DESC_PRODUTO' suggests a product description, but the numeric content indicates it is not compatible with the 'Descrição' column.</t>
+          <t>The header 'DESC_PRODUTO' suggests a product description, but the numeric content indicates it may not align with the 'Descrição' column's semantic role.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="n">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="n">
         <v>0.1586</v>
       </c>
-      <c r="R36" t="n">
-        <v>0.8823</v>
-      </c>
-      <c r="S36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>0.8824</v>
+      </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2534,15 +2574,16 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
         <v>0.85</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>0.8</v>
       </c>
-      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2556,13 +2597,13 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>0.8365</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="F38" t="n">
         <v>0.8288</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0077</v>
+        <v>0.0075</v>
       </c>
       <c r="H38" t="n">
         <v>0.4187</v>
@@ -2589,15 +2630,16 @@
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
-        <v>0.4187</v>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
-        <v>0.8265</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
+        <v>0.8362000000000001</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.8362000000000001</v>
+      </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2611,16 +2653,16 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
+        <v>0.8106</v>
+      </c>
+      <c r="F39" t="n">
         <v>0.8288</v>
       </c>
-      <c r="F39" t="n">
-        <v>0.7987</v>
-      </c>
       <c r="G39" t="n">
-        <v>0.0301</v>
+        <v>-0.0181</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.2181</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2637,22 +2679,23 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' conflicts semantically with the expected role of 'Nº ID fiscal 1', which is a tax ID, not a document ID.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2666,16 +2709,16 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
+        <v>0.7173</v>
+      </c>
+      <c r="F40" t="n">
         <v>0.8043</v>
       </c>
-      <c r="F40" t="n">
-        <v>0.7581</v>
-      </c>
       <c r="G40" t="n">
-        <v>0.0462</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.425</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2692,22 +2735,23 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Região' based on header names and data evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>0.7173</v>
+      </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2753,22 +2797,23 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>The 'TOTAL DO ITEM' column has a compatible numeric type and no semantic conflicts, aligning closely with the 'Val.Total NF' values.</t>
+          <t>The 'TOTAL DO ITEM' column has a compatible numeric type and no semantic conflicts, aligning closely with the 'Val.Total NF' role.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
         <v>0.9</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>0.85</v>
       </c>
-      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2819,11 +2864,16 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for icms on 2540 rows at fit 1.0</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2874,11 +2924,16 @@
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for icms on 2540 rows at fit 1.0</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2898,10 +2953,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.8066</v>
+        <v>0.8067</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8045</v>
+        <v>0.8046</v>
       </c>
       <c r="G44" t="n">
         <v>0.0021</v>
@@ -2910,7 +2965,7 @@
         <v>0.84</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8166</v>
+        <v>0.8167</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2931,15 +2986,16 @@
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2979,22 +3035,23 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a semantic header conflict with 'ICMS', indicating a tax-family mismatch.</t>
+          <t>The candidate 'IND TRIB ICMS' conflicts semantically with the role of 'Isentas ICMS' as it refers to a tax indicator rather than an exemption amount.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3047,15 +3104,16 @@
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
         <v>0.8968</v>
       </c>
-      <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3069,10 +3127,10 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>0.7948</v>
+        <v>0.795</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="G47" t="n">
         <v>0.005</v>
@@ -3102,15 +3160,16 @@
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3124,10 +3183,10 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.805</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8014</v>
+        <v>0.8015</v>
       </c>
       <c r="G48" t="n">
         <v>0.0035</v>
@@ -3150,22 +3209,23 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP value, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the ICEP value, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3188,10 +3248,10 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8938</v>
+        <v>0.8939</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1062</v>
+        <v>0.1061</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -3216,11 +3276,16 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for ipi on 333 rows at fit 1.0</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3271,11 +3336,16 @@
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for ipi on 333 rows at fit 1.0</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3295,10 +3365,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8776</v>
+        <v>0.8777</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8085</v>
+        <v>0.8084</v>
       </c>
       <c r="G51" t="n">
         <v>0.0692</v>
@@ -3307,7 +3377,7 @@
         <v>0.7498</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8776</v>
+        <v>0.8777</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3328,15 +3398,16 @@
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="n">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
         <v>0.5</v>
       </c>
-      <c r="R51" t="n">
-        <v>0.8776</v>
-      </c>
-      <c r="S51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>0.8777</v>
+      </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3359,10 +3430,10 @@
         <v>0.8832</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8275</v>
+        <v>0.8274</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0557</v>
+        <v>0.0558</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -3382,22 +3453,23 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a high name confidence but lacks supporting data evidence, as it conflicts with the IPI tax type.</t>
+          <t>The candidate 'IND TRIB IPI' has a strong name match but lacks supporting data evidence, as it conflicts with the all-zero evidence from 'Outras IPI'.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
         <v>0.8832</v>
       </c>
-      <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3420,10 +3492,10 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7652</v>
+        <v>0.7651</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2348</v>
+        <v>0.2349</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
@@ -3453,6 +3525,7 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3508,6 +3581,7 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3530,10 +3604,10 @@
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0.823</v>
+        <v>0.8237</v>
       </c>
       <c r="G55" t="n">
-        <v>0.177</v>
+        <v>0.1763</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
@@ -3563,6 +3637,7 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3585,10 +3660,10 @@
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1769</v>
+        <v>0.1759</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
@@ -3618,6 +3693,7 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3637,7 +3713,7 @@
         <v>0.7665999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0009</v>
+        <v>0.0008</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -3657,22 +3733,23 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>All candidate columns are unrelated to 'Frete' as they either represent product codes, descriptions, or other identifiers, with no relevant numeric or monetary values.</t>
+          <t>All candidate columns contain non-numeric or zero-only values, making them incompatible with the 'Frete' column.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="n">
-        <v>0.7544</v>
-      </c>
-      <c r="S57" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3686,7 +3763,7 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>0.8061</v>
+        <v>0.8062</v>
       </c>
       <c r="F58" t="n">
         <v>0.7996</v>
@@ -3712,22 +3789,23 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>All candidates are incompatible due to distinct content types and all-zero evidence.</t>
+          <t>All candidates are incompatible due to distinct types and all-zero evidence.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="n">
-        <v>0.7861</v>
-      </c>
-      <c r="S58" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.7863</v>
+      </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3767,22 +3845,23 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>The 'DESC_PRODUTO' column contains product descriptions, which do not match the 'Observações' column's content.</t>
+          <t>The 'Observações' column contains strings that do not match the numeric or product code context of 'COD_PRODUTO'.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3822,22 +3901,23 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No client column matches the semantic role or format of the 'Chave de acesso'.</t>
+          <t>No client column matches the semantic role of 'Chave de acesso' (NFe key) with sufficient evidence.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3851,7 +3931,7 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>0.8067</v>
+        <v>0.8066</v>
       </c>
       <c r="F61" t="n">
         <v>0.8149</v>
@@ -3884,15 +3964,16 @@
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="n">
-        <v>0.8067</v>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>0.8067</v>
-      </c>
-      <c r="S61" t="inlineStr"/>
+        <v>0.8066</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.8066</v>
+      </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3938,22 +4019,23 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>The header 'DATA GL' closely matches the expected date format and has strong evidence from the sample values.</t>
+          <t>The column 'DATA GL' has a high name confidence and matches the datetime format of 'Data documento'.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S62" t="inlineStr"/>
+        <v>0.8722</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.8722</v>
+      </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3967,16 +4049,16 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>0.7271</v>
+        <v>0.7687</v>
       </c>
       <c r="F63" t="n">
-        <v>0.769</v>
+        <v>0.7438</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.0419</v>
+        <v>0.0249</v>
       </c>
       <c r="H63" t="n">
-        <v>0.264</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -3993,22 +4075,23 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The header 'FORNECEDOR' does not match the semantic role of 'Criado por', which indicates a creator or author, not a supplier.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="n">
-        <v>0.7271</v>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="n">
-        <v>0.7271</v>
-      </c>
-      <c r="S63" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4025,10 +4108,10 @@
         <v>0.7612</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7608</v>
+        <v>0.7604</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0004</v>
+        <v>0.0008</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -4055,15 +4138,16 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4080,7 +4164,7 @@
         <v>0.8071</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7947</v>
+        <v>0.7948</v>
       </c>
       <c r="G65" t="n">
         <v>0.0123</v>
@@ -4110,15 +4194,16 @@
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4132,13 +4217,13 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>0.792</v>
+        <v>0.7906</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8136</v>
+        <v>0.8129</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.0216</v>
+        <v>-0.0223</v>
       </c>
       <c r="H66" t="n">
         <v>0.73</v>
@@ -4165,15 +4250,16 @@
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S66" t="inlineStr"/>
+        <v>0.73</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.7906</v>
+      </c>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4193,19 +4279,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8017</v>
+        <v>0.8016</v>
       </c>
       <c r="F67" t="n">
         <v>0.8331</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0314</v>
+        <v>-0.0315</v>
       </c>
       <c r="H67" t="n">
         <v>0.73</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8017</v>
+        <v>0.8016</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4226,15 +4312,16 @@
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S67" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.85</v>
+      </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4251,10 +4338,10 @@
         <v>0.829</v>
       </c>
       <c r="F68" t="n">
-        <v>0.8203</v>
+        <v>0.8202</v>
       </c>
       <c r="G68" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -4281,15 +4368,16 @@
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr"/>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4312,10 +4400,10 @@
         <v>0.8231000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8089</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0141</v>
+        <v>0.0142</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -4335,22 +4423,23 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>The 'NUMERO NF' column has a strong numeric profile and high name confidence, aligning well with the expected invoice number.</t>
+          <t>The header 'NUMERO NF' closely matches the semantic role of 'Nº FCI' as both refer to invoice numbers, supported by a high non-empty count and numeric profile.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="n">
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="n">
         <v>0.9</v>
       </c>
-      <c r="R69" t="n">
+      <c r="S69" t="n">
         <v>0.85</v>
       </c>
-      <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4390,22 +4479,23 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Condições pagamento' as all candidates are unrelated to payment conditions.</t>
+          <t>No candidate column matches the semantic role of 'Condições pagamento' as they all pertain to product codes or identifiers.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
         <v>0.75</v>
       </c>
-      <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4419,13 +4509,13 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>0.804</v>
+        <v>0.8041</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7938</v>
+        <v>0.7936</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0103</v>
+        <v>0.0104</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -4452,15 +4542,16 @@
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr"/>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4474,13 +4565,13 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7897</v>
       </c>
       <c r="F72" t="n">
         <v>0.7882</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0016</v>
+        <v>0.0015</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -4500,22 +4591,23 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax role of 'Aliquota ICAP', indicating they do not match the intended meaning.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family for 'Aliquota ICAP'.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr"/>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4529,13 +4621,13 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>0.7937</v>
+        <v>0.7944</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8176</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0239</v>
+        <v>-0.0247</v>
       </c>
       <c r="H73" t="n">
         <v>0.4751</v>
@@ -4562,15 +4654,16 @@
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="n">
-        <v>0.7937</v>
-      </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="n">
-        <v>0.7937</v>
-      </c>
-      <c r="S73" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4593,7 +4686,7 @@
         <v>0.8437</v>
       </c>
       <c r="F74" t="n">
-        <v>0.8101</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G74" t="n">
         <v>0.0337</v>
@@ -4623,15 +4716,16 @@
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="n">
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="n">
         <v>0.5</v>
       </c>
-      <c r="R74" t="n">
+      <c r="S74" t="n">
         <v>0.6718</v>
       </c>
-      <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4671,22 +4765,23 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No candidate column matches the semantic role of 'Mensagem' as all candidates are unrelated to message content.</t>
+          <t>No candidate column matches the semantic role of 'Mensagem' based on header and data evidence.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4703,7 +4798,7 @@
         <v>0.8246</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7895</v>
+        <v>0.7896</v>
       </c>
       <c r="G76" t="n">
         <v>0.0351</v>
@@ -4726,22 +4821,23 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>All candidate columns are empty or lack relevant data to support a mapping.</t>
+          <t>No suitable candidate found due to lack of evidence and empty profiles.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4781,22 +4877,23 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>The candidate 'COD_FIS_JUR' does not match the expected numeric format of 'Domicílio fiscal', which is a specific identifier.</t>
+          <t>The candidate 'COD_FIS_JUR' has a numeric profile but does not match the expected string format of 'Domicílio fiscal'.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4843,15 +4940,16 @@
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="n">
-        <v>0.7916</v>
-      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="n">
         <v>0.7916</v>
       </c>
-      <c r="S78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>0.7916</v>
+      </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4874,7 +4972,7 @@
         <v>0.8209</v>
       </c>
       <c r="F79" t="n">
-        <v>0.7875</v>
+        <v>0.7874</v>
       </c>
       <c r="G79" t="n">
         <v>0.0335</v>
@@ -4897,22 +4995,23 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' closely matches the expected 'Nº de serviço' and has substantial numeric evidence.</t>
+          <t>The column 'NUMERO NF' has a strong numeric profile and matches the semantic role of 'Nº de serviço' despite the empty evidence.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="n">
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="n">
         <v>0.9</v>
       </c>
-      <c r="R79" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="S79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>0.8209</v>
+      </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4932,10 +5031,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8016</v>
+        <v>0.8017</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.7869</v>
       </c>
       <c r="G80" t="n">
         <v>0.0148</v>
@@ -4944,7 +5043,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8016</v>
+        <v>0.8017</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4958,22 +5057,23 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>The column 'DESC_PRODUTO' has a high name confidence and contains descriptive product information, aligning with the expected content for 'Texto breve serviço'.</t>
+          <t>The header 'DESC_PRODUTO' suggests a description of products, which aligns with the expected content for 'Texto breve serviço'.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="n">
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="n">
         <v>0.8</v>
       </c>
-      <c r="R80" t="n">
-        <v>0.8016</v>
-      </c>
-      <c r="S80" t="inlineStr"/>
+      <c r="S80" t="n">
+        <v>0.8017</v>
+      </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4990,7 +5090,7 @@
         <v>0.7657</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8134</v>
+        <v>0.8135</v>
       </c>
       <c r="G81" t="n">
         <v>-0.0478</v>
@@ -5020,15 +5120,16 @@
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="n">
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="n">
         <v>0.85</v>
       </c>
-      <c r="R81" t="n">
+      <c r="S81" t="n">
         <v>0.8</v>
       </c>
-      <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5042,16 +5143,16 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F82" t="n">
         <v>0.7895</v>
       </c>
-      <c r="F82" t="n">
-        <v>0.7859</v>
-      </c>
       <c r="G82" t="n">
-        <v>0.0036</v>
+        <v>-0.0395</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -5068,22 +5169,23 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Utilização de material' based on the provided evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="inlineStr"/>
+        <v>0.85</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0.85</v>
+      </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5100,10 +5202,10 @@
         <v>0.7931</v>
       </c>
       <c r="F83" t="n">
-        <v>0.7779</v>
+        <v>0.778</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0152</v>
+        <v>0.0151</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -5130,15 +5232,16 @@
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="n">
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="n">
         <v>0.646</v>
       </c>
-      <c r="R83" t="n">
+      <c r="S83" t="n">
         <v>0.7931</v>
       </c>
-      <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5152,10 +5255,10 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>0.7402</v>
+        <v>0.74</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7368</v>
+        <v>0.7366</v>
       </c>
       <c r="G84" t="n">
         <v>0.0034</v>
@@ -5178,22 +5281,23 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>All candidate columns have semantic-role conflicts or do not match the expected type for 'Mont.líquido frete', which should represent a monetary value.</t>
+          <t>All candidate columns have semantic conflicts or do not match the expected type for 'Mont.líquido frete', which should represent a monetary value.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5207,13 +5311,13 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>0.7622</v>
+        <v>0.7621</v>
       </c>
       <c r="F85" t="n">
-        <v>0.7562</v>
+        <v>0.7563</v>
       </c>
       <c r="G85" t="n">
-        <v>0.006</v>
+        <v>0.0058</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -5240,15 +5344,16 @@
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
         <v>0.7453</v>
       </c>
-      <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5262,13 +5367,13 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>0.8227</v>
+        <v>0.8169</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8223</v>
+        <v>0.8228</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -5288,22 +5393,23 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>All candidates have conflicting semantic roles or lack relevant data evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0.85</v>
+      </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5326,10 +5432,10 @@
         <v>0.8881</v>
       </c>
       <c r="F87" t="n">
-        <v>0.862</v>
+        <v>0.8621</v>
       </c>
       <c r="G87" t="n">
-        <v>0.026</v>
+        <v>0.0261</v>
       </c>
       <c r="H87" t="n">
         <v>0.7375</v>
@@ -5356,15 +5462,16 @@
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="n">
-        <v>0.8881</v>
-      </c>
+      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="n">
         <v>0.8881</v>
       </c>
-      <c r="S87" t="inlineStr"/>
+      <c r="S87" t="n">
+        <v>0.8881</v>
+      </c>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5375,8 +5482,14 @@
           <t>Base Reduzida ICMS</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
+      <c r="C88" t="n">
+        <v>21</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
       <c r="E88" t="n">
         <v>0.8587</v>
       </c>
@@ -5387,10 +5500,10 @@
         <v>0.0295</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>0.8587</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -5399,27 +5512,28 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Base Reduzida ICMS'.</t>
+          <t>The candidate 'IND TRIB ICMS' has a high name confidence but conflicts semantically with the expected role of a tax base.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5439,7 +5553,7 @@
         <v>0.782</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0047</v>
+        <v>0.0048</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -5459,22 +5573,23 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type, indicating they do not match the intended role of 'Tipo de Imposto ICAP'.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type, indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr"/>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5488,13 +5603,13 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>0.7875</v>
+        <v>0.7876</v>
       </c>
       <c r="F90" t="n">
-        <v>0.7812</v>
+        <v>0.7811</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0063</v>
+        <v>0.0065</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -5514,22 +5629,23 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and do not match the expected tax base context.</t>
+          <t>All candidates conflict semantically with the expected tax situation for 'Isentas ICAP'.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr"/>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5569,22 +5685,23 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
+          <t>All candidates have semantic header conflicts and do not match the expected role of 'Outras ICAP'.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr"/>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5624,22 +5741,23 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
+          <t>All candidates have semantic header conflicts with the expected role of 'Base Reduzida ICAP' and provide no valid row evidence.</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr"/>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5653,13 +5771,13 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>0.785</v>
+        <v>0.7851</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7783</v>
+        <v>0.7782</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0067</v>
+        <v>0.0068</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -5679,22 +5797,23 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no relevant data evidence.</t>
+          <t>All candidates have semantic header conflicts with the target column.</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q93" t="inlineStr"/>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr"/>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5711,7 +5830,7 @@
         <v>0.8079</v>
       </c>
       <c r="F94" t="n">
-        <v>0.8024</v>
+        <v>0.8025</v>
       </c>
       <c r="G94" t="n">
         <v>0.0054</v>
@@ -5734,22 +5853,23 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the ICEP base, indicating they do not represent the same business meaning.</t>
+          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr"/>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5763,13 +5883,13 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>0.786</v>
+        <v>0.7859</v>
       </c>
       <c r="F95" t="n">
         <v>0.7833</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -5789,22 +5909,23 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the ICEP tax type, indicating they do not match the intended meaning.</t>
+          <t>All candidates have semantic header conflicts with the ICEP tax type, indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="inlineStr"/>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5818,13 +5939,13 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>0.787</v>
+        <v>0.7871</v>
       </c>
       <c r="F96" t="n">
-        <v>0.786</v>
+        <v>0.7861</v>
       </c>
       <c r="G96" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -5844,22 +5965,23 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
+          <t>All candidates conflict semantically with the tax situation of 'Isentas ICEP'.</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr"/>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5873,13 +5995,13 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.823</v>
       </c>
       <c r="F97" t="n">
         <v>0.8214</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -5899,22 +6021,23 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or insufficient evidence to support a mapping.</t>
+          <t>All candidates have semantic header conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr"/>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5954,22 +6077,23 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the ICEP role, indicating they do not match the intended mapping.</t>
+          <t>All candidates have semantic header conflicts with the ICEP role, indicating incompatible tax-family contexts.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr"/>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5983,13 +6107,13 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>0.7772</v>
+        <v>0.7771</v>
       </c>
       <c r="F99" t="n">
         <v>0.7766</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0005</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -6009,22 +6133,23 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the model column.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type.</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr"/>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6041,10 +6166,10 @@
         <v>0.7997</v>
       </c>
       <c r="F100" t="n">
-        <v>0.7865</v>
+        <v>0.7864</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0132</v>
+        <v>0.0134</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -6071,15 +6196,16 @@
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr"/>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6093,13 +6219,13 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>0.7995</v>
+        <v>0.7994</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7947</v>
+        <v>0.7948</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0048</v>
+        <v>0.0046</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -6119,22 +6245,23 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family context of ICSP, providing no valid mapping.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family, indicating no suitable mapping.</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q101" t="inlineStr"/>
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr"/>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6174,22 +6301,23 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the expected tax role, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr"/>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6203,13 +6331,13 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
-        <v>0.7842</v>
+        <v>0.7843</v>
       </c>
       <c r="F103" t="n">
         <v>0.7803</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0039</v>
+        <v>0.004</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -6236,15 +6364,16 @@
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q103" t="inlineStr"/>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr"/>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6284,22 +6413,23 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the original column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have a tax-family conflict with the original column, indicating incompatible meanings.</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q104" t="inlineStr"/>
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr"/>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6319,7 +6449,7 @@
         <v>0.7756999999999999</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0102</v>
+        <v>0.0103</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -6339,22 +6469,23 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the expected tax role, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q105" t="inlineStr"/>
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr"/>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6371,10 +6502,10 @@
         <v>0.803</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8102</v>
+        <v>0.8103</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.0072</v>
+        <v>-0.0073</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -6401,15 +6532,16 @@
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="n">
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="n">
         <v>0.8</v>
       </c>
-      <c r="R106" t="n">
+      <c r="S106" t="n">
         <v>0.803</v>
       </c>
-      <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6449,22 +6581,23 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>All candidate columns contain zero values, indicating no relevant data to support a mapping.</t>
+          <t>All candidate columns contain no relevant data to map to 'Base DIF_ALIQ', which requires a numeric base value.</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q107" t="inlineStr"/>
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr"/>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6481,10 +6614,10 @@
         <v>0.7875</v>
       </c>
       <c r="F108" t="n">
-        <v>0.784</v>
+        <v>0.7839</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0035</v>
+        <v>0.0037</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -6504,22 +6637,23 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>All candidates have non-zero values, while the model column only contains zeros, indicating a mismatch in semantic roles.</t>
+          <t>The candidate columns have conflicting semantic roles and no distinctive sample overlap, making them unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q108" t="inlineStr"/>
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr"/>
+      <c r="S108" t="n">
+        <v>0.7875</v>
+      </c>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6559,22 +6693,23 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Valor DIF_ALIQ' as all candidates either conflict semantically or provide no relevant data.</t>
+          <t>No suitable candidate matches the semantic role of 'Valor DIF_ALIQ' as all candidates have conflicting roles or irrelevant data.</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q109" t="inlineStr"/>
       <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
         <v>0.7976</v>
       </c>
-      <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6594,7 +6729,7 @@
         <v>0.8058999999999999</v>
       </c>
       <c r="G110" t="n">
-        <v>0.002</v>
+        <v>0.0021</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -6614,22 +6749,23 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates have non-zero values, while the model column is entirely zero, indicating a mismatch in semantic meaning.</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q110" t="inlineStr"/>
       <c r="R110" t="n">
-        <v>0.8079</v>
-      </c>
-      <c r="S110" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6669,22 +6805,23 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to all-zero evidence and lack of semantic alignment.</t>
+          <t>No suitable candidate matches the semantic role of 'Outras DIF_ALIQ' as all candidates are unrelated to tax rates or amounts.</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q111" t="inlineStr"/>
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr"/>
+      <c r="S111" t="n">
+        <v>0.8097</v>
+      </c>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6731,15 +6868,16 @@
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q112" t="inlineStr"/>
       <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
         <v>0.7779</v>
       </c>
-      <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6779,22 +6917,23 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
+          <t>All candidates have significant semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q113" t="inlineStr"/>
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="inlineStr"/>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6805,19 +6944,13 @@
           <t>Aliquota ICMS_FECP</t>
         </is>
       </c>
-      <c r="C114" t="n">
-        <v>21</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>IND TRIB ICMS</t>
-        </is>
-      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="n">
-        <v>0.8551</v>
+        <v>0.855</v>
       </c>
       <c r="F114" t="n">
-        <v>0.8272</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="G114" t="n">
         <v>0.028</v>
@@ -6826,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8551</v>
+        <v>0</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6835,27 +6968,28 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a high name confidence but does not match the all-zero evidence of the source column.</t>
+          <t>All candidates have conflicting semantic roles or insufficient evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q114" t="inlineStr"/>
       <c r="R114" t="n">
-        <v>0.8551</v>
-      </c>
-      <c r="S114" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6866,13 +7000,19 @@
           <t>Valor ICMS_FECP</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
+      <c r="C115" t="n">
+        <v>21</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
       <c r="E115" t="n">
-        <v>0.8587</v>
+        <v>0.8588</v>
       </c>
       <c r="F115" t="n">
-        <v>0.8296</v>
+        <v>0.8297</v>
       </c>
       <c r="G115" t="n">
         <v>0.0291</v>
@@ -6881,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>0.8588</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -6890,27 +7030,28 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to all candidates having conflicting semantic roles or insufficient evidence.</t>
+          <t>The candidate 'IND TRIB ICMS' has a high name confidence but conflicts with the expected role of a tax base, as it contains non-zero values.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q115" t="inlineStr"/>
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="inlineStr"/>
+      <c r="S115" t="n">
+        <v>0.8588</v>
+      </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6950,22 +7091,23 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
+          <t>All candidates have significant semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q116" t="inlineStr"/>
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr"/>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6976,14 +7118,8 @@
           <t>Outras ICMS_FECP</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>21</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>IND TRIB ICMS</t>
-        </is>
-      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
         <v>0.8659</v>
       </c>
@@ -6997,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8659</v>
+        <v>0</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -7006,27 +7142,28 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a high name confidence and aligns with the tax context despite its numeric values being non-zero.</t>
+          <t>All candidate columns contain non-zero values, while the source column has only zeros, indicating a mismatch in data meaning.</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="n">
-        <v>0.8659</v>
-      </c>
+      <c r="Q117" t="inlineStr"/>
       <c r="R117" t="n">
-        <v>0.8659</v>
-      </c>
-      <c r="S117" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7040,13 +7177,13 @@
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
-        <v>0.7784</v>
+        <v>0.8304</v>
       </c>
       <c r="F118" t="n">
-        <v>0.8304</v>
+        <v>0.803</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.052</v>
+        <v>0.0274</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -7066,22 +7203,23 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates have significant semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="n">
-        <v>0.7784</v>
-      </c>
+      <c r="Q118" t="inlineStr"/>
       <c r="R118" t="n">
-        <v>0.7784</v>
-      </c>
-      <c r="S118" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
       <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7104,10 +7242,10 @@
         <v>0.8535</v>
       </c>
       <c r="F119" t="n">
-        <v>0.792</v>
+        <v>0.7919</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0615</v>
+        <v>0.0616</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -7127,22 +7265,23 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a strong name match but conflicts with the tax-family context of 'Base Reduzida IPI', and the data evidence is all zeros.</t>
+          <t>The candidate 'IND TRIB IPI' has a strong name match but lacks supporting data evidence, as all values are non-informative zeros.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q119" t="inlineStr"/>
       <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
         <v>0.8535</v>
       </c>
-      <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7156,13 +7295,13 @@
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="n">
-        <v>0.8084</v>
+        <v>0.8083</v>
       </c>
       <c r="F120" t="n">
-        <v>0.8057</v>
+        <v>0.8056</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0028</v>
+        <v>0.0027</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -7182,22 +7321,23 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, making them incompatible.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context of COFINS.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q120" t="inlineStr"/>
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="inlineStr"/>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7214,10 +7354,10 @@
         <v>0.8073</v>
       </c>
       <c r="F121" t="n">
-        <v>0.8063</v>
+        <v>0.8062</v>
       </c>
       <c r="G121" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -7237,22 +7377,23 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended meaning of 'Isentas COFINS'.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context of COFINS.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q121" t="inlineStr"/>
       <c r="R121" t="n">
         <v>0</v>
       </c>
-      <c r="S121" t="inlineStr"/>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7266,13 +7407,13 @@
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="n">
-        <v>0.8266</v>
+        <v>0.8276</v>
       </c>
       <c r="F122" t="n">
-        <v>0.8204</v>
+        <v>0.8202</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0063</v>
+        <v>0.0074</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -7299,15 +7440,16 @@
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q122" t="inlineStr"/>
       <c r="R122" t="n">
         <v>0</v>
       </c>
-      <c r="S122" t="inlineStr"/>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7321,13 +7463,13 @@
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
-        <v>0.7755</v>
+        <v>0.7754</v>
       </c>
       <c r="F123" t="n">
         <v>0.7734</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0021</v>
+        <v>0.002</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -7347,22 +7489,23 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the required COFINS base, and no suitable mapping evidence is present.</t>
+          <t>All candidates have semantic header conflicts with the COFINS tax family, making them incompatible.</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q123" t="inlineStr"/>
       <c r="R123" t="n">
         <v>0</v>
       </c>
-      <c r="S123" t="inlineStr"/>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7382,7 +7525,7 @@
         <v>0.7818000000000001</v>
       </c>
       <c r="G124" t="n">
-        <v>0.004</v>
+        <v>0.0039</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -7402,22 +7545,23 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the PIS tax family and provide no valid mapping evidence.</t>
+          <t>All candidates have semantic header conflicts with the PIS tax family and provide no relevant row evidence.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q124" t="inlineStr"/>
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr"/>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7431,13 +7575,13 @@
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="n">
-        <v>0.8</v>
+        <v>0.7998</v>
       </c>
       <c r="F125" t="n">
         <v>0.799</v>
       </c>
       <c r="G125" t="n">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -7457,22 +7601,23 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the PIS tax family and provide no relevant row evidence.</t>
+          <t>The candidate columns conflict with the tax-family context of 'Outras PIS' and provide no relevant row evidence.</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q125" t="inlineStr"/>
       <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
         <v>0.5</v>
       </c>
-      <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7489,10 +7634,10 @@
         <v>0.7726</v>
       </c>
       <c r="F126" t="n">
-        <v>0.7725</v>
+        <v>0.7724</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -7519,15 +7664,16 @@
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q126" t="inlineStr"/>
       <c r="R126" t="n">
         <v>0</v>
       </c>
-      <c r="S126" t="inlineStr"/>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
       <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7544,10 +7690,10 @@
         <v>0.7673</v>
       </c>
       <c r="F127" t="n">
-        <v>0.7637</v>
+        <v>0.7635</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0036</v>
+        <v>0.0038</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -7567,22 +7713,23 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the PIS tax base, and the evidence does not support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the PIS tax base, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q127" t="inlineStr"/>
       <c r="R127" t="n">
         <v>0</v>
       </c>
-      <c r="S127" t="inlineStr"/>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7599,7 +7746,7 @@
         <v>0.7795</v>
       </c>
       <c r="F128" t="n">
-        <v>0.7742</v>
+        <v>0.7741</v>
       </c>
       <c r="G128" t="n">
         <v>0.0054</v>
@@ -7622,22 +7769,23 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type (ISS), providing no valid mapping.</t>
+          <t>All candidates conflict semantically with the required tax type (ISS) and provide no relevant data evidence.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q128" t="inlineStr"/>
       <c r="R128" t="n">
         <v>0</v>
       </c>
-      <c r="S128" t="inlineStr"/>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
       <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7651,13 +7799,13 @@
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
-        <v>0.7635</v>
+        <v>0.7634</v>
       </c>
       <c r="F129" t="n">
         <v>0.7532</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0103</v>
+        <v>0.0102</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -7677,22 +7825,23 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of the target column, and no valid mapping evidence is present.</t>
+          <t>All candidates conflict with the tax-family of the target column, and no suitable mapping is supported by the data.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q129" t="inlineStr"/>
       <c r="R129" t="n">
         <v>0</v>
       </c>
-      <c r="S129" t="inlineStr"/>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7706,13 +7855,13 @@
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="n">
-        <v>0.7784</v>
+        <v>0.7783</v>
       </c>
       <c r="F130" t="n">
         <v>0.7711</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0073</v>
+        <v>0.0072</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -7732,22 +7881,23 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the tax family, making them incompatible.</t>
+          <t>All candidates conflict with the tax-family of ISS, making them incompatible.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q130" t="inlineStr"/>
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="inlineStr"/>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
       <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7787,22 +7937,23 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of 'Valor ISS' and provide no relevant mapping evidence.</t>
+          <t>All candidates conflict with the tax-family of 'Valor ISS' and provide no relevant evidence.</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q131" t="inlineStr"/>
       <c r="R131" t="n">
         <v>0</v>
       </c>
-      <c r="S131" t="inlineStr"/>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7819,10 +7970,10 @@
         <v>0.7833</v>
       </c>
       <c r="F132" t="n">
-        <v>0.77</v>
+        <v>0.7698</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0133</v>
+        <v>0.0134</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -7849,15 +8000,16 @@
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q132" t="inlineStr"/>
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="inlineStr"/>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7904,15 +8056,16 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q133" t="inlineStr"/>
       <c r="R133" t="n">
         <v>0</v>
       </c>
-      <c r="S133" t="inlineStr"/>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
       <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7926,13 +8079,13 @@
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="n">
-        <v>0.7668</v>
+        <v>0.7667</v>
       </c>
       <c r="F134" t="n">
-        <v>0.7597</v>
+        <v>0.7595</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0071</v>
+        <v>0.0072</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -7952,22 +8105,23 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column, and the evidence does not support a mapping.</t>
+          <t>All candidates conflict with the tax-family of the target column, and no suitable mapping exists.</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q134" t="inlineStr"/>
       <c r="R134" t="n">
         <v>0</v>
       </c>
-      <c r="S134" t="inlineStr"/>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7984,10 +8138,10 @@
         <v>0.8183</v>
       </c>
       <c r="F135" t="n">
-        <v>0.8112</v>
+        <v>0.8111</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0071</v>
+        <v>0.0072</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -8007,22 +8161,23 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic or data conflicts, and the evidence does not support a mapping.</t>
+          <t>All candidates have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q135" t="inlineStr"/>
       <c r="R135" t="n">
         <v>0</v>
       </c>
-      <c r="S135" t="inlineStr"/>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8036,13 +8191,13 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
-        <v>0.8147</v>
+        <v>0.8145</v>
       </c>
       <c r="F136" t="n">
         <v>0.802</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0127</v>
+        <v>0.0125</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -8062,22 +8217,23 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and all-zero evidence.</t>
+          <t>All candidates have semantic conflicts or do not match the expected type for 'Aliquota FECP_ST', which is a tax rate.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q136" t="inlineStr"/>
       <c r="R136" t="n">
-        <v>0.8147</v>
-      </c>
-      <c r="S136" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8091,13 +8247,13 @@
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
-        <v>0.8076</v>
+        <v>0.8084</v>
       </c>
       <c r="F137" t="n">
         <v>0.8074</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0002</v>
+        <v>0.0009</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -8117,22 +8273,23 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-distinctive or conflicting data, with no suitable mapping to the tax base for FECP.</t>
+          <t>All candidates have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q137" t="inlineStr"/>
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr"/>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8149,10 +8306,10 @@
         <v>0.8093</v>
       </c>
       <c r="F138" t="n">
-        <v>0.8042</v>
+        <v>0.8041</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0051</v>
+        <v>0.0052</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -8179,15 +8336,16 @@
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q138" t="inlineStr"/>
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr"/>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8204,10 +8362,10 @@
         <v>0.8285</v>
       </c>
       <c r="F139" t="n">
-        <v>0.8273</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0012</v>
+        <v>0.0005</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -8234,15 +8392,16 @@
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q139" t="inlineStr"/>
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr"/>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8256,13 +8415,13 @@
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
-        <v>0.7973</v>
+        <v>0.7835</v>
       </c>
       <c r="F140" t="n">
-        <v>0.7829</v>
+        <v>0.797</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0144</v>
+        <v>-0.0135</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -8282,22 +8441,23 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts or do not match the expected type for 'Base Reduzida FECP_ST', which is an integer with all zero values.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q140" t="inlineStr"/>
       <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="inlineStr"/>
+        <v>0.7835</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.7835</v>
+      </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8311,16 +8471,16 @@
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
-        <v>0.7836</v>
+        <v>0.8691</v>
       </c>
       <c r="F141" t="n">
-        <v>0.7735</v>
+        <v>0.8531</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0101</v>
+        <v>0.016</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>0.7375</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -8337,22 +8497,23 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the required tax type, indicating they do not match the intended role.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q141" t="inlineStr"/>
       <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8366,13 +8527,13 @@
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="n">
-        <v>0.7915</v>
+        <v>0.7914</v>
       </c>
       <c r="F142" t="n">
-        <v>0.7901</v>
+        <v>0.7902</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0014</v>
+        <v>0.0012</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -8392,22 +8553,23 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the expected role of 'Base ICMS_ST'.</t>
+          <t>All candidates have semantic conflicts with the expected role of 'Base ICMS_ST' and provide no relevant data evidence.</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q142" t="inlineStr"/>
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="inlineStr"/>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
       <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8421,13 +8583,13 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>0.7916</v>
+        <v>0.7915</v>
       </c>
       <c r="F143" t="n">
         <v>0.787</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0046</v>
+        <v>0.0045</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -8447,22 +8609,23 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the required tax role, indicating they do not match the 'Aliquota ICMS_ST' column.</t>
+          <t>All candidates have semantic conflicts with the tax role of 'Aliquota ICMS_ST' and do not provide sufficient evidence for a mapping.</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q143" t="inlineStr"/>
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr"/>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8479,10 +8642,10 @@
         <v>0.7801</v>
       </c>
       <c r="F144" t="n">
-        <v>0.7799</v>
+        <v>0.78</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -8502,22 +8665,23 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or do not match the expected tax base for ICMS_ST.</t>
+          <t>All candidates conflict with the tax qualifier or family, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q144" t="inlineStr"/>
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr"/>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8557,22 +8721,23 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and do not align with the tax situation of 'Outras ICMS_ST'.</t>
+          <t>All candidates have semantic header conflicts and do not align with the expected tax base for ICMS_ST.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q145" t="inlineStr"/>
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr"/>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8586,13 +8751,13 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
-        <v>0.7789</v>
+        <v>0.7786</v>
       </c>
       <c r="F146" t="n">
-        <v>0.7786</v>
+        <v>0.7781</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0004</v>
+        <v>0.0005</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -8619,15 +8784,16 @@
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q146" t="inlineStr"/>
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr"/>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8641,7 +8807,7 @@
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
-        <v>0.7997</v>
+        <v>0.7998</v>
       </c>
       <c r="F147" t="n">
         <v>0.8016</v>
@@ -8674,15 +8840,16 @@
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="Q147" t="inlineStr"/>
       <c r="R147" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S147" t="inlineStr"/>
+        <v>0.7998</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0.7998</v>
+      </c>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8699,7 +8866,7 @@
         <v>0.7684</v>
       </c>
       <c r="F148" t="n">
-        <v>0.766</v>
+        <v>0.7661</v>
       </c>
       <c r="G148" t="n">
         <v>0.0024</v>
@@ -8729,15 +8896,16 @@
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q148" t="inlineStr"/>
       <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
         <v>0.7684</v>
       </c>
-      <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8754,10 +8922,10 @@
         <v>0.7773</v>
       </c>
       <c r="F149" t="n">
-        <v>0.752</v>
+        <v>0.7519</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0253</v>
+        <v>0.0254</v>
       </c>
       <c r="H149" t="n">
         <v>0.84</v>
@@ -8784,15 +8952,16 @@
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="n">
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="n">
         <v>0.8</v>
       </c>
-      <c r="R149" t="n">
-        <v>0.7886</v>
-      </c>
-      <c r="S149" t="inlineStr"/>
+      <c r="S149" t="n">
+        <v>0.7883</v>
+      </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8809,10 +8978,10 @@
         <v>0.7074</v>
       </c>
       <c r="F150" t="n">
-        <v>0.704</v>
+        <v>0.7035</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0033</v>
+        <v>0.0039</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -8839,15 +9008,16 @@
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q150" t="inlineStr"/>
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="inlineStr"/>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -8861,13 +9031,13 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="n">
-        <v>0.8161</v>
+        <v>0.8162</v>
       </c>
       <c r="F151" t="n">
         <v>0.8048999999999999</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0113</v>
+        <v>0.0112</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -8887,22 +9057,23 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>The candidate columns are empty and do not provide any relevant data to support a mapping.</t>
+          <t>All candidate columns are empty or lack relevant data to support a mapping.</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q151" t="inlineStr"/>
       <c r="R151" t="n">
-        <v>0.8161</v>
-      </c>
-      <c r="S151" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8942,22 +9113,23 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>All candidates are incompatible due to distinct content types and zero-only evidence.</t>
+          <t>All candidate columns contain non-numeric or zero-only values, making them incompatible with the numeric nature of 'Redução'.</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q152" t="inlineStr"/>
       <c r="R152" t="n">
-        <v>0.7748</v>
-      </c>
-      <c r="S152" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8971,10 +9143,10 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="n">
-        <v>0.7453</v>
+        <v>0.7454</v>
       </c>
       <c r="F153" t="n">
-        <v>0.7372</v>
+        <v>0.7373</v>
       </c>
       <c r="G153" t="n">
         <v>0.0081</v>
@@ -9004,15 +9176,16 @@
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="n">
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="n">
         <v>0.8</v>
       </c>
-      <c r="R153" t="n">
+      <c r="S153" t="n">
         <v>0.7627</v>
       </c>
-      <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -9029,7 +9202,7 @@
         <v>0.8545</v>
       </c>
       <c r="F154" t="n">
-        <v>0.8226</v>
+        <v>0.8225</v>
       </c>
       <c r="G154" t="n">
         <v>0.0319</v>
@@ -9052,22 +9225,23 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>All candidate columns have empty or non-informative data, making it impossible to establish a valid mapping.</t>
+          <t>All candidate columns have insufficient evidence and do not match the expected content for 'Cód.domicílio fiscal'.</t>
         </is>
       </c>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q154" t="inlineStr"/>
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr"/>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -9081,7 +9255,7 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
-        <v>0.8293</v>
+        <v>0.8292</v>
       </c>
       <c r="F155" t="n">
         <v>0.8245</v>
@@ -9107,22 +9281,23 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>All candidate columns contain no relevant data or evidence to support a mapping.</t>
+          <t>All candidate columns contain no relevant data to support a mapping.</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q155" t="inlineStr"/>
       <c r="R155" t="n">
         <v>0</v>
       </c>
-      <c r="S155" t="inlineStr"/>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -9136,13 +9311,13 @@
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.7975</v>
       </c>
       <c r="F156" t="n">
         <v>0.7953</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0026</v>
+        <v>0.0022</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -9162,22 +9337,23 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of non-empty values in the model column.</t>
+          <t>All candidate columns contain no data, making it impossible to establish a mapping.</t>
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q156" t="inlineStr"/>
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr"/>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9191,16 +9367,16 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
-        <v>0.7796</v>
+        <v>0.7945</v>
       </c>
       <c r="F157" t="n">
-        <v>0.8222</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="G157" t="n">
-        <v>-0.0425</v>
+        <v>-0.0276</v>
       </c>
       <c r="H157" t="n">
-        <v>0.73</v>
+        <v>0.1714</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -9224,15 +9400,16 @@
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="Q157" t="inlineStr"/>
       <c r="R157" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S157" t="inlineStr"/>
+        <v>0.7945</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0.7945</v>
+      </c>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9246,7 +9423,7 @@
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
-        <v>0.7551</v>
+        <v>0.7552</v>
       </c>
       <c r="F158" t="n">
         <v>0.7927999999999999</v>
@@ -9279,15 +9456,16 @@
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="Q158" t="inlineStr"/>
       <c r="R158" t="n">
         <v>0.85</v>
       </c>
-      <c r="S158" t="inlineStr"/>
+      <c r="S158" t="n">
+        <v>0.85</v>
+      </c>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9333,22 +9511,23 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a high name confidence and contains numeric values consistent with invoice numbers.</t>
+          <t>The candidate 'NUMERO NF' has a high numeric fraction and matches the semantic role of 'Nº NF-e dos serviços'.</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="Q159" t="inlineStr"/>
       <c r="R159" t="n">
+        <v>1</v>
+      </c>
+      <c r="S159" t="n">
         <v>0.8556</v>
       </c>
-      <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9368,7 +9547,7 @@
         <v>0.8259</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0013</v>
+        <v>0.0012</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -9388,22 +9567,23 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of non-empty values in the model column.</t>
+          <t>No suitable candidate matches the semantic role of 'Código verificação' as all candidates are unrelated to verification codes.</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q160" t="inlineStr"/>
       <c r="R160" t="n">
-        <v>0.7803</v>
-      </c>
-      <c r="S160" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0.7804</v>
+      </c>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9417,13 +9597,13 @@
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
-        <v>0.8438</v>
+        <v>0.8437</v>
       </c>
       <c r="F161" t="n">
         <v>0.8113</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0325</v>
+        <v>0.0324</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -9443,22 +9623,23 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>The candidate 'ORGANIZACAO' has a high name confidence but no relevant data evidence to support a mapping.</t>
+          <t>The 'Ordem' column is empty, providing no evidence to support a mapping to any candidate.</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q161" t="inlineStr"/>
       <c r="R161" t="n">
-        <v>0.8438</v>
-      </c>
-      <c r="S161" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0.8437</v>
+      </c>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9475,10 +9656,10 @@
         <v>0.7992</v>
       </c>
       <c r="F162" t="n">
-        <v>0.7887</v>
+        <v>0.788</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0105</v>
+        <v>0.0112</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -9498,22 +9679,23 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>The candidate columns do not match the expected type or content for 'Despesas', which should represent expenses, while the candidates are unrelated to financial data.</t>
+          <t>The 'Despesas' column contains only zeros, providing no evidence to map to any candidate.</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q162" t="inlineStr"/>
       <c r="R162" t="n">
-        <v>0.7992</v>
-      </c>
-      <c r="S162" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0.7722</v>
+      </c>
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9527,13 +9709,13 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="n">
-        <v>0.8242</v>
+        <v>0.8243</v>
       </c>
       <c r="F163" t="n">
-        <v>0.7866</v>
+        <v>0.7874</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0376</v>
+        <v>0.0368</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -9553,22 +9735,23 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>The 'Centro custo' column is empty with no valid data to support a mapping.</t>
+          <t>The candidate 'PROFIT_CENTER' has a strong name match but lacks any row evidence, making it unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q163" t="inlineStr"/>
       <c r="R163" t="n">
         <v>0</v>
       </c>
-      <c r="S163" t="inlineStr"/>
+      <c r="S163" t="n">
+        <v>0.8243</v>
+      </c>
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9582,13 +9765,13 @@
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="n">
-        <v>0.7831</v>
+        <v>0.783</v>
       </c>
       <c r="F164" t="n">
         <v>0.7726</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0105</v>
+        <v>0.0104</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -9608,22 +9791,23 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>No viable candidates match the semantic role of 'Municipio Fim' as all candidates are unrelated to municipality identification.</t>
+          <t>All candidate columns lack relevant data evidence to support a mapping to 'Municipio Fim'.</t>
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q164" t="inlineStr"/>
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="inlineStr"/>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -9670,15 +9854,16 @@
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q165" t="inlineStr"/>
       <c r="R165" t="n">
         <v>0</v>
       </c>
-      <c r="S165" t="inlineStr"/>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -9724,22 +9909,23 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>The column 'COD_PRODUTO' has a high name confidence and contains numeric values that align with item codes, despite the empty evidence for the model column.</t>
+          <t>The column 'COD_PRODUTO' has a high name confidence and contains numeric values that align with item codes, despite the absence of sample overlap.</t>
         </is>
       </c>
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="n">
-        <v>0.8734</v>
-      </c>
+      <c r="Q166" t="inlineStr"/>
       <c r="R166" t="n">
         <v>0.8734</v>
       </c>
-      <c r="S166" t="inlineStr"/>
+      <c r="S166" t="n">
+        <v>0.8734</v>
+      </c>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -9762,10 +9948,10 @@
         <v>0.8369</v>
       </c>
       <c r="F167" t="n">
-        <v>0.7694</v>
+        <v>0.7693</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0675</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -9785,22 +9971,23 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>The column 'NUMERO NF' has a strong numeric profile and matches the semantic role of 'Número do NFC-e SAT'.</t>
+          <t>The candidate 'NUMERO NF' has a strong numeric profile and high name confidence, aligning well with the expected format of 'Número do NFC-e SAT'.</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q167" t="inlineStr"/>
       <c r="R167" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S167" t="n">
         <v>0.8369</v>
       </c>
-      <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -9847,15 +10034,16 @@
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="n">
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="n">
         <v>0.9</v>
       </c>
-      <c r="R168" t="n">
+      <c r="S168" t="n">
         <v>0.85</v>
       </c>
-      <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -9872,7 +10060,7 @@
         <v>0.8421</v>
       </c>
       <c r="F169" t="n">
-        <v>0.8176</v>
+        <v>0.8177</v>
       </c>
       <c r="G169" t="n">
         <v>0.0245</v>
@@ -9895,22 +10083,23 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the model column has only zeros, indicating a lack of semantic alignment.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q169" t="inlineStr"/>
       <c r="R169" t="n">
         <v>0</v>
       </c>
-      <c r="S169" t="inlineStr"/>
+      <c r="S169" t="n">
+        <v>0.8421</v>
+      </c>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -9924,13 +10113,13 @@
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="n">
-        <v>0.7902</v>
+        <v>0.7906</v>
       </c>
       <c r="F170" t="n">
-        <v>0.7887</v>
+        <v>0.7886</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0015</v>
+        <v>0.002</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -9957,15 +10146,16 @@
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q170" t="inlineStr"/>
       <c r="R170" t="n">
         <v>0</v>
       </c>
-      <c r="S170" t="inlineStr"/>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
       <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -9979,13 +10169,13 @@
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="n">
-        <v>0.8003</v>
+        <v>0.8002</v>
       </c>
       <c r="F171" t="n">
-        <v>0.7983</v>
+        <v>0.7984</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0021</v>
+        <v>0.0017</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -10005,22 +10195,23 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family, and the evidence does not support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q171" t="inlineStr"/>
       <c r="R171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="inlineStr"/>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -10034,13 +10225,13 @@
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8207</v>
       </c>
       <c r="F172" t="n">
-        <v>0.8204</v>
+        <v>0.8008</v>
       </c>
       <c r="G172" t="n">
-        <v>-0.0195</v>
+        <v>0.0199</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -10060,22 +10251,23 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates have semantic conflicts or insufficient evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q172" t="inlineStr"/>
       <c r="R172" t="n">
-        <v>0.8008999999999999</v>
-      </c>
-      <c r="S172" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S172" t="n">
+        <v>0</v>
+      </c>
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -10089,13 +10281,13 @@
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="n">
-        <v>0.8004</v>
+        <v>0.8007</v>
       </c>
       <c r="F173" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.7988</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0016</v>
+        <v>0.0019</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -10115,22 +10307,23 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
+          <t>All candidates have a tax-family conflict with the source column, and no valid mapping evidence supports a connection.</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q173" t="inlineStr"/>
       <c r="R173" t="n">
         <v>0</v>
       </c>
-      <c r="S173" t="inlineStr"/>
+      <c r="S173" t="n">
+        <v>0</v>
+      </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -10144,13 +10337,13 @@
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
-        <v>0.8273</v>
+        <v>0.8278</v>
       </c>
       <c r="F174" t="n">
-        <v>0.8174</v>
+        <v>0.8173</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0098</v>
+        <v>0.0105</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -10170,22 +10363,23 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of distinctive row evidence.</t>
+          <t>No suitable candidate due to semantic header conflicts and lack of distinctive sample evidence.</t>
         </is>
       </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q174" t="inlineStr"/>
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="inlineStr"/>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10211,7 +10405,7 @@
         <v>0.7859</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0451</v>
+        <v>0.0452</v>
       </c>
       <c r="H175" t="n">
         <v>0.7405</v>
@@ -10231,22 +10425,23 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' suggests a document number, but the sample values do not align with the expected format of an invoice number.</t>
+          <t>The header 'NUMERO NF' suggests an invoice number, but the numeric profile and sample values do not align with the expected format of a 'Numero do Pedido'.</t>
         </is>
       </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="n">
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="n">
         <v>0.5</v>
       </c>
-      <c r="R175" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="S175" t="inlineStr"/>
+      <c r="S175" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10266,19 +10461,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.8643</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="F176" t="n">
-        <v>0.797</v>
+        <v>0.7973</v>
       </c>
       <c r="G176" t="n">
-        <v>0.0673</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H176" t="n">
         <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>0.8643</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -10299,15 +10494,16 @@
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="Q176" t="inlineStr"/>
       <c r="R176" t="n">
         <v>0.8</v>
       </c>
-      <c r="S176" t="inlineStr"/>
+      <c r="S176" t="n">
+        <v>0.8</v>
+      </c>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -10321,13 +10517,13 @@
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="n">
-        <v>0.8037</v>
+        <v>0.8036</v>
       </c>
       <c r="F177" t="n">
-        <v>0.7862</v>
+        <v>0.7861</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0176</v>
+        <v>0.0174</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -10347,22 +10543,23 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the target column and lack sufficient evidence.</t>
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q177" t="inlineStr"/>
       <c r="R177" t="n">
         <v>0</v>
       </c>
-      <c r="S177" t="inlineStr"/>
+      <c r="S177" t="n">
+        <v>0</v>
+      </c>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -10376,13 +10573,13 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="n">
-        <v>0.7832</v>
+        <v>0.7831</v>
       </c>
       <c r="F178" t="n">
         <v>0.7748</v>
       </c>
       <c r="G178" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0083</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -10402,22 +10599,23 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax classification, making them incompatible.</t>
+          <t>All candidates have semantic header conflicts with the expected tax classification role.</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q178" t="inlineStr"/>
       <c r="R178" t="n">
         <v>0</v>
       </c>
-      <c r="S178" t="inlineStr"/>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -10437,10 +10635,10 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.8387</v>
+        <v>0.8388</v>
       </c>
       <c r="F179" t="n">
-        <v>0.8398</v>
+        <v>0.8399</v>
       </c>
       <c r="G179" t="n">
         <v>-0.0011</v>
@@ -10449,7 +10647,7 @@
         <v>0.5</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8387</v>
+        <v>0.8388</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -10463,22 +10661,23 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' closely matches the semantic role of 'Nº documento' and has strong numeric evidence.</t>
+          <t>The column 'NUMERO NF' closely matches the expected format and type for invoice document numbers, with strong numeric evidence.</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="n">
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="n">
         <v>0.9</v>
       </c>
-      <c r="R179" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="S179" t="inlineStr"/>
+      <c r="S179" t="n">
+        <v>0.85</v>
+      </c>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -10492,16 +10691,16 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>0.8449</v>
+        <v>0.751</v>
       </c>
       <c r="F180" t="n">
         <v>0.8505</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.0057</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="H180" t="n">
-        <v>0.7123</v>
+        <v>0.82</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
@@ -10525,15 +10724,16 @@
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="n">
-        <v>0.8449</v>
-      </c>
+      <c r="Q180" t="inlineStr"/>
       <c r="R180" t="n">
-        <v>0.8449</v>
-      </c>
-      <c r="S180" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="S180" t="n">
+        <v>0.825</v>
+      </c>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -10553,19 +10753,19 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>0.861</v>
+        <v>0.8606</v>
       </c>
       <c r="F181" t="n">
         <v>0.8268</v>
       </c>
       <c r="G181" t="n">
-        <v>0.0342</v>
+        <v>0.0338</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>0.861</v>
+        <v>0.8606</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -10579,22 +10779,23 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>The 'FORNECEDOR' column contains valid supplier names, aligning with the 'Exportador' role.</t>
+          <t>The 'FORNECEDOR' column has strong evidence with many non-empty values and a high name confidence, aligning with the role of 'Exportador'.</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="n">
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="n">
         <v>0.9</v>
       </c>
-      <c r="R181" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="S181" t="inlineStr"/>
+      <c r="S181" t="n">
+        <v>0.8606</v>
+      </c>
       <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -10641,15 +10842,16 @@
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="n">
-        <v>0.788</v>
-      </c>
+      <c r="Q182" t="inlineStr"/>
       <c r="R182" t="n">
         <v>0.788</v>
       </c>
-      <c r="S182" t="inlineStr"/>
+      <c r="S182" t="n">
+        <v>0.788</v>
+      </c>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -10663,7 +10865,7 @@
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
-        <v>0.8127</v>
+        <v>0.8126</v>
       </c>
       <c r="F183" t="n">
         <v>0.8282</v>
@@ -10696,15 +10898,16 @@
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="n">
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="n">
         <v>0.8</v>
       </c>
-      <c r="R183" t="n">
-        <v>0.8127</v>
-      </c>
-      <c r="S183" t="inlineStr"/>
+      <c r="S183" t="n">
+        <v>0.8126</v>
+      </c>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -10718,16 +10921,16 @@
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="n">
-        <v>0.857</v>
+        <v>0.7873</v>
       </c>
       <c r="F184" t="n">
-        <v>0.8091</v>
+        <v>0.8566</v>
       </c>
       <c r="G184" t="n">
-        <v>0.048</v>
+        <v>-0.0693</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
@@ -10744,22 +10947,23 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Código Fornecedor Início' based on header and data evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q184" t="inlineStr"/>
       <c r="R184" t="n">
-        <v>0</v>
-      </c>
-      <c r="S184" t="inlineStr"/>
+        <v>0.85</v>
+      </c>
+      <c r="S184" t="n">
+        <v>0.85</v>
+      </c>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -10782,10 +10986,10 @@
         <v>0.98</v>
       </c>
       <c r="F185" t="n">
-        <v>0.8147</v>
+        <v>0.8146</v>
       </c>
       <c r="G185" t="n">
-        <v>0.1653</v>
+        <v>0.1654</v>
       </c>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
@@ -10815,6 +11019,7 @@
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -10828,10 +11033,10 @@
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="n">
-        <v>0.8021</v>
+        <v>0.802</v>
       </c>
       <c r="F186" t="n">
-        <v>0.7861</v>
+        <v>0.786</v>
       </c>
       <c r="G186" t="n">
         <v>0.016</v>
@@ -10861,15 +11066,16 @@
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="n">
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="n">
         <v>0.8</v>
       </c>
-      <c r="R186" t="n">
-        <v>0.8021</v>
-      </c>
-      <c r="S186" t="inlineStr"/>
+      <c r="S186" t="n">
+        <v>0.802</v>
+      </c>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -10916,15 +11122,16 @@
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="Q187" t="inlineStr"/>
       <c r="R187" t="n">
         <v>0.8016</v>
       </c>
-      <c r="S187" t="inlineStr"/>
+      <c r="S187" t="n">
+        <v>0.8016</v>
+      </c>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -10947,10 +11154,10 @@
         <v>0.8401</v>
       </c>
       <c r="F188" t="n">
-        <v>0.8217</v>
+        <v>0.8216</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0184</v>
+        <v>0.0185</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -10977,15 +11184,16 @@
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q188" t="inlineStr"/>
       <c r="R188" t="n">
         <v>0</v>
       </c>
-      <c r="S188" t="inlineStr"/>
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -11008,10 +11216,10 @@
         <v>0.9036</v>
       </c>
       <c r="F189" t="n">
-        <v>0.8623</v>
+        <v>0.8622</v>
       </c>
       <c r="G189" t="n">
-        <v>0.0413</v>
+        <v>0.0414</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -11031,22 +11239,23 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>The header 'NUM_ITEM' suggests an item identifier, but the data is all zeros, indicating it may not be a valid mapping.</t>
+          <t>The header 'NUM_ITEM' suggests an item identifier, but the data is all zeros, indicating it does not provide meaningful evidence.</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q189" t="inlineStr"/>
       <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="n">
         <v>0.9036</v>
       </c>
-      <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -11060,10 +11269,10 @@
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="n">
-        <v>0.7823</v>
+        <v>0.7821</v>
       </c>
       <c r="F190" t="n">
-        <v>0.7811</v>
+        <v>0.781</v>
       </c>
       <c r="G190" t="n">
         <v>0.0011</v>
@@ -11086,22 +11295,23 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>All candidate columns are empty, providing no evidence for mapping.</t>
+          <t>All candidate columns are empty with no distinctive content or evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q190" t="inlineStr"/>
       <c r="R190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="inlineStr"/>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -11152,11 +11362,16 @@
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for icms on 2540 rows at fit 1.0</t>
+        </is>
+      </c>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
       <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -11173,10 +11388,10 @@
         <v>0.7774</v>
       </c>
       <c r="F192" t="n">
-        <v>0.7988</v>
+        <v>0.7987</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.0213</v>
+        <v>-0.0212</v>
       </c>
       <c r="H192" t="n">
         <v>0.4214</v>
@@ -11203,15 +11418,16 @@
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="n">
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="n">
         <v>0.5</v>
       </c>
-      <c r="R192" t="n">
-        <v>0.7774</v>
-      </c>
-      <c r="S192" t="inlineStr"/>
+      <c r="S192" t="n">
+        <v>0.75</v>
+      </c>
       <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -11234,10 +11450,10 @@
         <v>0.98</v>
       </c>
       <c r="F193" t="n">
-        <v>0.8932</v>
+        <v>0.8933</v>
       </c>
       <c r="G193" t="n">
-        <v>0.0868</v>
+        <v>0.0867</v>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
@@ -11262,11 +11478,16 @@
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for ipi on 333 rows at fit 1.0</t>
+        </is>
+      </c>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -11286,7 +11507,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.8927</v>
       </c>
       <c r="F194" t="n">
         <v>0.8123</v>
@@ -11298,7 +11519,7 @@
         <v>0.7375</v>
       </c>
       <c r="I194" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.8927</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -11312,22 +11533,23 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' closely matches the tax type 'Tipo de Imposto IPI' with high name confidence and consistent numeric values.</t>
+          <t>The candidate 'IND TRIB IPI' has a high name confidence and matches the IPI tax type despite some numeric discrepancies.</t>
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="n">
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="n">
         <v>0.8</v>
       </c>
-      <c r="R194" t="n">
+      <c r="S194" t="n">
         <v>0.85</v>
       </c>
-      <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -11353,7 +11575,7 @@
         <v>0.8105</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0648</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="H195" t="n">
         <v>0.225</v>
@@ -11373,22 +11595,23 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>The candidate 'NUM_ITEM' has a high name confidence but does not match the expected item ID role.</t>
+          <t>The candidate 'NUM_ITEM' has a high name confidence but does not match the expected item ID role, leading to a semantic conflict.</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q195" t="inlineStr"/>
       <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="n">
         <v>0.8752</v>
       </c>
-      <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -11408,19 +11631,19 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>0.8823</v>
+        <v>0.8824</v>
       </c>
       <c r="F196" t="n">
         <v>0.8250999999999999</v>
       </c>
       <c r="G196" t="n">
-        <v>0.0572</v>
+        <v>0.0573</v>
       </c>
       <c r="H196" t="n">
         <v>0.7981</v>
       </c>
       <c r="I196" t="n">
-        <v>0.8823</v>
+        <v>0.8824</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -11434,22 +11657,23 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>The candidate 'DESC_PRODUTO' has a high name confidence and a strong profile similarity, indicating it likely represents product descriptions.</t>
+          <t>The column 'DESC_PRODUTO' has a high name confidence and a strong profile similarity, indicating it likely represents product descriptions.</t>
         </is>
       </c>
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="n">
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="n">
         <v>0.7981</v>
       </c>
-      <c r="R196" t="n">
-        <v>0.8352000000000001</v>
-      </c>
-      <c r="S196" t="inlineStr"/>
+      <c r="S196" t="n">
+        <v>0.8401999999999999</v>
+      </c>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11463,10 +11687,10 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="n">
-        <v>0.7216</v>
+        <v>0.7242</v>
       </c>
       <c r="F197" t="n">
-        <v>0.8365</v>
+        <v>0.8391</v>
       </c>
       <c r="G197" t="n">
         <v>-0.1148</v>
@@ -11496,15 +11720,16 @@
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="Q197" t="inlineStr"/>
       <c r="R197" t="n">
         <v>0.85</v>
       </c>
-      <c r="S197" t="inlineStr"/>
+      <c r="S197" t="n">
+        <v>0.85</v>
+      </c>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11551,15 +11776,16 @@
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="n">
-        <v>0.8062</v>
-      </c>
+      <c r="Q198" t="inlineStr"/>
       <c r="R198" t="n">
         <v>0.8062</v>
       </c>
-      <c r="S198" t="inlineStr"/>
+      <c r="S198" t="n">
+        <v>0.8062</v>
+      </c>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -11582,10 +11808,10 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="F199" t="n">
-        <v>0.8072</v>
+        <v>0.8073</v>
       </c>
       <c r="G199" t="n">
-        <v>0.0391</v>
+        <v>0.039</v>
       </c>
       <c r="H199" t="n">
         <v>0.45</v>
@@ -11612,15 +11838,16 @@
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="n">
-        <v>0.8463000000000001</v>
-      </c>
+      <c r="Q199" t="inlineStr"/>
       <c r="R199" t="n">
         <v>0.8463000000000001</v>
       </c>
-      <c r="S199" t="inlineStr"/>
+      <c r="S199" t="n">
+        <v>0.8463000000000001</v>
+      </c>
       <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -11676,6 +11903,7 @@
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -11692,7 +11920,7 @@
         <v>0.7675999999999999</v>
       </c>
       <c r="F201" t="n">
-        <v>0.7185</v>
+        <v>0.7184</v>
       </c>
       <c r="G201" t="n">
         <v>0.0491</v>
@@ -11722,15 +11950,16 @@
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q201" t="inlineStr"/>
       <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="n">
         <v>0.7675999999999999</v>
       </c>
-      <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -11770,22 +11999,23 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>The candidate 'LOCATION' does not semantically match 'Município do Local de Início' as it lacks relevant municipal data.</t>
+          <t>The candidate 'LOCATION' has low name confidence and no relevant data overlap with the expected municipality values.</t>
         </is>
       </c>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q202" t="inlineStr"/>
       <c r="R202" t="n">
         <v>0</v>
       </c>
-      <c r="S202" t="inlineStr"/>
+      <c r="S202" t="n">
+        <v>0</v>
+      </c>
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -11825,22 +12055,23 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax role of IVA.</t>
+          <t>All candidates have semantic header conflicts with the IVA role, indicating incompatible tax-family contexts.</t>
         </is>
       </c>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q203" t="inlineStr"/>
       <c r="R203" t="n">
         <v>0</v>
       </c>
-      <c r="S203" t="inlineStr"/>
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
       <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -11854,13 +12085,13 @@
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="n">
-        <v>0.8044</v>
+        <v>0.804</v>
       </c>
       <c r="F204" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7748</v>
       </c>
       <c r="G204" t="n">
-        <v>0.0296</v>
+        <v>0.0293</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -11887,15 +12118,16 @@
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="n">
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="n">
         <v>0.8</v>
       </c>
-      <c r="R204" t="n">
-        <v>0.8044</v>
-      </c>
-      <c r="S204" t="inlineStr"/>
+      <c r="S204" t="n">
+        <v>0.804</v>
+      </c>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -11935,22 +12167,23 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' does not match the semantic role of 'Nº do NCM', which is a tax classification code.</t>
+          <t>The header 'NUMERO NF' conflicts semantically with 'Nº do NCM', which is a tax classification code.</t>
         </is>
       </c>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q205" t="inlineStr"/>
       <c r="R205" t="n">
         <v>0</v>
       </c>
-      <c r="S205" t="inlineStr"/>
+      <c r="S205" t="n">
+        <v>0</v>
+      </c>
       <c r="T205" t="inlineStr"/>
       <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -12003,15 +12236,16 @@
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q206" t="inlineStr"/>
       <c r="R206" t="n">
         <v>0</v>
       </c>
-      <c r="S206" t="inlineStr"/>
+      <c r="S206" t="n">
+        <v>0</v>
+      </c>
       <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -12057,22 +12291,23 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>The candidate 'PRECO UNITARIO' has a high name confidence and a similar numeric profile, indicating it likely represents a unit price.</t>
+          <t>The candidate 'PRECO UNITARIO' closely matches the semantic role of 'Preço líq.' as both represent unit prices, despite some numeric discrepancies.</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="Q207" t="inlineStr"/>
       <c r="R207" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="S207" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="S207" t="n">
+        <v>0.8532999999999999</v>
+      </c>
       <c r="T207" t="inlineStr"/>
       <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -12119,15 +12354,16 @@
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="n">
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="n">
         <v>0.8</v>
       </c>
-      <c r="R208" t="n">
+      <c r="S208" t="n">
         <v>0.785</v>
       </c>
-      <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -12174,15 +12410,16 @@
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q209" t="inlineStr"/>
       <c r="R209" t="n">
         <v>0</v>
       </c>
-      <c r="S209" t="inlineStr"/>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
       <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -12205,7 +12442,7 @@
         <v>0.8629</v>
       </c>
       <c r="F210" t="n">
-        <v>0.7884</v>
+        <v>0.7883</v>
       </c>
       <c r="G210" t="n">
         <v>0.0745</v>
@@ -12228,22 +12465,23 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>The column 'NUMERO NF' has a high numeric fraction and matches the expected format for invoice numbers.</t>
+          <t>The candidate 'NUMERO NF' has a high name confidence and a substantial non-empty count, indicating it likely represents the invoice number.</t>
         </is>
       </c>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="n">
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="n">
         <v>1</v>
       </c>
-      <c r="R210" t="n">
+      <c r="S210" t="n">
         <v>0.8629</v>
       </c>
-      <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -12289,22 +12527,23 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>The candidate 'TOTAL DO ITEM' closely matches the canonical 'Valor Total do Item' in both name and numeric profile.</t>
+          <t>The name 'TOTAL DO ITEM' closely matches 'Valor Total do Item' with high name confidence and consistent numeric evidence.</t>
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="n">
-        <v>0.9388</v>
-      </c>
+      <c r="Q211" t="inlineStr"/>
       <c r="R211" t="n">
         <v>0.9388</v>
       </c>
-      <c r="S211" t="inlineStr"/>
+      <c r="S211" t="n">
+        <v>0.9388</v>
+      </c>
       <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12324,7 +12563,7 @@
         <v>0.7799</v>
       </c>
       <c r="G212" t="n">
-        <v>0.051</v>
+        <v>0.0509</v>
       </c>
       <c r="H212" t="n">
         <v>0.4406</v>
@@ -12351,15 +12590,16 @@
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="n">
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="n">
         <v>0.8</v>
       </c>
-      <c r="R212" t="n">
+      <c r="S212" t="n">
         <v>0.8154</v>
       </c>
-      <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12376,10 +12616,10 @@
         <v>0.8137</v>
       </c>
       <c r="F213" t="n">
-        <v>0.8087</v>
+        <v>0.8086</v>
       </c>
       <c r="G213" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -12399,22 +12639,23 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>The candidate columns contain numeric product codes, which do not match the expected transportadora code.</t>
+          <t>All candidate columns contain no relevant data, making mapping impossible.</t>
         </is>
       </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q213" t="inlineStr"/>
       <c r="R213" t="n">
-        <v>0.8137</v>
-      </c>
-      <c r="S213" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
       <c r="T213" t="inlineStr"/>
       <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12437,10 +12678,10 @@
         <v>0.98</v>
       </c>
       <c r="F214" t="n">
-        <v>0.7889</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="G214" t="n">
-        <v>0.1911</v>
+        <v>0.1912</v>
       </c>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
@@ -12470,6 +12711,7 @@
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="inlineStr"/>
       <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12483,13 +12725,13 @@
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="n">
-        <v>0.7821</v>
+        <v>0.782</v>
       </c>
       <c r="F215" t="n">
         <v>0.8137</v>
       </c>
       <c r="G215" t="n">
-        <v>-0.0316</v>
+        <v>-0.0318</v>
       </c>
       <c r="H215" t="n">
         <v>0.1802</v>
@@ -12516,15 +12758,16 @@
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="n">
-        <v>0.7821</v>
-      </c>
+      <c r="Q215" t="inlineStr"/>
       <c r="R215" t="n">
-        <v>0.7821</v>
-      </c>
-      <c r="S215" t="inlineStr"/>
+        <v>0.782</v>
+      </c>
+      <c r="S215" t="n">
+        <v>0.782</v>
+      </c>
       <c r="T215" t="inlineStr"/>
       <c r="U215" t="inlineStr"/>
+      <c r="V215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -12577,15 +12820,16 @@
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q216" t="inlineStr"/>
       <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="n">
         <v>0.889</v>
       </c>
-      <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr"/>
       <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -12631,22 +12875,23 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a strong name match and aligns with the expected integer type for IPI indicators, despite the numeric values being limited.</t>
+          <t>The name 'IND TRIB IPI' closely matches the expected role for IPI tax identification despite numeric discrepancies.</t>
         </is>
       </c>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="Q217" t="inlineStr"/>
       <c r="R217" t="n">
-        <v>0.8256</v>
-      </c>
-      <c r="S217" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="S217" t="n">
+        <v>0.8806</v>
+      </c>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -12663,10 +12908,10 @@
         <v>0.8172</v>
       </c>
       <c r="F218" t="n">
-        <v>0.8287</v>
+        <v>0.8295</v>
       </c>
       <c r="G218" t="n">
-        <v>-0.0115</v>
+        <v>-0.0124</v>
       </c>
       <c r="H218" t="n">
         <v>0.1834</v>
@@ -12693,15 +12938,16 @@
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="n">
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" t="n">
         <v>0.8172</v>
       </c>
-      <c r="R218" t="n">
-        <v>0.8172</v>
-      </c>
-      <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -12715,13 +12961,13 @@
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="n">
-        <v>0.7873</v>
+        <v>0.7872</v>
       </c>
       <c r="F219" t="n">
         <v>0.7846</v>
       </c>
       <c r="G219" t="n">
-        <v>0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -12748,15 +12994,16 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q219" t="inlineStr"/>
       <c r="R219" t="n">
         <v>0</v>
       </c>
-      <c r="S219" t="inlineStr"/>
+      <c r="S219" t="n">
+        <v>0</v>
+      </c>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -12779,10 +13026,10 @@
         <v>1</v>
       </c>
       <c r="F220" t="n">
-        <v>0.8827</v>
+        <v>0.8828</v>
       </c>
       <c r="G220" t="n">
-        <v>0.1173</v>
+        <v>0.1172</v>
       </c>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
@@ -12822,6 +13069,7 @@
       <c r="S220" t="inlineStr"/>
       <c r="T220" t="inlineStr"/>
       <c r="U220" t="inlineStr"/>
+      <c r="V220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -12844,10 +13092,10 @@
         <v>1</v>
       </c>
       <c r="F221" t="n">
-        <v>0.8317</v>
+        <v>0.8316</v>
       </c>
       <c r="G221" t="n">
-        <v>0.1683</v>
+        <v>0.1684</v>
       </c>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
@@ -12887,6 +13135,7 @@
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
+      <c r="V221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -12909,10 +13158,10 @@
         <v>1</v>
       </c>
       <c r="F222" t="n">
-        <v>0.8064</v>
+        <v>0.8063</v>
       </c>
       <c r="G222" t="n">
-        <v>0.1936</v>
+        <v>0.1937</v>
       </c>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
@@ -12952,6 +13201,7 @@
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr"/>
       <c r="U222" t="inlineStr"/>
+      <c r="V222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -13017,6 +13267,7 @@
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr"/>
       <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -13056,22 +13307,23 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of the canonical column.</t>
+          <t>No suitable candidate found due to lack of relevant data evidence.</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q224" t="inlineStr"/>
       <c r="R224" t="n">
-        <v>0.7998</v>
-      </c>
-      <c r="S224" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
       <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr"/>
+      <c r="V224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -13088,10 +13340,10 @@
         <v>0.7815</v>
       </c>
       <c r="F225" t="n">
-        <v>0.7762</v>
+        <v>0.7761</v>
       </c>
       <c r="G225" t="n">
-        <v>0.0053</v>
+        <v>0.0054</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -13111,22 +13363,23 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of non-empty values in the model column.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q225" t="inlineStr"/>
       <c r="R225" t="n">
         <v>0</v>
       </c>
-      <c r="S225" t="inlineStr"/>
+      <c r="S225" t="n">
+        <v>0.7815</v>
+      </c>
       <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -13166,22 +13419,23 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>The candidate 'FORNECEDOR' does not match the expected content of 'UF do Local de Início', which should contain state abbreviations.</t>
+          <t>The candidate 'LOCATION' does not semantically match 'UF do Local de Início' as it lacks relevant content evidence.</t>
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q226" t="inlineStr"/>
       <c r="R226" t="n">
         <v>0</v>
       </c>
-      <c r="S226" t="inlineStr"/>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr"/>
+      <c r="V226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -13195,13 +13449,13 @@
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="n">
-        <v>0.7721</v>
+        <v>0.7725</v>
       </c>
       <c r="F227" t="n">
         <v>0.8193</v>
       </c>
       <c r="G227" t="n">
-        <v>-0.0472</v>
+        <v>-0.0468</v>
       </c>
       <c r="H227" t="n">
         <v>0.84</v>
@@ -13228,15 +13482,16 @@
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="n">
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="n">
         <v>0.85</v>
       </c>
-      <c r="R227" t="n">
+      <c r="S227" t="n">
         <v>0.8</v>
       </c>
-      <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
       <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -13253,10 +13508,10 @@
         <v>0.8005</v>
       </c>
       <c r="F228" t="n">
-        <v>0.7703</v>
+        <v>0.7704</v>
       </c>
       <c r="G228" t="n">
-        <v>0.0302</v>
+        <v>0.0301</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -13276,22 +13531,23 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate 'LOCATION' has a high name confidence but lacks relevant data evidence, making it unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q228" t="inlineStr"/>
       <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="n">
         <v>0.8005</v>
       </c>
-      <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr"/>
       <c r="U228" t="inlineStr"/>
+      <c r="V228" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13337,7 +13593,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25T04:28:48.772469+00:00</t>
+          <t>2026-08-25T05:08:37.593263+00:00</t>
         </is>
       </c>
     </row>

--- a/mapping_oracle_full.xlsx
+++ b/mapping_oracle_full.xlsx
@@ -579,7 +579,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates exhibit semantic header conflicts with the expected tax type, and there is no supporting data evidence.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or do not match the expected type for 'Base CBS', which is a tax base.</t>
+          <t>All candidates have semantic header conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -665,10 +665,10 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.7842</v>
+        <v>0.7841</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7746</v>
       </c>
       <c r="G4" t="n">
         <v>0.0095</v>
@@ -721,7 +721,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>0.7937</v>
+        <v>0.7938</v>
       </c>
       <c r="F5" t="n">
         <v>0.7896</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax family and provide no valid row evidence.</t>
+          <t>All candidates have a tax-family conflict with the 'Isentas CBS' column, indicating incompatible semantic roles.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -859,7 +859,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of relevant data evidence.</t>
+          <t>No suitable candidate due to semantic header conflicts and lack of distinctive sample evidence.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates have semantic header conflicts with the canonical column, indicating incompatible tax roles.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -945,7 +945,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.7938</v>
       </c>
       <c r="F9" t="n">
         <v>0.7832</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column, and the evidence quality is insufficient.</t>
+          <t>All candidates have semantic header conflicts with the target column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the 'Base IBSM' role.</t>
+          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>0.7864</v>
+        <v>0.7865</v>
       </c>
       <c r="F11" t="n">
         <v>0.7842</v>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the tax-family of the model column.</t>
+          <t>All candidates have a semantic header conflict with the target column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.8216</v>
+        <v>0.8215</v>
       </c>
       <c r="F12" t="n">
         <v>0.8145</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of the target column, and no valid mapping evidence exists.</t>
+          <t>All candidates have semantic header conflicts with the IBSM value, and no suitable mapping is supported by the data.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1169,13 +1169,13 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.7912</v>
+        <v>0.7913</v>
       </c>
       <c r="F13" t="n">
         <v>0.787</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0042</v>
+        <v>0.0043</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context of the source column.</t>
+          <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8169</v>
       </c>
       <c r="F14" t="n">
         <v>0.7991</v>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the tax-family of the model column.</t>
+          <t>All candidates conflict with the tax-family of the target column, and no valid mapping evidence exists.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>0.781</v>
+        <v>0.7809</v>
       </c>
       <c r="F15" t="n">
         <v>0.7735</v>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates conflict with the semantic role of the target column, which is a tax base.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
+          <t>All candidates have semantic header conflicts with the target column and lack sufficient row evidence.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>All candidates conflict semantically with the tax base role of 'Base IBS'.</t>
+          <t>All candidates have semantic header conflicts with the 'Base IBS' column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, and the evidence does not support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended role of 'Aliquota IBS'.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>0.8272</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8198</v>
+        <v>0.8197</v>
       </c>
       <c r="G19" t="n">
         <v>0.0074</v>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the tax family, and the evidence does not support a mapping.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1564,7 +1564,7 @@
         <v>0.8008</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7911</v>
+        <v>0.791</v>
       </c>
       <c r="G20" t="n">
         <v>0.0098</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the original column, indicating they do not represent the same business meaning.</t>
+          <t>All candidates have a semantic header conflict with the tax-family context, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1617,13 +1617,13 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>0.8224</v>
+        <v>0.8233</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8072</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0151</v>
+        <v>0.0153</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the 'Outras IBS' column, indicating incompatible tax-family roles.</t>
+          <t>All candidates conflict with the tax-family context of 'Outras IBS', indicating they are not compatible.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.8233</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.7829</v>
       </c>
       <c r="F22" t="n">
         <v>0.7765</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates have semantic header conflicts with the target column, indicating incompatible tax roles.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1729,7 +1729,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>0.8319</v>
+        <v>0.832</v>
       </c>
       <c r="F23" t="n">
         <v>0.8288</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>All candidates have strong semantic conflicts or lack relevant data evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -1764,10 +1764,10 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.832</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column has only zeros, indicating a mismatch in semantic meaning.</t>
+          <t>All candidate columns contain non-zero values, while the source column is entirely zero.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -1841,13 +1841,13 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>0.8149</v>
+        <v>0.8148</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8058</v>
+        <v>0.8057</v>
       </c>
       <c r="G25" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0091</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>All candidates have non-zero values, while the model column contains only zeros, indicating a mismatch in data semantics.</t>
+          <t>All candidates have non-zero values, but none align semantically with 'Aliquota IS'.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.7942</v>
+        <v>0.7948</v>
       </c>
       <c r="F26" t="n">
-        <v>0.789</v>
+        <v>0.7904</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0053</v>
+        <v>0.0044</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column 'Valor IS' has only zeros, indicating a mismatch in semantic meaning.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>0.7948</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.8108</v>
+        <v>0.8107</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7993</v>
+        <v>0.7992</v>
       </c>
       <c r="G27" t="n">
         <v>0.0115</v>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column has only zeros, indicating no compatible mapping.</t>
+          <t>All candidate columns contain non-zero values, while the source column 'Outras IS' has only zeros, indicating no compatible mapping.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>0.7844</v>
+        <v>0.7845</v>
       </c>
       <c r="F29" t="n">
         <v>0.7778</v>
@@ -2121,13 +2121,13 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>0.7521</v>
+        <v>0.7523</v>
       </c>
       <c r="F30" t="n">
         <v>0.844</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.0917</v>
       </c>
       <c r="H30" t="n">
         <v>0.84</v>
@@ -2177,10 +2177,10 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>0.7902</v>
+        <v>0.7903</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7704</v>
+        <v>0.7705</v>
       </c>
       <c r="G31" t="n">
         <v>0.0198</v>
@@ -2215,7 +2215,7 @@
         <v>0.8</v>
       </c>
       <c r="S31" t="n">
-        <v>0.7951</v>
+        <v>0.7953</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.8339</v>
+        <v>0.834</v>
       </c>
       <c r="F32" t="n">
         <v>0.8280999999999999</v>
@@ -2251,7 +2251,7 @@
         <v>0.8071</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8339</v>
+        <v>0.834</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a similar numeric structure but a lower median length than the expected 7 digits for document numbers.</t>
+          <t>The candidate 'NUMERO NF' has a high name confidence and matches the numeric format of the document number, despite a lower median length.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>0.6669</v>
+        <v>0.834</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -2292,14 +2292,8 @@
           <t>Nº da Nota Fiscal</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NUMERO NF</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
         <v>0.8557</v>
       </c>
@@ -2310,10 +2304,10 @@
         <v>0.0533</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7833</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8557</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2322,12 +2316,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' closely matches 'Nº da Nota Fiscal' and has a high name confidence, but the numeric profile indicates a mismatch in expected digit length.</t>
+          <t>The candidate 'NUMERO NF' has a significantly lower median length and digit count compared to 'Nº da Nota Fiscal', indicating a mismatch in expected formats.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -2336,10 +2330,10 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.8557</v>
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -2366,10 +2360,10 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8111</v>
       </c>
       <c r="G34" t="n">
-        <v>0.189</v>
+        <v>0.1889</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -2419,19 +2413,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.842</v>
+        <v>0.8429</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8238</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0182</v>
+        <v>0.0168</v>
       </c>
       <c r="H35" t="n">
         <v>0.8824</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8541</v>
+        <v>0.8547</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2511,7 +2505,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>The header 'DESC_PRODUTO' suggests a product description, but the numeric content indicates it may not align with the 'Descrição' column's semantic role.</t>
+          <t>The header 'DESC_PRODUTO' suggests a product description, but the numeric profile indicates mixed content, conflicting with the expected string type for 'Descrição'.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -2603,7 +2597,7 @@
         <v>0.8288</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0075</v>
+        <v>0.0074</v>
       </c>
       <c r="H38" t="n">
         <v>0.4187</v>
@@ -2632,10 +2626,10 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="S38" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.8175</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -2653,13 +2647,13 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>0.8106</v>
+        <v>0.8115</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8288</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0181</v>
+        <v>-0.0186</v>
       </c>
       <c r="H39" t="n">
         <v>0.2181</v>
@@ -2709,16 +2703,16 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>0.7173</v>
+        <v>0.7241</v>
       </c>
       <c r="F40" t="n">
         <v>0.8043</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.425</v>
+        <v>0.45</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2744,10 +2738,10 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S40" t="n">
-        <v>0.7173</v>
+        <v>0.8</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -2771,13 +2765,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.8278</v>
+        <v>0.8279</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7916</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0362</v>
+        <v>0.0361</v>
       </c>
       <c r="H41" t="n">
         <v>0.84</v>
@@ -2797,7 +2791,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>The 'TOTAL DO ITEM' column has a compatible numeric type and no semantic conflicts, aligning closely with the 'Val.Total NF' role.</t>
+          <t>The header 'TOTAL DO ITEM' aligns with the numeric nature of 'Val.Total NF' and has no semantic conflicts.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -2806,10 +2800,10 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
-        <v>0.9</v>
+        <v>0.9368</v>
       </c>
       <c r="S41" t="n">
-        <v>0.85</v>
+        <v>0.8312</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -2896,10 +2890,10 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9024</v>
+        <v>0.9025</v>
       </c>
       <c r="G43" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0975</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
@@ -2953,19 +2947,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.8067</v>
+        <v>0.8068</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8046</v>
+        <v>0.8044</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0021</v>
+        <v>0.0024</v>
       </c>
       <c r="H44" t="n">
         <v>0.84</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8167</v>
+        <v>0.8168</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3009,10 +3003,10 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>0.8794</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8489</v>
+        <v>0.849</v>
       </c>
       <c r="G45" t="n">
         <v>0.0305</v>
@@ -3035,7 +3029,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' conflicts semantically with the role of 'Isentas ICMS' as it refers to a tax indicator rather than an exemption amount.</t>
+          <t>The candidate 'IND TRIB ICMS' has a semantic header conflict with the expected role of 'Isentas ICMS'.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -3062,14 +3056,8 @@
           <t>Outras ICMS</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>21</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>IND TRIB ICMS</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
         <v>0.8968</v>
       </c>
@@ -3080,10 +3068,10 @@
         <v>0.0347</v>
       </c>
       <c r="H46" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8968</v>
+        <v>0</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3092,12 +3080,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a high name confidence but lacks relevant data evidence to support a mapping.</t>
+          <t>The candidate 'IND TRIB ICMS' has a strong name match but shows no relevant data overlap with 'Outras ICMS', indicating a semantic mismatch.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
@@ -3109,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8968</v>
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
@@ -3127,10 +3115,10 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>0.795</v>
+        <v>0.7946</v>
       </c>
       <c r="F47" t="n">
-        <v>0.79</v>
+        <v>0.7896</v>
       </c>
       <c r="G47" t="n">
         <v>0.005</v>
@@ -3209,7 +3197,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP value, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the ICEP value, and no distinctive row evidence supports a mapping.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -3391,7 +3379,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a high name confidence and matches the tax type, despite a lack of distinctive sample overlap.</t>
+          <t>The candidate 'IND TRIB IPI' has a high name confidence and matches the IPI tax type, despite a lack of strong numeric evidence.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -3453,7 +3441,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a strong name match but lacks supporting data evidence, as it conflicts with the all-zero evidence from 'Outras IPI'.</t>
+          <t>The candidate 'IND TRIB IPI' has a strong name match but lacks supporting data evidence, as all values are zero.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -3548,10 +3536,10 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7901</v>
+        <v>0.79</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2099</v>
+        <v>0.21</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
@@ -3733,7 +3721,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-numeric or zero-only values, making them incompatible with the 'Frete' column.</t>
+          <t>All candidate columns are unrelated to 'Frete' as they represent different semantic roles.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -3745,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>0.7544</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -3766,10 +3754,10 @@
         <v>0.8062</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7996</v>
+        <v>0.7995</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0066</v>
+        <v>0.0067</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -3789,7 +3777,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>All candidates are incompatible due to distinct types and all-zero evidence.</t>
+          <t>All candidate columns contain only zeros or non-numeric values, failing to provide any relevant mapping evidence.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -3801,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.7863</v>
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -3845,7 +3833,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>The 'Observações' column contains strings that do not match the numeric or product code context of 'COD_PRODUTO'.</t>
+          <t>The 'Observações' column contains strings that do not match any candidate's semantic role or content.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -3901,7 +3889,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No client column matches the semantic role of 'Chave de acesso' (NFe key) with sufficient evidence.</t>
+          <t>No client column matches the semantic role of 'Chave de acesso' (NF-e key) with sufficient evidence.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -4019,7 +4007,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>The column 'DATA GL' has a high name confidence and matches the datetime format of 'Data documento'.</t>
+          <t>The header 'DATA GL' closely matches the expected date format and has a high name confidence.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
@@ -4028,10 +4016,10 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="n">
-        <v>0.8722</v>
+        <v>0.9</v>
       </c>
       <c r="S62" t="n">
-        <v>0.8722</v>
+        <v>0.88</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -4049,16 +4037,16 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>0.7687</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7438</v>
+        <v>0.7437</v>
       </c>
       <c r="G63" t="n">
         <v>0.0249</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.2357</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -4075,7 +4063,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>The header 'FORNECEDOR' does not match the semantic role of 'Criado por', which indicates a creator or author, not a supplier.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -4084,10 +4072,10 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -4105,13 +4093,13 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>0.7612</v>
+        <v>0.7649</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7604</v>
+        <v>0.7629</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0008</v>
+        <v>0.002</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -4131,7 +4119,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No candidate column matches the semantic role of 'Modificado por'.</t>
+          <t>No suitable candidate matches the semantic role of 'Modificado por'.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -4279,19 +4267,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8016</v>
+        <v>0.8017</v>
       </c>
       <c r="F67" t="n">
         <v>0.8331</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0315</v>
+        <v>-0.0314</v>
       </c>
       <c r="H67" t="n">
         <v>0.73</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8016</v>
+        <v>0.8017</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4423,7 +4411,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' closely matches the semantic role of 'Nº FCI' as both refer to invoice numbers, supported by a high non-empty count and numeric profile.</t>
+          <t>The 'NUMERO NF' column has a strong numeric profile and high name confidence, aligning well with the 'Nº FCI' semantic role.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -4491,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -4509,7 +4497,7 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>0.8041</v>
+        <v>0.804</v>
       </c>
       <c r="F71" t="n">
         <v>0.7936</v>
@@ -4535,7 +4523,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected role of 'Base ICAP', indicating incompatible mappings.</t>
+          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -4565,10 +4553,10 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>0.7897</v>
+        <v>0.7896</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7882</v>
+        <v>0.7881</v>
       </c>
       <c r="G72" t="n">
         <v>0.0015</v>
@@ -4624,7 +4612,7 @@
         <v>0.7944</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.8192</v>
       </c>
       <c r="G73" t="n">
         <v>-0.0247</v>
@@ -4683,19 +4671,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.8437</v>
+        <v>0.8436</v>
       </c>
       <c r="F74" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0337</v>
+        <v>0.0336</v>
       </c>
       <c r="H74" t="n">
         <v>0.73</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8437</v>
+        <v>0.8436</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -4709,7 +4697,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' suggests a document number, conflicting with the item reference role of 'Item referência NF'.</t>
+          <t>The header 'NUMERO NF' closely matches the semantic role of 'Item referência NF' despite some numeric discrepancies.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -4718,10 +4706,10 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S74" t="n">
-        <v>0.6718</v>
+        <v>0.8208</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -4765,7 +4753,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No candidate column matches the semantic role of 'Mensagem' based on header and data evidence.</t>
+          <t>No candidate column matches the semantic role of 'Mensagem', which contains descriptive text rather than product codes or identifiers.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -4795,7 +4783,7 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>0.8246</v>
+        <v>0.8247</v>
       </c>
       <c r="F76" t="n">
         <v>0.7896</v>
@@ -4821,7 +4809,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of evidence and empty profiles.</t>
+          <t>No suitable candidate found due to lack of non-empty values in all columns.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -4877,7 +4865,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>The candidate 'COD_FIS_JUR' has a numeric profile but does not match the expected string format of 'Domicílio fiscal'.</t>
+          <t>The candidate 'COD_FIS_JUR' has a numeric profile with no overlap in samples or valid values, indicating it does not match the 'Domicílio fiscal' which is expected to be a string.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -4907,10 +4895,10 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>0.7916</v>
+        <v>0.7917</v>
       </c>
       <c r="F78" t="n">
-        <v>0.858</v>
+        <v>0.8581</v>
       </c>
       <c r="G78" t="n">
         <v>-0.0664</v>
@@ -4942,10 +4930,10 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="n">
-        <v>0.7916</v>
+        <v>0.7917</v>
       </c>
       <c r="S78" t="n">
-        <v>0.7916</v>
+        <v>0.7917</v>
       </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
@@ -4995,7 +4983,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>The column 'NUMERO NF' has a strong numeric profile and matches the semantic role of 'Nº de serviço' despite the empty evidence.</t>
+          <t>The column 'NUMERO NF' has a strong numeric profile and matches the semantic role of an invoice number.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -5057,7 +5045,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>The header 'DESC_PRODUTO' suggests a description of products, which aligns with the expected content for 'Texto breve serviço'.</t>
+          <t>The header 'DESC_PRODUTO' suggests a description of the service, aligning with the empty 'Texto breve serviço'.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -5093,7 +5081,7 @@
         <v>0.8135</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.0478</v>
+        <v>-0.0477</v>
       </c>
       <c r="H81" t="n">
         <v>0.84</v>
@@ -5146,7 +5134,7 @@
         <v>0.75</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7895</v>
+        <v>0.7896</v>
       </c>
       <c r="G82" t="n">
         <v>-0.0395</v>
@@ -5225,7 +5213,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate matches the empty evidence of the model column.</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -5234,10 +5222,10 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>0.646</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.7931</v>
+        <v>0.7526</v>
       </c>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
@@ -5281,7 +5269,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>All candidate columns have semantic conflicts or do not match the expected type for 'Mont.líquido frete', which should represent a monetary value.</t>
+          <t>The candidate headers conflict semantically with the expected role of 'Mont.líquido frete', and all candidate values are non-numeric.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -5293,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>0.7537</v>
       </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
@@ -5367,13 +5355,13 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>0.8169</v>
+        <v>0.8228</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8228</v>
+        <v>0.8224</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.0059</v>
+        <v>0.0005</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -5393,7 +5381,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate matches the semantic role of 'Grupo de imposto' as all candidates are tax indicators, not tax groups.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -5402,10 +5390,10 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.85</v>
+        <v>0.8228</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -5432,7 +5420,7 @@
         <v>0.8881</v>
       </c>
       <c r="F87" t="n">
-        <v>0.8621</v>
+        <v>0.862</v>
       </c>
       <c r="G87" t="n">
         <v>0.0261</v>
@@ -5494,7 +5482,7 @@
         <v>0.8587</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8292</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="G88" t="n">
         <v>0.0295</v>
@@ -5517,7 +5505,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a high name confidence but conflicts semantically with the expected role of a tax base.</t>
+          <t>The candidate 'IND TRIB ICMS' has a high name confidence and matches the expected tax base role despite a lack of distinctive sample overlap.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -5526,10 +5514,10 @@
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
-        <v>0.5</v>
+        <v>0.8587</v>
       </c>
       <c r="S88" t="n">
-        <v>0.5</v>
+        <v>0.8587</v>
       </c>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
@@ -5550,7 +5538,7 @@
         <v>0.7867</v>
       </c>
       <c r="F89" t="n">
-        <v>0.782</v>
+        <v>0.7819</v>
       </c>
       <c r="G89" t="n">
         <v>0.0048</v>
@@ -5609,7 +5597,7 @@
         <v>0.7811</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0065</v>
+        <v>0.0064</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -5629,7 +5617,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>All candidates conflict semantically with the expected tax situation for 'Isentas ICAP'.</t>
+          <t>All candidates have semantic header conflicts and do not match the expected tax base context.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -5662,7 +5650,7 @@
         <v>0.8223</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="G91" t="n">
         <v>0.0022</v>
@@ -5685,7 +5673,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and do not match the expected role of 'Outras ICAP'.</t>
+          <t>All candidates have semantic header conflicts and do not align with the expected tax base for 'Outras ICAP', which is not supported by the data.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -5741,7 +5729,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected role of 'Base Reduzida ICAP' and provide no valid row evidence.</t>
+          <t>All candidates have semantic header conflicts with the expected role of 'Base Reduzida ICAP'.</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -5774,7 +5762,7 @@
         <v>0.7851</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7782</v>
+        <v>0.7783</v>
       </c>
       <c r="G93" t="n">
         <v>0.0068</v>
@@ -5797,7 +5785,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type.</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -5830,7 +5818,7 @@
         <v>0.8079</v>
       </c>
       <c r="F94" t="n">
-        <v>0.8025</v>
+        <v>0.8024</v>
       </c>
       <c r="G94" t="n">
         <v>0.0054</v>
@@ -5853,7 +5841,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates have semantic header conflicts with the ICEP base, and the evidence does not support a mapping.</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -5883,10 +5871,10 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>0.7859</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="F95" t="n">
-        <v>0.7833</v>
+        <v>0.7832</v>
       </c>
       <c r="G95" t="n">
         <v>0.0026</v>
@@ -5909,7 +5897,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP tax type, indicating incompatible mappings.</t>
+          <t>All candidates conflict with the tax-family role of ICEP, providing no valid mapping.</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -5942,7 +5930,7 @@
         <v>0.7871</v>
       </c>
       <c r="F96" t="n">
-        <v>0.7861</v>
+        <v>0.786</v>
       </c>
       <c r="G96" t="n">
         <v>0.0011</v>
@@ -5965,7 +5953,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>All candidates conflict semantically with the tax situation of 'Isentas ICEP'.</t>
+          <t>All candidates have a semantic header conflict with the ICEP tax situation, indicating they do not match the intended meaning.</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -5998,10 +5986,10 @@
         <v>0.823</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8214</v>
+        <v>0.8213</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0016</v>
+        <v>0.0017</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -6021,7 +6009,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or lack relevant data evidence.</t>
+          <t>No suitable candidate due to semantic header conflicts and lack of distinctive sample evidence.</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -6051,13 +6039,13 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>0.787</v>
+        <v>0.7867</v>
       </c>
       <c r="F98" t="n">
-        <v>0.7831</v>
+        <v>0.7826</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0039</v>
+        <v>0.0041</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -6110,7 +6098,7 @@
         <v>0.7771</v>
       </c>
       <c r="F99" t="n">
-        <v>0.7766</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="G99" t="n">
         <v>0.0005</v>
@@ -6166,7 +6154,7 @@
         <v>0.7997</v>
       </c>
       <c r="F100" t="n">
-        <v>0.7864</v>
+        <v>0.7863</v>
       </c>
       <c r="G100" t="n">
         <v>0.0134</v>
@@ -6189,7 +6177,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and do not match the expected role of 'Base ICSP'.</t>
+          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -6222,7 +6210,7 @@
         <v>0.7994</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7948</v>
+        <v>0.7947</v>
       </c>
       <c r="G101" t="n">
         <v>0.0046</v>
@@ -6301,7 +6289,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax role, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -6331,13 +6319,13 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
-        <v>0.7843</v>
+        <v>0.7842</v>
       </c>
       <c r="F103" t="n">
         <v>0.7803</v>
       </c>
       <c r="G103" t="n">
-        <v>0.004</v>
+        <v>0.0039</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -6390,10 +6378,10 @@
         <v>0.8174</v>
       </c>
       <c r="F104" t="n">
-        <v>0.8167</v>
+        <v>0.8166</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0007</v>
+        <v>0.0008</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -6413,7 +6401,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with the original column, indicating incompatible meanings.</t>
+          <t>All candidates have a semantic header conflict with the original column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -6443,7 +6431,7 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
-        <v>0.7859</v>
+        <v>0.786</v>
       </c>
       <c r="F105" t="n">
         <v>0.7756999999999999</v>
@@ -6499,10 +6487,10 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
-        <v>0.803</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8103</v>
+        <v>0.8102</v>
       </c>
       <c r="G106" t="n">
         <v>-0.0073</v>
@@ -6537,7 +6525,7 @@
         <v>0.8</v>
       </c>
       <c r="S106" t="n">
-        <v>0.803</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
@@ -6558,7 +6546,7 @@
         <v>0.7927999999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>0.7879</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="G107" t="n">
         <v>0.0049</v>
@@ -6581,7 +6569,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>All candidate columns contain no relevant data to map to 'Base DIF_ALIQ', which requires a numeric base value.</t>
+          <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating a mismatch in semantic roles.</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -6593,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
@@ -6611,13 +6599,13 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
+        <v>0.7835</v>
+      </c>
+      <c r="F108" t="n">
         <v>0.7875</v>
       </c>
-      <c r="F108" t="n">
-        <v>0.7839</v>
-      </c>
       <c r="G108" t="n">
-        <v>0.0037</v>
+        <v>-0.0039</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -6637,7 +6625,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>The candidate columns have conflicting semantic roles and no distinctive sample overlap, making them unsuitable for mapping.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -6646,10 +6634,10 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>0.7835</v>
       </c>
       <c r="S108" t="n">
-        <v>0.7875</v>
+        <v>0.7835</v>
       </c>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
@@ -6670,10 +6658,10 @@
         <v>0.7976</v>
       </c>
       <c r="F109" t="n">
-        <v>0.7865</v>
+        <v>0.7864</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0111</v>
+        <v>0.0112</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -6726,7 +6714,7 @@
         <v>0.8079</v>
       </c>
       <c r="F110" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.8058</v>
       </c>
       <c r="G110" t="n">
         <v>0.0021</v>
@@ -6749,7 +6737,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>All candidates have non-zero values, while the model column is entirely zero, indicating a mismatch in semantic meaning.</t>
+          <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating a lack of semantic alignment.</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -6779,13 +6767,13 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>0.8097</v>
+        <v>0.8096</v>
       </c>
       <c r="F111" t="n">
         <v>0.8080000000000001</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0016</v>
+        <v>0.0017</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -6805,7 +6793,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Outras DIF_ALIQ' as all candidates are unrelated to tax rates or amounts.</t>
+          <t>No suitable candidate found; all candidates have conflicting semantic roles or insufficient evidence.</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -6817,7 +6805,7 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>0.8097</v>
+        <v>0.8096</v>
       </c>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
@@ -6861,7 +6849,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating a mismatch in semantic roles.</t>
+          <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating a semantic mismatch.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -6891,7 +6879,7 @@
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="n">
-        <v>0.8563</v>
+        <v>0.8562</v>
       </c>
       <c r="F113" t="n">
         <v>0.8273</v>
@@ -6944,10 +6932,16 @@
           <t>Aliquota ICMS_FECP</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
+      <c r="C114" t="n">
+        <v>21</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
       <c r="E114" t="n">
-        <v>0.855</v>
+        <v>0.8551</v>
       </c>
       <c r="F114" t="n">
         <v>0.8270999999999999</v>
@@ -6959,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>0.8551</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6968,12 +6962,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>All candidates have conflicting semantic roles or insufficient evidence to support a mapping.</t>
+          <t>The candidate 'IND TRIB ICMS' has a high name confidence but does not match the all-zero evidence of the source column.</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -6985,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>0.8551</v>
       </c>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
@@ -7000,28 +6994,22 @@
           <t>Valor ICMS_FECP</t>
         </is>
       </c>
-      <c r="C115" t="n">
-        <v>21</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>IND TRIB ICMS</t>
-        </is>
-      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
-        <v>0.8588</v>
+        <v>0.7909</v>
       </c>
       <c r="F115" t="n">
-        <v>0.8297</v>
+        <v>0.8587</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0291</v>
+        <v>-0.0678</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0.8588</v>
+        <v>0</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7030,12 +7018,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a high name confidence but conflicts with the expected role of a tax base, as it contains non-zero values.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -7044,10 +7032,10 @@
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>0.7909</v>
       </c>
       <c r="S115" t="n">
-        <v>0.8588</v>
+        <v>0.7909</v>
       </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
@@ -7065,10 +7053,10 @@
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="n">
-        <v>0.853</v>
+        <v>0.8529</v>
       </c>
       <c r="F116" t="n">
-        <v>0.8254</v>
+        <v>0.8253</v>
       </c>
       <c r="G116" t="n">
         <v>0.0276</v>
@@ -7091,7 +7079,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or lack relevant data evidence.</t>
+          <t>All candidates have significant semantic conflicts or do not match the expected role of a tax exemption indicator.</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -7121,13 +7109,13 @@
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
-        <v>0.8659</v>
+        <v>0.8646</v>
       </c>
       <c r="F117" t="n">
-        <v>0.8351</v>
+        <v>0.831</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0308</v>
+        <v>0.0337</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -7147,7 +7135,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column has only zeros, indicating a mismatch in data meaning.</t>
+          <t>All candidate columns contain non-zero values, while the source column has only zeros, indicating a lack of compatible data.</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -7177,10 +7165,10 @@
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
-        <v>0.8304</v>
+        <v>0.8303</v>
       </c>
       <c r="F118" t="n">
-        <v>0.803</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="G118" t="n">
         <v>0.0274</v>
@@ -7245,7 +7233,7 @@
         <v>0.7919</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0616</v>
+        <v>0.0615</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -7265,7 +7253,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a strong name match but lacks supporting data evidence, as all values are non-informative zeros.</t>
+          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -7277,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>0.8535</v>
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
@@ -7298,7 +7286,7 @@
         <v>0.8083</v>
       </c>
       <c r="F120" t="n">
-        <v>0.8056</v>
+        <v>0.8057</v>
       </c>
       <c r="G120" t="n">
         <v>0.0027</v>
@@ -7321,7 +7309,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context of COFINS.</t>
+          <t>All candidates have semantic conflicts with the tax-family context of COFINS.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -7377,7 +7365,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context of COFINS.</t>
+          <t>All candidates have semantic header conflicts with the target column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -7463,10 +7451,10 @@
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
-        <v>0.7754</v>
+        <v>0.776</v>
       </c>
       <c r="F123" t="n">
-        <v>0.7734</v>
+        <v>0.774</v>
       </c>
       <c r="G123" t="n">
         <v>0.002</v>
@@ -7519,7 +7507,7 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>0.7857</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="F124" t="n">
         <v>0.7818000000000001</v>
@@ -7545,7 +7533,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the PIS tax family and provide no relevant row evidence.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -7575,10 +7563,10 @@
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="n">
-        <v>0.7998</v>
+        <v>0.7997</v>
       </c>
       <c r="F125" t="n">
-        <v>0.799</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="G125" t="n">
         <v>0.0008</v>
@@ -7601,7 +7589,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>The candidate columns conflict with the tax-family context of 'Outras PIS' and provide no relevant row evidence.</t>
+          <t>The candidate columns conflict with the tax-family context of 'Outras PIS' and provide no relevant data evidence.</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -7613,7 +7601,7 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>0.5</v>
+        <v>0.7997</v>
       </c>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
@@ -7657,7 +7645,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the tax family of PIS, making them incompatible.</t>
+          <t>All candidates have semantic conflicts with the PIS tax type, making them incompatible.</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -7713,7 +7701,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the PIS tax base, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the PIS tax base, and the evidence does not support a mapping.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -7769,7 +7757,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>All candidates conflict semantically with the required tax type (ISS) and provide no relevant data evidence.</t>
+          <t>All candidates conflict with the tax-family of ISS, providing no valid mapping.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -7799,7 +7787,7 @@
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
-        <v>0.7634</v>
+        <v>0.7633</v>
       </c>
       <c r="F129" t="n">
         <v>0.7532</v>
@@ -7825,7 +7813,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of the target column, and no suitable mapping is supported by the data.</t>
+          <t>All candidates conflict with the semantic role of 'Base ISS' and provide no relevant mapping evidence.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -7881,7 +7869,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of ISS, making them incompatible.</t>
+          <t>All candidates conflict with the tax-family of ISS, providing no valid mapping.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -7914,7 +7902,7 @@
         <v>0.7897999999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>0.7796</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="G131" t="n">
         <v>0.0102</v>
@@ -7937,7 +7925,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of 'Valor ISS' and provide no relevant evidence.</t>
+          <t>All candidates conflict with the semantic role of 'Valor ISS' and provide no relevant evidence.</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -7970,7 +7958,7 @@
         <v>0.7833</v>
       </c>
       <c r="F132" t="n">
-        <v>0.7698</v>
+        <v>0.7699</v>
       </c>
       <c r="G132" t="n">
         <v>0.0134</v>
@@ -8029,7 +8017,7 @@
         <v>0.7946</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0028</v>
+        <v>0.0027</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -8079,13 +8067,13 @@
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="n">
-        <v>0.7667</v>
+        <v>0.7673</v>
       </c>
       <c r="F134" t="n">
-        <v>0.7595</v>
+        <v>0.7597</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0072</v>
+        <v>0.0076</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -8105,7 +8093,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of the target column, and no suitable mapping exists.</t>
+          <t>All candidates conflict with the tax-family of the target column, and no strong evidence supports a mapping.</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
@@ -8191,13 +8179,13 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
+        <v>0.7903</v>
+      </c>
+      <c r="F136" t="n">
         <v>0.8145</v>
       </c>
-      <c r="F136" t="n">
-        <v>0.802</v>
-      </c>
       <c r="G136" t="n">
-        <v>0.0125</v>
+        <v>-0.0242</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -8217,7 +8205,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts or do not match the expected type for 'Aliquota FECP_ST', which is a tax rate.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
@@ -8229,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>0</v>
+        <v>0.7903</v>
       </c>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
@@ -8273,7 +8261,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
+          <t>All candidate columns have significant semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
@@ -8329,7 +8317,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or do not match the expected tax situation for 'Isentas FECP_ST'.</t>
+          <t>No suitable candidate due to semantic header conflicts and lack of distinctive sample evidence.</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -8365,7 +8353,7 @@
         <v>0.8280999999999999</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0005</v>
+        <v>0.0004</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -8385,7 +8373,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>All candidate columns contain conflicting semantic roles or lack relevant data evidence.</t>
+          <t>All candidates have significant semantic and numeric discrepancies, with no viable mapping to the 'Outras FECP_ST' column.</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -8415,10 +8403,10 @@
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
-        <v>0.7835</v>
+        <v>0.7836</v>
       </c>
       <c r="F140" t="n">
-        <v>0.797</v>
+        <v>0.7971</v>
       </c>
       <c r="G140" t="n">
         <v>-0.0135</v>
@@ -8450,10 +8438,10 @@
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="n">
-        <v>0.7835</v>
+        <v>0.7836</v>
       </c>
       <c r="S140" t="n">
-        <v>0.7835</v>
+        <v>0.7836</v>
       </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
@@ -8474,10 +8462,10 @@
         <v>0.8691</v>
       </c>
       <c r="F141" t="n">
-        <v>0.8531</v>
+        <v>0.853</v>
       </c>
       <c r="G141" t="n">
-        <v>0.016</v>
+        <v>0.0161</v>
       </c>
       <c r="H141" t="n">
         <v>0.7375</v>
@@ -8553,7 +8541,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the expected role of 'Base ICMS_ST' and provide no relevant data evidence.</t>
+          <t>All candidates have semantic conflicts with the expected role of 'Base ICMS_ST' and do not provide relevant evidence.</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
@@ -8586,7 +8574,7 @@
         <v>0.7915</v>
       </c>
       <c r="F143" t="n">
-        <v>0.787</v>
+        <v>0.7871</v>
       </c>
       <c r="G143" t="n">
         <v>0.0045</v>
@@ -8609,7 +8597,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the tax role of 'Aliquota ICMS_ST' and do not provide sufficient evidence for a mapping.</t>
+          <t>All candidates have semantic conflicts with the required tax role, indicating they do not match the 'Aliquota ICMS_ST' column.</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
@@ -8665,7 +8653,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax qualifier or family, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
@@ -8695,13 +8683,13 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
-        <v>0.8132</v>
+        <v>0.8131</v>
       </c>
       <c r="F145" t="n">
         <v>0.8069</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0063</v>
+        <v>0.0062</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -8721,7 +8709,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and do not align with the expected tax base for ICMS_ST.</t>
+          <t>All candidates have semantic header conflicts or do not match the expected tax role.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
@@ -8754,7 +8742,7 @@
         <v>0.7786</v>
       </c>
       <c r="F146" t="n">
-        <v>0.7781</v>
+        <v>0.778</v>
       </c>
       <c r="G146" t="n">
         <v>0.0005</v>
@@ -8777,7 +8765,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the required tax base role.</t>
+          <t>All candidates conflict with the semantic role of the target column, indicating they do not represent a compatible mapping.</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
@@ -8789,7 +8777,7 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
@@ -8866,7 +8854,7 @@
         <v>0.7684</v>
       </c>
       <c r="F148" t="n">
-        <v>0.7661</v>
+        <v>0.766</v>
       </c>
       <c r="G148" t="n">
         <v>0.0024</v>
@@ -8957,7 +8945,7 @@
         <v>0.8</v>
       </c>
       <c r="S149" t="n">
-        <v>0.7883</v>
+        <v>0.7853</v>
       </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
@@ -9001,7 +8989,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>The header 'DATA GL' does not match the time format of 'Criado às:'.</t>
+          <t>The candidate 'DATA GL' does not match the time format of 'Criado às:'.</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
@@ -9031,10 +9019,10 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="n">
-        <v>0.8162</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F151" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.8048</v>
       </c>
       <c r="G151" t="n">
         <v>0.0112</v>
@@ -9090,10 +9078,10 @@
         <v>0.7748</v>
       </c>
       <c r="F152" t="n">
-        <v>0.7746</v>
+        <v>0.7745</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -9113,7 +9101,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-numeric or zero-only values, making them incompatible with the numeric nature of 'Redução'.</t>
+          <t>The candidate columns contain non-matching types and values, with 'Redução' being all zeros and the candidates being strings or unrelated integers.</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
@@ -9125,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>0</v>
+        <v>0.7748</v>
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
@@ -9143,10 +9131,10 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="n">
-        <v>0.7454</v>
+        <v>0.7453</v>
       </c>
       <c r="F153" t="n">
-        <v>0.7373</v>
+        <v>0.7372</v>
       </c>
       <c r="G153" t="n">
         <v>0.0081</v>
@@ -9196,10 +9184,16 @@
           <t>Cód.domicílio fiscal</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
+      <c r="C154" t="n">
+        <v>6</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>COD_FIS_JUR</t>
+        </is>
+      </c>
       <c r="E154" t="n">
-        <v>0.8545</v>
+        <v>0.8544</v>
       </c>
       <c r="F154" t="n">
         <v>0.8225</v>
@@ -9211,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>0.8544</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -9220,24 +9214,32 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>All candidate columns have insufficient evidence and do not match the expected content for 'Cód.domicílio fiscal'.</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+          <t>The column 'COD_FIS_JUR' has a high name confidence and contains valid numeric data, but lacks specific evidence to confirm a mapping to 'Cód.domicílio fiscal'.</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>ibge_municipality</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="n">
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>0</v>
+        <v>0.8544</v>
       </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
@@ -9255,10 +9257,10 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
-        <v>0.8292</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="F155" t="n">
-        <v>0.8245</v>
+        <v>0.8244</v>
       </c>
       <c r="G155" t="n">
         <v>0.0047</v>
@@ -9281,7 +9283,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>All candidate columns contain no relevant data to support a mapping.</t>
+          <t>All candidate columns contain no relevant data or evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
@@ -9337,7 +9339,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>All candidate columns contain no data, making it impossible to establish a mapping.</t>
+          <t>No suitable candidate found due to lack of non-empty values in the model column.</t>
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
@@ -9367,16 +9369,16 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
-        <v>0.7945</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="F157" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.8032</v>
       </c>
       <c r="G157" t="n">
-        <v>-0.0276</v>
+        <v>0.0188</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1714</v>
+        <v>0</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -9393,7 +9395,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate matches the semantic role of 'ID do consumidor final' based on name and data evidence.</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
@@ -9402,10 +9404,10 @@
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="n">
-        <v>0.7945</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>0.7945</v>
+        <v>0</v>
       </c>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
@@ -9426,10 +9428,10 @@
         <v>0.7552</v>
       </c>
       <c r="F158" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7929</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.0376</v>
+        <v>-0.0377</v>
       </c>
       <c r="H158" t="n">
         <v>0.84</v>
@@ -9485,10 +9487,10 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.8556</v>
+        <v>0.8555</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8018</v>
+        <v>0.8017</v>
       </c>
       <c r="G159" t="n">
         <v>0.0538</v>
@@ -9497,7 +9499,7 @@
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8556</v>
+        <v>0.8555</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -9511,7 +9513,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a high numeric fraction and matches the semantic role of 'Nº NF-e dos serviços'.</t>
+          <t>The candidate 'NUMERO NF' has a high name confidence and matches the expected numeric format for invoice numbers.</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
@@ -9523,7 +9525,7 @@
         <v>1</v>
       </c>
       <c r="S159" t="n">
-        <v>0.8556</v>
+        <v>0.8555</v>
       </c>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
@@ -9541,13 +9543,13 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8268</v>
       </c>
       <c r="F160" t="n">
-        <v>0.8259</v>
+        <v>0.8256</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0012</v>
+        <v>0.0013</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -9567,7 +9569,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Código verificação' as all candidates are unrelated to verification codes.</t>
+          <t>All candidate columns contain no relevant data, making mapping impossible.</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
@@ -9579,7 +9581,7 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>0.7804</v>
+        <v>0</v>
       </c>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
@@ -9623,7 +9625,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>The 'Ordem' column is empty, providing no evidence to support a mapping to any candidate.</t>
+          <t>The candidate columns contain no relevant data, making it impossible to establish a mapping despite the name confidence.</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
@@ -9656,7 +9658,7 @@
         <v>0.7992</v>
       </c>
       <c r="F162" t="n">
-        <v>0.788</v>
+        <v>0.7881</v>
       </c>
       <c r="G162" t="n">
         <v>0.0112</v>
@@ -9679,7 +9681,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>The 'Despesas' column contains only zeros, providing no evidence to map to any candidate.</t>
+          <t>The candidate columns contain no relevant data to map to 'Despesas', which is entirely zero.</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
@@ -9691,7 +9693,7 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>0.7722</v>
+        <v>0.7992</v>
       </c>
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
@@ -9712,7 +9714,7 @@
         <v>0.8243</v>
       </c>
       <c r="F163" t="n">
-        <v>0.7874</v>
+        <v>0.7875</v>
       </c>
       <c r="G163" t="n">
         <v>0.0368</v>
@@ -9735,7 +9737,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>The candidate 'PROFIT_CENTER' has a strong name match but lacks any row evidence, making it unsuitable for mapping.</t>
+          <t>The 'Centro custo' column has no non-empty values, making it impossible to establish a mapping.</t>
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
@@ -9747,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>0.8243</v>
+        <v>0</v>
       </c>
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
@@ -9771,7 +9773,7 @@
         <v>0.7726</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0104</v>
+        <v>0.0103</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -9791,7 +9793,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>All candidate columns lack relevant data evidence to support a mapping to 'Municipio Fim'.</t>
+          <t>All candidate columns lack relevant data evidence and do not align semantically with 'Municipio Fim'.</t>
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
@@ -9821,10 +9823,10 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
-        <v>0.784</v>
+        <v>0.7839</v>
       </c>
       <c r="F165" t="n">
-        <v>0.7815</v>
+        <v>0.7814</v>
       </c>
       <c r="G165" t="n">
         <v>0.0025</v>
@@ -9883,7 +9885,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.8734</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="F166" t="n">
         <v>0.8619</v>
@@ -9895,7 +9897,7 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0.8734</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -9909,7 +9911,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>The column 'COD_PRODUTO' has a high name confidence and contains numeric values that align with item codes, despite the absence of sample overlap.</t>
+          <t>The column 'COD_PRODUTO' has a high name confidence and contains numeric values, but lacks any non-empty evidence to support a mapping to 'Código do Item'.</t>
         </is>
       </c>
       <c r="M166" t="inlineStr"/>
@@ -9918,10 +9920,10 @@
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="n">
-        <v>0.8734</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>0.8734</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
@@ -9971,7 +9973,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a strong numeric profile and high name confidence, aligning well with the expected format of 'Número do NFC-e SAT'.</t>
+          <t>The column 'NUMERO NF' has a strong numeric profile and matches the semantic role of 'Número do NFC-e SAT'.</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
@@ -9980,7 +9982,7 @@
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S167" t="n">
         <v>0.8369</v>
@@ -10083,7 +10085,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidate columns contain non-zero values, while the model column has only zeros, indicating a mismatch in semantic meaning.</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
@@ -10095,7 +10097,7 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>0.8421</v>
+        <v>0</v>
       </c>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
@@ -10116,7 +10118,7 @@
         <v>0.7906</v>
       </c>
       <c r="F170" t="n">
-        <v>0.7886</v>
+        <v>0.7885</v>
       </c>
       <c r="G170" t="n">
         <v>0.002</v>
@@ -10169,7 +10171,7 @@
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="n">
-        <v>0.8002</v>
+        <v>0.8001</v>
       </c>
       <c r="F171" t="n">
         <v>0.7984</v>
@@ -10195,7 +10197,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family, and the evidence does not support a mapping.</t>
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
@@ -10251,7 +10253,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts or insufficient evidence to support a mapping.</t>
+          <t>No suitable candidate due to semantic header conflicts and lack of distinctive row evidence.</t>
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
@@ -10464,10 +10466,10 @@
         <v>0.8643999999999999</v>
       </c>
       <c r="F176" t="n">
-        <v>0.7973</v>
+        <v>0.7972</v>
       </c>
       <c r="G176" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="H176" t="n">
         <v>0.84</v>
@@ -10543,7 +10545,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column and lack sufficient evidence.</t>
+          <t>All candidates have semantic header conflicts with the target column, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
@@ -10573,10 +10575,10 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="n">
-        <v>0.7831</v>
+        <v>0.7832</v>
       </c>
       <c r="F178" t="n">
-        <v>0.7748</v>
+        <v>0.7749</v>
       </c>
       <c r="G178" t="n">
         <v>0.0083</v>
@@ -10599,7 +10601,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax classification role.</t>
+          <t>All candidates exhibit semantic header conflicts with the required tax classification role.</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
@@ -10638,7 +10640,7 @@
         <v>0.8388</v>
       </c>
       <c r="F179" t="n">
-        <v>0.8399</v>
+        <v>0.8398</v>
       </c>
       <c r="G179" t="n">
         <v>-0.0011</v>
@@ -10661,7 +10663,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>The column 'NUMERO NF' closely matches the expected format and type for invoice document numbers, with strong numeric evidence.</t>
+          <t>The column 'NUMERO NF' closely matches the semantic role of 'Nº documento' with high numeric consistency and a strong name match.</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
@@ -10691,16 +10693,16 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>0.751</v>
+        <v>0.8445</v>
       </c>
       <c r="F180" t="n">
-        <v>0.8505</v>
+        <v>0.8506</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.006</v>
       </c>
       <c r="H180" t="n">
-        <v>0.82</v>
+        <v>0.7123</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
@@ -10726,10 +10728,10 @@
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="n">
-        <v>0.8</v>
+        <v>0.8445</v>
       </c>
       <c r="S180" t="n">
-        <v>0.825</v>
+        <v>0.8445</v>
       </c>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
@@ -10779,7 +10781,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>The 'FORNECEDOR' column has strong evidence with many non-empty values and a high name confidence, aligning with the role of 'Exportador'.</t>
+          <t>The 'FORNECEDOR' column has a strong name match and informative sample values indicating it represents suppliers, aligning with the 'Exportador' role.</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
@@ -10809,13 +10811,13 @@
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
+        <v>0.7904</v>
+      </c>
+      <c r="F182" t="n">
         <v>0.788</v>
       </c>
-      <c r="F182" t="n">
-        <v>0.7904</v>
-      </c>
       <c r="G182" t="n">
-        <v>-0.0024</v>
+        <v>0.0024</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -10835,7 +10837,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidate columns are empty with no distinctive content or evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M182" t="inlineStr"/>
@@ -10844,10 +10846,10 @@
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="n">
-        <v>0.788</v>
+        <v>0</v>
       </c>
       <c r="S182" t="n">
-        <v>0.788</v>
+        <v>0</v>
       </c>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
@@ -11124,7 +11126,7 @@
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
       <c r="R187" t="n">
-        <v>0.8016</v>
+        <v>0.8</v>
       </c>
       <c r="S187" t="n">
         <v>0.8016</v>
@@ -11239,7 +11241,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>The header 'NUM_ITEM' suggests an item identifier, but the data is all zeros, indicating it does not provide meaningful evidence.</t>
+          <t>The header 'NUM_ITEM' suggests an item identifier, but the data is all zeros, indicating it may not be a valid mapping.</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
@@ -11269,10 +11271,10 @@
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="n">
-        <v>0.7821</v>
+        <v>0.7822</v>
       </c>
       <c r="F190" t="n">
-        <v>0.781</v>
+        <v>0.7811</v>
       </c>
       <c r="G190" t="n">
         <v>0.0011</v>
@@ -11295,7 +11297,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>All candidate columns are empty with no distinctive content or evidence to support a mapping.</t>
+          <t>No viable candidates due to lack of non-empty values in the client column.</t>
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
@@ -11385,7 +11387,7 @@
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
-        <v>0.7774</v>
+        <v>0.7775</v>
       </c>
       <c r="F192" t="n">
         <v>0.7987</v>
@@ -11569,19 +11571,19 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>0.8752</v>
+        <v>0.8753</v>
       </c>
       <c r="F195" t="n">
         <v>0.8105</v>
       </c>
       <c r="G195" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0648</v>
       </c>
       <c r="H195" t="n">
         <v>0.225</v>
       </c>
       <c r="I195" t="n">
-        <v>0.8752</v>
+        <v>0.8753</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -11595,7 +11597,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>The candidate 'NUM_ITEM' has a high name confidence but does not match the expected item ID role, leading to a semantic conflict.</t>
+          <t>The header 'NUM_ITEM' closely matches 'Nº item do documento' in name, but the numeric values and context suggest it may not represent the same semantic role.</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
@@ -11604,10 +11606,10 @@
       <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S195" t="n">
-        <v>0.8752</v>
+        <v>0.8753</v>
       </c>
       <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr"/>
@@ -11657,7 +11659,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>The column 'DESC_PRODUTO' has a high name confidence and a strong profile similarity, indicating it likely represents product descriptions.</t>
+          <t>The column 'DESC_PRODUTO' has a high name confidence and a significant number of non-empty values that align with product descriptions.</t>
         </is>
       </c>
       <c r="M196" t="inlineStr"/>
@@ -11666,10 +11668,10 @@
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="n">
-        <v>0.7981</v>
+        <v>0.8</v>
       </c>
       <c r="S196" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
@@ -11693,7 +11695,7 @@
         <v>0.8391</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.1148</v>
+        <v>-0.1149</v>
       </c>
       <c r="H197" t="n">
         <v>0.84</v>
@@ -11743,10 +11745,10 @@
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="n">
-        <v>0.8062</v>
+        <v>0.8063</v>
       </c>
       <c r="F198" t="n">
-        <v>0.8212</v>
+        <v>0.8213</v>
       </c>
       <c r="G198" t="n">
         <v>-0.015</v>
@@ -11778,10 +11780,10 @@
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="n">
-        <v>0.8062</v>
+        <v>0.8063</v>
       </c>
       <c r="S198" t="n">
-        <v>0.8062</v>
+        <v>0.8063</v>
       </c>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
@@ -11811,7 +11813,7 @@
         <v>0.8073</v>
       </c>
       <c r="G199" t="n">
-        <v>0.039</v>
+        <v>0.0391</v>
       </c>
       <c r="H199" t="n">
         <v>0.45</v>
@@ -11831,7 +11833,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>The header 'COD_MEDIDA' aligns semantically with 'Unidade de medida' and has no conflicting evidence.</t>
+          <t>The header 'COD_MEDIDA' aligns with 'Unidade de medida' as both represent measurement units, and the profile evidence supports this mapping.</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
@@ -11840,10 +11842,10 @@
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
       <c r="R199" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="S199" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
@@ -11917,13 +11919,13 @@
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7675</v>
       </c>
       <c r="F201" t="n">
         <v>0.7184</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0491</v>
+        <v>0.0492</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -11955,7 +11957,7 @@
         <v>0</v>
       </c>
       <c r="S201" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7675</v>
       </c>
       <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
@@ -12032,7 +12034,7 @@
         <v>0.8247</v>
       </c>
       <c r="F203" t="n">
-        <v>0.8125</v>
+        <v>0.8124</v>
       </c>
       <c r="G203" t="n">
         <v>0.0123</v>
@@ -12055,7 +12057,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the IVA role, indicating incompatible tax-family contexts.</t>
+          <t>All candidates have semantic header conflicts with the expected tax role of IVA.</t>
         </is>
       </c>
       <c r="M203" t="inlineStr"/>
@@ -12088,10 +12090,10 @@
         <v>0.804</v>
       </c>
       <c r="F204" t="n">
-        <v>0.7748</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="G204" t="n">
-        <v>0.0293</v>
+        <v>0.0292</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -12141,7 +12143,7 @@
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="n">
-        <v>0.8375</v>
+        <v>0.8374</v>
       </c>
       <c r="F205" t="n">
         <v>0.7997</v>
@@ -12167,7 +12169,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' conflicts semantically with 'Nº do NCM', which is a tax classification code.</t>
+          <t>The header 'NUMERO NF' does not match the semantic role of 'Nº do NCM', which is a tax classification code.</t>
         </is>
       </c>
       <c r="M205" t="inlineStr"/>
@@ -12268,7 +12270,7 @@
         <v>0.8532999999999999</v>
       </c>
       <c r="F207" t="n">
-        <v>0.7803</v>
+        <v>0.7804</v>
       </c>
       <c r="G207" t="n">
         <v>0.073</v>
@@ -12291,7 +12293,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>The candidate 'PRECO UNITARIO' closely matches the semantic role of 'Preço líq.' as both represent unit prices, despite some numeric discrepancies.</t>
+          <t>The name 'PRECO UNITARIO' closely aligns with 'Preço líq.' and both contain numeric values indicative of pricing.</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
@@ -12303,7 +12305,7 @@
         <v>0.9</v>
       </c>
       <c r="S207" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="T207" t="inlineStr"/>
       <c r="U207" t="inlineStr"/>
@@ -12321,13 +12323,13 @@
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="n">
-        <v>0.7917</v>
+        <v>0.7916</v>
       </c>
       <c r="F208" t="n">
-        <v>0.7693</v>
+        <v>0.7691</v>
       </c>
       <c r="G208" t="n">
-        <v>0.0224</v>
+        <v>0.0225</v>
       </c>
       <c r="H208" t="n">
         <v>0.84</v>
@@ -12359,7 +12361,7 @@
         <v>0.8</v>
       </c>
       <c r="S208" t="n">
-        <v>0.785</v>
+        <v>0.79</v>
       </c>
       <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr"/>
@@ -12374,8 +12376,14 @@
           <t>NF/NF-e do serviço</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
+      <c r="C209" t="n">
+        <v>8</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
       <c r="E209" t="n">
         <v>0.8511</v>
       </c>
@@ -12386,10 +12394,10 @@
         <v>0.0062</v>
       </c>
       <c r="H209" t="n">
-        <v>0</v>
+        <v>0.0301</v>
       </c>
       <c r="I209" t="n">
-        <v>0</v>
+        <v>0.8511</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -12398,12 +12406,12 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' is numeric while 'NF/NF-e do serviço' is a string, indicating a semantic mismatch.</t>
+          <t>The header 'NUMERO NF' suggests a document number, but the values are numeric and do not match the expected format for NF-e.</t>
         </is>
       </c>
       <c r="M209" t="inlineStr"/>
@@ -12415,7 +12423,7 @@
         <v>0</v>
       </c>
       <c r="S209" t="n">
-        <v>0</v>
+        <v>0.8511</v>
       </c>
       <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr"/>
@@ -12445,7 +12453,7 @@
         <v>0.7883</v>
       </c>
       <c r="G210" t="n">
-        <v>0.0745</v>
+        <v>0.0746</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -12465,7 +12473,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a high name confidence and a substantial non-empty count, indicating it likely represents the invoice number.</t>
+          <t>The column 'NUMERO NF' has a high numeric fraction and matches the expected format for invoice numbers.</t>
         </is>
       </c>
       <c r="M210" t="inlineStr"/>
@@ -12527,7 +12535,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>The name 'TOTAL DO ITEM' closely matches 'Valor Total do Item' with high name confidence and consistent numeric evidence.</t>
+          <t>The name 'TOTAL DO ITEM' closely matches 'Valor Total do Item' with high numeric consistency and no semantic conflicts.</t>
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
@@ -12557,13 +12565,13 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
-        <v>0.8308</v>
+        <v>0.8306</v>
       </c>
       <c r="F212" t="n">
         <v>0.7799</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0509</v>
+        <v>0.0506</v>
       </c>
       <c r="H212" t="n">
         <v>0.4406</v>
@@ -12592,10 +12600,10 @@
       <c r="P212" t="inlineStr"/>
       <c r="Q212" t="inlineStr"/>
       <c r="R212" t="n">
-        <v>0.8</v>
+        <v>0.4406</v>
       </c>
       <c r="S212" t="n">
-        <v>0.8154</v>
+        <v>0.8306</v>
       </c>
       <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr"/>
@@ -12616,7 +12624,7 @@
         <v>0.8137</v>
       </c>
       <c r="F213" t="n">
-        <v>0.8086</v>
+        <v>0.8087</v>
       </c>
       <c r="G213" t="n">
         <v>0.0051</v>
@@ -12725,10 +12733,10 @@
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="n">
-        <v>0.782</v>
+        <v>0.7819</v>
       </c>
       <c r="F215" t="n">
-        <v>0.8137</v>
+        <v>0.8136</v>
       </c>
       <c r="G215" t="n">
         <v>-0.0318</v>
@@ -12760,10 +12768,10 @@
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
       <c r="R215" t="n">
-        <v>0.782</v>
+        <v>0.5</v>
       </c>
       <c r="S215" t="n">
-        <v>0.782</v>
+        <v>0.75</v>
       </c>
       <c r="T215" t="inlineStr"/>
       <c r="U215" t="inlineStr"/>
@@ -12787,10 +12795,10 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>0.889</v>
+        <v>0.8889</v>
       </c>
       <c r="F216" t="n">
-        <v>0.8631</v>
+        <v>0.863</v>
       </c>
       <c r="G216" t="n">
         <v>0.0259</v>
@@ -12799,7 +12807,7 @@
         <v>0.7321</v>
       </c>
       <c r="I216" t="n">
-        <v>0.889</v>
+        <v>0.8889</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -12813,7 +12821,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>The header 'IND TRIB ICMS' suggests a tax indicator for ICMS, but the numeric values and type do not align with the expected text format of 'Texto ICMS'.</t>
+          <t>The header 'IND TRIB ICMS' suggests a tax indicator for ICMS, but the numeric profile indicates it is an integer with limited unique values, conflicting with the expected string format of 'Texto ICMS'.</t>
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
@@ -12825,7 +12833,7 @@
         <v>0</v>
       </c>
       <c r="S216" t="n">
-        <v>0.889</v>
+        <v>0.8889</v>
       </c>
       <c r="T216" t="inlineStr"/>
       <c r="U216" t="inlineStr"/>
@@ -12875,7 +12883,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>The name 'IND TRIB IPI' closely matches the expected role for IPI tax identification despite numeric discrepancies.</t>
+          <t>The header 'IND TRIB IPI' aligns with the IPI tax context, despite the numeric profile indicating integer values.</t>
         </is>
       </c>
       <c r="M217" t="inlineStr"/>
@@ -12884,10 +12892,10 @@
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="inlineStr"/>
       <c r="R217" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="S217" t="n">
-        <v>0.8806</v>
+        <v>0.825</v>
       </c>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr"/>
@@ -12940,10 +12948,10 @@
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S218" t="n">
-        <v>0.8172</v>
+        <v>0.5</v>
       </c>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
@@ -12961,13 +12969,13 @@
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="n">
-        <v>0.7872</v>
+        <v>0.7871</v>
       </c>
       <c r="F219" t="n">
-        <v>0.7846</v>
+        <v>0.7844</v>
       </c>
       <c r="G219" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -12987,7 +12995,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the PIS tax family, indicating they do not match the intended mapping.</t>
+          <t>All candidates have semantic header conflicts with the PIS tax family, indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M219" t="inlineStr"/>
@@ -13092,10 +13100,10 @@
         <v>1</v>
       </c>
       <c r="F221" t="n">
-        <v>0.8316</v>
+        <v>0.8315</v>
       </c>
       <c r="G221" t="n">
-        <v>0.1684</v>
+        <v>0.1685</v>
       </c>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
@@ -13158,10 +13166,10 @@
         <v>1</v>
       </c>
       <c r="F222" t="n">
-        <v>0.8063</v>
+        <v>0.8066</v>
       </c>
       <c r="G222" t="n">
-        <v>0.1937</v>
+        <v>0.1934</v>
       </c>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
@@ -13287,7 +13295,7 @@
         <v>0.7693</v>
       </c>
       <c r="G224" t="n">
-        <v>0.0304</v>
+        <v>0.0305</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -13307,7 +13315,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of relevant data evidence.</t>
+          <t>The client column 'LOCATION' has a high non-empty count but lacks relevant content to match the semantic role of 'Região do local do desembaraço aduaneiro'.</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
@@ -13319,7 +13327,7 @@
         <v>0</v>
       </c>
       <c r="S224" t="n">
-        <v>0</v>
+        <v>0.7998</v>
       </c>
       <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr"/>
@@ -13337,7 +13345,7 @@
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="n">
-        <v>0.7815</v>
+        <v>0.7816</v>
       </c>
       <c r="F225" t="n">
         <v>0.7761</v>
@@ -13375,7 +13383,7 @@
         <v>0</v>
       </c>
       <c r="S225" t="n">
-        <v>0.7815</v>
+        <v>0.7816</v>
       </c>
       <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr"/>
@@ -13396,7 +13404,7 @@
         <v>0.7806999999999999</v>
       </c>
       <c r="F226" t="n">
-        <v>0.756</v>
+        <v>0.7559</v>
       </c>
       <c r="G226" t="n">
         <v>0.0247</v>
@@ -13419,7 +13427,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>The candidate 'LOCATION' does not semantically match 'UF do Local de Início' as it lacks relevant content evidence.</t>
+          <t>The candidate 'LOCATION' does not semantically match 'UF do Local de Início' as it lacks relevant content and context.</t>
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
@@ -13511,7 +13519,7 @@
         <v>0.7704</v>
       </c>
       <c r="G228" t="n">
-        <v>0.0301</v>
+        <v>0.0302</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -13531,7 +13539,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>The candidate 'LOCATION' has a high name confidence but lacks relevant data evidence, making it unsuitable for mapping.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M228" t="inlineStr"/>
@@ -13593,7 +13601,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25T05:08:37.593263+00:00</t>
+          <t>2026-08-25T05:39:46.554512+00:00</t>
         </is>
       </c>
     </row>

--- a/mapping_oracle_full.xlsx
+++ b/mapping_oracle_full.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mappings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unmatched Client Columns" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -579,7 +580,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts with the expected tax type, and there is no supporting data evidence.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type, and there is no supporting data evidence.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -612,7 +613,7 @@
         <v>0.7956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7944</v>
+        <v>0.7943</v>
       </c>
       <c r="G3" t="n">
         <v>0.0013</v>
@@ -635,7 +636,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or lack relevant data evidence.</t>
+          <t>All candidates conflict with the semantic role of the target column, and no suitable mapping is supported by the data.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -668,7 +669,7 @@
         <v>0.7841</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7746</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.0095</v>
@@ -691,7 +692,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family for 'Aliquota CBS'.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -721,7 +722,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>0.7938</v>
+        <v>0.7937</v>
       </c>
       <c r="F5" t="n">
         <v>0.7896</v>
@@ -803,7 +804,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with the 'Isentas CBS' column, indicating incompatible semantic roles.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -915,7 +916,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the canonical column, indicating incompatible tax roles.</t>
+          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -945,7 +946,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>0.7938</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0.7832</v>
@@ -1057,7 +1058,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>0.7865</v>
+        <v>0.7864</v>
       </c>
       <c r="F11" t="n">
         <v>0.7842</v>
@@ -1083,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the target column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family, indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1113,7 +1114,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.8215</v>
+        <v>0.8216</v>
       </c>
       <c r="F12" t="n">
         <v>0.8145</v>
@@ -1139,7 +1140,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the IBSM value, and no suitable mapping is supported by the data.</t>
+          <t>All candidates have a semantic header conflict with the IBSM value, indicating they do not represent the same business meaning.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1195,7 +1196,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the IBSM column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1225,7 +1226,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>0.8169</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>0.7991</v>
@@ -1251,7 +1252,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of the target column, and no valid mapping evidence exists.</t>
+          <t>All candidates have a tax-family conflict with the IBSM column, indicating incompatible semantic roles.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1281,7 +1282,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>0.7809</v>
+        <v>0.781</v>
       </c>
       <c r="F15" t="n">
         <v>0.7735</v>
@@ -1307,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>All candidates conflict with the semantic role of the target column, which is a tax base.</t>
+          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1363,7 +1364,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column and lack sufficient row evidence.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1419,7 +1420,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the 'Base IBS' column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts and do not match the expected role of 'Base IBS'.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1531,7 +1532,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax family, and the evidence does not support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the 'Valor IBS' column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1561,7 +1562,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>0.8008</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="F20" t="n">
         <v>0.791</v>
@@ -1587,7 +1588,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the tax-family context, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts and no valid row evidence.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1620,7 +1621,7 @@
         <v>0.8233</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8081</v>
       </c>
       <c r="G21" t="n">
         <v>0.0153</v>
@@ -1643,7 +1644,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family context of 'Outras IBS', indicating they are not compatible.</t>
+          <t>All candidates have semantic header conflicts with the 'Outras IBS' column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1655,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8233</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -1673,13 +1674,13 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>0.7829</v>
+        <v>0.7845</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7765</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0063</v>
+        <v>0.0067</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1699,7 +1700,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column, indicating incompatible tax roles.</t>
+          <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax roles.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1729,7 +1730,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>0.832</v>
+        <v>0.8319</v>
       </c>
       <c r="F23" t="n">
         <v>0.8288</v>
@@ -1755,7 +1756,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate found due to lack of relevant data evidence.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -1764,10 +1765,10 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -1811,7 +1812,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column is entirely zero.</t>
+          <t>All candidate columns contain non-zero values, while the source column is entirely zero, indicating a mismatch in semantic meaning.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -1844,7 +1845,7 @@
         <v>0.8148</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8057</v>
+        <v>0.8058</v>
       </c>
       <c r="G25" t="n">
         <v>0.0091</v>
@@ -1867,7 +1868,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>All candidates have non-zero values, but none align semantically with 'Aliquota IS'.</t>
+          <t>All candidates have non-zero values, while the model column only contains zeros, indicating a mismatch in data semantics.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -1897,13 +1898,13 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.7948</v>
+        <v>0.7942</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7904</v>
+        <v>0.789</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0044</v>
+        <v>0.0053</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1923,7 +1924,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate columns contain non-zero values, while 'Valor IS' has only zeros, indicating a mismatch in semantic meaning.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -1935,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7948</v>
+        <v>0.7942</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -1953,10 +1954,10 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.8107</v>
+        <v>0.8108</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7992</v>
+        <v>0.7993</v>
       </c>
       <c r="G27" t="n">
         <v>0.0115</v>
@@ -1979,7 +1980,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column is entirely zero.</t>
+          <t>All candidate columns contain non-zero values, while the source column 'Isentas IS' has only zeros, indicating no compatible mapping.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -2065,10 +2066,10 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>0.7845</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7778</v>
+        <v>0.7781</v>
       </c>
       <c r="G29" t="n">
         <v>0.0067</v>
@@ -2121,16 +2122,16 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>0.7523</v>
+        <v>0.7766</v>
       </c>
       <c r="F30" t="n">
         <v>0.844</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0917</v>
+        <v>-0.0674</v>
       </c>
       <c r="H30" t="n">
-        <v>0.84</v>
+        <v>0.2357</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2156,10 +2157,10 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="S30" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -2239,7 +2240,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.834</v>
+        <v>0.8339</v>
       </c>
       <c r="F32" t="n">
         <v>0.8280999999999999</v>
@@ -2251,7 +2252,7 @@
         <v>0.8071</v>
       </c>
       <c r="I32" t="n">
-        <v>0.834</v>
+        <v>0.8339</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2277,7 +2278,7 @@
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>0.834</v>
+        <v>0.6669</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -2292,22 +2293,28 @@
           <t>Nº da Nota Fiscal</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
       <c r="E33" t="n">
-        <v>0.8557</v>
+        <v>0.8556</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8024</v>
+        <v>0.8023</v>
       </c>
       <c r="G33" t="n">
         <v>0.0533</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.7833</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.8556</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2316,12 +2323,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a significantly lower median length and digit count compared to 'Nº da Nota Fiscal', indicating a mismatch in expected formats.</t>
+          <t>The candidate 'NUMERO NF' has a high name confidence and matches the numeric format of the invoice number.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -2330,10 +2337,10 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -2413,10 +2420,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.8429</v>
+        <v>0.8428</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="G35" t="n">
         <v>0.0168</v>
@@ -2482,10 +2489,10 @@
         <v>0.8824</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.8252</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0573</v>
+        <v>0.0572</v>
       </c>
       <c r="H36" t="n">
         <v>0.1586</v>
@@ -2505,7 +2512,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>The header 'DESC_PRODUTO' suggests a product description, but the numeric profile indicates mixed content, conflicting with the expected string type for 'Descrição'.</t>
+          <t>The header 'DESC_PRODUTO' suggests a product description, but the numeric content indicates it is not compatible with the 'Descrição' column.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -2535,7 +2542,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>0.7705</v>
+        <v>0.7704</v>
       </c>
       <c r="F37" t="n">
         <v>0.805</v>
@@ -2597,7 +2604,7 @@
         <v>0.8288</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0074</v>
+        <v>0.0075</v>
       </c>
       <c r="H38" t="n">
         <v>0.4187</v>
@@ -2629,7 +2636,7 @@
         <v>0.8</v>
       </c>
       <c r="S38" t="n">
-        <v>0.8175</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -2653,7 +2660,7 @@
         <v>0.8300999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0186</v>
+        <v>-0.0187</v>
       </c>
       <c r="H39" t="n">
         <v>0.2181</v>
@@ -2703,16 +2710,16 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>0.7241</v>
+        <v>0.8043</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8043</v>
+        <v>0.758</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.0462</v>
       </c>
       <c r="H40" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2729,7 +2736,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate matches the semantic role of 'Região' based on header names and data evidence.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -2738,10 +2745,10 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -2765,19 +2772,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.8279</v>
+        <v>0.828</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7922</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0361</v>
+        <v>0.0358</v>
       </c>
       <c r="H41" t="n">
         <v>0.84</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8315</v>
+        <v>0.8316</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2791,7 +2798,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>The header 'TOTAL DO ITEM' aligns with the numeric nature of 'Val.Total NF' and has no semantic conflicts.</t>
+          <t>The header 'TOTAL DO ITEM' aligns with the numeric nature and range of 'Val.Total NF', indicating it represents a total value.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -2800,10 +2807,10 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
-        <v>0.9368</v>
+        <v>0.9</v>
       </c>
       <c r="S41" t="n">
-        <v>0.8312</v>
+        <v>0.85</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -2890,10 +2897,10 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9025</v>
+        <v>0.9024</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0975</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
@@ -2947,19 +2954,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.8068</v>
+        <v>0.8065</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8044</v>
+        <v>0.8052</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0024</v>
+        <v>0.0013</v>
       </c>
       <c r="H44" t="n">
         <v>0.84</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8168</v>
+        <v>0.8166</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3003,16 +3010,16 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.849</v>
+        <v>0.8794</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0305</v>
+        <v>-0.0735</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.7498</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -3029,7 +3036,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a semantic header conflict with the expected role of 'Isentas ICMS'.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -3038,10 +3045,10 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -3085,7 +3092,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a strong name match but shows no relevant data overlap with 'Outras ICMS', indicating a semantic mismatch.</t>
+          <t>The candidate 'IND TRIB ICMS' has a strong name match but lacks relevant data evidence, showing only two unique values.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
@@ -3115,13 +3122,13 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>0.7946</v>
+        <v>0.7948</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7896</v>
+        <v>0.7899</v>
       </c>
       <c r="G47" t="n">
-        <v>0.005</v>
+        <v>0.0049</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -3171,7 +3178,7 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>0.805</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="F48" t="n">
         <v>0.8015</v>
@@ -3197,7 +3204,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP value, and no distinctive row evidence supports a mapping.</t>
+          <t>All candidates have semantic header conflicts with the ICEP value, and no suitable mapping is supported by the data.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -3353,7 +3360,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8777</v>
+        <v>0.8776</v>
       </c>
       <c r="F51" t="n">
         <v>0.8084</v>
@@ -3365,7 +3372,7 @@
         <v>0.7498</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8777</v>
+        <v>0.8776</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3379,7 +3386,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a high name confidence and matches the IPI tax type, despite a lack of strong numeric evidence.</t>
+          <t>The candidate 'IND TRIB IPI' has a high name confidence and matches the tax type, despite a lack of distinctive sample overlap.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -3391,7 +3398,7 @@
         <v>0.5</v>
       </c>
       <c r="S51" t="n">
-        <v>0.8777</v>
+        <v>0.8776</v>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
@@ -3536,10 +3543,10 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0.79</v>
+        <v>0.7901</v>
       </c>
       <c r="G54" t="n">
-        <v>0.21</v>
+        <v>0.2099</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
@@ -3721,7 +3728,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>All candidate columns are unrelated to 'Frete' as they represent different semantic roles.</t>
+          <t>All candidate columns contain only zeros, indicating no relevant mapping to the 'Frete' column.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -3733,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.7544</v>
+        <v>0.75</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -3777,7 +3784,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>All candidate columns contain only zeros or non-numeric values, failing to provide any relevant mapping evidence.</t>
+          <t>All candidates are incompatible due to their content being non-numeric and the target column requiring numeric values.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -3789,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>0.7863</v>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -3833,7 +3840,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>The 'Observações' column contains strings that do not match any candidate's semantic role or content.</t>
+          <t>No suitable candidate matches the semantic role of 'Observações' based on header and data evidence.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -3889,7 +3896,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No client column matches the semantic role of 'Chave de acesso' (NF-e key) with sufficient evidence.</t>
+          <t>No client column matches the semantic role of 'Chave de acesso' as all candidates are unrelated.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -4037,16 +4044,16 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.7271</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7437</v>
+        <v>0.7687</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0249</v>
+        <v>-0.0416</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2357</v>
+        <v>0.264</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -4072,10 +4079,10 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="n">
-        <v>0.5</v>
+        <v>0.7271</v>
       </c>
       <c r="S63" t="n">
-        <v>0.5</v>
+        <v>0.7271</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -4093,13 +4100,13 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>0.7649</v>
+        <v>0.7612</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7629</v>
+        <v>0.7604</v>
       </c>
       <c r="G64" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -4119,7 +4126,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Modificado por'.</t>
+          <t>No candidate column matches the semantic role of 'Modificado por'.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -4175,7 +4182,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Criado Manualmente'.</t>
+          <t>No suitable candidate matches the semantic role of 'Criado Manualmente' as all candidates are unrelated to a binary indicator.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -4267,19 +4274,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8017</v>
+        <v>0.8016</v>
       </c>
       <c r="F67" t="n">
         <v>0.8331</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0314</v>
+        <v>-0.0315</v>
       </c>
       <c r="H67" t="n">
         <v>0.73</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8017</v>
+        <v>0.8016</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4302,10 +4309,10 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S67" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -4388,10 +4395,10 @@
         <v>0.8231000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8089</v>
+        <v>0.8088</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0142</v>
+        <v>0.0143</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -4411,7 +4418,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>The 'NUMERO NF' column has a strong numeric profile and high name confidence, aligning well with the 'Nº FCI' semantic role.</t>
+          <t>The 'NUMERO NF' column has a strong numeric profile and matches the semantic role of 'Nº FCI' as an invoice number.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -4444,10 +4451,10 @@
         <v>0.7979000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7796</v>
+        <v>0.7795</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0183</v>
+        <v>0.0184</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -4479,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -4497,7 +4504,7 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>0.804</v>
+        <v>0.8041</v>
       </c>
       <c r="F71" t="n">
         <v>0.7936</v>
@@ -4553,10 +4560,10 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>0.7896</v>
+        <v>0.7897</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7881</v>
+        <v>0.7882</v>
       </c>
       <c r="G72" t="n">
         <v>0.0015</v>
@@ -4609,13 +4616,13 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>0.7944</v>
+        <v>0.7937</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8192</v>
+        <v>0.8175</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0247</v>
+        <v>-0.0239</v>
       </c>
       <c r="H73" t="n">
         <v>0.4751</v>
@@ -4644,10 +4651,10 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="n">
-        <v>0.5</v>
+        <v>0.7937</v>
       </c>
       <c r="S73" t="n">
-        <v>0.5</v>
+        <v>0.7937</v>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -4671,19 +4678,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.8436</v>
+        <v>0.8437</v>
       </c>
       <c r="F74" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0336</v>
+        <v>0.0337</v>
       </c>
       <c r="H74" t="n">
         <v>0.73</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8436</v>
+        <v>0.8437</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -4697,7 +4704,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' closely matches the semantic role of 'Item referência NF' despite some numeric discrepancies.</t>
+          <t>The header 'NUMERO NF' suggests a document number, conflicting with the item reference role of 'Item referência NF'.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -4706,10 +4713,10 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="S74" t="n">
-        <v>0.8208</v>
+        <v>0.6718</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -4753,7 +4760,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No candidate column matches the semantic role of 'Mensagem', which contains descriptive text rather than product codes or identifiers.</t>
+          <t>No candidate column matches the semantic role of 'Mensagem', which contains descriptive text, while all candidates are unrelated to this content.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -4865,7 +4872,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>The candidate 'COD_FIS_JUR' has a numeric profile with no overlap in samples or valid values, indicating it does not match the 'Domicílio fiscal' which is expected to be a string.</t>
+          <t>The candidate 'COD_FIS_JUR' does not semantically match 'Domicílio fiscal' as it represents a different concept.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -4963,7 +4970,7 @@
         <v>0.7874</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0335</v>
+        <v>0.0334</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -4983,7 +4990,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>The column 'NUMERO NF' has a strong numeric profile and matches the semantic role of an invoice number.</t>
+          <t>The column 'NUMERO NF' has a strong numeric profile and aligns with the expected format for invoice numbers.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -4995,7 +5002,7 @@
         <v>0.9</v>
       </c>
       <c r="S79" t="n">
-        <v>0.8209</v>
+        <v>0.85</v>
       </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
@@ -5045,7 +5052,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>The header 'DESC_PRODUTO' suggests a description of the service, aligning with the empty 'Texto breve serviço'.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -5054,10 +5061,10 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.8017</v>
+        <v>0.7664</v>
       </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
@@ -5075,16 +5082,16 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>0.7657</v>
+        <v>0.8135</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8135</v>
+        <v>0.798</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.0477</v>
+        <v>0.0155</v>
       </c>
       <c r="H81" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -5101,7 +5108,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate matches the semantic role of 'Origem do material' based on the provided evidence.</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -5110,10 +5117,10 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
@@ -5131,16 +5138,16 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>0.75</v>
+        <v>0.7895</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7896</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.0395</v>
+        <v>0.0037</v>
       </c>
       <c r="H82" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -5157,7 +5164,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate matches the semantic role of 'Utilização de material' based on the provided evidence.</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -5166,10 +5173,10 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
@@ -5187,7 +5194,7 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>0.7931</v>
+        <v>0.793</v>
       </c>
       <c r="F83" t="n">
         <v>0.778</v>
@@ -5213,7 +5220,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the empty evidence of the model column.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -5222,10 +5229,10 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>0.646</v>
       </c>
       <c r="S83" t="n">
-        <v>0.7526</v>
+        <v>0.793</v>
       </c>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
@@ -5269,7 +5276,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>The candidate headers conflict semantically with the expected role of 'Mont.líquido frete', and all candidate values are non-numeric.</t>
+          <t>All candidates have semantic-role conflicts and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -5325,7 +5332,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts or do not match the expected numeric type for 'Mont.líquido seguro', which is expected to be a monetary value.</t>
+          <t>All candidates have semantic conflicts or lack relevant evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -5355,13 +5362,13 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
+        <v>0.8169</v>
+      </c>
+      <c r="F86" t="n">
         <v>0.8228</v>
       </c>
-      <c r="F86" t="n">
-        <v>0.8224</v>
-      </c>
       <c r="G86" t="n">
-        <v>0.0005</v>
+        <v>-0.0059</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -5381,7 +5388,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Grupo de imposto' as all candidates are tax indicators, not tax groups.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -5390,10 +5397,10 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>0.8169</v>
       </c>
       <c r="S86" t="n">
-        <v>0.8228</v>
+        <v>0.8169</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -5420,7 +5427,7 @@
         <v>0.8881</v>
       </c>
       <c r="F87" t="n">
-        <v>0.862</v>
+        <v>0.8621</v>
       </c>
       <c r="G87" t="n">
         <v>0.0261</v>
@@ -5482,7 +5489,7 @@
         <v>0.8587</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.8292</v>
       </c>
       <c r="G88" t="n">
         <v>0.0295</v>
@@ -5505,7 +5512,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a high name confidence and matches the expected tax base role despite a lack of distinctive sample overlap.</t>
+          <t>The candidate 'IND TRIB ICMS' has a high name confidence but conflicts semantically with the expected role of 'Base Reduzida ICMS'.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -5514,10 +5521,10 @@
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
-        <v>0.8587</v>
+        <v>0.5</v>
       </c>
       <c r="S88" t="n">
-        <v>0.8587</v>
+        <v>0.5</v>
       </c>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
@@ -5538,7 +5545,7 @@
         <v>0.7867</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7819</v>
+        <v>0.782</v>
       </c>
       <c r="G89" t="n">
         <v>0.0048</v>
@@ -5561,7 +5568,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type, indicating incompatible mappings.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type.</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -5617,7 +5624,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and do not match the expected tax base context.</t>
+          <t>All candidates conflict semantically with the expected tax role of 'Isentas ICAP'.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -5650,7 +5657,7 @@
         <v>0.8223</v>
       </c>
       <c r="F91" t="n">
-        <v>0.82</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="G91" t="n">
         <v>0.0022</v>
@@ -5673,7 +5680,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and do not align with the expected tax base for 'Outras ICAP', which is not supported by the data.</t>
+          <t>All candidates have semantic header conflicts and do not match the expected role of 'Outras ICAP'.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -5729,7 +5736,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected role of 'Base Reduzida ICAP'.</t>
+          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -5762,7 +5769,7 @@
         <v>0.7851</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7783</v>
+        <v>0.7782</v>
       </c>
       <c r="G93" t="n">
         <v>0.0068</v>
@@ -5818,7 +5825,7 @@
         <v>0.8079</v>
       </c>
       <c r="F94" t="n">
-        <v>0.8024</v>
+        <v>0.8025</v>
       </c>
       <c r="G94" t="n">
         <v>0.0054</v>
@@ -5841,7 +5848,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP base, and the evidence does not support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -5871,10 +5878,10 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7859</v>
       </c>
       <c r="F95" t="n">
-        <v>0.7832</v>
+        <v>0.7833</v>
       </c>
       <c r="G95" t="n">
         <v>0.0026</v>
@@ -5897,7 +5904,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family role of ICEP, providing no valid mapping.</t>
+          <t>All candidates have semantic header conflicts with the ICEP tax type, indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -5930,7 +5937,7 @@
         <v>0.7871</v>
       </c>
       <c r="F96" t="n">
-        <v>0.786</v>
+        <v>0.7861</v>
       </c>
       <c r="G96" t="n">
         <v>0.0011</v>
@@ -5953,7 +5960,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the ICEP tax situation, indicating they do not match the intended meaning.</t>
+          <t>All candidates have semantic header conflicts with the ICEP tax situation, indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -5986,10 +5993,10 @@
         <v>0.823</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8213</v>
+        <v>0.8214</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -6039,10 +6046,10 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>0.7867</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>0.7826</v>
+        <v>0.7827</v>
       </c>
       <c r="G98" t="n">
         <v>0.0041</v>
@@ -6065,7 +6072,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP role, indicating incompatible tax-family contexts.</t>
+          <t>All candidates have semantic header conflicts with the ICEP field, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -6095,7 +6102,7 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>0.7771</v>
+        <v>0.7772</v>
       </c>
       <c r="F99" t="n">
         <v>0.7766999999999999</v>
@@ -6154,7 +6161,7 @@
         <v>0.7997</v>
       </c>
       <c r="F100" t="n">
-        <v>0.7863</v>
+        <v>0.7864</v>
       </c>
       <c r="G100" t="n">
         <v>0.0134</v>
@@ -6177,7 +6184,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates have semantic header conflicts and no valid row evidence.</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -6210,7 +6217,7 @@
         <v>0.7994</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7947</v>
+        <v>0.7948</v>
       </c>
       <c r="G101" t="n">
         <v>0.0046</v>
@@ -6233,7 +6240,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family, indicating no suitable mapping.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family, indicating they do not match the intended role of 'Aliquota ICSP'.</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -6289,7 +6296,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the expected tax role, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -6319,13 +6326,13 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
-        <v>0.7842</v>
+        <v>0.7843</v>
       </c>
       <c r="F103" t="n">
         <v>0.7803</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0039</v>
+        <v>0.004</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -6345,7 +6352,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with the source column, indicating incompatible meanings.</t>
+          <t>All candidates have a semantic header conflict with the tax-family context, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -6378,10 +6385,10 @@
         <v>0.8174</v>
       </c>
       <c r="F104" t="n">
-        <v>0.8166</v>
+        <v>0.8167</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0008</v>
+        <v>0.0007</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -6431,7 +6438,7 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
-        <v>0.786</v>
+        <v>0.7859</v>
       </c>
       <c r="F105" t="n">
         <v>0.7756999999999999</v>
@@ -6487,10 +6494,10 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.803</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8102</v>
+        <v>0.8103</v>
       </c>
       <c r="G106" t="n">
         <v>-0.0073</v>
@@ -6525,7 +6532,7 @@
         <v>0.8</v>
       </c>
       <c r="S106" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.803</v>
       </c>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
@@ -6546,7 +6553,7 @@
         <v>0.7927999999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7879</v>
       </c>
       <c r="G107" t="n">
         <v>0.0049</v>
@@ -6569,7 +6576,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating a mismatch in semantic roles.</t>
+          <t>All candidate columns contain non-matching data types and values, with the only candidate being a date format.</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -6599,13 +6606,13 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
-        <v>0.7835</v>
+        <v>0.7875</v>
       </c>
       <c r="F108" t="n">
-        <v>0.7875</v>
+        <v>0.7839</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0039</v>
+        <v>0.0037</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -6625,7 +6632,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating a lack of semantic alignment.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -6634,10 +6641,10 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="n">
-        <v>0.7835</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>0.7835</v>
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
@@ -6681,7 +6688,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Valor DIF_ALIQ' as all candidates have conflicting roles or irrelevant data.</t>
+          <t>All candidate columns have significant semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -6711,13 +6718,13 @@
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="n">
-        <v>0.8079</v>
+        <v>0.8072</v>
       </c>
       <c r="F110" t="n">
-        <v>0.8058</v>
+        <v>0.8057</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0021</v>
+        <v>0.0014</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -6737,7 +6744,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating a lack of semantic alignment.</t>
+          <t>All candidate columns contain non-zero values, while the source column is entirely zero, indicating no semantic match.</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -6767,13 +6774,13 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>0.8096</v>
+        <v>0.8091</v>
       </c>
       <c r="F111" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0017</v>
+        <v>0.0021</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -6793,7 +6800,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No suitable candidate found; all candidates have conflicting semantic roles or insufficient evidence.</t>
+          <t>No suitable candidate found; all candidates have conflicting semantic roles or lack relevant data.</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -6805,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>0.8096</v>
+        <v>0.8091</v>
       </c>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
@@ -6823,13 +6830,13 @@
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
+        <v>0.7781</v>
+      </c>
+      <c r="F112" t="n">
         <v>0.7779</v>
       </c>
-      <c r="F112" t="n">
-        <v>0.7776</v>
-      </c>
       <c r="G112" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -6849,7 +6856,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating a semantic mismatch.</t>
+          <t>All candidate columns contain only zeros or are semantically unrelated to the 'Base Reduzida DIF_ALIQ'.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -6861,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>0.7779</v>
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
@@ -6876,8 +6883,14 @@
           <t>Base ICMS_FECP</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+      <c r="C113" t="n">
+        <v>21</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
       <c r="E113" t="n">
         <v>0.8562</v>
       </c>
@@ -6891,7 +6904,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>0.8562</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -6900,12 +6913,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or lack relevant data evidence.</t>
+          <t>The candidate 'IND TRIB ICMS' has a high name confidence but does not match the expected numeric characteristics of 'Base ICMS_FECP', which is all zeros.</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -6917,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>0.8562</v>
       </c>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
@@ -6941,7 +6954,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.8551</v>
+        <v>0.855</v>
       </c>
       <c r="F114" t="n">
         <v>0.8270999999999999</v>
@@ -6953,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8551</v>
+        <v>0.855</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6979,7 +6992,7 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>0.8551</v>
+        <v>0.855</v>
       </c>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
@@ -6994,22 +7007,28 @@
           <t>Valor ICMS_FECP</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
+      <c r="C115" t="n">
+        <v>21</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
       <c r="E115" t="n">
-        <v>0.7909</v>
+        <v>0.8588</v>
       </c>
       <c r="F115" t="n">
-        <v>0.8587</v>
+        <v>0.8297</v>
       </c>
       <c r="G115" t="n">
-        <v>-0.0678</v>
+        <v>0.0291</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>0.8588</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7018,12 +7037,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate 'IND TRIB ICMS' has a high name confidence but does not match the all-zero evidence of 'Valor ICMS_FECP'.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -7032,10 +7051,10 @@
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="n">
-        <v>0.7909</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>0.7909</v>
+        <v>0.8588</v>
       </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
@@ -7050,13 +7069,19 @@
           <t>Isentas ICMS_FECP</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
+      <c r="C116" t="n">
+        <v>21</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
       <c r="E116" t="n">
-        <v>0.8529</v>
+        <v>0.853</v>
       </c>
       <c r="F116" t="n">
-        <v>0.8253</v>
+        <v>0.8254</v>
       </c>
       <c r="G116" t="n">
         <v>0.0276</v>
@@ -7065,7 +7090,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>0.853</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -7074,12 +7099,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or do not match the expected role of a tax exemption indicator.</t>
+          <t>The candidate 'IND TRIB ICMS' has a strong name match but lacks relevant data evidence, as it contains non-zero values while the source column is all zeros.</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -7091,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>0</v>
+        <v>0.853</v>
       </c>
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
@@ -7109,13 +7134,13 @@
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
-        <v>0.8646</v>
+        <v>0.8659</v>
       </c>
       <c r="F117" t="n">
-        <v>0.831</v>
+        <v>0.8351</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0337</v>
+        <v>0.0308</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -7135,7 +7160,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column has only zeros, indicating a lack of compatible data.</t>
+          <t>All candidate columns contain non-zero values, while the source column has only zeros, indicating no compatible mapping.</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -7165,10 +7190,10 @@
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
-        <v>0.8303</v>
+        <v>0.8304</v>
       </c>
       <c r="F118" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.803</v>
       </c>
       <c r="G118" t="n">
         <v>0.0274</v>
@@ -7233,7 +7258,7 @@
         <v>0.7919</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0615</v>
+        <v>0.0616</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -7253,7 +7278,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
+          <t>The candidate 'IND TRIB IPI' has a strong name match but lacks supporting data evidence, as all values are non-informative zeros.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -7265,7 +7290,7 @@
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>0.8535</v>
       </c>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
@@ -7286,7 +7311,7 @@
         <v>0.8083</v>
       </c>
       <c r="F120" t="n">
-        <v>0.8057</v>
+        <v>0.8056</v>
       </c>
       <c r="G120" t="n">
         <v>0.0027</v>
@@ -7365,7 +7390,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context of 'Isentas COFINS'.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -7451,10 +7476,10 @@
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
-        <v>0.776</v>
+        <v>0.7754</v>
       </c>
       <c r="F123" t="n">
-        <v>0.774</v>
+        <v>0.7734</v>
       </c>
       <c r="G123" t="n">
         <v>0.002</v>
@@ -7477,7 +7502,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the COFINS tax family, making them incompatible.</t>
+          <t>All candidates have semantic header conflicts with the COFINS tax family, indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -7507,7 +7532,7 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7857</v>
       </c>
       <c r="F124" t="n">
         <v>0.7818000000000001</v>
@@ -7533,7 +7558,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context of 'Isentas PIS'.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -7563,10 +7588,10 @@
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="n">
-        <v>0.7997</v>
+        <v>0.7998</v>
       </c>
       <c r="F125" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.799</v>
       </c>
       <c r="G125" t="n">
         <v>0.0008</v>
@@ -7589,7 +7614,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>The candidate columns conflict with the tax-family context of 'Outras PIS' and provide no relevant data evidence.</t>
+          <t>All candidates have semantic header conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -7601,7 +7626,7 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
@@ -7645,7 +7670,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the PIS tax type, making them incompatible.</t>
+          <t>All candidates have semantic header conflicts with the PIS tax type, indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -7701,7 +7726,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the PIS tax base, and the evidence does not support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the PIS tax base, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -7787,7 +7812,7 @@
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
-        <v>0.7633</v>
+        <v>0.7634</v>
       </c>
       <c r="F129" t="n">
         <v>0.7532</v>
@@ -7813,7 +7838,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>All candidates conflict with the semantic role of 'Base ISS' and provide no relevant mapping evidence.</t>
+          <t>All candidates conflict with the tax-family of 'Base ISS' and provide no relevant mapping evidence.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -7825,7 +7850,7 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
@@ -7869,7 +7894,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of ISS, providing no valid mapping.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -7925,7 +7950,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>All candidates conflict with the semantic role of 'Valor ISS' and provide no relevant evidence.</t>
+          <t>All candidates conflict with the tax-family of 'Valor ISS' and provide no relevant mapping evidence.</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -7958,10 +7983,10 @@
         <v>0.7833</v>
       </c>
       <c r="F132" t="n">
-        <v>0.7699</v>
+        <v>0.7698</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0134</v>
+        <v>0.0135</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -7981,7 +8006,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family context of 'Isentas ISS'.</t>
+          <t>All candidates have a tax-family conflict with the 'Isentas ISS' column, indicating incompatible semantic roles.</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
@@ -8011,10 +8036,10 @@
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
-        <v>0.7974</v>
+        <v>0.7975</v>
       </c>
       <c r="F133" t="n">
-        <v>0.7946</v>
+        <v>0.7947</v>
       </c>
       <c r="G133" t="n">
         <v>0.0027</v>
@@ -8093,7 +8118,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of the target column, and no strong evidence supports a mapping.</t>
+          <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
@@ -8149,7 +8174,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
+          <t>All candidate columns contain zero values, providing no evidence for a valid mapping.</t>
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
@@ -8179,13 +8204,13 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
-        <v>0.7903</v>
+        <v>0.8145</v>
       </c>
       <c r="F136" t="n">
-        <v>0.8145</v>
+        <v>0.802</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.0242</v>
+        <v>0.0125</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -8205,7 +8230,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates have semantic conflicts or lack relevant evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
@@ -8217,7 +8242,7 @@
         <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>0.7903</v>
+        <v>0</v>
       </c>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
@@ -8261,7 +8286,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>All candidate columns have significant semantic conflicts or lack relevant data evidence.</t>
+          <t>All candidate columns contain non-distinctive or zero-only values, lacking sufficient evidence for a valid mapping.</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
@@ -8317,7 +8342,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of distinctive sample evidence.</t>
+          <t>No suitable candidate due to semantic header conflicts and lack of relevant data evidence.</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -8353,7 +8378,7 @@
         <v>0.8280999999999999</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0004</v>
+        <v>0.0005</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -8373,7 +8398,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic and numeric discrepancies, with no viable mapping to the 'Outras FECP_ST' column.</t>
+          <t>All candidates have conflicting semantic roles or insufficient evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -8403,13 +8428,13 @@
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
-        <v>0.7836</v>
+        <v>0.797</v>
       </c>
       <c r="F140" t="n">
-        <v>0.7971</v>
+        <v>0.7822</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0135</v>
+        <v>0.0149</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -8429,7 +8454,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidate columns have significant semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -8438,10 +8463,10 @@
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="n">
-        <v>0.7836</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>0.7836</v>
+        <v>0.797</v>
       </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
@@ -8462,10 +8487,10 @@
         <v>0.8691</v>
       </c>
       <c r="F141" t="n">
-        <v>0.853</v>
+        <v>0.8531</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0161</v>
+        <v>0.016</v>
       </c>
       <c r="H141" t="n">
         <v>0.7375</v>
@@ -8541,7 +8566,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the expected role of 'Base ICMS_ST' and do not provide relevant evidence.</t>
+          <t>All candidates have semantic conflicts with the expected role of 'Base ICMS_ST'.</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
@@ -8574,7 +8599,7 @@
         <v>0.7915</v>
       </c>
       <c r="F143" t="n">
-        <v>0.7871</v>
+        <v>0.787</v>
       </c>
       <c r="G143" t="n">
         <v>0.0045</v>
@@ -8653,7 +8678,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
+          <t>All candidates have semantic header conflicts or do not match the expected tax base for ICMS_ST.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
@@ -8683,7 +8708,7 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
-        <v>0.8131</v>
+        <v>0.8132</v>
       </c>
       <c r="F145" t="n">
         <v>0.8069</v>
@@ -8709,7 +8734,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or do not match the expected tax role.</t>
+          <t>All candidates have semantic header conflicts or insufficient evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
@@ -8739,13 +8764,13 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="F146" t="n">
         <v>0.7786</v>
       </c>
-      <c r="F146" t="n">
-        <v>0.778</v>
-      </c>
       <c r="G146" t="n">
-        <v>0.0005</v>
+        <v>0.0004</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -8765,7 +8790,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>All candidates conflict with the semantic role of the target column, indicating they do not represent a compatible mapping.</t>
+          <t>All candidates have semantic conflicts with the required tax base role, making them incompatible.</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
@@ -8777,7 +8802,7 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
@@ -8795,10 +8820,10 @@
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
-        <v>0.7998</v>
+        <v>0.7997</v>
       </c>
       <c r="F147" t="n">
-        <v>0.8016</v>
+        <v>0.8015</v>
       </c>
       <c r="G147" t="n">
         <v>-0.0018</v>
@@ -8830,10 +8855,10 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="n">
-        <v>0.7998</v>
+        <v>0.8</v>
       </c>
       <c r="S147" t="n">
-        <v>0.7998</v>
+        <v>0.8</v>
       </c>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
@@ -8945,7 +8970,7 @@
         <v>0.8</v>
       </c>
       <c r="S149" t="n">
-        <v>0.7853</v>
+        <v>0.7886</v>
       </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
@@ -8989,7 +9014,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>The candidate 'DATA GL' does not match the time format of 'Criado às:'.</t>
+          <t>No suitable candidate matches the time format and semantic role of the 'Criado às:' column.</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
@@ -9019,10 +9044,10 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8161</v>
       </c>
       <c r="F151" t="n">
-        <v>0.8048</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="G151" t="n">
         <v>0.0112</v>
@@ -9045,7 +9070,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>All candidate columns are empty or lack relevant data to support a mapping.</t>
+          <t>No suitable candidate exists as all client columns are empty or unrelated to 'Exercício'.</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
@@ -9057,7 +9082,7 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>0</v>
+        <v>0.8161</v>
       </c>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
@@ -9078,10 +9103,10 @@
         <v>0.7748</v>
       </c>
       <c r="F152" t="n">
-        <v>0.7745</v>
+        <v>0.7746</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -9101,7 +9126,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>The candidate columns contain non-matching types and values, with 'Redução' being all zeros and the candidates being strings or unrelated integers.</t>
+          <t>All candidate columns contain only zeros or non-distinctive values, lacking any relevant mapping evidence.</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
@@ -9113,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>0.7748</v>
+        <v>0</v>
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
@@ -9193,10 +9218,10 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8544</v>
+        <v>0.8545</v>
       </c>
       <c r="F154" t="n">
-        <v>0.8225</v>
+        <v>0.8226</v>
       </c>
       <c r="G154" t="n">
         <v>0.0319</v>
@@ -9205,7 +9230,7 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>0.8544</v>
+        <v>0.8545</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -9219,7 +9244,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>The column 'COD_FIS_JUR' has a high name confidence and contains valid numeric data, but lacks specific evidence to confirm a mapping to 'Cód.domicílio fiscal'.</t>
+          <t>The candidate 'COD_FIS_JUR' has a high name confidence but lacks any row evidence, making it unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -9239,7 +9264,7 @@
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>0.8544</v>
+        <v>0.8545</v>
       </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
@@ -9257,10 +9282,10 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.8292</v>
       </c>
       <c r="F155" t="n">
-        <v>0.8244</v>
+        <v>0.8245</v>
       </c>
       <c r="G155" t="n">
         <v>0.0047</v>
@@ -9283,7 +9308,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>All candidate columns contain no relevant data or evidence to support a mapping.</t>
+          <t>No suitable candidate found due to lack of evidence and empty data.</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
@@ -9372,7 +9397,7 @@
         <v>0.8221000000000001</v>
       </c>
       <c r="F157" t="n">
-        <v>0.8032</v>
+        <v>0.8033</v>
       </c>
       <c r="G157" t="n">
         <v>0.0188</v>
@@ -9425,10 +9450,10 @@
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
-        <v>0.7552</v>
+        <v>0.7551</v>
       </c>
       <c r="F158" t="n">
-        <v>0.7929</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="G158" t="n">
         <v>-0.0377</v>
@@ -9487,7 +9512,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.8555</v>
+        <v>0.8556</v>
       </c>
       <c r="F159" t="n">
         <v>0.8017</v>
@@ -9499,7 +9524,7 @@
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8555</v>
+        <v>0.8556</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -9525,7 +9550,7 @@
         <v>1</v>
       </c>
       <c r="S159" t="n">
-        <v>0.8555</v>
+        <v>0.8556</v>
       </c>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
@@ -9543,13 +9568,13 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
-        <v>0.8268</v>
+        <v>0.8272</v>
       </c>
       <c r="F160" t="n">
-        <v>0.8256</v>
+        <v>0.8259</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0013</v>
+        <v>0.0012</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -9569,7 +9594,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>All candidate columns contain no relevant data, making mapping impossible.</t>
+          <t>No suitable candidate matches the empty evidence of the model column.</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
@@ -9581,7 +9606,7 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>0</v>
+        <v>0.7804</v>
       </c>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
@@ -9658,7 +9683,7 @@
         <v>0.7992</v>
       </c>
       <c r="F162" t="n">
-        <v>0.7881</v>
+        <v>0.788</v>
       </c>
       <c r="G162" t="n">
         <v>0.0112</v>
@@ -9681,7 +9706,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>The candidate columns contain no relevant data to map to 'Despesas', which is entirely zero.</t>
+          <t>All candidate columns contain non-relevant data types or zero values, lacking any meaningful mapping to 'Despesas'.</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
@@ -9693,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>0.7992</v>
+        <v>0</v>
       </c>
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
@@ -9737,7 +9762,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>The 'Centro custo' column has no non-empty values, making it impossible to establish a mapping.</t>
+          <t>The candidate columns contain no relevant data to support a mapping to 'Centro custo'.</t>
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
@@ -9767,13 +9792,13 @@
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="n">
-        <v>0.783</v>
+        <v>0.7829</v>
       </c>
       <c r="F164" t="n">
         <v>0.7726</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0103</v>
+        <v>0.0104</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -9793,7 +9818,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>All candidate columns lack relevant data evidence and do not align semantically with 'Municipio Fim'.</t>
+          <t>No suitable candidate found due to lack of non-empty values in the target column.</t>
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
@@ -9849,7 +9874,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of evidence and semantic conflicts.</t>
+          <t>All candidate columns have semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
@@ -9885,7 +9910,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.8734</v>
       </c>
       <c r="F166" t="n">
         <v>0.8619</v>
@@ -9897,7 +9922,7 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.8734</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -9911,7 +9936,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>The column 'COD_PRODUTO' has a high name confidence and contains numeric values, but lacks any non-empty evidence to support a mapping to 'Código do Item'.</t>
+          <t>The name 'COD_PRODUTO' closely matches the semantic role of 'Código do Item' despite the absence of row evidence.</t>
         </is>
       </c>
       <c r="M166" t="inlineStr"/>
@@ -9920,10 +9945,10 @@
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>0.8734</v>
       </c>
       <c r="S166" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.8734</v>
       </c>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
@@ -9982,7 +10007,7 @@
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S167" t="n">
         <v>0.8369</v>
@@ -10003,13 +10028,13 @@
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
-        <v>0.7264</v>
+        <v>0.7269</v>
       </c>
       <c r="F168" t="n">
-        <v>0.8082</v>
+        <v>0.8075</v>
       </c>
       <c r="G168" t="n">
-        <v>-0.0818</v>
+        <v>-0.0806</v>
       </c>
       <c r="H168" t="n">
         <v>0.7937</v>
@@ -10062,7 +10087,7 @@
         <v>0.8421</v>
       </c>
       <c r="F169" t="n">
-        <v>0.8177</v>
+        <v>0.8176</v>
       </c>
       <c r="G169" t="n">
         <v>0.0245</v>
@@ -10085,7 +10110,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the model column has only zeros, indicating a mismatch in semantic meaning.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
@@ -10097,7 +10122,7 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>0</v>
+        <v>0.8421</v>
       </c>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
@@ -10118,7 +10143,7 @@
         <v>0.7906</v>
       </c>
       <c r="F170" t="n">
-        <v>0.7885</v>
+        <v>0.7886</v>
       </c>
       <c r="G170" t="n">
         <v>0.002</v>
@@ -10171,10 +10196,10 @@
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="n">
-        <v>0.8001</v>
+        <v>0.8003</v>
       </c>
       <c r="F171" t="n">
-        <v>0.7984</v>
+        <v>0.7985</v>
       </c>
       <c r="G171" t="n">
         <v>0.0017</v>
@@ -10197,7 +10222,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family, and the evidence does not support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
@@ -10253,7 +10278,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of distinctive row evidence.</t>
+          <t>All candidates have semantic header conflicts or insufficient evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
@@ -10283,10 +10308,10 @@
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="n">
-        <v>0.8007</v>
+        <v>0.8006</v>
       </c>
       <c r="F173" t="n">
-        <v>0.7988</v>
+        <v>0.7987</v>
       </c>
       <c r="G173" t="n">
         <v>0.0019</v>
@@ -10309,7 +10334,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with the source column, and no valid mapping evidence supports a connection.</t>
+          <t>All candidates have a tax-family conflict with the source column, indicating incompatible meanings.</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
@@ -10365,7 +10390,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of distinctive sample evidence.</t>
+          <t>All candidates have significant semantic header conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M174" t="inlineStr"/>
@@ -10407,7 +10432,7 @@
         <v>0.7859</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0452</v>
+        <v>0.0451</v>
       </c>
       <c r="H175" t="n">
         <v>0.7405</v>
@@ -10522,7 +10547,7 @@
         <v>0.8036</v>
       </c>
       <c r="F177" t="n">
-        <v>0.7861</v>
+        <v>0.7862</v>
       </c>
       <c r="G177" t="n">
         <v>0.0174</v>
@@ -10545,7 +10570,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts with the target column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
@@ -10575,10 +10600,10 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="n">
-        <v>0.7832</v>
+        <v>0.7831</v>
       </c>
       <c r="F178" t="n">
-        <v>0.7749</v>
+        <v>0.7748</v>
       </c>
       <c r="G178" t="n">
         <v>0.0083</v>
@@ -10601,7 +10626,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts with the required tax classification role.</t>
+          <t>All candidates have semantic header conflicts with the tax classification, making them incompatible.</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
@@ -10637,7 +10662,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.8388</v>
+        <v>0.8387</v>
       </c>
       <c r="F179" t="n">
         <v>0.8398</v>
@@ -10649,7 +10674,7 @@
         <v>0.5</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8388</v>
+        <v>0.8387</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -10663,7 +10688,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>The column 'NUMERO NF' closely matches the semantic role of 'Nº documento' with high numeric consistency and a strong name match.</t>
+          <t>The column 'NUMERO NF' closely matches the expected format and type for invoice document numbers, with high numeric consistency.</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
@@ -10693,16 +10718,16 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>0.8445</v>
+        <v>0.751</v>
       </c>
       <c r="F180" t="n">
-        <v>0.8506</v>
+        <v>0.8505</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.006</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="H180" t="n">
-        <v>0.7123</v>
+        <v>0.82</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
@@ -10728,10 +10753,10 @@
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="n">
-        <v>0.8445</v>
+        <v>0.9</v>
       </c>
       <c r="S180" t="n">
-        <v>0.8445</v>
+        <v>0.85</v>
       </c>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
@@ -10781,7 +10806,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>The 'FORNECEDOR' column has a strong name match and informative sample values indicating it represents suppliers, aligning with the 'Exportador' role.</t>
+          <t>The 'FORNECEDOR' column has a strong name match and informative data, indicating it likely represents the 'Exportador' role.</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
@@ -10811,10 +10836,10 @@
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
-        <v>0.7904</v>
+        <v>0.7905</v>
       </c>
       <c r="F182" t="n">
-        <v>0.788</v>
+        <v>0.7881</v>
       </c>
       <c r="G182" t="n">
         <v>0.0024</v>
@@ -10837,7 +10862,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>All candidate columns are empty with no distinctive content or evidence to support a mapping.</t>
+          <t>All candidate columns are empty, providing no evidence for a mapping.</t>
         </is>
       </c>
       <c r="M182" t="inlineStr"/>
@@ -10849,7 +10874,7 @@
         <v>0</v>
       </c>
       <c r="S182" t="n">
-        <v>0</v>
+        <v>0.7905</v>
       </c>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
@@ -10867,7 +10892,7 @@
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
-        <v>0.8126</v>
+        <v>0.8127</v>
       </c>
       <c r="F183" t="n">
         <v>0.8282</v>
@@ -10905,7 +10930,7 @@
         <v>0.8</v>
       </c>
       <c r="S183" t="n">
-        <v>0.8126</v>
+        <v>0.8127</v>
       </c>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
@@ -11035,13 +11060,13 @@
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="n">
-        <v>0.802</v>
+        <v>0.8021</v>
       </c>
       <c r="F186" t="n">
         <v>0.786</v>
       </c>
       <c r="G186" t="n">
-        <v>0.016</v>
+        <v>0.0161</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -11070,10 +11095,10 @@
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="n">
-        <v>0.8</v>
+        <v>0.8021</v>
       </c>
       <c r="S186" t="n">
-        <v>0.802</v>
+        <v>0.8021</v>
       </c>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
@@ -11156,10 +11181,10 @@
         <v>0.8401</v>
       </c>
       <c r="F188" t="n">
-        <v>0.8216</v>
+        <v>0.8217</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0185</v>
+        <v>0.0184</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -11218,7 +11243,7 @@
         <v>0.9036</v>
       </c>
       <c r="F189" t="n">
-        <v>0.8622</v>
+        <v>0.8623</v>
       </c>
       <c r="G189" t="n">
         <v>0.0414</v>
@@ -11241,7 +11266,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>The header 'NUM_ITEM' suggests an item identifier, but the data is all zeros, indicating it may not be a valid mapping.</t>
+          <t>The header 'NUM_ITEM' suggests an item identifier, but the data is all zeros, indicating it does not provide meaningful evidence.</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
@@ -11297,7 +11322,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>No viable candidates due to lack of non-empty values in the client column.</t>
+          <t>All candidate columns are empty or lack relevant data to support a mapping.</t>
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
@@ -11309,7 +11334,7 @@
         <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>0</v>
+        <v>0.7536</v>
       </c>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
@@ -11512,7 +11537,7 @@
         <v>0.8927</v>
       </c>
       <c r="F194" t="n">
-        <v>0.8123</v>
+        <v>0.8122</v>
       </c>
       <c r="G194" t="n">
         <v>0.0804</v>
@@ -11535,7 +11560,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a high name confidence and matches the IPI tax type despite some numeric discrepancies.</t>
+          <t>The candidate 'IND TRIB IPI' closely matches the tax type 'Tipo de Imposto IPI' with high name confidence and consistent numeric values.</t>
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
@@ -11571,7 +11596,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>0.8753</v>
+        <v>0.8752</v>
       </c>
       <c r="F195" t="n">
         <v>0.8105</v>
@@ -11583,7 +11608,7 @@
         <v>0.225</v>
       </c>
       <c r="I195" t="n">
-        <v>0.8753</v>
+        <v>0.8752</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -11597,7 +11622,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>The header 'NUM_ITEM' closely matches 'Nº item do documento' in name, but the numeric values and context suggest it may not represent the same semantic role.</t>
+          <t>The candidate 'NUM_ITEM' has a high name confidence but does not match the expected item ID role.</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
@@ -11606,10 +11631,10 @@
       <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
-        <v>0.8753</v>
+        <v>0.8752</v>
       </c>
       <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr"/>
@@ -11636,10 +11661,10 @@
         <v>0.8824</v>
       </c>
       <c r="F196" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.8252</v>
       </c>
       <c r="G196" t="n">
-        <v>0.0573</v>
+        <v>0.0572</v>
       </c>
       <c r="H196" t="n">
         <v>0.7981</v>
@@ -11659,7 +11684,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>The column 'DESC_PRODUTO' has a high name confidence and a significant number of non-empty values that align with product descriptions.</t>
+          <t>The column 'DESC_PRODUTO' has a high name confidence and a strong profile similarity, indicating it likely represents product descriptions.</t>
         </is>
       </c>
       <c r="M196" t="inlineStr"/>
@@ -11689,13 +11714,13 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="n">
-        <v>0.7242</v>
+        <v>0.7229</v>
       </c>
       <c r="F197" t="n">
-        <v>0.8391</v>
+        <v>0.8365</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.1149</v>
+        <v>-0.1136</v>
       </c>
       <c r="H197" t="n">
         <v>0.84</v>
@@ -11745,10 +11770,10 @@
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="n">
-        <v>0.8063</v>
+        <v>0.8062</v>
       </c>
       <c r="F198" t="n">
-        <v>0.8213</v>
+        <v>0.8212</v>
       </c>
       <c r="G198" t="n">
         <v>-0.015</v>
@@ -11780,10 +11805,10 @@
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="n">
-        <v>0.8063</v>
+        <v>0.8062</v>
       </c>
       <c r="S198" t="n">
-        <v>0.8063</v>
+        <v>0.8062</v>
       </c>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
@@ -11813,7 +11838,7 @@
         <v>0.8073</v>
       </c>
       <c r="G199" t="n">
-        <v>0.0391</v>
+        <v>0.039</v>
       </c>
       <c r="H199" t="n">
         <v>0.45</v>
@@ -11833,7 +11858,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>The header 'COD_MEDIDA' aligns with 'Unidade de medida' as both represent measurement units, and the profile evidence supports this mapping.</t>
+          <t>The header 'COD_MEDIDA' aligns semantically with 'Unidade de medida' and has no conflicting evidence.</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
@@ -11842,10 +11867,10 @@
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
       <c r="R199" t="n">
-        <v>0.8</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="S199" t="n">
-        <v>0.825</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
@@ -11919,13 +11944,13 @@
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="n">
-        <v>0.7675</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="F201" t="n">
         <v>0.7184</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0492</v>
+        <v>0.0491</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -11957,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="S201" t="n">
-        <v>0.7675</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
@@ -12057,7 +12082,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax role of IVA.</t>
+          <t>All candidates have semantic header conflicts with the IVA role, indicating incompatible tax-family contexts.</t>
         </is>
       </c>
       <c r="M203" t="inlineStr"/>
@@ -12090,10 +12115,10 @@
         <v>0.804</v>
       </c>
       <c r="F204" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7748</v>
       </c>
       <c r="G204" t="n">
-        <v>0.0292</v>
+        <v>0.0293</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -12143,7 +12168,7 @@
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="n">
-        <v>0.8374</v>
+        <v>0.8375</v>
       </c>
       <c r="F205" t="n">
         <v>0.7997</v>
@@ -12169,7 +12194,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' does not match the semantic role of 'Nº do NCM', which is a tax classification code.</t>
+          <t>The header 'NUMERO NF' conflicts semantically with 'Nº do NCM', which is a tax classification code.</t>
         </is>
       </c>
       <c r="M205" t="inlineStr"/>
@@ -12197,27 +12222,27 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>TIPO DOC</t>
+          <t>NUMERO NF</t>
         </is>
       </c>
       <c r="E206" t="n">
+        <v>0.8143</v>
+      </c>
+      <c r="F206" t="n">
         <v>0.8336</v>
       </c>
-      <c r="F206" t="n">
-        <v>0.8183</v>
-      </c>
       <c r="G206" t="n">
-        <v>0.0153</v>
+        <v>-0.0194</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>0.8336</v>
+        <v>0.8143</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -12231,7 +12256,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>The header 'NUMERO NF' closely matches the semantic role of 'Nº doc.importação' and has strong numeric evidence.</t>
         </is>
       </c>
       <c r="M206" t="inlineStr"/>
@@ -12240,10 +12265,10 @@
       <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="S206" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr"/>
@@ -12267,19 +12292,19 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8532</v>
       </c>
       <c r="F207" t="n">
-        <v>0.7804</v>
+        <v>0.7803</v>
       </c>
       <c r="G207" t="n">
-        <v>0.073</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H207" t="n">
         <v>0.84</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8532</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -12293,7 +12318,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>The name 'PRECO UNITARIO' closely aligns with 'Preço líq.' and both contain numeric values indicative of pricing.</t>
+          <t>The header 'PRECO UNITARIO' closely aligns with 'Preço líq.' in terms of name and numeric profile, despite some differences in sample values.</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
@@ -12302,10 +12327,10 @@
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S207" t="n">
-        <v>0.85</v>
+        <v>0.8266</v>
       </c>
       <c r="T207" t="inlineStr"/>
       <c r="U207" t="inlineStr"/>
@@ -12323,13 +12348,13 @@
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="n">
-        <v>0.7916</v>
+        <v>0.7917</v>
       </c>
       <c r="F208" t="n">
-        <v>0.7691</v>
+        <v>0.7693</v>
       </c>
       <c r="G208" t="n">
-        <v>0.0225</v>
+        <v>0.0224</v>
       </c>
       <c r="H208" t="n">
         <v>0.84</v>
@@ -12361,7 +12386,7 @@
         <v>0.8</v>
       </c>
       <c r="S208" t="n">
-        <v>0.79</v>
+        <v>0.785</v>
       </c>
       <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr"/>
@@ -12376,14 +12401,8 @@
           <t>NF/NF-e do serviço</t>
         </is>
       </c>
-      <c r="C209" t="n">
-        <v>8</v>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>NUMERO NF</t>
-        </is>
-      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
       <c r="E209" t="n">
         <v>0.8511</v>
       </c>
@@ -12394,10 +12413,10 @@
         <v>0.0062</v>
       </c>
       <c r="H209" t="n">
-        <v>0.0301</v>
+        <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>0.8511</v>
+        <v>0</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -12406,12 +12425,12 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' suggests a document number, but the values are numeric and do not match the expected format for NF-e.</t>
+          <t>The candidate 'NUMERO NF' is numeric while 'NF/NF-e do serviço' is a string, indicating a semantic mismatch.</t>
         </is>
       </c>
       <c r="M209" t="inlineStr"/>
@@ -12423,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="S209" t="n">
-        <v>0.8511</v>
+        <v>0</v>
       </c>
       <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr"/>
@@ -12453,7 +12472,7 @@
         <v>0.7883</v>
       </c>
       <c r="G210" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -12535,7 +12554,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>The name 'TOTAL DO ITEM' closely matches 'Valor Total do Item' with high numeric consistency and no semantic conflicts.</t>
+          <t>The column 'TOTAL DO ITEM' closely matches the canonical 'Valor Total do Item' in both name and numeric profile.</t>
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
@@ -12565,13 +12584,13 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
-        <v>0.8306</v>
+        <v>0.8308</v>
       </c>
       <c r="F212" t="n">
         <v>0.7799</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0506</v>
+        <v>0.0509</v>
       </c>
       <c r="H212" t="n">
         <v>0.4406</v>
@@ -12603,7 +12622,7 @@
         <v>0.4406</v>
       </c>
       <c r="S212" t="n">
-        <v>0.8306</v>
+        <v>0.8308</v>
       </c>
       <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr"/>
@@ -12624,7 +12643,7 @@
         <v>0.8137</v>
       </c>
       <c r="F213" t="n">
-        <v>0.8087</v>
+        <v>0.8086</v>
       </c>
       <c r="G213" t="n">
         <v>0.0051</v>
@@ -12686,10 +12705,10 @@
         <v>0.98</v>
       </c>
       <c r="F214" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.7887</v>
       </c>
       <c r="G214" t="n">
-        <v>0.1912</v>
+        <v>0.1913</v>
       </c>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
@@ -12733,13 +12752,13 @@
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="n">
-        <v>0.7819</v>
+        <v>0.782</v>
       </c>
       <c r="F215" t="n">
-        <v>0.8136</v>
+        <v>0.8137</v>
       </c>
       <c r="G215" t="n">
-        <v>-0.0318</v>
+        <v>-0.0317</v>
       </c>
       <c r="H215" t="n">
         <v>0.1802</v>
@@ -12768,10 +12787,10 @@
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
       <c r="R215" t="n">
-        <v>0.5</v>
+        <v>0.782</v>
       </c>
       <c r="S215" t="n">
-        <v>0.75</v>
+        <v>0.782</v>
       </c>
       <c r="T215" t="inlineStr"/>
       <c r="U215" t="inlineStr"/>
@@ -12795,10 +12814,10 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>0.8889</v>
+        <v>0.889</v>
       </c>
       <c r="F216" t="n">
-        <v>0.863</v>
+        <v>0.8631</v>
       </c>
       <c r="G216" t="n">
         <v>0.0259</v>
@@ -12807,7 +12826,7 @@
         <v>0.7321</v>
       </c>
       <c r="I216" t="n">
-        <v>0.8889</v>
+        <v>0.889</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -12833,7 +12852,7 @@
         <v>0</v>
       </c>
       <c r="S216" t="n">
-        <v>0.8889</v>
+        <v>0.889</v>
       </c>
       <c r="T216" t="inlineStr"/>
       <c r="U216" t="inlineStr"/>
@@ -12883,7 +12902,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>The header 'IND TRIB IPI' aligns with the IPI tax context, despite the numeric profile indicating integer values.</t>
+          <t>The header 'IND TRIB IPI' aligns with the IPI tax context, despite the numeric profile indicating a different type.</t>
         </is>
       </c>
       <c r="M217" t="inlineStr"/>
@@ -12895,7 +12914,7 @@
         <v>0.75</v>
       </c>
       <c r="S217" t="n">
-        <v>0.825</v>
+        <v>0.8256</v>
       </c>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr"/>
@@ -12948,10 +12967,10 @@
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="n">
-        <v>0.5</v>
+        <v>0.1834</v>
       </c>
       <c r="S218" t="n">
-        <v>0.5</v>
+        <v>0.8172</v>
       </c>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
@@ -12969,13 +12988,13 @@
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="n">
-        <v>0.7871</v>
+        <v>0.7872</v>
       </c>
       <c r="F219" t="n">
-        <v>0.7844</v>
+        <v>0.7845</v>
       </c>
       <c r="G219" t="n">
-        <v>0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -13100,10 +13119,10 @@
         <v>1</v>
       </c>
       <c r="F221" t="n">
-        <v>0.8315</v>
+        <v>0.8316</v>
       </c>
       <c r="G221" t="n">
-        <v>0.1685</v>
+        <v>0.1684</v>
       </c>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
@@ -13166,10 +13185,10 @@
         <v>1</v>
       </c>
       <c r="F222" t="n">
-        <v>0.8066</v>
+        <v>0.8063</v>
       </c>
       <c r="G222" t="n">
-        <v>0.1934</v>
+        <v>0.1937</v>
       </c>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
@@ -13315,7 +13334,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>The client column 'LOCATION' has a high non-empty count but lacks relevant content to match the semantic role of 'Região do local do desembaraço aduaneiro'.</t>
+          <t>No suitable candidate found due to lack of relevant data evidence.</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
@@ -13327,7 +13346,7 @@
         <v>0</v>
       </c>
       <c r="S224" t="n">
-        <v>0.7998</v>
+        <v>0</v>
       </c>
       <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr"/>
@@ -13345,7 +13364,7 @@
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="n">
-        <v>0.7816</v>
+        <v>0.7815</v>
       </c>
       <c r="F225" t="n">
         <v>0.7761</v>
@@ -13371,7 +13390,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All client candidates have insufficient evidence and do not semantically match the required column.</t>
         </is>
       </c>
       <c r="M225" t="inlineStr"/>
@@ -13383,7 +13402,7 @@
         <v>0</v>
       </c>
       <c r="S225" t="n">
-        <v>0.7816</v>
+        <v>0</v>
       </c>
       <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr"/>
@@ -13401,16 +13420,16 @@
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="n">
+        <v>0.7186</v>
+      </c>
+      <c r="F226" t="n">
         <v>0.7806999999999999</v>
       </c>
-      <c r="F226" t="n">
-        <v>0.7559</v>
-      </c>
       <c r="G226" t="n">
-        <v>0.0247</v>
+        <v>-0.0621</v>
       </c>
       <c r="H226" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -13427,7 +13446,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>The candidate 'LOCATION' does not semantically match 'UF do Local de Início' as it lacks relevant content and context.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
@@ -13436,10 +13455,10 @@
       <c r="P226" t="inlineStr"/>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S226" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr"/>
@@ -13516,7 +13535,7 @@
         <v>0.8005</v>
       </c>
       <c r="F228" t="n">
-        <v>0.7704</v>
+        <v>0.7703</v>
       </c>
       <c r="G228" t="n">
         <v>0.0302</v>
@@ -13539,7 +13558,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate columns contain no relevant data, making it impossible to establish a mapping.</t>
         </is>
       </c>
       <c r="M228" t="inlineStr"/>
@@ -13601,7 +13620,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25T05:39:46.554512+00:00</t>
+          <t>2026-08-25T07:25:38.310233+00:00</t>
         </is>
       </c>
     </row>
@@ -13793,6 +13812,1280 @@
         <is>
           <t>c4e2106d5da8d59bb0b3ba304cd6c68500a22be3972e6bce81c122fc29a677f1</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>client_column_number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>client_column</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>review_priority</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>rows_with_value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>distinct_values</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>signals</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>signal_detail</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>closest_model_column</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>closest_name_confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DATA GL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>holds dates</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Data de lançamento</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.436</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TIPO DOC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Tipo de avaliação</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.492</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COD_FIS_JUR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F4" t="n">
+        <v>250</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nº ID fiscal 1</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.392</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FORNECEDOR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F5" t="n">
+        <v>250</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Código Fornecedor Início</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5118</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3469</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Número do NFC-e SAT</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>COD_PRODUTO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>7334</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1636</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Código do Item</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.436</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DESC_PRODUTO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>7060</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4318</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NUM_ITEM</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>7334</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1636</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6167</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CFO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>88.2% of its 17 distinct codes are valid cfop</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CFOP</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>COD_MEDIDA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Unidade de medida</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5148</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PRECO UNITARIO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3824</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Preço líq.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5261</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TOTAL DO ITEM</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4430</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Valor Total do Item</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7687</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Isentas ICMS</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.523</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>29</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IND TRIB IPI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Isentas IPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5011</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>41</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PROFIT_CENTER</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>proposed_not_accepted</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>shortlist</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F16" t="n">
+        <v>31</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3684</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ORGANIZACAO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>7339</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Região</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.4118</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MODALIDADE NF</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Val.Total NF</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.411</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>IDENT_FIS_JUR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Isentas IS</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.3652</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SINAL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IND_PRODUTO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>No values in this column.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ID parceiro</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3818</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>COD_UND_PADRAO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>7334</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Condições pagamento</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3818</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>27</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS_1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Isentas ICMS</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4748</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>31</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TOTAL DO ITEM_1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4430</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Valor Total do Item</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.6853</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>42</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ACCOUNT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F25" t="n">
+        <v>75</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Data documento</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>43</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SUB_ACCOUNT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F26" t="n">
+        <v>49</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Base COFINS</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3182</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>44</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Região</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.3818</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>45</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F28" t="n">
+        <v>160</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Frete</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>46</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LIFE_CYCLE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Isentas ICEP</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3182</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>47</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>INTERCOMPANY</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Documento de compras</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>48</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LOCATION</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>never_referenced</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>7338</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Valor COFINS</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>

--- a/mapping_oracle_full.xlsx
+++ b/mapping_oracle_full.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mappings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Metadata" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unmatched Client Columns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjudication Queue" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -613,7 +614,7 @@
         <v>0.7956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7943</v>
+        <v>0.7944</v>
       </c>
       <c r="G3" t="n">
         <v>0.0013</v>
@@ -636,7 +637,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>All candidates conflict with the semantic role of the target column, and no suitable mapping is supported by the data.</t>
+          <t>All candidates have semantic header conflicts or do not match the expected type for 'Base CBS', which is a tax base.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -666,7 +667,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.7841</v>
+        <v>0.7842</v>
       </c>
       <c r="F4" t="n">
         <v>0.7747000000000001</v>
@@ -692,7 +693,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family for 'Aliquota CBS'.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended role of 'Aliquota CBS'.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -722,13 +723,13 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>0.7937</v>
+        <v>0.7936</v>
       </c>
       <c r="F5" t="n">
         <v>0.7896</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0041</v>
+        <v>0.004</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -860,7 +861,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of distinctive sample evidence.</t>
+          <t>The candidate columns conflict semantically with the tax family of 'Outras CBS' and provide no relevant data evidence.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -972,7 +973,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the target column, and the evidence quality is insufficient.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1028,7 +1029,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates have semantic header conflicts with the 'Base IBSM' column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1084,7 +1085,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family, indicating incompatible mappings.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family, indicating no suitable mapping.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1140,7 +1141,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the IBSM value, indicating they do not represent the same business meaning.</t>
+          <t>All candidates have semantic header conflicts and no distinctive sample overlap.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1196,7 +1197,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the IBSM column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context of 'Isentas IBSM', indicating they do not represent the same business meaning.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1252,7 +1253,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with the IBSM column, indicating incompatible semantic roles.</t>
+          <t>All candidates have a tax-family conflict with the 'Outras IBSM' column, indicating incompatible semantic roles.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1420,7 +1421,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and do not match the expected role of 'Base IBS'.</t>
+          <t>All candidates have semantic header conflicts with the 'Base IBS' column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1476,7 +1477,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended role of 'Aliquota IBS'.</t>
+          <t>All candidates have a semantic header conflict with the expected tax family for 'Aliquota IBS'.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1532,7 +1533,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the 'Valor IBS' column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the tax family, indicating they do not match the intended role of 'Valor IBS'.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1544,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -1588,7 +1589,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no valid row evidence.</t>
+          <t>All candidates have a semantic header conflict with the tax-family context, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1618,13 +1619,13 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>0.8233</v>
+        <v>0.8224</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8081</v>
+        <v>0.8072</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0153</v>
+        <v>0.0151</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1674,13 +1675,13 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>0.7845</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.7765</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0067</v>
+        <v>0.0063</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1700,7 +1701,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax roles.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended role of 'Base Reduzida IBS'.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1730,10 +1731,10 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>0.8319</v>
+        <v>0.832</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8288</v>
+        <v>0.8287</v>
       </c>
       <c r="G23" t="n">
         <v>0.0032</v>
@@ -1756,7 +1757,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of relevant data evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -1765,10 +1766,10 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.832</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -1786,13 +1787,13 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>0.8171</v>
+        <v>0.8172</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8074</v>
+        <v>0.8073</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0097</v>
+        <v>0.0098</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1812,7 +1813,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column is entirely zero, indicating a mismatch in semantic meaning.</t>
+          <t>All candidate columns contain non-zero values, while the 'Base IS' column only has zeros, indicating a mismatch in semantic meaning.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -1842,7 +1843,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>0.8148</v>
+        <v>0.8149</v>
       </c>
       <c r="F25" t="n">
         <v>0.8058</v>
@@ -1868,7 +1869,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>All candidates have non-zero values, while the model column only contains zeros, indicating a mismatch in data semantics.</t>
+          <t>All candidates have non-zero values, while the model column contains only zeros, indicating a mismatch in data semantics.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -1898,7 +1899,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.7942</v>
+        <v>0.7943</v>
       </c>
       <c r="F26" t="n">
         <v>0.789</v>
@@ -1924,7 +1925,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>The candidate columns contain non-zero values, while 'Valor IS' has only zeros, indicating a mismatch in semantic meaning.</t>
+          <t>The candidate columns contain non-zero values while 'Valor IS' has only zeros, indicating a mismatch in semantic meaning.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -1936,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7942</v>
+        <v>0.7943</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -1957,10 +1958,10 @@
         <v>0.8108</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7993</v>
+        <v>0.7992</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0115</v>
+        <v>0.0116</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1980,7 +1981,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column 'Isentas IS' has only zeros, indicating no compatible mapping.</t>
+          <t>All candidate columns contain non-zero values, while the source column is entirely zero.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -2066,13 +2067,13 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7844</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7781</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0067</v>
+        <v>0.0068</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2122,16 +2123,16 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>0.7766</v>
+        <v>0.7522</v>
       </c>
       <c r="F30" t="n">
         <v>0.844</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0674</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2357</v>
+        <v>0.84</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2157,10 +2158,10 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -2216,7 +2217,7 @@
         <v>0.8</v>
       </c>
       <c r="S31" t="n">
-        <v>0.7953</v>
+        <v>0.795</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
@@ -2266,7 +2267,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a high name confidence and matches the numeric format of the document number, despite a lower median length.</t>
+          <t>The candidate 'NUMERO NF' has a similar numeric structure but a lower median length and lacks distinctive sample overlap with the document number.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -2278,7 +2279,7 @@
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>0.6669</v>
+        <v>0.5</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -2328,7 +2329,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a high name confidence and matches the numeric format of the invoice number.</t>
+          <t>The candidate 'NUMERO NF' has a high name confidence but a low profile similarity and no distinctive sample overlap, indicating it does not semantically match 'Nº da Nota Fiscal' despite the name similarity.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -2337,10 +2338,10 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.8</v>
+        <v>0.8556</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -2420,10 +2421,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.8428</v>
+        <v>0.8429</v>
       </c>
       <c r="F35" t="n">
-        <v>0.826</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="G35" t="n">
         <v>0.0168</v>
@@ -2486,10 +2487,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.8824</v>
+        <v>0.8823</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8252</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0.0572</v>
@@ -2498,7 +2499,7 @@
         <v>0.1586</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8824</v>
+        <v>0.8823</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2512,7 +2513,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>The header 'DESC_PRODUTO' suggests a product description, but the numeric content indicates it is not compatible with the 'Descrição' column.</t>
+          <t>The header 'DESC_PRODUTO' suggests a product description, but the numeric profile indicates mixed content, conflicting with the string nature of 'Descrição'.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -2524,7 +2525,7 @@
         <v>0.1586</v>
       </c>
       <c r="S36" t="n">
-        <v>0.8824</v>
+        <v>0.8823</v>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
@@ -2545,10 +2546,10 @@
         <v>0.7704</v>
       </c>
       <c r="F37" t="n">
-        <v>0.805</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0345</v>
+        <v>-0.0346</v>
       </c>
       <c r="H37" t="n">
         <v>0.84</v>
@@ -2633,10 +2634,10 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
-        <v>0.8</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="S38" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -2654,16 +2655,16 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>0.8115</v>
+        <v>0.8288</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.7986</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0187</v>
+        <v>0.0302</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2181</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2680,7 +2681,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The header 'NUMERO NF' conflicts semantically with the expected role of 'Nº ID fiscal 1', which is a tax ID, not a document ID.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -2689,10 +2690,10 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -2713,7 +2714,7 @@
         <v>0.8043</v>
       </c>
       <c r="F40" t="n">
-        <v>0.758</v>
+        <v>0.7581</v>
       </c>
       <c r="G40" t="n">
         <v>0.0462</v>
@@ -2736,7 +2737,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Região' based on header names and data evidence.</t>
+          <t>The candidate 'SINAL' does not semantically match 'Região', which represents geographical regions.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -2772,19 +2773,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.828</v>
+        <v>0.8278</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7922</v>
+        <v>0.7916</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0358</v>
+        <v>0.0362</v>
       </c>
       <c r="H41" t="n">
         <v>0.84</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8316</v>
+        <v>0.8315</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2798,7 +2799,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>The header 'TOTAL DO ITEM' aligns with the numeric nature and range of 'Val.Total NF', indicating it represents a total value.</t>
+          <t>The column 'TOTAL DO ITEM' has a compatible numeric type and no semantic conflicts, aligning well with the 'Val.Total NF'.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -2807,10 +2808,10 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
-        <v>0.9</v>
+        <v>0.9368</v>
       </c>
       <c r="S41" t="n">
-        <v>0.85</v>
+        <v>0.8313</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -2954,13 +2955,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.8065</v>
+        <v>0.8066</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8052</v>
+        <v>0.8044</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0013</v>
+        <v>0.0021</v>
       </c>
       <c r="H44" t="n">
         <v>0.84</v>
@@ -3007,22 +3008,28 @@
           <t>Isentas ICMS</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="C45" t="n">
+        <v>21</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
       <c r="E45" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8794</v>
+        <v>0.849</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.0735</v>
+        <v>0.0305</v>
       </c>
       <c r="H45" t="n">
         <v>0.7498</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3031,12 +3038,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate 'IND TRIB ICMS' has a high name confidence but conflicts semantically with the tax base role of 'Isentas ICMS'.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -3045,10 +3052,10 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="S45" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -3066,7 +3073,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>0.8968</v>
+        <v>0.8969</v>
       </c>
       <c r="F46" t="n">
         <v>0.8622</v>
@@ -3092,7 +3099,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a strong name match but lacks relevant data evidence, showing only two unique values.</t>
+          <t>The candidate 'IND TRIB ICMS' has a semantic header conflict with the expected role of 'Outras ICMS'.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
@@ -3125,10 +3132,10 @@
         <v>0.7948</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7899</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0049</v>
+        <v>0.005</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -3148,7 +3155,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax role of 'Valor ICAP'.</t>
+          <t>All candidates have semantic header conflicts with the expected tax role of 'Valor ICAP', indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -3181,7 +3188,7 @@
         <v>0.8048999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8015</v>
+        <v>0.8014</v>
       </c>
       <c r="G48" t="n">
         <v>0.0035</v>
@@ -3204,7 +3211,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP value, and no suitable mapping is supported by the data.</t>
+          <t>All candidates have a semantic header conflict with the ICEP value, indicating they do not represent the same business meaning.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -3303,10 +3310,10 @@
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8908</v>
+        <v>0.8907</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1092</v>
+        <v>0.1093</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -3428,7 +3435,7 @@
         <v>0.8274</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0558</v>
+        <v>0.0557</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -3448,7 +3455,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a strong name match but lacks supporting data evidence, as all values are zero.</t>
+          <t>The candidate 'IND TRIB IPI' has a high name confidence but lacks supporting data evidence, and the all-zero profile indicates no valid mapping.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -3487,10 +3494,10 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7651</v>
+        <v>0.765</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2349</v>
+        <v>0.235</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
@@ -3599,10 +3606,10 @@
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8237</v>
+        <v>0.8236</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1763</v>
+        <v>0.1764</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
@@ -3708,7 +3715,7 @@
         <v>0.7665999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0008</v>
+        <v>0.0009</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -3728,7 +3735,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>All candidate columns contain only zeros, indicating no relevant mapping to the 'Frete' column.</t>
+          <t>The 'Frete' column contains only zeros, making it incompatible with any candidate that has meaningful non-zero values.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -3740,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.75</v>
+        <v>0.7543</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -3758,7 +3765,7 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>0.8062</v>
+        <v>0.8061</v>
       </c>
       <c r="F58" t="n">
         <v>0.7995</v>
@@ -3784,7 +3791,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>All candidates are incompatible due to their content being non-numeric and the target column requiring numeric values.</t>
+          <t>All candidate columns contain non-numeric values, while 'Seguros' is entirely zero, indicating no valid mapping.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -3840,7 +3847,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Observações' based on header and data evidence.</t>
+          <t>The 'Observações' column contains strings that do not match any candidate's semantic role or content.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -3870,7 +3877,7 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7637</v>
       </c>
       <c r="F60" t="n">
         <v>0.7628</v>
@@ -3908,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -3932,7 +3939,7 @@
         <v>0.8149</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0083</v>
       </c>
       <c r="H61" t="n">
         <v>0.6901</v>
@@ -3961,10 +3968,10 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>0.8066</v>
+        <v>0.8</v>
       </c>
       <c r="S61" t="n">
-        <v>0.8066</v>
+        <v>0.8</v>
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -4014,7 +4021,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>The header 'DATA GL' closely matches the expected date format and has a high name confidence.</t>
+          <t>The column 'DATA GL' has a high name confidence and matches the datetime format of 'Data documento'.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
@@ -4026,7 +4033,7 @@
         <v>0.9</v>
       </c>
       <c r="S62" t="n">
-        <v>0.88</v>
+        <v>0.8722</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -4044,16 +4051,16 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>0.7271</v>
+        <v>0.7687</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7687</v>
+        <v>0.7437</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.0416</v>
+        <v>0.0249</v>
       </c>
       <c r="H63" t="n">
-        <v>0.264</v>
+        <v>0.2357</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -4079,10 +4086,10 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="n">
-        <v>0.7271</v>
+        <v>0.5</v>
       </c>
       <c r="S63" t="n">
-        <v>0.7271</v>
+        <v>0.5</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -4100,10 +4107,10 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>0.7612</v>
+        <v>0.7614</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7604</v>
+        <v>0.7605</v>
       </c>
       <c r="G64" t="n">
         <v>0.0008</v>
@@ -4159,10 +4166,10 @@
         <v>0.8071</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7948</v>
+        <v>0.7947</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0123</v>
+        <v>0.0124</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -4182,7 +4189,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Criado Manualmente' as all candidates are unrelated to a binary indicator.</t>
+          <t>No suitable candidate matches the semantic role of 'Criado Manualmente'.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -4274,19 +4281,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8016</v>
+        <v>0.8017</v>
       </c>
       <c r="F67" t="n">
         <v>0.8331</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0315</v>
+        <v>-0.0314</v>
       </c>
       <c r="H67" t="n">
         <v>0.73</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8016</v>
+        <v>0.8017</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4395,10 +4402,10 @@
         <v>0.8231000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8088</v>
+        <v>0.8089</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0143</v>
+        <v>0.0142</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -4418,7 +4425,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>The 'NUMERO NF' column has a strong numeric profile and matches the semantic role of 'Nº FCI' as an invoice number.</t>
+          <t>The 'NUMERO NF' column has a strong numeric profile and high name confidence, aligning well with the 'Nº FCI' semantic role.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -4448,10 +4455,10 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.798</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7795</v>
+        <v>0.7796</v>
       </c>
       <c r="G70" t="n">
         <v>0.0184</v>
@@ -4474,7 +4481,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No candidate column matches the semantic role of 'Condições pagamento' as they all pertain to product codes or identifiers.</t>
+          <t>No suitable candidate matches the semantic role of 'Condições pagamento' as all candidates are unrelated to payment conditions.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
@@ -4530,7 +4537,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates have semantic header conflicts with the expected role of 'Base ICAP', indicating incompatible tax-family contexts.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -4586,7 +4593,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax family for 'Aliquota ICAP'.</t>
+          <t>All candidates have semantic header conflicts with the expected tax family for 'Aliquota ICAP', indicating they do not represent the same business meaning.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -4616,13 +4623,13 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>0.7937</v>
+        <v>0.7944</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8175</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0239</v>
+        <v>-0.0247</v>
       </c>
       <c r="H73" t="n">
         <v>0.4751</v>
@@ -4651,10 +4658,10 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="n">
-        <v>0.7937</v>
+        <v>0.5</v>
       </c>
       <c r="S73" t="n">
-        <v>0.7937</v>
+        <v>0.5</v>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -4704,7 +4711,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' suggests a document number, conflicting with the item reference role of 'Item referência NF'.</t>
+          <t>The header 'NUMERO NF' closely matches the semantic role of 'Item referência NF' despite some numeric discrepancies.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -4713,10 +4720,10 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S74" t="n">
-        <v>0.6718</v>
+        <v>0.8205</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -4790,7 +4797,7 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>0.8247</v>
+        <v>0.8246</v>
       </c>
       <c r="F76" t="n">
         <v>0.7896</v>
@@ -4816,7 +4823,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of non-empty values in all columns.</t>
+          <t>No suitable candidate found due to lack of non-empty values in both the model and client columns.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -4872,7 +4879,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>The candidate 'COD_FIS_JUR' does not semantically match 'Domicílio fiscal' as it represents a different concept.</t>
+          <t>The candidate 'COD_FIS_JUR' has a numeric profile with no overlap in samples, conflicting with the string nature of 'Domicílio fiscal'.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -4902,7 +4909,7 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>0.7917</v>
+        <v>0.7916</v>
       </c>
       <c r="F78" t="n">
         <v>0.8581</v>
@@ -4937,10 +4944,10 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="n">
-        <v>0.7917</v>
+        <v>0.7916</v>
       </c>
       <c r="S78" t="n">
-        <v>0.7917</v>
+        <v>0.7916</v>
       </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
@@ -4970,7 +4977,7 @@
         <v>0.7874</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0334</v>
+        <v>0.0335</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -4990,7 +4997,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>The column 'NUMERO NF' has a strong numeric profile and aligns with the expected format for invoice numbers.</t>
+          <t>The column 'NUMERO NF' has a strong numeric profile and matches the semantic role of 'Nº de serviço' as an invoice number.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -5002,7 +5009,7 @@
         <v>0.9</v>
       </c>
       <c r="S79" t="n">
-        <v>0.85</v>
+        <v>0.8209</v>
       </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
@@ -5052,7 +5059,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>The header 'DESC_PRODUTO' suggests a description of the service, aligning with 'Texto breve serviço' despite the lack of row evidence.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -5061,10 +5068,10 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S80" t="n">
-        <v>0.7664</v>
+        <v>0.8017</v>
       </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
@@ -5082,16 +5089,16 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
+        <v>0.7657</v>
+      </c>
+      <c r="F81" t="n">
         <v>0.8135</v>
       </c>
-      <c r="F81" t="n">
-        <v>0.798</v>
-      </c>
       <c r="G81" t="n">
-        <v>0.0155</v>
+        <v>-0.0477</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -5108,7 +5115,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Origem do material' based on the provided evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -5117,10 +5124,10 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
@@ -5197,7 +5204,7 @@
         <v>0.793</v>
       </c>
       <c r="F83" t="n">
-        <v>0.778</v>
+        <v>0.7779</v>
       </c>
       <c r="G83" t="n">
         <v>0.0151</v>
@@ -5253,10 +5260,10 @@
         <v>0.74</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7366</v>
+        <v>0.7365</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0034</v>
+        <v>0.0035</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -5276,7 +5283,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>All candidates have semantic-role conflicts and the evidence is insufficient to support a mapping.</t>
+          <t>All candidate columns have semantic conflicts or do not match the expected numeric type for 'Mont.líquido frete', which should represent a monetary value.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -5288,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.7537</v>
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
@@ -5332,7 +5339,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts or lack relevant evidence to support a mapping.</t>
+          <t>No suitable candidate due to semantic header conflicts and all-zero evidence.</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -5344,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.7453</v>
+        <v>0.7621</v>
       </c>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
@@ -5362,13 +5369,13 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>0.8169</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="F86" t="n">
         <v>0.8228</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.0059</v>
+        <v>-0.0058</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -5397,10 +5404,10 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="n">
-        <v>0.8169</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="S86" t="n">
-        <v>0.8169</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -5424,7 +5431,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.8881</v>
+        <v>0.8882</v>
       </c>
       <c r="F87" t="n">
         <v>0.8621</v>
@@ -5436,7 +5443,7 @@
         <v>0.7375</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8881</v>
+        <v>0.8882</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -5459,10 +5466,10 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="n">
-        <v>0.8881</v>
+        <v>0.8882</v>
       </c>
       <c r="S87" t="n">
-        <v>0.8881</v>
+        <v>0.8882</v>
       </c>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
@@ -5512,7 +5519,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a high name confidence but conflicts semantically with the expected role of 'Base Reduzida ICMS'.</t>
+          <t>The candidate 'IND TRIB ICMS' has a high name confidence and matches the integer type of 'Base Reduzida ICMS', despite the lack of distinctive sample overlap.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -5521,10 +5528,10 @@
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="S88" t="n">
-        <v>0.5</v>
+        <v>0.8587</v>
       </c>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
@@ -5568,7 +5575,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type, indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -5624,7 +5631,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>All candidates conflict semantically with the expected tax role of 'Isentas ICAP'.</t>
+          <t>All candidates have a semantic header conflict with the expected tax family and provide no valid row evidence.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -5680,7 +5687,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and do not match the expected role of 'Outras ICAP'.</t>
+          <t>All candidates have semantic header conflicts with the original column, and the evidence does not support a mapping.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -5736,7 +5743,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
+          <t>All candidates have semantic header conflicts with the expected role of 'Base Reduzida ICAP'.</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -5792,7 +5799,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type.</t>
+          <t>All candidates have semantic header conflicts with the expected tax type, and there is no supporting data evidence.</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -5848,7 +5855,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
+          <t>All candidates have semantic header conflicts with the ICEP base, and no distinctive row evidence supports a mapping.</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -5904,7 +5911,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP tax type, indicating incompatible mappings.</t>
+          <t>All candidates conflict with the tax-family context of ICEP.</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -5960,7 +5967,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP tax situation, indicating incompatible mappings.</t>
+          <t>All candidates have a semantic header conflict with the tax-family context, indicating they do not match the intended meaning of 'Isentas ICEP'.</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -6016,7 +6023,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No suitable candidate due to semantic header conflicts and lack of distinctive sample evidence.</t>
+          <t>No suitable candidate due to semantic header conflicts and lack of distinctive row evidence.</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -6046,13 +6053,13 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.787</v>
       </c>
       <c r="F98" t="n">
-        <v>0.7827</v>
+        <v>0.7831</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0041</v>
+        <v>0.0039</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -6072,7 +6079,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the ICEP field, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the ICEP role, indicating incompatible tax-family contexts.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -6102,10 +6109,10 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>0.7772</v>
+        <v>0.7771</v>
       </c>
       <c r="F99" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7766</v>
       </c>
       <c r="G99" t="n">
         <v>0.0005</v>
@@ -6158,7 +6165,7 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
-        <v>0.7997</v>
+        <v>0.7998</v>
       </c>
       <c r="F100" t="n">
         <v>0.7864</v>
@@ -6184,7 +6191,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and no valid row evidence.</t>
+          <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -6296,7 +6303,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax role, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates have semantic header conflicts and do not match the expected tax base for ICSP.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -6352,7 +6359,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the tax-family context, and the evidence is insufficient to support a mapping.</t>
+          <t>All candidates conflict with the tax-family context and provide no valid evidence.</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -6408,7 +6415,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the original column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -6438,7 +6445,7 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
-        <v>0.7859</v>
+        <v>0.786</v>
       </c>
       <c r="F105" t="n">
         <v>0.7756999999999999</v>
@@ -6497,10 +6504,10 @@
         <v>0.803</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8103</v>
+        <v>0.8102</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.0073</v>
+        <v>-0.0072</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -6550,13 +6557,13 @@
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7929</v>
       </c>
       <c r="F107" t="n">
         <v>0.7879</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0049</v>
+        <v>0.005</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -6576,7 +6583,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-matching data types and values, with the only candidate being a date format.</t>
+          <t>No suitable candidate found due to all-zero evidence in the model column.</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -6588,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>0.7927999999999999</v>
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
@@ -6606,13 +6613,13 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
+        <v>0.7836</v>
+      </c>
+      <c r="F108" t="n">
         <v>0.7875</v>
       </c>
-      <c r="F108" t="n">
-        <v>0.7839</v>
-      </c>
       <c r="G108" t="n">
-        <v>0.0037</v>
+        <v>-0.0039</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -6632,7 +6639,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating a lack of semantic alignment.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -6641,10 +6648,10 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>0.7836</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>0.7836</v>
       </c>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
@@ -6688,7 +6695,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>All candidate columns have significant semantic conflicts or lack relevant data evidence.</t>
+          <t>No suitable candidate matches the semantic role of 'Valor DIF_ALIQ' as all candidates have conflicting roles or irrelevant data.</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -6718,13 +6725,13 @@
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="n">
-        <v>0.8072</v>
+        <v>0.8079</v>
       </c>
       <c r="F110" t="n">
-        <v>0.8057</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0014</v>
+        <v>0.0021</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -6744,7 +6751,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-zero values, while the source column is entirely zero, indicating no semantic match.</t>
+          <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating no compatible mapping.</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -6774,13 +6781,13 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>0.8091</v>
+        <v>0.8097</v>
       </c>
       <c r="F111" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8081</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0021</v>
+        <v>0.0016</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -6800,7 +6807,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No suitable candidate found; all candidates have conflicting semantic roles or lack relevant data.</t>
+          <t>All candidate columns contain non-numeric or empty data, while 'Outras DIF_ALIQ' is entirely zero.</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -6812,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>0.8091</v>
+        <v>0.8097</v>
       </c>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
@@ -6830,13 +6837,13 @@
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
-        <v>0.7781</v>
+        <v>0.7779</v>
       </c>
       <c r="F112" t="n">
-        <v>0.7779</v>
+        <v>0.7776</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -6856,7 +6863,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>All candidate columns contain only zeros or are semantically unrelated to the 'Base Reduzida DIF_ALIQ'.</t>
+          <t>All candidate columns have semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -6883,19 +6890,13 @@
           <t>Base ICMS_FECP</t>
         </is>
       </c>
-      <c r="C113" t="n">
-        <v>21</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>IND TRIB ICMS</t>
-        </is>
-      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="n">
-        <v>0.8562</v>
+        <v>0.8563</v>
       </c>
       <c r="F113" t="n">
-        <v>0.8273</v>
+        <v>0.8274</v>
       </c>
       <c r="G113" t="n">
         <v>0.0289</v>
@@ -6904,7 +6905,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8562</v>
+        <v>0</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -6913,12 +6914,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a high name confidence but does not match the expected numeric characteristics of 'Base ICMS_FECP', which is all zeros.</t>
+          <t>All candidates have significant semantic conflicts or do not match the expected numeric characteristics of 'Base ICMS_FECP'.</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -6930,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>0.8562</v>
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
@@ -6945,19 +6946,13 @@
           <t>Aliquota ICMS_FECP</t>
         </is>
       </c>
-      <c r="C114" t="n">
-        <v>21</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>IND TRIB ICMS</t>
-        </is>
-      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="n">
-        <v>0.855</v>
+        <v>0.8552</v>
       </c>
       <c r="F114" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8272</v>
       </c>
       <c r="G114" t="n">
         <v>0.028</v>
@@ -6966,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>0.855</v>
+        <v>0</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6975,12 +6970,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a high name confidence but does not match the all-zero evidence of the source column.</t>
+          <t>All candidates have conflicting semantic roles or insufficient evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -6992,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>0.855</v>
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
@@ -7007,28 +7002,22 @@
           <t>Valor ICMS_FECP</t>
         </is>
       </c>
-      <c r="C115" t="n">
-        <v>21</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>IND TRIB ICMS</t>
-        </is>
-      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
+        <v>0.7909</v>
+      </c>
+      <c r="F115" t="n">
         <v>0.8588</v>
       </c>
-      <c r="F115" t="n">
-        <v>0.8297</v>
-      </c>
       <c r="G115" t="n">
-        <v>0.0291</v>
+        <v>-0.0679</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0.8588</v>
+        <v>0</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7037,12 +7026,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a high name confidence but does not match the all-zero evidence of 'Valor ICMS_FECP'.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -7051,10 +7040,10 @@
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>0.7909</v>
       </c>
       <c r="S115" t="n">
-        <v>0.8588</v>
+        <v>0.7909</v>
       </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
@@ -7069,14 +7058,8 @@
           <t>Isentas ICMS_FECP</t>
         </is>
       </c>
-      <c r="C116" t="n">
-        <v>21</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>IND TRIB ICMS</t>
-        </is>
-      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="n">
         <v>0.853</v>
       </c>
@@ -7090,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>0.853</v>
+        <v>0</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -7099,12 +7082,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB ICMS' has a strong name match but lacks relevant data evidence, as it contains non-zero values while the source column is all zeros.</t>
+          <t>All candidates have conflicting semantic roles or insufficient evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -7116,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>0.853</v>
+        <v>0</v>
       </c>
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
@@ -7134,13 +7117,13 @@
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
-        <v>0.8659</v>
+        <v>0.8647</v>
       </c>
       <c r="F117" t="n">
-        <v>0.8351</v>
+        <v>0.831</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0308</v>
+        <v>0.0337</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -7196,7 +7179,7 @@
         <v>0.803</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0274</v>
+        <v>0.0275</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -7278,7 +7261,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' has a strong name match but lacks supporting data evidence, as all values are non-informative zeros.</t>
+          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -7290,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>0.8535</v>
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
@@ -7390,7 +7373,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context of 'Isentas COFINS'.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended meaning of 'Isentas COFINS'.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -7426,7 +7409,7 @@
         <v>0.8202</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0074</v>
+        <v>0.0073</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -7446,7 +7429,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or lack relevant data evidence.</t>
+          <t>No suitable candidate found due to all candidates having semantic conflicts or insufficient evidence.</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -7482,7 +7465,7 @@
         <v>0.7734</v>
       </c>
       <c r="G123" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -7502,7 +7485,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the COFINS tax family, indicating incompatible mappings.</t>
+          <t>All candidates have semantic header conflicts with the required tax base for COFINS.</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -7558,7 +7541,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context of 'Isentas PIS'.</t>
+          <t>All candidates have semantic header conflicts with the PIS tax family and provide no relevant row evidence.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -7614,7 +7597,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or lack relevant data evidence.</t>
+          <t>No suitable candidate due to tax-family conflicts and all-zero evidence.</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -7670,7 +7653,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the PIS tax type, indicating incompatible mappings.</t>
+          <t>All candidates have semantic conflicts with the PIS tax type, making them incompatible.</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -7782,7 +7765,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of ISS, providing no valid mapping.</t>
+          <t>All candidates conflict with the tax-family of the target column.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -7838,7 +7821,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of 'Base ISS' and provide no relevant mapping evidence.</t>
+          <t>All candidates conflict with the tax-family of the target column, and no suitable mapping is supported by the data.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -7850,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
@@ -7894,7 +7877,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the expected tax type.</t>
+          <t>All candidates have semantic header conflicts with the tax family, making them incompatible.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -7950,7 +7933,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family of 'Valor ISS' and provide no relevant mapping evidence.</t>
+          <t>All candidates conflict with the tax-family of 'Valor ISS' and provide no relevant evidence.</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -8006,7 +7989,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with the 'Isentas ISS' column, indicating incompatible semantic roles.</t>
+          <t>All candidates conflict with the tax-family context of 'Isentas ISS'.</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
@@ -8062,7 +8045,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>All candidates conflict with the tax-family context of 'Outras ISS'.</t>
+          <t>All candidates have a tax-family conflict with the ISS column, indicating incompatible semantic roles.</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
@@ -8118,7 +8101,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the target column, indicating incompatible tax roles.</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
@@ -8174,7 +8157,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>All candidate columns contain zero values, providing no evidence for a valid mapping.</t>
+          <t>All candidates have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
@@ -8204,13 +8187,13 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
+        <v>0.8093</v>
+      </c>
+      <c r="F136" t="n">
         <v>0.8145</v>
       </c>
-      <c r="F136" t="n">
-        <v>0.802</v>
-      </c>
       <c r="G136" t="n">
-        <v>0.0125</v>
+        <v>-0.0052</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -8230,7 +8213,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts or lack relevant evidence to support a mapping.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
@@ -8242,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>0</v>
+        <v>0.8093</v>
       </c>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
@@ -8286,7 +8269,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-distinctive or zero-only values, lacking sufficient evidence for a valid mapping.</t>
+          <t>All candidate columns have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
@@ -8428,13 +8411,13 @@
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
+        <v>0.7835</v>
+      </c>
+      <c r="F140" t="n">
         <v>0.797</v>
       </c>
-      <c r="F140" t="n">
-        <v>0.7822</v>
-      </c>
       <c r="G140" t="n">
-        <v>0.0149</v>
+        <v>-0.0135</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -8454,7 +8437,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>All candidate columns have significant semantic conflicts or lack relevant data evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -8463,10 +8446,10 @@
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>0.7835</v>
       </c>
       <c r="S140" t="n">
-        <v>0.797</v>
+        <v>0.7835</v>
       </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
@@ -8490,7 +8473,7 @@
         <v>0.8531</v>
       </c>
       <c r="G141" t="n">
-        <v>0.016</v>
+        <v>0.0161</v>
       </c>
       <c r="H141" t="n">
         <v>0.7375</v>
@@ -8622,7 +8605,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the required tax role, indicating they do not match the 'Aliquota ICMS_ST' column.</t>
+          <t>All candidates have semantic conflicts with the tax role of 'Aliquota ICMS_ST' and do not provide relevant mapping evidence.</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
@@ -8678,7 +8661,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or do not match the expected tax base for ICMS_ST.</t>
+          <t>All candidates have semantic header conflicts or do not match the expected tax situation for ICMS_ST.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
@@ -8714,7 +8697,7 @@
         <v>0.8069</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0062</v>
+        <v>0.0063</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -8734,7 +8717,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or insufficient evidence to support a mapping.</t>
+          <t>All candidates have semantic header conflicts or do not match the expected tax base role.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
@@ -8767,7 +8750,7 @@
         <v>0.779</v>
       </c>
       <c r="F146" t="n">
-        <v>0.7786</v>
+        <v>0.7785</v>
       </c>
       <c r="G146" t="n">
         <v>0.0004</v>
@@ -8790,7 +8773,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts with the required tax base role, making them incompatible.</t>
+          <t>All candidates have semantic header conflicts and do not align with the expected role of 'Base Reduzida ICMS_ST'.</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
@@ -8802,7 +8785,7 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
@@ -8820,10 +8803,10 @@
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
-        <v>0.7997</v>
+        <v>0.7998</v>
       </c>
       <c r="F147" t="n">
-        <v>0.8015</v>
+        <v>0.8016</v>
       </c>
       <c r="G147" t="n">
         <v>-0.0018</v>
@@ -8876,10 +8859,10 @@
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="n">
-        <v>0.7684</v>
+        <v>0.7685</v>
       </c>
       <c r="F148" t="n">
-        <v>0.766</v>
+        <v>0.7661</v>
       </c>
       <c r="G148" t="n">
         <v>0.0024</v>
@@ -8914,7 +8897,7 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>0.7684</v>
+        <v>0.7685</v>
       </c>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
@@ -8997,7 +8980,7 @@
         <v>0.0039</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>0.1633</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
@@ -9014,7 +8997,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the time format and semantic role of the 'Criado às:' column.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
@@ -9023,10 +9006,10 @@
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S150" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
@@ -9047,10 +9030,10 @@
         <v>0.8161</v>
       </c>
       <c r="F151" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.8048</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0112</v>
+        <v>0.0113</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -9070,7 +9053,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>No suitable candidate exists as all client columns are empty or unrelated to 'Exercício'.</t>
+          <t>All candidate columns are empty, providing no evidence for a mapping.</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
@@ -9126,7 +9109,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>All candidate columns contain only zeros or non-distinctive values, lacking any relevant mapping evidence.</t>
+          <t>No suitable candidate matches the semantic role of 'Redução' as all candidates are unrelated.</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
@@ -9156,7 +9139,7 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="n">
-        <v>0.7453</v>
+        <v>0.7454</v>
       </c>
       <c r="F153" t="n">
         <v>0.7372</v>
@@ -9209,14 +9192,8 @@
           <t>Cód.domicílio fiscal</t>
         </is>
       </c>
-      <c r="C154" t="n">
-        <v>6</v>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>COD_FIS_JUR</t>
-        </is>
-      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
         <v>0.8545</v>
       </c>
@@ -9230,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>0.8545</v>
+        <v>0</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -9239,32 +9216,24 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>The candidate 'COD_FIS_JUR' has a high name confidence but lacks any row evidence, making it unsuitable for mapping.</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>ibge_municipality</t>
-        </is>
-      </c>
-      <c r="N154" t="n">
-        <v>0</v>
-      </c>
+          <t>All candidate columns have empty or non-informative profiles, providing no evidence for a mapping.</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
+      <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="n">
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>0.8545</v>
+        <v>0</v>
       </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
@@ -9308,7 +9277,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of evidence and empty data.</t>
+          <t>No viable candidates match the semantic role of 'Domicílio Fiscal' as all candidates are unrelated identifiers.</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
@@ -9394,16 +9363,16 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
+        <v>0.7703</v>
+      </c>
+      <c r="F157" t="n">
         <v>0.8221000000000001</v>
       </c>
-      <c r="F157" t="n">
-        <v>0.8033</v>
-      </c>
       <c r="G157" t="n">
-        <v>0.0188</v>
+        <v>-0.0518</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -9420,7 +9389,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'ID do consumidor final' based on name and data evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
@@ -9429,10 +9398,10 @@
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
@@ -9515,7 +9484,7 @@
         <v>0.8556</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8017</v>
+        <v>0.8018</v>
       </c>
       <c r="G159" t="n">
         <v>0.0538</v>
@@ -9538,7 +9507,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' has a high name confidence and matches the expected numeric format for invoice numbers.</t>
+          <t>The candidate 'NUMERO NF' has a high numeric fraction and matches the semantic role of 'Nº NF-e dos serviços'.</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
@@ -9574,7 +9543,7 @@
         <v>0.8259</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0012</v>
+        <v>0.0013</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -9594,7 +9563,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the empty evidence of the model column.</t>
+          <t>All candidate columns have insufficient evidence and the model column is empty.</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
@@ -9606,7 +9575,7 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>0.7804</v>
+        <v>0.7829</v>
       </c>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
@@ -9624,13 +9593,13 @@
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
-        <v>0.8437</v>
+        <v>0.8438</v>
       </c>
       <c r="F161" t="n">
         <v>0.8113</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0324</v>
+        <v>0.0325</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -9650,7 +9619,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>The candidate columns contain no relevant data, making it impossible to establish a mapping despite the name confidence.</t>
+          <t>The candidate 'ORGANIZACAO' has a high name confidence but no relevant data evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
@@ -9662,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>0.8437</v>
+        <v>0.8438</v>
       </c>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
@@ -9680,13 +9649,13 @@
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="n">
-        <v>0.7992</v>
+        <v>0.7991</v>
       </c>
       <c r="F162" t="n">
         <v>0.788</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0112</v>
+        <v>0.0111</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -9706,7 +9675,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-relevant data types or zero values, lacking any meaningful mapping to 'Despesas'.</t>
+          <t>All candidate columns contain non-relevant data types or all-zero values, lacking any semantic match.</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
@@ -9736,13 +9705,13 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="n">
-        <v>0.8243</v>
+        <v>0.8242</v>
       </c>
       <c r="F163" t="n">
-        <v>0.7875</v>
+        <v>0.7874</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0368</v>
+        <v>0.0369</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -9762,7 +9731,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>The candidate columns contain no relevant data to support a mapping to 'Centro custo'.</t>
+          <t>The 'Centro custo' column is empty with no valid data to support a mapping.</t>
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
@@ -9792,7 +9761,7 @@
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="n">
-        <v>0.7829</v>
+        <v>0.783</v>
       </c>
       <c r="F164" t="n">
         <v>0.7726</v>
@@ -9818,7 +9787,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of non-empty values in the target column.</t>
+          <t>All candidate columns have insufficient evidence and do not match the expected content for 'Municipio Fim'.</t>
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
@@ -9848,10 +9817,10 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
-        <v>0.7839</v>
+        <v>0.784</v>
       </c>
       <c r="F165" t="n">
-        <v>0.7814</v>
+        <v>0.7815</v>
       </c>
       <c r="G165" t="n">
         <v>0.0025</v>
@@ -9874,7 +9843,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>All candidate columns have semantic conflicts or lack relevant data evidence.</t>
+          <t>No suitable candidate found due to lack of evidence and semantic conflicts.</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
@@ -9913,7 +9882,7 @@
         <v>0.8734</v>
       </c>
       <c r="F166" t="n">
-        <v>0.8619</v>
+        <v>0.8618</v>
       </c>
       <c r="G166" t="n">
         <v>0.0116</v>
@@ -9936,7 +9905,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>The name 'COD_PRODUTO' closely matches the semantic role of 'Código do Item' despite the absence of row evidence.</t>
+          <t>The column 'COD_PRODUTO' has a high name confidence and contains numeric values that align with item codes, making it a suitable match for 'Código do Item'.</t>
         </is>
       </c>
       <c r="M166" t="inlineStr"/>
@@ -9975,10 +9944,10 @@
         <v>0.8369</v>
       </c>
       <c r="F167" t="n">
-        <v>0.7693</v>
+        <v>0.7694</v>
       </c>
       <c r="G167" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0675</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -9998,7 +9967,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>The column 'NUMERO NF' has a strong numeric profile and matches the semantic role of 'Número do NFC-e SAT'.</t>
+          <t>The candidate 'NUMERO NF' has a strong numeric profile and matches the semantic role of 'Número do NFC-e SAT'.</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
@@ -10007,7 +9976,7 @@
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S167" t="n">
         <v>0.8369</v>
@@ -10028,13 +9997,13 @@
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
-        <v>0.7269</v>
+        <v>0.7264</v>
       </c>
       <c r="F168" t="n">
-        <v>0.8075</v>
+        <v>0.8081</v>
       </c>
       <c r="G168" t="n">
-        <v>-0.0806</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="H168" t="n">
         <v>0.7937</v>
@@ -10087,10 +10056,10 @@
         <v>0.8421</v>
       </c>
       <c r="F169" t="n">
-        <v>0.8176</v>
+        <v>0.8177</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0245</v>
+        <v>0.0244</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -10196,7 +10165,7 @@
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="n">
-        <v>0.8003</v>
+        <v>0.8002</v>
       </c>
       <c r="F171" t="n">
         <v>0.7985</v>
@@ -10222,7 +10191,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
@@ -10252,7 +10221,7 @@
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
-        <v>0.8207</v>
+        <v>0.8208</v>
       </c>
       <c r="F172" t="n">
         <v>0.8008</v>
@@ -10278,7 +10247,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts or insufficient evidence to support a mapping.</t>
+          <t>No suitable candidate due to semantic header conflicts and lack of distinctive row evidence.</t>
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
@@ -10334,7 +10303,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with the source column, indicating incompatible meanings.</t>
+          <t>All candidates have semantic header conflicts and do not match the expected tax situation.</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
@@ -10452,7 +10421,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' suggests an invoice number, but the numeric profile and sample values do not align with the expected format of a 'Numero do Pedido'.</t>
+          <t>The header 'NUMERO NF' suggests a document number, but the numeric profile indicates a mismatch with the 'Numero do Pedido' which is more varied and includes non-numeric values.</t>
         </is>
       </c>
       <c r="M175" t="inlineStr"/>
@@ -10464,7 +10433,7 @@
         <v>0.5</v>
       </c>
       <c r="S175" t="n">
-        <v>0.5</v>
+        <v>0.831</v>
       </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
@@ -10488,19 +10457,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8643</v>
       </c>
       <c r="F176" t="n">
-        <v>0.7972</v>
+        <v>0.797</v>
       </c>
       <c r="G176" t="n">
-        <v>0.0672</v>
+        <v>0.0673</v>
       </c>
       <c r="H176" t="n">
         <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8643</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -10570,7 +10539,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the target column, indicating incompatible tax-family roles.</t>
+          <t>All candidates have semantic header conflicts with the required tax situation, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
@@ -10603,7 +10572,7 @@
         <v>0.7831</v>
       </c>
       <c r="F178" t="n">
-        <v>0.7748</v>
+        <v>0.7749</v>
       </c>
       <c r="G178" t="n">
         <v>0.0083</v>
@@ -10626,7 +10595,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax classification, making them incompatible.</t>
+          <t>All candidates have semantic header conflicts with the required tax classification.</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
@@ -10688,7 +10657,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>The column 'NUMERO NF' closely matches the expected format and type for invoice document numbers, with high numeric consistency.</t>
+          <t>The column 'NUMERO NF' closely matches the semantic role of 'Nº documento' with high numeric consistency and a strong name match.</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
@@ -10718,10 +10687,10 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>0.751</v>
+        <v>0.7511</v>
       </c>
       <c r="F180" t="n">
-        <v>0.8505</v>
+        <v>0.8506</v>
       </c>
       <c r="G180" t="n">
         <v>-0.09950000000000001</v>
@@ -10806,7 +10775,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>The 'FORNECEDOR' column has a strong name match and informative data, indicating it likely represents the 'Exportador' role.</t>
+          <t>The 'FORNECEDOR' column has a strong name match and informative data, indicating it likely corresponds to the 'Exportador' role.</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
@@ -10839,10 +10808,10 @@
         <v>0.7905</v>
       </c>
       <c r="F182" t="n">
-        <v>0.7881</v>
+        <v>0.788</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0024</v>
+        <v>0.0025</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -11095,7 +11064,7 @@
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="n">
-        <v>0.8021</v>
+        <v>0.8</v>
       </c>
       <c r="S186" t="n">
         <v>0.8021</v>
@@ -11122,7 +11091,7 @@
         <v>0.7849</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0167</v>
+        <v>0.0168</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -11240,13 +11209,13 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0.9036</v>
+        <v>0.9035</v>
       </c>
       <c r="F189" t="n">
         <v>0.8623</v>
       </c>
       <c r="G189" t="n">
-        <v>0.0414</v>
+        <v>0.0413</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -11266,7 +11235,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>The header 'NUM_ITEM' suggests an item identifier, but the data is all zeros, indicating it does not provide meaningful evidence.</t>
+          <t>The header 'NUM_ITEM' suggests an item identifier, but the data is all zeros, indicating it may not be a valid mapping.</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
@@ -11278,7 +11247,7 @@
         <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>0.9036</v>
+        <v>0.9035</v>
       </c>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
@@ -11322,7 +11291,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>All candidate columns are empty or lack relevant data to support a mapping.</t>
+          <t>All candidate columns are empty or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
@@ -11334,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>0.7536</v>
+        <v>0</v>
       </c>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
@@ -11537,7 +11506,7 @@
         <v>0.8927</v>
       </c>
       <c r="F194" t="n">
-        <v>0.8122</v>
+        <v>0.8124</v>
       </c>
       <c r="G194" t="n">
         <v>0.0804</v>
@@ -11560,7 +11529,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>The candidate 'IND TRIB IPI' closely matches the tax type 'Tipo de Imposto IPI' with high name confidence and consistent numeric values.</t>
+          <t>The candidate 'IND TRIB IPI' has a high name confidence and matches the IPI tax type despite some numeric discrepancies.</t>
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
@@ -11602,7 +11571,7 @@
         <v>0.8105</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0648</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="H195" t="n">
         <v>0.225</v>
@@ -11622,7 +11591,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>The candidate 'NUM_ITEM' has a high name confidence but does not match the expected item ID role.</t>
+          <t>The header 'NUM_ITEM' suggests an item number, but the numeric values and profile do not align with the expected format for invoice item numbers.</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
@@ -11658,10 +11627,10 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>0.8824</v>
+        <v>0.8823</v>
       </c>
       <c r="F196" t="n">
-        <v>0.8252</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="G196" t="n">
         <v>0.0572</v>
@@ -11670,7 +11639,7 @@
         <v>0.7981</v>
       </c>
       <c r="I196" t="n">
-        <v>0.8824</v>
+        <v>0.8823</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -11684,7 +11653,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>The column 'DESC_PRODUTO' has a high name confidence and a strong profile similarity, indicating it likely represents product descriptions.</t>
+          <t>The header 'DESC_PRODUTO' closely matches 'Descrição' and the sample values indicate product descriptions.</t>
         </is>
       </c>
       <c r="M196" t="inlineStr"/>
@@ -11714,13 +11683,13 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="n">
-        <v>0.7229</v>
+        <v>0.7242</v>
       </c>
       <c r="F197" t="n">
-        <v>0.8365</v>
+        <v>0.8391</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.1136</v>
+        <v>-0.1149</v>
       </c>
       <c r="H197" t="n">
         <v>0.84</v>
@@ -11858,7 +11827,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>The header 'COD_MEDIDA' aligns semantically with 'Unidade de medida' and has no conflicting evidence.</t>
+          <t>The header 'COD_MEDIDA' aligns semantically with 'Unidade de medida' and has no conflicting roles.</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
@@ -12026,7 +11995,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>The candidate 'LOCATION' has low name confidence and no relevant data overlap with the expected municipality values.</t>
+          <t>The candidate 'LOCATION' does not semantically match 'Município do Local de Início' as it lacks relevant municipal data.</t>
         </is>
       </c>
       <c r="M202" t="inlineStr"/>
@@ -12115,7 +12084,7 @@
         <v>0.804</v>
       </c>
       <c r="F204" t="n">
-        <v>0.7748</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="G204" t="n">
         <v>0.0293</v>
@@ -12174,7 +12143,7 @@
         <v>0.7997</v>
       </c>
       <c r="G205" t="n">
-        <v>0.0378</v>
+        <v>0.0377</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -12222,28 +12191,28 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NUMERO NF</t>
+          <t>TIPO DOC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>0.8143</v>
+        <v>0.8336</v>
       </c>
       <c r="F206" t="n">
+        <v>0.8183</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+      <c r="I206" t="n">
         <v>0.8336</v>
       </c>
-      <c r="G206" t="n">
-        <v>-0.0194</v>
-      </c>
-      <c r="H206" t="n">
-        <v>0</v>
-      </c>
-      <c r="I206" t="n">
-        <v>0.8143</v>
-      </c>
       <c r="J206" t="inlineStr">
         <is>
           <t>data</t>
@@ -12256,7 +12225,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>The header 'NUMERO NF' closely matches the semantic role of 'Nº doc.importação' and has strong numeric evidence.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M206" t="inlineStr"/>
@@ -12265,10 +12234,10 @@
       <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
       <c r="R206" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S206" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr"/>
@@ -12318,7 +12287,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>The header 'PRECO UNITARIO' closely aligns with 'Preço líq.' in terms of name and numeric profile, despite some differences in sample values.</t>
+          <t>The name 'PRECO UNITARIO' suggests a unit price, while 'Preço líq.' indicates a net price, leading to a semantic conflict.</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
@@ -12351,10 +12320,10 @@
         <v>0.7917</v>
       </c>
       <c r="F208" t="n">
-        <v>0.7693</v>
+        <v>0.7692</v>
       </c>
       <c r="G208" t="n">
-        <v>0.0224</v>
+        <v>0.0225</v>
       </c>
       <c r="H208" t="n">
         <v>0.84</v>
@@ -12404,13 +12373,13 @@
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="n">
-        <v>0.8511</v>
+        <v>0.851</v>
       </c>
       <c r="F209" t="n">
         <v>0.8449</v>
       </c>
       <c r="G209" t="n">
-        <v>0.0062</v>
+        <v>0.0061</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -12430,7 +12399,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>The candidate 'NUMERO NF' is numeric while 'NF/NF-e do serviço' is a string, indicating a semantic mismatch.</t>
+          <t>The candidate 'NUMERO NF' is numeric and does not match the string type of 'NF/NF-e do serviço'.</t>
         </is>
       </c>
       <c r="M209" t="inlineStr"/>
@@ -12466,19 +12435,19 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>0.8629</v>
+        <v>0.8627</v>
       </c>
       <c r="F210" t="n">
-        <v>0.7883</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="G210" t="n">
-        <v>0.0745</v>
+        <v>0.074</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>0.8629</v>
+        <v>0.8627</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -12492,7 +12461,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>The column 'NUMERO NF' has a high numeric fraction and matches the expected format for invoice numbers.</t>
+          <t>The candidate 'NUMERO NF' has a high name confidence and a substantial non-empty count, indicating it likely represents the invoice number.</t>
         </is>
       </c>
       <c r="M210" t="inlineStr"/>
@@ -12504,7 +12473,7 @@
         <v>1</v>
       </c>
       <c r="S210" t="n">
-        <v>0.8629</v>
+        <v>0.8627</v>
       </c>
       <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr"/>
@@ -12584,13 +12553,13 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
-        <v>0.8308</v>
+        <v>0.8307</v>
       </c>
       <c r="F212" t="n">
         <v>0.7799</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0509</v>
+        <v>0.0508</v>
       </c>
       <c r="H212" t="n">
         <v>0.4406</v>
@@ -12622,7 +12591,7 @@
         <v>0.4406</v>
       </c>
       <c r="S212" t="n">
-        <v>0.8308</v>
+        <v>0.8307</v>
       </c>
       <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr"/>
@@ -12640,13 +12609,13 @@
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="n">
-        <v>0.8137</v>
+        <v>0.8136</v>
       </c>
       <c r="F213" t="n">
         <v>0.8086</v>
       </c>
       <c r="G213" t="n">
-        <v>0.0051</v>
+        <v>0.005</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -12666,7 +12635,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>All candidate columns contain no relevant data, making mapping impossible.</t>
+          <t>No suitable candidate found due to lack of evidence and all candidates being unrelated to 'Cód Transportadora'.</t>
         </is>
       </c>
       <c r="M213" t="inlineStr"/>
@@ -12705,10 +12674,10 @@
         <v>0.98</v>
       </c>
       <c r="F214" t="n">
-        <v>0.7887</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="G214" t="n">
-        <v>0.1913</v>
+        <v>0.1912</v>
       </c>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
@@ -12752,10 +12721,10 @@
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="n">
-        <v>0.782</v>
+        <v>0.7819</v>
       </c>
       <c r="F215" t="n">
-        <v>0.8137</v>
+        <v>0.8136</v>
       </c>
       <c r="G215" t="n">
         <v>-0.0317</v>
@@ -12787,10 +12756,10 @@
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
       <c r="R215" t="n">
-        <v>0.782</v>
+        <v>0.5</v>
       </c>
       <c r="S215" t="n">
-        <v>0.782</v>
+        <v>0.75</v>
       </c>
       <c r="T215" t="inlineStr"/>
       <c r="U215" t="inlineStr"/>
@@ -12840,7 +12809,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>The header 'IND TRIB ICMS' suggests a tax indicator for ICMS, but the numeric profile indicates it is an integer with limited unique values, conflicting with the expected string format of 'Texto ICMS'.</t>
+          <t>The header 'IND TRIB ICMS' suggests a tax indicator for ICMS, but the numeric values and type do not align with the expected text format of 'Texto ICMS'.</t>
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
@@ -12876,19 +12845,19 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>0.8806</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="F217" t="n">
         <v>0.8249</v>
       </c>
       <c r="G217" t="n">
-        <v>0.0557</v>
+        <v>0.0556</v>
       </c>
       <c r="H217" t="n">
         <v>0.75</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8806</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -12911,10 +12880,10 @@
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="inlineStr"/>
       <c r="R217" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="S217" t="n">
-        <v>0.8256</v>
+        <v>0.835</v>
       </c>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr"/>
@@ -12932,13 +12901,13 @@
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="n">
-        <v>0.8172</v>
+        <v>0.8171</v>
       </c>
       <c r="F218" t="n">
         <v>0.8295</v>
       </c>
       <c r="G218" t="n">
-        <v>-0.0124</v>
+        <v>-0.0123</v>
       </c>
       <c r="H218" t="n">
         <v>0.1834</v>
@@ -12967,10 +12936,10 @@
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="n">
-        <v>0.1834</v>
+        <v>0.8171</v>
       </c>
       <c r="S218" t="n">
-        <v>0.8172</v>
+        <v>0.8171</v>
       </c>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
@@ -12988,7 +12957,7 @@
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="n">
-        <v>0.7872</v>
+        <v>0.7871</v>
       </c>
       <c r="F219" t="n">
         <v>0.7845</v>
@@ -13185,10 +13154,10 @@
         <v>1</v>
       </c>
       <c r="F222" t="n">
-        <v>0.8063</v>
+        <v>0.8066</v>
       </c>
       <c r="G222" t="n">
-        <v>0.1937</v>
+        <v>0.1934</v>
       </c>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
@@ -13334,7 +13303,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of relevant data evidence.</t>
+          <t>The candidate 'LOCATION' has a high non-empty count but lacks relevant content to match the semantic role of 'Região do local do desembaraço aduaneiro'.</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
@@ -13346,7 +13315,7 @@
         <v>0</v>
       </c>
       <c r="S224" t="n">
-        <v>0</v>
+        <v>0.7998</v>
       </c>
       <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr"/>
@@ -13364,13 +13333,13 @@
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="n">
-        <v>0.7815</v>
+        <v>0.7813</v>
       </c>
       <c r="F225" t="n">
-        <v>0.7761</v>
+        <v>0.776</v>
       </c>
       <c r="G225" t="n">
-        <v>0.0054</v>
+        <v>0.0053</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -13390,7 +13359,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>All client candidates have insufficient evidence and do not semantically match the required column.</t>
+          <t>All client candidates have insufficient evidence and do not match the semantic role of 'UF do Local de Fim'.</t>
         </is>
       </c>
       <c r="M225" t="inlineStr"/>
@@ -13420,16 +13389,16 @@
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="n">
-        <v>0.7186</v>
+        <v>0.7805</v>
       </c>
       <c r="F226" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.756</v>
       </c>
       <c r="G226" t="n">
-        <v>-0.0621</v>
+        <v>0.0245</v>
       </c>
       <c r="H226" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -13446,7 +13415,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate 'LOCATION' does not semantically match 'UF do Local de Início' as it lacks relevant content evidence.</t>
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
@@ -13455,10 +13424,10 @@
       <c r="P226" t="inlineStr"/>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S226" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr"/>
@@ -13558,7 +13527,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>The candidate columns contain no relevant data, making it impossible to establish a mapping.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M228" t="inlineStr"/>
@@ -13567,7 +13536,7 @@
       <c r="P228" t="inlineStr"/>
       <c r="Q228" t="inlineStr"/>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S228" t="n">
         <v>0.8005</v>
@@ -13620,7 +13589,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25T07:25:38.310233+00:00</t>
+          <t>2026-08-25T17:25:34.581621+00:00</t>
         </is>
       </c>
     </row>
@@ -13966,11 +13935,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COD_FIS_JUR</t>
+          <t>FORNECEDOR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13997,20 +13966,20 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Nº ID fiscal 1</t>
+          <t>Código Fornecedor Início</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.392</v>
+        <v>0.5118</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FORNECEDOR</t>
+          <t>NUMERO NF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -14027,7 +13996,7 @@
         <v>7338</v>
       </c>
       <c r="F5" t="n">
-        <v>250</v>
+        <v>3469</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -14037,20 +14006,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Código Fornecedor Início</t>
+          <t>Número do NFC-e SAT</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.5118</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NUMERO NF</t>
+          <t>COD_PRODUTO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14064,10 +14033,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7338</v>
+        <v>7334</v>
       </c>
       <c r="F6" t="n">
-        <v>3469</v>
+        <v>1636</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -14077,20 +14046,20 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Número do NFC-e SAT</t>
+          <t>Código do Item</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.51</v>
+        <v>0.436</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>COD_PRODUTO</t>
+          <t>DESC_PRODUTO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14104,10 +14073,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7334</v>
+        <v>7060</v>
       </c>
       <c r="F7" t="n">
-        <v>1636</v>
+        <v>4318</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -14117,20 +14086,20 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Código do Item</t>
+          <t>Descrição</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.436</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DESC_PRODUTO</t>
+          <t>NUM_ITEM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14144,10 +14113,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7060</v>
+        <v>7334</v>
       </c>
       <c r="F8" t="n">
-        <v>4318</v>
+        <v>1636</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
@@ -14157,20 +14126,20 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Descrição</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.55</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NUM_ITEM</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14184,33 +14153,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7334</v>
+        <v>7338</v>
       </c>
       <c r="F9" t="n">
-        <v>1636</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>88.2% of its 17 distinct codes are valid cfop</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>CFOP</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.6167</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>COD_MEDIDA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -14227,34 +14200,30 @@
         <v>7338</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>catalog</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>88.2% of its 17 distinct codes are valid cfop</t>
+          <t>Carries data, but no signal matched. Listed for completeness.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CFOP</t>
+          <t>Unidade de medida</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.5148</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COD_MEDIDA</t>
+          <t>PRECO UNITARIO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14271,7 +14240,7 @@
         <v>7338</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>3824</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -14281,20 +14250,20 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Unidade de medida</t>
+          <t>Preço líq.</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.5148</v>
+        <v>0.5261</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PRECO UNITARIO</t>
+          <t>TOTAL DO ITEM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14311,7 +14280,7 @@
         <v>7338</v>
       </c>
       <c r="F12" t="n">
-        <v>3824</v>
+        <v>4430</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -14321,20 +14290,20 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Preço líq.</t>
+          <t>Valor Total do Item</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.5261</v>
+        <v>0.7687</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOTAL DO ITEM</t>
+          <t>IND TRIB ICMS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14351,7 +14320,7 @@
         <v>7338</v>
       </c>
       <c r="F13" t="n">
-        <v>4430</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
@@ -14361,20 +14330,20 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Valor Total do Item</t>
+          <t>Isentas ICMS</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.7687</v>
+        <v>0.523</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IND TRIB ICMS</t>
+          <t>IND TRIB IPI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14401,20 +14370,20 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Isentas ICMS</t>
+          <t>Isentas IPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.523</v>
+        <v>0.5011</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IND TRIB IPI</t>
+          <t>PROFIT_CENTER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14431,7 +14400,7 @@
         <v>7338</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
@@ -14441,37 +14410,37 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Isentas IPI</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.5011</v>
+        <v>0.3684</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PROFIT_CENTER</t>
+          <t>ORGANIZACAO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>never_referenced</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7338</v>
+        <v>7339</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
@@ -14481,20 +14450,20 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Região</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.3684</v>
+        <v>0.4118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORGANIZACAO</t>
+          <t>MODALIDADE NF</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -14508,10 +14477,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7339</v>
+        <v>7338</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
@@ -14521,20 +14490,20 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Região</t>
+          <t>Val.Total NF</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.4118</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MODALIDADE NF</t>
+          <t>IDENT_FIS_JUR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -14551,7 +14520,7 @@
         <v>7338</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
@@ -14561,20 +14530,20 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Val.Total NF</t>
+          <t>Isentas IS</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.411</v>
+        <v>0.3652</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IDENT_FIS_JUR</t>
+          <t>COD_FIS_JUR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -14591,7 +14560,7 @@
         <v>7338</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>250</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
@@ -14601,11 +14570,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Isentas IS</t>
+          <t>Nº ID fiscal 1</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.3652</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="20">
@@ -15086,6 +15055,1776 @@
       </c>
       <c r="J31" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>model_column_number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>model_column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>proposed_client_column_number</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>proposed_client_column</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>final_confidence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>gate_distance</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>name_margin</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rows_with_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>resolver_disagrees</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>arithmetic_proof</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>client_sample_values</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>why_held</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>210</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Valor Total do Item</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TOTAL DO ITEM</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>18567 | 14488 | -2390413 | 235 | 808.5 | 2077.92</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>name evidence only - this branch cannot auto-accept however well the headers match</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>188</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NUM_ITEM</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7334</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>999991 | 0 | 1720894 | 1882854 | 2185041 | 2595237</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>name evidence only - this branch cannot auto-accept however well the headers match</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>193</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tipo de Imposto IPI</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>IND TRIB IPI</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8927</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2 | 3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>215</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Texto ICMS</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2 | 3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>86</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tipo de Imposto ICMS</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8882</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2 | 3</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>51</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Outras IPI</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>29</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>IND TRIB IPI</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8832</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2 | 3</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>35</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DESC_PRODUTO</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8823</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7060</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PORT STORAGE | EMBRATEL TV | PORTABLE GAS DETECTOR FOR CALIBRATION - Serial #4000232 #4000560 #174334 | GLUCAGEN HYPOKIT INJETAVEL 1MG (1UI) REG.MS:1176600140018 | DOXICICLINA 100MG C/ 15 CPR | 19 - 9044107 - TALHA MANUAL - SWL 2,00 TON X 5,00 METROS</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>195</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DESC_PRODUTO</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8823</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="I9" t="n">
+        <v>7060</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PORT STORAGE | EMBRATEL TV | PORTABLE GAS DETECTOR FOR CALIBRATION - Serial #4000232 #4000560 #174334 | GLUCAGEN HYPOKIT INJETAVEL 1MG (1UI) REG.MS:1176600140018 | DOXICICLINA 100MG C/ 15 CPR | 19 - 9044107 - TALHA MANUAL - SWL 2,00 TON X 5,00 METROS</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>216</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Texto IPI</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IND TRIB IPI</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8804999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2 | 3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Isentas ICMS</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>21</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8794999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>resolver scored it 0.1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2 | 3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>50</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Isentas IPI</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>IND TRIB IPI</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8776</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2 | 3</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>194</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nº item do documento</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NUM_ITEM</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8752</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7334</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>999991 | 0 | 1720894 | 1882854 | 2185041 | 2595237</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>165</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Código do Item</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>COD_PRODUTO</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8734</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7334</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>999991 | 0 | 1720894 | 1882854 | 2185041 | 2595237</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>61</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Data documento</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DATA GL</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8722</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00 | 2025-10-02 00:00:00 | 2025-10-01 00:00:00 | 2025-10-10 00:00:00 | 2025-10-22 00:00:00 | 2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>175</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Centro de lucro</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>41</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PROFIT_CENTER</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8643</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="I16" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>' | '2318 | '2270 | '2321 | '9006 | '9015</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>209</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Número de nota fiscal eletrônica</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8627</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>180</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Exportador</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FORNECEDOR</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>DRAGER SAFETY DO BRASIL EQUIPAMENTOS DE SEGURANCA LTDA. | ALIANCA COMERCIO IMPORTACAO E EXPORTACAO LTDA | S3 SAFETY LTDA | BOOT-TEC ELETRONICA E INFORMATICA LTDA | DISTRIBUIDORA SUED OFFSHORE LTDA (DROGARCIA) | HUMBERTO AVILA SOCIEDADE DE ADVOGADOS</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Base Reduzida ICMS</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>21</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>IND TRIB ICMS</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.8587</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2 | 3</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>158</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nº NF-e dos serviços</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8556</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>32</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nº da Nota Fiscal</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.8556</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>34</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CFOP</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>16</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CFO</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1128 | 1999 | 1554 | 1556 | 1916 | 1949</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>118</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Base Reduzida IPI</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>29</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>IND TRIB IPI</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.8535</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0616</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>resolver scored it 0.0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2 | 3</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>206</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Preço líq.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>19</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PRECO UNITARIO</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.8532</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>18567 | 395 | -164122.47 | 39.84 | 279.87 | 1080</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>198</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Unidade de medida</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>18</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>COD_MEDIDA</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8463000000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ea | Piece | Hours | Inches | Kilograms | Kit</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>73</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Item referência NF</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0563</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>187</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Documento de compras</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TIPO DOC</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.8401</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="I27" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>resolver scored it 0.0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>55 | NFS-E | FATURA | NFSC</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>178</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Nº documento</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.8387</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>166</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Número do NFC-e SAT</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.8369</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>31</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nº de documento</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8339</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.06610000000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>resolver scored it 0.5</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>205</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Nº doc.importação</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TIPO DOC</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0.8336</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>resolver scored it 0.0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>55 | NFS-E | FATURA | NFSC</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>40</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Val.Total NF</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TOTAL DO ITEM</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.8315</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>18567 | 14488 | -2390413 | 235 | 808.5 | 2077.92</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>174</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Numero do Pedido</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>68</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Nº FCI</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.8231000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Nº de serviço</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.8209</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0791</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="I35" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>43</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Valor ICMS_ST</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>TOTAL DO ITEM</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.8166</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0834</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>resolver scored it 0.0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>18567 | 14488 | -2390413 | 235 | 808.5 | 2077.92</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Texto breve serviço</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DESC_PRODUTO</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0.8017</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7060</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>PORT STORAGE | EMBRATEL TV | PORTABLE GAS DETECTOR FOR CALIBRATION - Serial #4000232 #4000560 #174334 | GLUCAGEN HYPOKIT INJETAVEL 1MG (1UI) REG.MS:1176600140018 | DOXICICLINA 100MG C/ 15 CPR | 19 - 9044107 - TALHA MANUAL - SWL 2,00 TON X 5,00 METROS</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>66</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Nº doc.original</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NUMERO NF</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.8017</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.0314</v>
+      </c>
+      <c r="I38" t="n">
+        <v>7338</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>below the accept threshold</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/mapping_oracle_full.xlsx
+++ b/mapping_oracle_full.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V228"/>
+  <dimension ref="A1:Y228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,32 +512,47 @@
           <t>catalog_confidence</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>decided_by</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>supported_by</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>vetoed_by</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>arithmetic_proof</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>llm_data_confidence</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>llm_final_confidence</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>reviewer_status</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>correct_client_column</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>reviewer_note</t>
         </is>
@@ -552,8 +567,6 @@
           <t>Tipo de Imposto CBS</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>0.7675</v>
       </c>
@@ -584,20 +597,12 @@
           <t>All candidates have semantic header conflicts with the expected tax type, and there is no supporting data evidence.</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -608,8 +613,6 @@
           <t>Base CBS</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>0.7956</v>
       </c>
@@ -640,20 +643,12 @@
           <t>All candidates have semantic header conflicts or do not match the expected type for 'Base CBS', which is a tax base.</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -664,8 +659,6 @@
           <t>Aliquota CBS</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>0.7842</v>
       </c>
@@ -696,20 +689,12 @@
           <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended role of 'Aliquota CBS'.</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -720,8 +705,6 @@
           <t>Valor CBS</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>0.7936</v>
       </c>
@@ -752,20 +735,12 @@
           <t>All candidates have semantic conflicts or insufficient evidence to support a mapping.</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -776,8 +751,6 @@
           <t>Isentas CBS</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>0.7913</v>
       </c>
@@ -808,20 +781,12 @@
           <t>All candidates have semantic header conflicts with the tax-family context, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -832,8 +797,6 @@
           <t>Outras CBS</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>0.8206</v>
       </c>
@@ -864,20 +827,12 @@
           <t>The candidate columns conflict semantically with the tax family of 'Outras CBS' and provide no relevant data evidence.</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -888,8 +843,6 @@
           <t>Base Reduzida CBS</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>0.7722</v>
       </c>
@@ -920,20 +873,12 @@
           <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -944,8 +889,6 @@
           <t>Tipo de Imposto IBSM</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>0.7939000000000001</v>
       </c>
@@ -976,20 +919,12 @@
           <t>All candidates have semantic header conflicts with the target column, and the evidence quality is insufficient.</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1000,8 +935,6 @@
           <t>Base IBSM</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
         <v>0.797</v>
       </c>
@@ -1032,20 +965,12 @@
           <t>All candidates have semantic header conflicts with the 'Base IBSM' column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1056,8 +981,6 @@
           <t>Aliquota IBSM</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>0.7864</v>
       </c>
@@ -1088,20 +1011,12 @@
           <t>All candidates have semantic header conflicts with the expected tax family, indicating no suitable mapping.</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1112,8 +1027,6 @@
           <t>Valor IBSM</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>0.8216</v>
       </c>
@@ -1144,20 +1057,12 @@
           <t>All candidates have semantic header conflicts and no distinctive sample overlap.</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1168,8 +1073,6 @@
           <t>Isentas IBSM</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>0.7913</v>
       </c>
@@ -1200,20 +1103,12 @@
           <t>All candidates have semantic header conflicts with the tax-family context of 'Isentas IBSM', indicating they do not represent the same business meaning.</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1224,8 +1119,6 @@
           <t>Outras IBSM</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>0.8169999999999999</v>
       </c>
@@ -1256,20 +1149,12 @@
           <t>All candidates have a tax-family conflict with the 'Outras IBSM' column, indicating incompatible semantic roles.</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1280,8 +1165,6 @@
           <t>Base Reduzida IBSM</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>0.781</v>
       </c>
@@ -1312,20 +1195,12 @@
           <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1336,8 +1211,6 @@
           <t>Tipo de Imposto IBS</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
         <v>0.801</v>
       </c>
@@ -1368,20 +1241,12 @@
           <t>All candidates have semantic header conflicts with the expected tax type.</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1392,8 +1257,6 @@
           <t>Base IBS</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>0.8095</v>
       </c>
@@ -1424,20 +1287,12 @@
           <t>All candidates have semantic header conflicts with the 'Base IBS' column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1448,8 +1303,6 @@
           <t>Aliquota IBS</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
         <v>0.7884</v>
       </c>
@@ -1480,20 +1333,12 @@
           <t>All candidates have a semantic header conflict with the expected tax family for 'Aliquota IBS'.</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1504,8 +1349,6 @@
           <t>Valor IBS</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>0.8270999999999999</v>
       </c>
@@ -1536,20 +1379,12 @@
           <t>All candidates have semantic header conflicts with the tax family, indicating they do not match the intended role of 'Valor IBS'.</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
         <v>0.8270999999999999</v>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1560,8 +1395,6 @@
           <t>Isentas IBS</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
         <v>0.8008999999999999</v>
       </c>
@@ -1592,20 +1425,12 @@
           <t>All candidates have a semantic header conflict with the tax-family context, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1616,8 +1441,6 @@
           <t>Outras IBS</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>0.8224</v>
       </c>
@@ -1648,20 +1471,12 @@
           <t>All candidates have semantic header conflicts with the 'Outras IBS' column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1672,8 +1487,6 @@
           <t>Base Reduzida IBS</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>0.7828000000000001</v>
       </c>
@@ -1704,20 +1517,12 @@
           <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended role of 'Base Reduzida IBS'.</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1728,8 +1533,6 @@
           <t>Tipo de Imposto IS</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>0.832</v>
       </c>
@@ -1760,20 +1563,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
         <v>0.8</v>
       </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
         <v>0.832</v>
       </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1784,8 +1579,6 @@
           <t>Base IS</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
         <v>0.8172</v>
       </c>
@@ -1816,20 +1609,12 @@
           <t>All candidate columns contain non-zero values, while the 'Base IS' column only has zeros, indicating a mismatch in semantic meaning.</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1840,8 +1625,6 @@
           <t>Aliquota IS</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>0.8149</v>
       </c>
@@ -1872,20 +1655,12 @@
           <t>All candidates have non-zero values, while the model column contains only zeros, indicating a mismatch in data semantics.</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1896,8 +1671,6 @@
           <t>Valor IS</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
         <v>0.7943</v>
       </c>
@@ -1928,20 +1701,12 @@
           <t>The candidate columns contain non-zero values while 'Valor IS' has only zeros, indicating a mismatch in semantic meaning.</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
         <v>0.7943</v>
       </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1952,8 +1717,6 @@
           <t>Isentas IS</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
         <v>0.8108</v>
       </c>
@@ -1984,20 +1747,12 @@
           <t>All candidate columns contain non-zero values, while the source column is entirely zero.</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2008,8 +1763,6 @@
           <t>Outras IS</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
         <v>0.836</v>
       </c>
@@ -2040,20 +1793,12 @@
           <t>All candidate columns contain non-zero values, while the source column 'Outras IS' has only zeros, indicating no compatible mapping.</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2064,8 +1809,6 @@
           <t>Base Reduzida IS</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>0.7844</v>
       </c>
@@ -2096,20 +1839,12 @@
           <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating a lack of semantic alignment.</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2120,8 +1855,6 @@
           <t>Local de negócios</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
         <v>0.7522</v>
       </c>
@@ -2152,20 +1885,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
         <v>0.85</v>
       </c>
-      <c r="S30" t="n">
+      <c r="V30" t="n">
         <v>0.85</v>
       </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2176,8 +1901,6 @@
           <t>Data de lançamento</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>0.7903</v>
       </c>
@@ -2208,20 +1931,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="n">
+      <c r="U31" t="n">
         <v>0.8</v>
       </c>
-      <c r="S31" t="n">
+      <c r="V31" t="n">
         <v>0.795</v>
       </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2270,20 +1985,23 @@
           <t>The candidate 'NUMERO NF' has a similar numeric structure but a lower median length and lacks distinctive sample overlap with the document number.</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="U32" t="n">
         <v>0.5</v>
       </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
         <v>0.5</v>
       </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2332,20 +2050,23 @@
           <t>The candidate 'NUMERO NF' has a high name confidence but a low profile similarity and no distinctive sample overlap, indicating it does not semantically match 'Nº da Nota Fiscal' despite the name similarity.</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
         <v>0.8556</v>
       </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2373,7 +2094,6 @@
       <c r="G34" t="n">
         <v>0.1889</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
         <v>1</v>
       </c>
@@ -2392,16 +2112,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2458,16 +2179,20 @@
       <c r="N35" t="n">
         <v>0.6673</v>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
         <v>0.8824</v>
       </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>semantic + catalog</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2516,20 +2241,23 @@
           <t>The header 'DESC_PRODUTO' suggests a product description, but the numeric profile indicates mixed content, conflicting with the string nature of 'Descrição'.</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="n">
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="U36" t="n">
         <v>0.1586</v>
       </c>
-      <c r="S36" t="n">
+      <c r="V36" t="n">
         <v>0.8823</v>
       </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2540,8 +2268,6 @@
           <t>ID parceiro</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>0.7704</v>
       </c>
@@ -2572,20 +2298,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
+      <c r="U37" t="n">
         <v>0.85</v>
       </c>
-      <c r="S37" t="n">
+      <c r="V37" t="n">
         <v>0.8</v>
       </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2596,8 +2314,6 @@
           <t>Nome</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>0.8362000000000001</v>
       </c>
@@ -2628,20 +2344,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="n">
+      <c r="U38" t="n">
         <v>0.8362000000000001</v>
       </c>
-      <c r="S38" t="n">
+      <c r="V38" t="n">
         <v>0.8362000000000001</v>
       </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2652,8 +2360,6 @@
           <t>Nº ID fiscal 1</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
         <v>0.8288</v>
       </c>
@@ -2684,20 +2390,12 @@
           <t>The header 'NUMERO NF' conflicts semantically with the expected role of 'Nº ID fiscal 1', which is a tax ID, not a document ID.</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2708,8 +2406,6 @@
           <t>Região</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
         <v>0.8043</v>
       </c>
@@ -2740,20 +2436,12 @@
           <t>The candidate 'SINAL' does not semantically match 'Região', which represents geographical regions.</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2802,20 +2490,23 @@
           <t>The column 'TOTAL DO ITEM' has a compatible numeric type and no semantic conflicts, aligning well with the 'Val.Total NF'.</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="n">
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="U41" t="n">
         <v>0.9368</v>
       </c>
-      <c r="S41" t="n">
+      <c r="V41" t="n">
         <v>0.8313</v>
       </c>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2843,7 +2534,6 @@
       <c r="G42" t="n">
         <v>0.0969</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>1</v>
       </c>
@@ -2862,20 +2552,22 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>valor = base x aliquota holds for icms on 2540 rows at fit 1.0</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2903,7 +2595,6 @@
       <c r="G43" t="n">
         <v>0.09760000000000001</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>1</v>
       </c>
@@ -2922,20 +2613,22 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
           <t>valor = base x aliquota holds for icms on 2540 rows at fit 1.0</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2984,20 +2677,23 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3046,20 +2742,23 @@
           <t>The candidate 'IND TRIB ICMS' has a high name confidence but conflicts semantically with the tax base role of 'Isentas ICMS'.</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="n">
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="U45" t="n">
         <v>0.1</v>
       </c>
-      <c r="S45" t="n">
+      <c r="V45" t="n">
         <v>0.1</v>
       </c>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3070,8 +2769,6 @@
           <t>Outras ICMS</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
         <v>0.8969</v>
       </c>
@@ -3102,20 +2799,12 @@
           <t>The candidate 'IND TRIB ICMS' has a semantic header conflict with the expected role of 'Outras ICMS'.</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3126,8 +2815,6 @@
           <t>Valor ICAP</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
         <v>0.7948</v>
       </c>
@@ -3158,20 +2845,12 @@
           <t>All candidates have semantic header conflicts with the expected tax role of 'Valor ICAP', indicating incompatible mappings.</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3182,8 +2861,6 @@
           <t>Valor ICEP</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
         <v>0.8048999999999999</v>
       </c>
@@ -3214,20 +2891,12 @@
           <t>All candidates have a semantic header conflict with the ICEP value, indicating they do not represent the same business meaning.</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3255,7 +2924,6 @@
       <c r="G49" t="n">
         <v>0.1061</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>1</v>
       </c>
@@ -3274,20 +2942,22 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
           <t>valor = base x aliquota holds for ipi on 333 rows at fit 1.0</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3315,7 +2985,6 @@
       <c r="G50" t="n">
         <v>0.1093</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>1</v>
       </c>
@@ -3334,20 +3003,22 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
+        <is>
           <t>valor = base x aliquota holds for ipi on 333 rows at fit 1.0</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3396,20 +3067,23 @@
           <t>The candidate 'IND TRIB IPI' has a high name confidence and matches the tax type, despite a lack of distinctive sample overlap.</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="n">
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="U51" t="n">
         <v>0.5</v>
       </c>
-      <c r="S51" t="n">
+      <c r="V51" t="n">
         <v>0.8776</v>
       </c>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3458,20 +3132,23 @@
           <t>The candidate 'IND TRIB IPI' has a high name confidence but lacks supporting data evidence, and the all-zero profile indicates no valid mapping.</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
         <v>0.8832</v>
       </c>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3499,7 +3176,6 @@
       <c r="G53" t="n">
         <v>0.235</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>1</v>
       </c>
@@ -3518,16 +3194,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
       <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3555,7 +3232,6 @@
       <c r="G54" t="n">
         <v>0.2099</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>1</v>
       </c>
@@ -3574,16 +3250,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
       <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3611,7 +3288,6 @@
       <c r="G55" t="n">
         <v>0.1764</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>1</v>
       </c>
@@ -3630,16 +3306,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
       <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3667,7 +3344,6 @@
       <c r="G56" t="n">
         <v>0.1759</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>1</v>
       </c>
@@ -3686,16 +3362,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3706,8 +3383,6 @@
           <t>Frete</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
         <v>0.7674</v>
       </c>
@@ -3738,20 +3413,12 @@
           <t>The 'Frete' column contains only zeros, making it incompatible with any candidate that has meaningful non-zero values.</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
         <v>0.7543</v>
       </c>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3762,8 +3429,6 @@
           <t>Seguros</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
         <v>0.8061</v>
       </c>
@@ -3794,20 +3459,12 @@
           <t>All candidate columns contain non-numeric values, while 'Seguros' is entirely zero, indicating no valid mapping.</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
         <v>0.7863</v>
       </c>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3818,8 +3475,6 @@
           <t>Observações</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
         <v>0.7943</v>
       </c>
@@ -3850,20 +3505,12 @@
           <t>The 'Observações' column contains strings that do not match any candidate's semantic role or content.</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3874,8 +3521,6 @@
           <t>Chave de acesso</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
         <v>0.7637</v>
       </c>
@@ -3906,20 +3551,12 @@
           <t>No client column matches the semantic role of 'Chave de acesso' as all candidates are unrelated.</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
         <v>0.75</v>
       </c>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3930,8 +3567,6 @@
           <t>Ctg.nota fiscal</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
         <v>0.8066</v>
       </c>
@@ -3962,20 +3597,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="U61" t="n">
         <v>0.8</v>
       </c>
-      <c r="S61" t="n">
+      <c r="V61" t="n">
         <v>0.8</v>
       </c>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4024,20 +3651,23 @@
           <t>The column 'DATA GL' has a high name confidence and matches the datetime format of 'Data documento'.</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="n">
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="U62" t="n">
         <v>0.9</v>
       </c>
-      <c r="S62" t="n">
+      <c r="V62" t="n">
         <v>0.8722</v>
       </c>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4048,8 +3678,6 @@
           <t>Criado por</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
         <v>0.7687</v>
       </c>
@@ -4080,20 +3708,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="n">
+      <c r="U63" t="n">
         <v>0.5</v>
       </c>
-      <c r="S63" t="n">
+      <c r="V63" t="n">
         <v>0.5</v>
       </c>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4104,8 +3724,6 @@
           <t>Modificado por</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
         <v>0.7614</v>
       </c>
@@ -4136,20 +3754,12 @@
           <t>No candidate column matches the semantic role of 'Modificado por'.</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4160,8 +3770,6 @@
           <t>Criado Manualmente</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
         <v>0.8071</v>
       </c>
@@ -4192,20 +3800,12 @@
           <t>No suitable candidate matches the semantic role of 'Criado Manualmente'.</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4216,8 +3816,6 @@
           <t>Nº doc.original Cabeçalho</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
         <v>0.7906</v>
       </c>
@@ -4248,20 +3846,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="n">
+      <c r="U66" t="n">
         <v>0.73</v>
       </c>
-      <c r="S66" t="n">
+      <c r="V66" t="n">
         <v>0.7906</v>
       </c>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4310,20 +3900,23 @@
           <t>The header 'NUMERO NF' closely matches the semantic role of 'Nº doc.original' as both represent document identifiers, supported by numeric evidence.</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="n">
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="U67" t="n">
         <v>0.8</v>
       </c>
-      <c r="S67" t="n">
+      <c r="V67" t="n">
         <v>0.8</v>
       </c>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4334,8 +3927,6 @@
           <t>Código da situação do documento</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
         <v>0.829</v>
       </c>
@@ -4366,20 +3957,12 @@
           <t>No suitable candidate matches the semantic role of the document situation code.</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4428,20 +4011,23 @@
           <t>The 'NUMERO NF' column has a strong numeric profile and high name confidence, aligning well with the 'Nº FCI' semantic role.</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="n">
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="U69" t="n">
         <v>0.9</v>
       </c>
-      <c r="S69" t="n">
+      <c r="V69" t="n">
         <v>0.85</v>
       </c>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4452,8 +4038,6 @@
           <t>Condições pagamento</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
         <v>0.798</v>
       </c>
@@ -4484,20 +4068,12 @@
           <t>No suitable candidate matches the semantic role of 'Condições pagamento' as all candidates are unrelated to payment conditions.</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
         <v>0.75</v>
       </c>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4508,8 +4084,6 @@
           <t>Base ICAP</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
         <v>0.8041</v>
       </c>
@@ -4540,20 +4114,12 @@
           <t>All candidates have semantic header conflicts with the expected role of 'Base ICAP', indicating incompatible tax-family contexts.</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4564,8 +4130,6 @@
           <t>Aliquota ICAP</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
         <v>0.7897</v>
       </c>
@@ -4596,20 +4160,12 @@
           <t>All candidates have semantic header conflicts with the expected tax family for 'Aliquota ICAP', indicating they do not represent the same business meaning.</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4620,8 +4176,6 @@
           <t>NºID fiscal regional</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
         <v>0.7944</v>
       </c>
@@ -4652,20 +4206,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="n">
+      <c r="U73" t="n">
         <v>0.5</v>
       </c>
-      <c r="S73" t="n">
+      <c r="V73" t="n">
         <v>0.5</v>
       </c>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4714,20 +4260,23 @@
           <t>The header 'NUMERO NF' closely matches the semantic role of 'Item referência NF' despite some numeric discrepancies.</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="n">
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="U74" t="n">
         <v>0.8</v>
       </c>
-      <c r="S74" t="n">
+      <c r="V74" t="n">
         <v>0.8205</v>
       </c>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4738,8 +4287,6 @@
           <t>Mensagem</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
         <v>0.7996</v>
       </c>
@@ -4770,20 +4317,12 @@
           <t>No candidate column matches the semantic role of 'Mensagem', which contains descriptive text, while all candidates are unrelated to this content.</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4794,8 +4333,6 @@
           <t>Setor industrial</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
         <v>0.8246</v>
       </c>
@@ -4826,20 +4363,12 @@
           <t>No suitable candidate found due to lack of non-empty values in both the model and client columns.</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4850,8 +4379,6 @@
           <t>Domicílio fiscal</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
         <v>0.8259</v>
       </c>
@@ -4882,20 +4409,12 @@
           <t>The candidate 'COD_FIS_JUR' has a numeric profile with no overlap in samples, conflicting with the string nature of 'Domicílio fiscal'.</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4906,8 +4425,6 @@
           <t>Modelo nota fiscal</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
         <v>0.7916</v>
       </c>
@@ -4938,20 +4455,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="n">
+      <c r="U78" t="n">
         <v>0.7916</v>
       </c>
-      <c r="S78" t="n">
+      <c r="V78" t="n">
         <v>0.7916</v>
       </c>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5000,20 +4509,23 @@
           <t>The column 'NUMERO NF' has a strong numeric profile and matches the semantic role of 'Nº de serviço' as an invoice number.</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="n">
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="U79" t="n">
         <v>0.9</v>
       </c>
-      <c r="S79" t="n">
+      <c r="V79" t="n">
         <v>0.8209</v>
       </c>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5062,20 +4574,23 @@
           <t>The header 'DESC_PRODUTO' suggests a description of the service, aligning with 'Texto breve serviço' despite the lack of row evidence.</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="n">
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="U80" t="n">
         <v>0.8</v>
       </c>
-      <c r="S80" t="n">
+      <c r="V80" t="n">
         <v>0.8017</v>
       </c>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5086,8 +4601,6 @@
           <t>Origem do material</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
         <v>0.7657</v>
       </c>
@@ -5118,20 +4631,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="n">
+      <c r="U81" t="n">
         <v>0.85</v>
       </c>
-      <c r="S81" t="n">
+      <c r="V81" t="n">
         <v>0.8</v>
       </c>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5142,8 +4647,6 @@
           <t>Utilização de material</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
         <v>0.7895</v>
       </c>
@@ -5174,20 +4677,12 @@
           <t>No suitable candidate matches the semantic role of 'Utilização de material' based on the provided evidence.</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5198,8 +4693,6 @@
           <t>Tipo de avaliação</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
         <v>0.793</v>
       </c>
@@ -5230,20 +4723,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="n">
+      <c r="U83" t="n">
         <v>0.646</v>
       </c>
-      <c r="S83" t="n">
+      <c r="V83" t="n">
         <v>0.793</v>
       </c>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5254,8 +4739,6 @@
           <t>Mont.líquido frete</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
         <v>0.74</v>
       </c>
@@ -5286,20 +4769,12 @@
           <t>All candidate columns have semantic conflicts or do not match the expected numeric type for 'Mont.líquido frete', which should represent a monetary value.</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5310,8 +4785,6 @@
           <t>Mont.líquido seguro</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
         <v>0.7621</v>
       </c>
@@ -5342,20 +4815,12 @@
           <t>No suitable candidate due to semantic header conflicts and all-zero evidence.</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
         <v>0.7621</v>
       </c>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5366,8 +4831,6 @@
           <t>Grupo de imposto</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
         <v>0.8169999999999999</v>
       </c>
@@ -5398,20 +4861,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="n">
+      <c r="U86" t="n">
         <v>0.8169999999999999</v>
       </c>
-      <c r="S86" t="n">
+      <c r="V86" t="n">
         <v>0.8169999999999999</v>
       </c>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5460,20 +4915,23 @@
           <t>The candidate 'IND TRIB ICMS' closely matches the semantic role of 'Tipo de Imposto ICMS' with high name confidence and consistent numeric values.</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="n">
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="U87" t="n">
         <v>0.8882</v>
       </c>
-      <c r="S87" t="n">
+      <c r="V87" t="n">
         <v>0.8882</v>
       </c>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5522,20 +4980,23 @@
           <t>The candidate 'IND TRIB ICMS' has a high name confidence and matches the integer type of 'Base Reduzida ICMS', despite the lack of distinctive sample overlap.</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="n">
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="U88" t="n">
         <v>0.9</v>
       </c>
-      <c r="S88" t="n">
+      <c r="V88" t="n">
         <v>0.8587</v>
       </c>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5546,8 +5007,6 @@
           <t>Tipo de Imposto ICAP</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
         <v>0.7867</v>
       </c>
@@ -5578,20 +5037,12 @@
           <t>All candidates have semantic header conflicts with the expected tax type, indicating incompatible mappings.</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5602,8 +5053,6 @@
           <t>Isentas ICAP</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
         <v>0.7876</v>
       </c>
@@ -5634,20 +5083,12 @@
           <t>All candidates have a semantic header conflict with the expected tax family and provide no valid row evidence.</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5658,8 +5099,6 @@
           <t>Outras ICAP</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
         <v>0.8223</v>
       </c>
@@ -5690,20 +5129,12 @@
           <t>All candidates have semantic header conflicts with the original column, and the evidence does not support a mapping.</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5714,8 +5145,6 @@
           <t>Base Reduzida ICAP</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
         <v>0.7914</v>
       </c>
@@ -5746,20 +5175,12 @@
           <t>All candidates have semantic header conflicts with the expected role of 'Base Reduzida ICAP'.</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5770,8 +5191,6 @@
           <t>Tipo de Imposto ICEP</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
         <v>0.7851</v>
       </c>
@@ -5802,20 +5221,12 @@
           <t>All candidates have semantic header conflicts with the expected tax type, and there is no supporting data evidence.</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5826,8 +5237,6 @@
           <t>Base ICEP</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
         <v>0.8079</v>
       </c>
@@ -5858,20 +5267,12 @@
           <t>All candidates have semantic header conflicts with the ICEP base, and no distinctive row evidence supports a mapping.</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5882,8 +5283,6 @@
           <t>Aliquota ICEP</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
         <v>0.7859</v>
       </c>
@@ -5914,20 +5313,12 @@
           <t>All candidates conflict with the tax-family context of ICEP.</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5938,8 +5329,6 @@
           <t>Isentas ICEP</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
         <v>0.7871</v>
       </c>
@@ -5970,20 +5359,12 @@
           <t>All candidates have a semantic header conflict with the tax-family context, indicating they do not match the intended meaning of 'Isentas ICEP'.</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5994,8 +5375,6 @@
           <t>Outras ICEP</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
         <v>0.823</v>
       </c>
@@ -6026,20 +5405,12 @@
           <t>No suitable candidate due to semantic header conflicts and lack of distinctive row evidence.</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6050,8 +5421,6 @@
           <t>Base Reduzida ICEP</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
         <v>0.787</v>
       </c>
@@ -6082,20 +5451,12 @@
           <t>All candidates have semantic header conflicts with the ICEP role, indicating incompatible tax-family contexts.</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6106,8 +5467,6 @@
           <t>Tipo de Imposto ICSP</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
         <v>0.7771</v>
       </c>
@@ -6138,20 +5497,12 @@
           <t>All candidates have semantic header conflicts with the expected tax type.</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" t="n">
-        <v>0</v>
-      </c>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6162,8 +5513,6 @@
           <t>Base ICSP</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
         <v>0.7998</v>
       </c>
@@ -6194,20 +5543,12 @@
           <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6218,8 +5559,6 @@
           <t>Aliquota ICSP</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
         <v>0.7994</v>
       </c>
@@ -6250,20 +5589,12 @@
           <t>All candidates have semantic header conflicts with the expected tax family, indicating they do not match the intended role of 'Aliquota ICSP'.</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6274,8 +5605,6 @@
           <t>Valor ICSP</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="n">
         <v>0.7988</v>
       </c>
@@ -6306,20 +5635,12 @@
           <t>All candidates have semantic header conflicts and do not match the expected tax base for ICSP.</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="inlineStr"/>
-      <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr"/>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6330,8 +5651,6 @@
           <t>Isentas ICSP</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
         <v>0.7843</v>
       </c>
@@ -6362,20 +5681,12 @@
           <t>All candidates conflict with the tax-family context and provide no valid evidence.</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="inlineStr"/>
-      <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6386,8 +5697,6 @@
           <t>Outras ICSP</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="n">
         <v>0.8174</v>
       </c>
@@ -6418,20 +5727,12 @@
           <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6442,8 +5743,6 @@
           <t>Base Reduzida ICSP</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
         <v>0.786</v>
       </c>
@@ -6474,20 +5773,12 @@
           <t>All candidates have semantic header conflicts with the expected tax role, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6498,8 +5789,6 @@
           <t>Tipo de Imposto DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
         <v>0.803</v>
       </c>
@@ -6530,20 +5819,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="n">
+      <c r="U106" t="n">
         <v>0.8</v>
       </c>
-      <c r="S106" t="n">
+      <c r="V106" t="n">
         <v>0.803</v>
       </c>
-      <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6554,8 +5835,6 @@
           <t>Base DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
         <v>0.7929</v>
       </c>
@@ -6586,20 +5865,12 @@
           <t>No suitable candidate found due to all-zero evidence in the model column.</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="inlineStr"/>
-      <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6610,8 +5881,6 @@
           <t>Aliquota DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
         <v>0.7836</v>
       </c>
@@ -6642,20 +5911,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="n">
+      <c r="U108" t="n">
         <v>0.7836</v>
       </c>
-      <c r="S108" t="n">
+      <c r="V108" t="n">
         <v>0.7836</v>
       </c>
-      <c r="T108" t="inlineStr"/>
-      <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6666,8 +5927,6 @@
           <t>Valor DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="n">
         <v>0.7976</v>
       </c>
@@ -6698,20 +5957,12 @@
           <t>No suitable candidate matches the semantic role of 'Valor DIF_ALIQ' as all candidates have conflicting roles or irrelevant data.</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" t="n">
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
         <v>0.7976</v>
       </c>
-      <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6722,8 +5973,6 @@
           <t>Isentas DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="n">
         <v>0.8079</v>
       </c>
@@ -6754,20 +6003,12 @@
           <t>All candidate columns contain non-zero values, while the model column is entirely zero, indicating no compatible mapping.</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6778,8 +6019,6 @@
           <t>Outras DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
         <v>0.8097</v>
       </c>
@@ -6810,20 +6049,12 @@
           <t>All candidate columns contain non-numeric or empty data, while 'Outras DIF_ALIQ' is entirely zero.</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="n">
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
         <v>0.8097</v>
       </c>
-      <c r="T111" t="inlineStr"/>
-      <c r="U111" t="inlineStr"/>
-      <c r="V111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6834,8 +6065,6 @@
           <t>Base Reduzida DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
         <v>0.7779</v>
       </c>
@@ -6866,20 +6095,12 @@
           <t>All candidate columns have semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="inlineStr"/>
-      <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6890,8 +6111,6 @@
           <t>Base ICMS_FECP</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="n">
         <v>0.8563</v>
       </c>
@@ -6922,20 +6141,12 @@
           <t>All candidates have significant semantic conflicts or do not match the expected numeric characteristics of 'Base ICMS_FECP'.</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" t="inlineStr"/>
-      <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr"/>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6946,8 +6157,6 @@
           <t>Aliquota ICMS_FECP</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="n">
         <v>0.8552</v>
       </c>
@@ -6978,20 +6187,12 @@
           <t>All candidates have conflicting semantic roles or insufficient evidence to support a mapping.</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" t="n">
-        <v>0</v>
-      </c>
-      <c r="T114" t="inlineStr"/>
-      <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7002,8 +6203,6 @@
           <t>Valor ICMS_FECP</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
         <v>0.7909</v>
       </c>
@@ -7034,20 +6233,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="n">
+      <c r="U115" t="n">
         <v>0.7909</v>
       </c>
-      <c r="S115" t="n">
+      <c r="V115" t="n">
         <v>0.7909</v>
       </c>
-      <c r="T115" t="inlineStr"/>
-      <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7058,8 +6249,6 @@
           <t>Isentas ICMS_FECP</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="n">
         <v>0.853</v>
       </c>
@@ -7090,20 +6279,12 @@
           <t>All candidates have conflicting semantic roles or insufficient evidence to support a mapping.</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="inlineStr"/>
-      <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7114,8 +6295,6 @@
           <t>Outras ICMS_FECP</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
         <v>0.8647</v>
       </c>
@@ -7146,20 +6325,12 @@
           <t>All candidate columns contain non-zero values, while the source column has only zeros, indicating no compatible mapping.</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" t="inlineStr"/>
-      <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
+      <c r="U117" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7170,8 +6341,6 @@
           <t>Base Reduzida ICMS_FECP</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
         <v>0.8304</v>
       </c>
@@ -7202,20 +6371,12 @@
           <t>All candidates have significant semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="inlineStr"/>
-      <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7264,20 +6425,23 @@
           <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" t="inlineStr"/>
-      <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr"/>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7288,8 +6452,6 @@
           <t>Tipo de Imposto COFINS</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="n">
         <v>0.8083</v>
       </c>
@@ -7320,20 +6482,12 @@
           <t>All candidates have semantic conflicts with the tax-family context of COFINS.</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="inlineStr"/>
-      <c r="U120" t="inlineStr"/>
-      <c r="V120" t="inlineStr"/>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7344,8 +6498,6 @@
           <t>Isentas COFINS</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
         <v>0.8073</v>
       </c>
@@ -7376,20 +6528,12 @@
           <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended meaning of 'Isentas COFINS'.</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="inlineStr"/>
-      <c r="U121" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7400,8 +6544,6 @@
           <t>Outras COFINS</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="n">
         <v>0.8276</v>
       </c>
@@ -7432,20 +6574,12 @@
           <t>No suitable candidate found due to all candidates having semantic conflicts or insufficient evidence.</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="inlineStr"/>
-      <c r="U122" t="inlineStr"/>
-      <c r="V122" t="inlineStr"/>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7456,8 +6590,6 @@
           <t>Base Reduzida COFINS</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
         <v>0.7754</v>
       </c>
@@ -7488,20 +6620,12 @@
           <t>All candidates have semantic header conflicts with the required tax base for COFINS.</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="inlineStr"/>
-      <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7512,8 +6636,6 @@
           <t>Isentas PIS</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
         <v>0.7857</v>
       </c>
@@ -7544,20 +6666,12 @@
           <t>All candidates have semantic header conflicts with the PIS tax family and provide no relevant row evidence.</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" t="inlineStr"/>
-      <c r="U124" t="inlineStr"/>
-      <c r="V124" t="inlineStr"/>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7568,8 +6682,6 @@
           <t>Outras PIS</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="n">
         <v>0.7998</v>
       </c>
@@ -7600,20 +6712,12 @@
           <t>No suitable candidate due to tax-family conflicts and all-zero evidence.</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" t="inlineStr"/>
-      <c r="U125" t="inlineStr"/>
-      <c r="V125" t="inlineStr"/>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7624,8 +6728,6 @@
           <t>Tipo de Imposto PIS</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="n">
         <v>0.7726</v>
       </c>
@@ -7656,20 +6758,12 @@
           <t>All candidates have semantic conflicts with the PIS tax type, making them incompatible.</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="inlineStr"/>
-      <c r="U126" t="inlineStr"/>
-      <c r="V126" t="inlineStr"/>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7680,8 +6774,6 @@
           <t>Base Reduzida PIS</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="n">
         <v>0.7673</v>
       </c>
@@ -7712,20 +6804,12 @@
           <t>All candidates have semantic header conflicts with the PIS tax base, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="inlineStr"/>
-      <c r="U127" t="inlineStr"/>
-      <c r="V127" t="inlineStr"/>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7736,8 +6820,6 @@
           <t>Tipo de Imposto ISS</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="n">
         <v>0.7795</v>
       </c>
@@ -7768,20 +6850,12 @@
           <t>All candidates conflict with the tax-family of the target column.</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="inlineStr"/>
-      <c r="U128" t="inlineStr"/>
-      <c r="V128" t="inlineStr"/>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7792,8 +6866,6 @@
           <t>Base ISS</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
         <v>0.7634</v>
       </c>
@@ -7824,20 +6896,12 @@
           <t>All candidates conflict with the tax-family of the target column, and no suitable mapping is supported by the data.</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="inlineStr"/>
-      <c r="U129" t="inlineStr"/>
-      <c r="V129" t="inlineStr"/>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7848,8 +6912,6 @@
           <t>Aliquota ISS</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="n">
         <v>0.7783</v>
       </c>
@@ -7880,20 +6942,12 @@
           <t>All candidates have semantic header conflicts with the tax family, making them incompatible.</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="n">
-        <v>0</v>
-      </c>
-      <c r="T130" t="inlineStr"/>
-      <c r="U130" t="inlineStr"/>
-      <c r="V130" t="inlineStr"/>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7904,8 +6958,6 @@
           <t>Valor ISS</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="n">
         <v>0.7897999999999999</v>
       </c>
@@ -7936,20 +6988,12 @@
           <t>All candidates conflict with the tax-family of 'Valor ISS' and provide no relevant evidence.</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" t="inlineStr"/>
-      <c r="U131" t="inlineStr"/>
-      <c r="V131" t="inlineStr"/>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7960,8 +7004,6 @@
           <t>Isentas ISS</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="n">
         <v>0.7833</v>
       </c>
@@ -7992,20 +7034,12 @@
           <t>All candidates conflict with the tax-family context of 'Isentas ISS'.</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="inlineStr"/>
-      <c r="U132" t="inlineStr"/>
-      <c r="V132" t="inlineStr"/>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8016,8 +7050,6 @@
           <t>Outras ISS</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
         <v>0.7975</v>
       </c>
@@ -8048,20 +7080,12 @@
           <t>All candidates have a tax-family conflict with the ISS column, indicating incompatible semantic roles.</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="inlineStr"/>
-      <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8072,8 +7096,6 @@
           <t>Base Reduzida ISS</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="n">
         <v>0.7673</v>
       </c>
@@ -8104,20 +7126,12 @@
           <t>All candidates have semantic header conflicts with the target column, indicating incompatible tax roles.</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="inlineStr"/>
-      <c r="U134" t="inlineStr"/>
-      <c r="V134" t="inlineStr"/>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8128,8 +7142,6 @@
           <t>Base FECP_ST</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="n">
         <v>0.8183</v>
       </c>
@@ -8160,20 +7172,12 @@
           <t>All candidates have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="inlineStr"/>
-      <c r="U135" t="inlineStr"/>
-      <c r="V135" t="inlineStr"/>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8184,8 +7188,6 @@
           <t>Aliquota FECP_ST</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
         <v>0.8093</v>
       </c>
@@ -8216,20 +7218,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="n">
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
         <v>0.8093</v>
       </c>
-      <c r="T136" t="inlineStr"/>
-      <c r="U136" t="inlineStr"/>
-      <c r="V136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8240,8 +7234,6 @@
           <t>Valor FECP_ST</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
         <v>0.8084</v>
       </c>
@@ -8272,20 +7264,12 @@
           <t>All candidate columns have significant semantic conflicts or lack relevant evidence to support a mapping.</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="inlineStr"/>
-      <c r="U137" t="inlineStr"/>
-      <c r="V137" t="inlineStr"/>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8296,8 +7280,6 @@
           <t>Isentas FECP_ST</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="n">
         <v>0.8093</v>
       </c>
@@ -8328,20 +7310,12 @@
           <t>No suitable candidate due to semantic header conflicts and lack of relevant data evidence.</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="inlineStr"/>
-      <c r="U138" t="inlineStr"/>
-      <c r="V138" t="inlineStr"/>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8352,8 +7326,6 @@
           <t>Outras FECP_ST</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="n">
         <v>0.8285</v>
       </c>
@@ -8384,20 +7356,12 @@
           <t>All candidates have conflicting semantic roles or insufficient evidence to support a mapping.</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="inlineStr"/>
-      <c r="U139" t="inlineStr"/>
-      <c r="V139" t="inlineStr"/>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8408,8 +7372,6 @@
           <t>Base Reduzida FECP_ST</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
         <v>0.7835</v>
       </c>
@@ -8440,20 +7402,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
-      <c r="R140" t="n">
+      <c r="U140" t="n">
         <v>0.7835</v>
       </c>
-      <c r="S140" t="n">
+      <c r="V140" t="n">
         <v>0.7835</v>
       </c>
-      <c r="T140" t="inlineStr"/>
-      <c r="U140" t="inlineStr"/>
-      <c r="V140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8464,8 +7418,6 @@
           <t>Tipo de Imposto ICMS_ST</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
         <v>0.8691</v>
       </c>
@@ -8496,20 +7448,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="n">
+      <c r="U141" t="n">
         <v>0.5</v>
       </c>
-      <c r="S141" t="n">
+      <c r="V141" t="n">
         <v>0.5</v>
       </c>
-      <c r="T141" t="inlineStr"/>
-      <c r="U141" t="inlineStr"/>
-      <c r="V141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8520,8 +7464,6 @@
           <t>Base ICMS_ST</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="n">
         <v>0.7914</v>
       </c>
@@ -8552,20 +7494,12 @@
           <t>All candidates have semantic conflicts with the expected role of 'Base ICMS_ST'.</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="inlineStr"/>
-      <c r="U142" t="inlineStr"/>
-      <c r="V142" t="inlineStr"/>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8576,8 +7510,6 @@
           <t>Aliquota ICMS_ST</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
         <v>0.7915</v>
       </c>
@@ -8608,20 +7540,12 @@
           <t>All candidates have semantic conflicts with the tax role of 'Aliquota ICMS_ST' and do not provide relevant mapping evidence.</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" t="inlineStr"/>
-      <c r="U143" t="inlineStr"/>
-      <c r="V143" t="inlineStr"/>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8632,8 +7556,6 @@
           <t>Isentas ICMS_ST</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="n">
         <v>0.7801</v>
       </c>
@@ -8664,20 +7586,12 @@
           <t>All candidates have semantic header conflicts or do not match the expected tax situation for ICMS_ST.</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" t="inlineStr"/>
-      <c r="U144" t="inlineStr"/>
-      <c r="V144" t="inlineStr"/>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8688,8 +7602,6 @@
           <t>Outras ICMS_ST</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
         <v>0.8132</v>
       </c>
@@ -8720,20 +7632,12 @@
           <t>All candidates have semantic header conflicts or do not match the expected tax base role.</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" t="inlineStr"/>
-      <c r="U145" t="inlineStr"/>
-      <c r="V145" t="inlineStr"/>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8744,8 +7648,6 @@
           <t>Base Reduzida ICMS_ST</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
         <v>0.779</v>
       </c>
@@ -8776,20 +7678,12 @@
           <t>All candidates have semantic header conflicts and do not align with the expected role of 'Base Reduzida ICMS_ST'.</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
-      <c r="R146" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" t="n">
+      <c r="U146" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" t="n">
         <v>0.75</v>
       </c>
-      <c r="T146" t="inlineStr"/>
-      <c r="U146" t="inlineStr"/>
-      <c r="V146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8800,8 +7694,6 @@
           <t>Ctg.class.cont.</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
         <v>0.7998</v>
       </c>
@@ -8832,20 +7724,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="n">
+      <c r="U147" t="n">
         <v>0.8</v>
       </c>
-      <c r="S147" t="n">
+      <c r="V147" t="n">
         <v>0.8</v>
       </c>
-      <c r="T147" t="inlineStr"/>
-      <c r="U147" t="inlineStr"/>
-      <c r="V147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8856,8 +7740,6 @@
           <t>Municipio Inicio</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="n">
         <v>0.7685</v>
       </c>
@@ -8888,20 +7770,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" t="n">
+      <c r="U148" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" t="n">
         <v>0.7685</v>
       </c>
-      <c r="T148" t="inlineStr"/>
-      <c r="U148" t="inlineStr"/>
-      <c r="V148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8912,8 +7786,6 @@
           <t>Data de criação</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="n">
         <v>0.7773</v>
       </c>
@@ -8944,20 +7816,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
-      <c r="R149" t="n">
+      <c r="U149" t="n">
         <v>0.8</v>
       </c>
-      <c r="S149" t="n">
+      <c r="V149" t="n">
         <v>0.7886</v>
       </c>
-      <c r="T149" t="inlineStr"/>
-      <c r="U149" t="inlineStr"/>
-      <c r="V149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8968,8 +7832,6 @@
           <t>Criado às:</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="n">
         <v>0.7074</v>
       </c>
@@ -9000,20 +7862,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
-      <c r="R150" t="n">
+      <c r="U150" t="n">
         <v>0.5</v>
       </c>
-      <c r="S150" t="n">
+      <c r="V150" t="n">
         <v>0.5</v>
       </c>
-      <c r="T150" t="inlineStr"/>
-      <c r="U150" t="inlineStr"/>
-      <c r="V150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -9024,8 +7878,6 @@
           <t>Exercício</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="n">
         <v>0.8161</v>
       </c>
@@ -9056,20 +7908,12 @@
           <t>All candidate columns are empty, providing no evidence for a mapping.</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
-      <c r="R151" t="n">
-        <v>0</v>
-      </c>
-      <c r="S151" t="n">
+      <c r="U151" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" t="n">
         <v>0.8161</v>
       </c>
-      <c r="T151" t="inlineStr"/>
-      <c r="U151" t="inlineStr"/>
-      <c r="V151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -9080,8 +7924,6 @@
           <t>Redução</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="n">
         <v>0.7748</v>
       </c>
@@ -9112,20 +7954,12 @@
           <t>No suitable candidate matches the semantic role of 'Redução' as all candidates are unrelated.</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
-      <c r="R152" t="n">
-        <v>0</v>
-      </c>
-      <c r="S152" t="n">
-        <v>0</v>
-      </c>
-      <c r="T152" t="inlineStr"/>
-      <c r="U152" t="inlineStr"/>
-      <c r="V152" t="inlineStr"/>
+      <c r="U152" t="n">
+        <v>0</v>
+      </c>
+      <c r="V152" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -9136,8 +7970,6 @@
           <t>Data de estorno</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="n">
         <v>0.7454</v>
       </c>
@@ -9168,20 +8000,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="n">
+      <c r="U153" t="n">
         <v>0.8</v>
       </c>
-      <c r="S153" t="n">
+      <c r="V153" t="n">
         <v>0.7627</v>
       </c>
-      <c r="T153" t="inlineStr"/>
-      <c r="U153" t="inlineStr"/>
-      <c r="V153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -9192,8 +8016,6 @@
           <t>Cód.domicílio fiscal</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
         <v>0.8545</v>
       </c>
@@ -9224,20 +8046,12 @@
           <t>All candidate columns have empty or non-informative profiles, providing no evidence for a mapping.</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="n">
-        <v>0</v>
-      </c>
-      <c r="S154" t="n">
-        <v>0</v>
-      </c>
-      <c r="T154" t="inlineStr"/>
-      <c r="U154" t="inlineStr"/>
-      <c r="V154" t="inlineStr"/>
+      <c r="U154" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -9248,8 +8062,6 @@
           <t>Domicílio Fiscal</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
         <v>0.8292</v>
       </c>
@@ -9280,20 +8092,12 @@
           <t>No viable candidates match the semantic role of 'Domicílio Fiscal' as all candidates are unrelated identifiers.</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" t="n">
-        <v>0</v>
-      </c>
-      <c r="T155" t="inlineStr"/>
-      <c r="U155" t="inlineStr"/>
-      <c r="V155" t="inlineStr"/>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -9304,8 +8108,6 @@
           <t>Dt. Faturamento Ent.</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="n">
         <v>0.7975</v>
       </c>
@@ -9336,20 +8138,12 @@
           <t>No suitable candidate found due to lack of non-empty values in the model column.</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="n">
-        <v>0</v>
-      </c>
-      <c r="S156" t="n">
-        <v>0</v>
-      </c>
-      <c r="T156" t="inlineStr"/>
-      <c r="U156" t="inlineStr"/>
-      <c r="V156" t="inlineStr"/>
+      <c r="U156" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9360,8 +8154,6 @@
           <t>ID do consumidor final</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
         <v>0.7703</v>
       </c>
@@ -9392,20 +8184,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="n">
+      <c r="U157" t="n">
         <v>0.85</v>
       </c>
-      <c r="S157" t="n">
+      <c r="V157" t="n">
         <v>0.85</v>
       </c>
-      <c r="T157" t="inlineStr"/>
-      <c r="U157" t="inlineStr"/>
-      <c r="V157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9416,8 +8200,6 @@
           <t>Dest.</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
         <v>0.7551</v>
       </c>
@@ -9448,20 +8230,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="n">
+      <c r="U158" t="n">
         <v>0.85</v>
       </c>
-      <c r="S158" t="n">
+      <c r="V158" t="n">
         <v>0.85</v>
       </c>
-      <c r="T158" t="inlineStr"/>
-      <c r="U158" t="inlineStr"/>
-      <c r="V158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9510,20 +8284,23 @@
           <t>The candidate 'NUMERO NF' has a high numeric fraction and matches the semantic role of 'Nº NF-e dos serviços'.</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="n">
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr"/>
+      <c r="U159" t="n">
         <v>1</v>
       </c>
-      <c r="S159" t="n">
+      <c r="V159" t="n">
         <v>0.8556</v>
       </c>
-      <c r="T159" t="inlineStr"/>
-      <c r="U159" t="inlineStr"/>
-      <c r="V159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9534,8 +8311,6 @@
           <t>Código verificação</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
         <v>0.8272</v>
       </c>
@@ -9566,20 +8341,12 @@
           <t>All candidate columns have insufficient evidence and the model column is empty.</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="n">
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" t="n">
         <v>0.7829</v>
       </c>
-      <c r="T160" t="inlineStr"/>
-      <c r="U160" t="inlineStr"/>
-      <c r="V160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9590,8 +8357,6 @@
           <t>Ordem</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
         <v>0.8438</v>
       </c>
@@ -9622,20 +8387,12 @@
           <t>The candidate 'ORGANIZACAO' has a high name confidence but no relevant data evidence to support a mapping.</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="n">
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" t="n">
         <v>0.8438</v>
       </c>
-      <c r="T161" t="inlineStr"/>
-      <c r="U161" t="inlineStr"/>
-      <c r="V161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9646,8 +8403,6 @@
           <t>Despesas</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="n">
         <v>0.7991</v>
       </c>
@@ -9678,20 +8433,12 @@
           <t>All candidate columns contain non-relevant data types or all-zero values, lacking any semantic match.</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="n">
-        <v>0</v>
-      </c>
-      <c r="T162" t="inlineStr"/>
-      <c r="U162" t="inlineStr"/>
-      <c r="V162" t="inlineStr"/>
+      <c r="U162" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9702,8 +8449,6 @@
           <t>Centro custo</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="n">
         <v>0.8242</v>
       </c>
@@ -9734,20 +8479,12 @@
           <t>The 'Centro custo' column is empty with no valid data to support a mapping.</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
-      <c r="R163" t="n">
-        <v>0</v>
-      </c>
-      <c r="S163" t="n">
-        <v>0</v>
-      </c>
-      <c r="T163" t="inlineStr"/>
-      <c r="U163" t="inlineStr"/>
-      <c r="V163" t="inlineStr"/>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9758,8 +8495,6 @@
           <t>Municipio Fim</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="n">
         <v>0.783</v>
       </c>
@@ -9790,20 +8525,12 @@
           <t>All candidate columns have insufficient evidence and do not match the expected content for 'Municipio Fim'.</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
-      <c r="R164" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" t="n">
-        <v>0</v>
-      </c>
-      <c r="T164" t="inlineStr"/>
-      <c r="U164" t="inlineStr"/>
-      <c r="V164" t="inlineStr"/>
+      <c r="U164" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -9814,8 +8541,6 @@
           <t>Nº material antigo</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
         <v>0.784</v>
       </c>
@@ -9846,20 +8571,12 @@
           <t>No suitable candidate found due to lack of evidence and semantic conflicts.</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
-      <c r="R165" t="n">
-        <v>0</v>
-      </c>
-      <c r="S165" t="n">
-        <v>0</v>
-      </c>
-      <c r="T165" t="inlineStr"/>
-      <c r="U165" t="inlineStr"/>
-      <c r="V165" t="inlineStr"/>
+      <c r="U165" t="n">
+        <v>0</v>
+      </c>
+      <c r="V165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -9908,20 +8625,23 @@
           <t>The column 'COD_PRODUTO' has a high name confidence and contains numeric values that align with item codes, making it a suitable match for 'Código do Item'.</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
-      <c r="R166" t="n">
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr"/>
+      <c r="U166" t="n">
         <v>0.8734</v>
       </c>
-      <c r="S166" t="n">
+      <c r="V166" t="n">
         <v>0.8734</v>
       </c>
-      <c r="T166" t="inlineStr"/>
-      <c r="U166" t="inlineStr"/>
-      <c r="V166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -9970,20 +8690,23 @@
           <t>The candidate 'NUMERO NF' has a strong numeric profile and matches the semantic role of 'Número do NFC-e SAT'.</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
-      <c r="R167" t="n">
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr"/>
+      <c r="U167" t="n">
         <v>1</v>
       </c>
-      <c r="S167" t="n">
+      <c r="V167" t="n">
         <v>0.8369</v>
       </c>
-      <c r="T167" t="inlineStr"/>
-      <c r="U167" t="inlineStr"/>
-      <c r="V167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -9994,8 +8717,6 @@
           <t>CódCtaAnalítica cont.D/C</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
         <v>0.7264</v>
       </c>
@@ -10026,20 +8747,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
-      <c r="R168" t="n">
+      <c r="U168" t="n">
         <v>0.9</v>
       </c>
-      <c r="S168" t="n">
+      <c r="V168" t="n">
         <v>0.85</v>
       </c>
-      <c r="T168" t="inlineStr"/>
-      <c r="U168" t="inlineStr"/>
-      <c r="V168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -10050,8 +8763,6 @@
           <t>Valor da isenção de ICMS</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="n">
         <v>0.8421</v>
       </c>
@@ -10082,20 +8793,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="n">
-        <v>0</v>
-      </c>
-      <c r="S169" t="n">
+      <c r="U169" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" t="n">
         <v>0.8421</v>
       </c>
-      <c r="T169" t="inlineStr"/>
-      <c r="U169" t="inlineStr"/>
-      <c r="V169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -10106,8 +8809,6 @@
           <t>Base de Cálculo ICOP FECP</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="n">
         <v>0.7906</v>
       </c>
@@ -10138,20 +8839,12 @@
           <t>All candidates have semantic header conflicts with the expected tax base role.</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
-      <c r="R170" t="n">
-        <v>0</v>
-      </c>
-      <c r="S170" t="n">
-        <v>0</v>
-      </c>
-      <c r="T170" t="inlineStr"/>
-      <c r="U170" t="inlineStr"/>
-      <c r="V170" t="inlineStr"/>
+      <c r="U170" t="n">
+        <v>0</v>
+      </c>
+      <c r="V170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -10162,8 +8855,6 @@
           <t>Alíquota ICOP FECP</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="n">
         <v>0.8002</v>
       </c>
@@ -10194,20 +8885,12 @@
           <t>All candidates have semantic header conflicts and no distinctive row evidence.</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
-      <c r="R171" t="n">
-        <v>0</v>
-      </c>
-      <c r="S171" t="n">
-        <v>0</v>
-      </c>
-      <c r="T171" t="inlineStr"/>
-      <c r="U171" t="inlineStr"/>
-      <c r="V171" t="inlineStr"/>
+      <c r="U171" t="n">
+        <v>0</v>
+      </c>
+      <c r="V171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -10218,8 +8901,6 @@
           <t>Valor ICOP FECP</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
         <v>0.8208</v>
       </c>
@@ -10250,20 +8931,12 @@
           <t>No suitable candidate due to semantic header conflicts and lack of distinctive row evidence.</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
-      <c r="R172" t="n">
-        <v>0</v>
-      </c>
-      <c r="S172" t="n">
-        <v>0</v>
-      </c>
-      <c r="T172" t="inlineStr"/>
-      <c r="U172" t="inlineStr"/>
-      <c r="V172" t="inlineStr"/>
+      <c r="U172" t="n">
+        <v>0</v>
+      </c>
+      <c r="V172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -10274,8 +8947,6 @@
           <t>Isentas ICOP FECP</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="n">
         <v>0.8006</v>
       </c>
@@ -10306,20 +8977,12 @@
           <t>All candidates have semantic header conflicts and do not match the expected tax situation.</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
-      <c r="R173" t="n">
-        <v>0</v>
-      </c>
-      <c r="S173" t="n">
-        <v>0</v>
-      </c>
-      <c r="T173" t="inlineStr"/>
-      <c r="U173" t="inlineStr"/>
-      <c r="V173" t="inlineStr"/>
+      <c r="U173" t="n">
+        <v>0</v>
+      </c>
+      <c r="V173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -10330,8 +8993,6 @@
           <t>Outras ICOP FECP</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
         <v>0.8278</v>
       </c>
@@ -10362,20 +9023,12 @@
           <t>All candidates have significant semantic header conflicts or lack relevant data evidence.</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
-      <c r="R174" t="n">
-        <v>0</v>
-      </c>
-      <c r="S174" t="n">
-        <v>0</v>
-      </c>
-      <c r="T174" t="inlineStr"/>
-      <c r="U174" t="inlineStr"/>
-      <c r="V174" t="inlineStr"/>
+      <c r="U174" t="n">
+        <v>0</v>
+      </c>
+      <c r="V174" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10424,20 +9077,23 @@
           <t>The header 'NUMERO NF' suggests a document number, but the numeric profile indicates a mismatch with the 'Numero do Pedido' which is more varied and includes non-numeric values.</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
-      <c r="R175" t="n">
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr"/>
+      <c r="U175" t="n">
         <v>0.5</v>
       </c>
-      <c r="S175" t="n">
+      <c r="V175" t="n">
         <v>0.831</v>
       </c>
-      <c r="T175" t="inlineStr"/>
-      <c r="U175" t="inlineStr"/>
-      <c r="V175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10486,20 +9142,23 @@
           <t>The candidate 'PROFIT_CENTER' has a high name confidence and a similar numeric profile, but lacks distinctive sample overlap.</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="n">
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr"/>
+      <c r="U176" t="n">
         <v>0.8</v>
       </c>
-      <c r="S176" t="n">
+      <c r="V176" t="n">
         <v>0.8</v>
       </c>
-      <c r="T176" t="inlineStr"/>
-      <c r="U176" t="inlineStr"/>
-      <c r="V176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -10510,8 +9169,6 @@
           <t>Código de Sit Tributária do CBS e IBD</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="n">
         <v>0.8036</v>
       </c>
@@ -10542,20 +9199,12 @@
           <t>All candidates have semantic header conflicts with the required tax situation, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="n">
-        <v>0</v>
-      </c>
-      <c r="S177" t="n">
-        <v>0</v>
-      </c>
-      <c r="T177" t="inlineStr"/>
-      <c r="U177" t="inlineStr"/>
-      <c r="V177" t="inlineStr"/>
+      <c r="U177" t="n">
+        <v>0</v>
+      </c>
+      <c r="V177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -10566,8 +9215,6 @@
           <t>Código Class Tributária para CBS e IBS</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
       <c r="E178" t="n">
         <v>0.7831</v>
       </c>
@@ -10598,20 +9245,12 @@
           <t>All candidates have semantic header conflicts with the required tax classification.</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="n">
-        <v>0</v>
-      </c>
-      <c r="S178" t="n">
-        <v>0</v>
-      </c>
-      <c r="T178" t="inlineStr"/>
-      <c r="U178" t="inlineStr"/>
-      <c r="V178" t="inlineStr"/>
+      <c r="U178" t="n">
+        <v>0</v>
+      </c>
+      <c r="V178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -10660,20 +9299,23 @@
           <t>The column 'NUMERO NF' closely matches the semantic role of 'Nº documento' with high numeric consistency and a strong name match.</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="n">
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr"/>
+      <c r="U179" t="n">
         <v>0.9</v>
       </c>
-      <c r="S179" t="n">
+      <c r="V179" t="n">
         <v>0.85</v>
       </c>
-      <c r="T179" t="inlineStr"/>
-      <c r="U179" t="inlineStr"/>
-      <c r="V179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -10684,8 +9326,6 @@
           <t>Empresa</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
         <v>0.7511</v>
       </c>
@@ -10716,20 +9356,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
-      <c r="R180" t="n">
+      <c r="U180" t="n">
         <v>0.9</v>
       </c>
-      <c r="S180" t="n">
+      <c r="V180" t="n">
         <v>0.85</v>
       </c>
-      <c r="T180" t="inlineStr"/>
-      <c r="U180" t="inlineStr"/>
-      <c r="V180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -10778,20 +9410,23 @@
           <t>The 'FORNECEDOR' column has a strong name match and informative data, indicating it likely corresponds to the 'Exportador' role.</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
-      <c r="R181" t="n">
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr"/>
+      <c r="U181" t="n">
         <v>0.9</v>
       </c>
-      <c r="S181" t="n">
+      <c r="V181" t="n">
         <v>0.8606</v>
       </c>
-      <c r="T181" t="inlineStr"/>
-      <c r="U181" t="inlineStr"/>
-      <c r="V181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -10802,8 +9437,6 @@
           <t>Lote</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
         <v>0.7905</v>
       </c>
@@ -10834,20 +9467,12 @@
           <t>All candidate columns are empty, providing no evidence for a mapping.</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" t="n">
+      <c r="U182" t="n">
+        <v>0</v>
+      </c>
+      <c r="V182" t="n">
         <v>0.7905</v>
       </c>
-      <c r="T182" t="inlineStr"/>
-      <c r="U182" t="inlineStr"/>
-      <c r="V182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -10858,8 +9483,6 @@
           <t>Tp.declar.importação</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
         <v>0.8127</v>
       </c>
@@ -10890,20 +9513,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="n">
+      <c r="U183" t="n">
         <v>0.8</v>
       </c>
-      <c r="S183" t="n">
+      <c r="V183" t="n">
         <v>0.8127</v>
       </c>
-      <c r="T183" t="inlineStr"/>
-      <c r="U183" t="inlineStr"/>
-      <c r="V183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -10914,8 +9529,6 @@
           <t>Código Fornecedor Início</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="n">
         <v>0.7873</v>
       </c>
@@ -10946,20 +9559,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
-      <c r="R184" t="n">
+      <c r="U184" t="n">
         <v>0.85</v>
       </c>
-      <c r="S184" t="n">
+      <c r="V184" t="n">
         <v>0.85</v>
       </c>
-      <c r="T184" t="inlineStr"/>
-      <c r="U184" t="inlineStr"/>
-      <c r="V184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -10987,7 +9592,6 @@
       <c r="G185" t="n">
         <v>0.1654</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>0.98</v>
       </c>
@@ -11006,16 +9610,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
-      <c r="R185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
       <c r="S185" t="inlineStr"/>
-      <c r="T185" t="inlineStr"/>
-      <c r="U185" t="inlineStr"/>
-      <c r="V185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -11026,8 +9631,6 @@
           <t>Data do desembaraço aduaneiro</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="n">
         <v>0.8021</v>
       </c>
@@ -11058,20 +9661,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
-      <c r="R186" t="n">
+      <c r="U186" t="n">
         <v>0.8</v>
       </c>
-      <c r="S186" t="n">
+      <c r="V186" t="n">
         <v>0.8021</v>
       </c>
-      <c r="T186" t="inlineStr"/>
-      <c r="U186" t="inlineStr"/>
-      <c r="V186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -11082,8 +9677,6 @@
           <t>Data de registro documento de importação</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
       <c r="E187" t="n">
         <v>0.8016</v>
       </c>
@@ -11114,20 +9707,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
-      <c r="R187" t="n">
+      <c r="U187" t="n">
         <v>0.8</v>
       </c>
-      <c r="S187" t="n">
+      <c r="V187" t="n">
         <v>0.8016</v>
       </c>
-      <c r="T187" t="inlineStr"/>
-      <c r="U187" t="inlineStr"/>
-      <c r="V187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -11176,20 +9761,23 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" t="n">
-        <v>0</v>
-      </c>
-      <c r="T188" t="inlineStr"/>
-      <c r="U188" t="inlineStr"/>
-      <c r="V188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr"/>
+      <c r="U188" t="n">
+        <v>0</v>
+      </c>
+      <c r="V188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -11238,20 +9826,23 @@
           <t>The header 'NUM_ITEM' suggests an item identifier, but the data is all zeros, indicating it may not be a valid mapping.</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
-      <c r="R189" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" t="n">
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr"/>
+      <c r="U189" t="n">
+        <v>0</v>
+      </c>
+      <c r="V189" t="n">
         <v>0.9035</v>
       </c>
-      <c r="T189" t="inlineStr"/>
-      <c r="U189" t="inlineStr"/>
-      <c r="V189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -11262,8 +9853,6 @@
           <t>Elemento PEP</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="n">
         <v>0.7822</v>
       </c>
@@ -11294,20 +9883,12 @@
           <t>All candidate columns are empty or lack relevant data evidence.</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
-      <c r="R190" t="n">
-        <v>0</v>
-      </c>
-      <c r="S190" t="n">
-        <v>0</v>
-      </c>
-      <c r="T190" t="inlineStr"/>
-      <c r="U190" t="inlineStr"/>
-      <c r="V190" t="inlineStr"/>
+      <c r="U190" t="n">
+        <v>0</v>
+      </c>
+      <c r="V190" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -11335,7 +9916,6 @@
       <c r="G191" t="n">
         <v>0.0804</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
         <v>0.98</v>
       </c>
@@ -11354,20 +9934,22 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr">
         <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr">
+        <is>
           <t>valor = base x aliquota holds for icms on 2540 rows at fit 1.0</t>
         </is>
       </c>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
-      <c r="T191" t="inlineStr"/>
-      <c r="U191" t="inlineStr"/>
-      <c r="V191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -11378,8 +9960,6 @@
           <t>Tipo Frete</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
         <v>0.7775</v>
       </c>
@@ -11410,20 +9990,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="n">
+      <c r="U192" t="n">
         <v>0.5</v>
       </c>
-      <c r="S192" t="n">
+      <c r="V192" t="n">
         <v>0.75</v>
       </c>
-      <c r="T192" t="inlineStr"/>
-      <c r="U192" t="inlineStr"/>
-      <c r="V192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -11451,7 +10023,6 @@
       <c r="G193" t="n">
         <v>0.0867</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
         <v>0.98</v>
       </c>
@@ -11470,20 +10041,22 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr">
         <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr">
+        <is>
           <t>valor = base x aliquota holds for ipi on 333 rows at fit 1.0</t>
         </is>
       </c>
-      <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
-      <c r="T193" t="inlineStr"/>
-      <c r="U193" t="inlineStr"/>
-      <c r="V193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -11532,20 +10105,23 @@
           <t>The candidate 'IND TRIB IPI' has a high name confidence and matches the IPI tax type despite some numeric discrepancies.</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
-      <c r="R194" t="n">
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr"/>
+      <c r="U194" t="n">
         <v>0.8</v>
       </c>
-      <c r="S194" t="n">
+      <c r="V194" t="n">
         <v>0.85</v>
       </c>
-      <c r="T194" t="inlineStr"/>
-      <c r="U194" t="inlineStr"/>
-      <c r="V194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -11594,20 +10170,23 @@
           <t>The header 'NUM_ITEM' suggests an item number, but the numeric values and profile do not align with the expected format for invoice item numbers.</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
-      <c r="R195" t="n">
-        <v>0</v>
-      </c>
-      <c r="S195" t="n">
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr"/>
+      <c r="U195" t="n">
+        <v>0</v>
+      </c>
+      <c r="V195" t="n">
         <v>0.8752</v>
       </c>
-      <c r="T195" t="inlineStr"/>
-      <c r="U195" t="inlineStr"/>
-      <c r="V195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -11656,20 +10235,23 @@
           <t>The header 'DESC_PRODUTO' closely matches 'Descrição' and the sample values indicate product descriptions.</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
-      <c r="R196" t="n">
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr"/>
+      <c r="U196" t="n">
         <v>0.8</v>
       </c>
-      <c r="S196" t="n">
+      <c r="V196" t="n">
         <v>0.85</v>
       </c>
-      <c r="T196" t="inlineStr"/>
-      <c r="U196" t="inlineStr"/>
-      <c r="V196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11680,8 +10262,6 @@
           <t>Grupo de mercadorias</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" t="n">
         <v>0.7242</v>
       </c>
@@ -11712,20 +10292,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
-      <c r="R197" t="n">
+      <c r="U197" t="n">
         <v>0.85</v>
       </c>
-      <c r="S197" t="n">
+      <c r="V197" t="n">
         <v>0.85</v>
       </c>
-      <c r="T197" t="inlineStr"/>
-      <c r="U197" t="inlineStr"/>
-      <c r="V197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11736,8 +10308,6 @@
           <t>Material</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
       <c r="E198" t="n">
         <v>0.8062</v>
       </c>
@@ -11768,20 +10338,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
-      <c r="R198" t="n">
+      <c r="U198" t="n">
         <v>0.8062</v>
       </c>
-      <c r="S198" t="n">
+      <c r="V198" t="n">
         <v>0.8062</v>
       </c>
-      <c r="T198" t="inlineStr"/>
-      <c r="U198" t="inlineStr"/>
-      <c r="V198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -11830,20 +10392,23 @@
           <t>The header 'COD_MEDIDA' aligns semantically with 'Unidade de medida' and has no conflicting roles.</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
-      <c r="R199" t="n">
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr"/>
+      <c r="U199" t="n">
         <v>0.8463000000000001</v>
       </c>
-      <c r="S199" t="n">
+      <c r="V199" t="n">
         <v>0.8463000000000001</v>
       </c>
-      <c r="T199" t="inlineStr"/>
-      <c r="U199" t="inlineStr"/>
-      <c r="V199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -11871,7 +10436,6 @@
       <c r="G200" t="n">
         <v>0.1652</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
         <v>1</v>
       </c>
@@ -11890,16 +10454,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
-      <c r="R200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
       <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr"/>
-      <c r="U200" t="inlineStr"/>
-      <c r="V200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -11910,8 +10475,6 @@
           <t>Município do Local de Fim</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="n">
         <v>0.7675999999999999</v>
       </c>
@@ -11942,20 +10505,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
-      <c r="S201" t="n">
+      <c r="U201" t="n">
+        <v>0</v>
+      </c>
+      <c r="V201" t="n">
         <v>0.7675999999999999</v>
       </c>
-      <c r="T201" t="inlineStr"/>
-      <c r="U201" t="inlineStr"/>
-      <c r="V201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -11966,8 +10521,6 @@
           <t>Município do Local de Início</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="n">
         <v>0.784</v>
       </c>
@@ -11998,20 +10551,12 @@
           <t>The candidate 'LOCATION' does not semantically match 'Município do Local de Início' as it lacks relevant municipal data.</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
-      <c r="R202" t="n">
-        <v>0</v>
-      </c>
-      <c r="S202" t="n">
-        <v>0</v>
-      </c>
-      <c r="T202" t="inlineStr"/>
-      <c r="U202" t="inlineStr"/>
-      <c r="V202" t="inlineStr"/>
+      <c r="U202" t="n">
+        <v>0</v>
+      </c>
+      <c r="V202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -12022,8 +10567,6 @@
           <t>IVA</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="n">
         <v>0.8247</v>
       </c>
@@ -12054,20 +10597,12 @@
           <t>All candidates have semantic header conflicts with the IVA role, indicating incompatible tax-family contexts.</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
-      <c r="R203" t="n">
-        <v>0</v>
-      </c>
-      <c r="S203" t="n">
-        <v>0</v>
-      </c>
-      <c r="T203" t="inlineStr"/>
-      <c r="U203" t="inlineStr"/>
-      <c r="V203" t="inlineStr"/>
+      <c r="U203" t="n">
+        <v>0</v>
+      </c>
+      <c r="V203" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -12078,8 +10613,6 @@
           <t>Nome Transportadora</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="n">
         <v>0.804</v>
       </c>
@@ -12110,20 +10643,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr"/>
-      <c r="R204" t="n">
+      <c r="U204" t="n">
         <v>0.8</v>
       </c>
-      <c r="S204" t="n">
+      <c r="V204" t="n">
         <v>0.804</v>
       </c>
-      <c r="T204" t="inlineStr"/>
-      <c r="U204" t="inlineStr"/>
-      <c r="V204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -12134,8 +10659,6 @@
           <t>Nº do NCM</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="n">
         <v>0.8375</v>
       </c>
@@ -12166,20 +10689,12 @@
           <t>The header 'NUMERO NF' conflicts semantically with 'Nº do NCM', which is a tax classification code.</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
-      <c r="R205" t="n">
-        <v>0</v>
-      </c>
-      <c r="S205" t="n">
-        <v>0</v>
-      </c>
-      <c r="T205" t="inlineStr"/>
-      <c r="U205" t="inlineStr"/>
-      <c r="V205" t="inlineStr"/>
+      <c r="U205" t="n">
+        <v>0</v>
+      </c>
+      <c r="V205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -12228,20 +10743,23 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
-      <c r="R206" t="n">
-        <v>0</v>
-      </c>
-      <c r="S206" t="n">
-        <v>0</v>
-      </c>
-      <c r="T206" t="inlineStr"/>
-      <c r="U206" t="inlineStr"/>
-      <c r="V206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr"/>
+      <c r="U206" t="n">
+        <v>0</v>
+      </c>
+      <c r="V206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -12290,20 +10808,23 @@
           <t>The name 'PRECO UNITARIO' suggests a unit price, while 'Preço líq.' indicates a net price, leading to a semantic conflict.</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr"/>
-      <c r="R207" t="n">
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr"/>
+      <c r="U207" t="n">
         <v>0.8</v>
       </c>
-      <c r="S207" t="n">
+      <c r="V207" t="n">
         <v>0.8266</v>
       </c>
-      <c r="T207" t="inlineStr"/>
-      <c r="U207" t="inlineStr"/>
-      <c r="V207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -12314,8 +10835,6 @@
           <t>Valor líquido</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
       <c r="E208" t="n">
         <v>0.7917</v>
       </c>
@@ -12346,20 +10865,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
-      <c r="R208" t="n">
+      <c r="U208" t="n">
         <v>0.8</v>
       </c>
-      <c r="S208" t="n">
+      <c r="V208" t="n">
         <v>0.785</v>
       </c>
-      <c r="T208" t="inlineStr"/>
-      <c r="U208" t="inlineStr"/>
-      <c r="V208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -12370,8 +10881,6 @@
           <t>NF/NF-e do serviço</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="n">
         <v>0.851</v>
       </c>
@@ -12402,20 +10911,12 @@
           <t>The candidate 'NUMERO NF' is numeric and does not match the string type of 'NF/NF-e do serviço'.</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr"/>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="n">
-        <v>0</v>
-      </c>
-      <c r="T209" t="inlineStr"/>
-      <c r="U209" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -12464,20 +10965,23 @@
           <t>The candidate 'NUMERO NF' has a high name confidence and a substantial non-empty count, indicating it likely represents the invoice number.</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
-      <c r="R210" t="n">
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr"/>
+      <c r="U210" t="n">
         <v>1</v>
       </c>
-      <c r="S210" t="n">
+      <c r="V210" t="n">
         <v>0.8627</v>
       </c>
-      <c r="T210" t="inlineStr"/>
-      <c r="U210" t="inlineStr"/>
-      <c r="V210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -12526,20 +11030,23 @@
           <t>The column 'TOTAL DO ITEM' closely matches the canonical 'Valor Total do Item' in both name and numeric profile.</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
-      <c r="R211" t="n">
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr"/>
+      <c r="U211" t="n">
         <v>0.9388</v>
       </c>
-      <c r="S211" t="n">
+      <c r="V211" t="n">
         <v>0.9388</v>
       </c>
-      <c r="T211" t="inlineStr"/>
-      <c r="U211" t="inlineStr"/>
-      <c r="V211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12550,8 +11057,6 @@
           <t>Nome do Fornecedor do Local de Início</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
         <v>0.8307</v>
       </c>
@@ -12582,20 +11087,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
-      <c r="R212" t="n">
+      <c r="U212" t="n">
         <v>0.4406</v>
       </c>
-      <c r="S212" t="n">
+      <c r="V212" t="n">
         <v>0.8307</v>
       </c>
-      <c r="T212" t="inlineStr"/>
-      <c r="U212" t="inlineStr"/>
-      <c r="V212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12606,8 +11103,6 @@
           <t>Cód Transportadora</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" t="n">
         <v>0.8136</v>
       </c>
@@ -12638,20 +11133,12 @@
           <t>No suitable candidate found due to lack of evidence and all candidates being unrelated to 'Cód Transportadora'.</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="n">
-        <v>0</v>
-      </c>
-      <c r="T213" t="inlineStr"/>
-      <c r="U213" t="inlineStr"/>
-      <c r="V213" t="inlineStr"/>
+      <c r="U213" t="n">
+        <v>0</v>
+      </c>
+      <c r="V213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12679,7 +11166,6 @@
       <c r="G214" t="n">
         <v>0.1912</v>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
         <v>0.98</v>
       </c>
@@ -12698,16 +11184,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
-      <c r="R214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
       <c r="S214" t="inlineStr"/>
-      <c r="T214" t="inlineStr"/>
-      <c r="U214" t="inlineStr"/>
-      <c r="V214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12718,8 +11205,6 @@
           <t>Ref.doc.origem</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
       <c r="E215" t="n">
         <v>0.7819</v>
       </c>
@@ -12750,20 +11235,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
-      <c r="R215" t="n">
+      <c r="U215" t="n">
         <v>0.5</v>
       </c>
-      <c r="S215" t="n">
+      <c r="V215" t="n">
         <v>0.75</v>
       </c>
-      <c r="T215" t="inlineStr"/>
-      <c r="U215" t="inlineStr"/>
-      <c r="V215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -12812,20 +11289,23 @@
           <t>The header 'IND TRIB ICMS' suggests a tax indicator for ICMS, but the numeric values and type do not align with the expected text format of 'Texto ICMS'.</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
-      <c r="R216" t="n">
-        <v>0</v>
-      </c>
-      <c r="S216" t="n">
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr"/>
+      <c r="U216" t="n">
+        <v>0</v>
+      </c>
+      <c r="V216" t="n">
         <v>0.889</v>
       </c>
-      <c r="T216" t="inlineStr"/>
-      <c r="U216" t="inlineStr"/>
-      <c r="V216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -12874,20 +11354,23 @@
           <t>The header 'IND TRIB IPI' aligns with the IPI tax context, despite the numeric profile indicating a different type.</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
-      <c r="R217" t="n">
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr"/>
+      <c r="U217" t="n">
         <v>0.5</v>
       </c>
-      <c r="S217" t="n">
+      <c r="V217" t="n">
         <v>0.835</v>
       </c>
-      <c r="T217" t="inlineStr"/>
-      <c r="U217" t="inlineStr"/>
-      <c r="V217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -12898,8 +11381,6 @@
           <t>Lei COFINS</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr"/>
       <c r="E218" t="n">
         <v>0.8171</v>
       </c>
@@ -12930,20 +11411,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
-      <c r="R218" t="n">
+      <c r="U218" t="n">
         <v>0.8171</v>
       </c>
-      <c r="S218" t="n">
+      <c r="V218" t="n">
         <v>0.8171</v>
       </c>
-      <c r="T218" t="inlineStr"/>
-      <c r="U218" t="inlineStr"/>
-      <c r="V218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -12954,8 +11427,6 @@
           <t>Lei tributária PIS</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
       <c r="E219" t="n">
         <v>0.7871</v>
       </c>
@@ -12986,20 +11457,12 @@
           <t>All candidates have semantic header conflicts with the PIS tax family, indicating incompatible mappings.</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
-      <c r="R219" t="n">
-        <v>0</v>
-      </c>
-      <c r="S219" t="n">
-        <v>0</v>
-      </c>
-      <c r="T219" t="inlineStr"/>
-      <c r="U219" t="inlineStr"/>
-      <c r="V219" t="inlineStr"/>
+      <c r="U219" t="n">
+        <v>0</v>
+      </c>
+      <c r="V219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -13027,7 +11490,6 @@
       <c r="G220" t="n">
         <v>0.1172</v>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
         <v>1</v>
       </c>
@@ -13060,12 +11522,17 @@
       <c r="P220" t="n">
         <v>0.55</v>
       </c>
-      <c r="Q220" t="inlineStr"/>
-      <c r="R220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>semantic + catalog (agrees)</t>
+        </is>
+      </c>
       <c r="S220" t="inlineStr"/>
-      <c r="T220" t="inlineStr"/>
-      <c r="U220" t="inlineStr"/>
-      <c r="V220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -13093,7 +11560,6 @@
       <c r="G221" t="n">
         <v>0.1684</v>
       </c>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
         <v>1</v>
       </c>
@@ -13126,12 +11592,17 @@
       <c r="P221" t="n">
         <v>0.55</v>
       </c>
-      <c r="Q221" t="inlineStr"/>
-      <c r="R221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>semantic + catalog (agrees)</t>
+        </is>
+      </c>
       <c r="S221" t="inlineStr"/>
-      <c r="T221" t="inlineStr"/>
-      <c r="U221" t="inlineStr"/>
-      <c r="V221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -13159,7 +11630,6 @@
       <c r="G222" t="n">
         <v>0.1934</v>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
         <v>1</v>
       </c>
@@ -13192,12 +11662,17 @@
       <c r="P222" t="n">
         <v>0.55</v>
       </c>
-      <c r="Q222" t="inlineStr"/>
-      <c r="R222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>semantic + catalog (agrees)</t>
+        </is>
+      </c>
       <c r="S222" t="inlineStr"/>
-      <c r="T222" t="inlineStr"/>
-      <c r="U222" t="inlineStr"/>
-      <c r="V222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -13225,7 +11700,6 @@
       <c r="G223" t="n">
         <v>0.1057</v>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="n">
         <v>1</v>
       </c>
@@ -13258,12 +11732,17 @@
       <c r="P223" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q223" t="inlineStr"/>
-      <c r="R223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>semantic + catalog (agrees)</t>
+        </is>
+      </c>
       <c r="S223" t="inlineStr"/>
-      <c r="T223" t="inlineStr"/>
-      <c r="U223" t="inlineStr"/>
-      <c r="V223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -13274,8 +11753,6 @@
           <t>Região do local do desembaraço aduaneiro</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" t="n">
         <v>0.7998</v>
       </c>
@@ -13306,20 +11783,12 @@
           <t>The candidate 'LOCATION' has a high non-empty count but lacks relevant content to match the semantic role of 'Região do local do desembaraço aduaneiro'.</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
-      <c r="R224" t="n">
-        <v>0</v>
-      </c>
-      <c r="S224" t="n">
+      <c r="U224" t="n">
+        <v>0</v>
+      </c>
+      <c r="V224" t="n">
         <v>0.7998</v>
       </c>
-      <c r="T224" t="inlineStr"/>
-      <c r="U224" t="inlineStr"/>
-      <c r="V224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -13330,8 +11799,6 @@
           <t>UF do Local de Fim</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" t="n">
         <v>0.7813</v>
       </c>
@@ -13362,20 +11829,12 @@
           <t>All client candidates have insufficient evidence and do not match the semantic role of 'UF do Local de Fim'.</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
-      <c r="R225" t="n">
-        <v>0</v>
-      </c>
-      <c r="S225" t="n">
-        <v>0</v>
-      </c>
-      <c r="T225" t="inlineStr"/>
-      <c r="U225" t="inlineStr"/>
-      <c r="V225" t="inlineStr"/>
+      <c r="U225" t="n">
+        <v>0</v>
+      </c>
+      <c r="V225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -13386,8 +11845,6 @@
           <t>UF do Local de Início</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="n">
         <v>0.7805</v>
       </c>
@@ -13418,20 +11875,12 @@
           <t>The candidate 'LOCATION' does not semantically match 'UF do Local de Início' as it lacks relevant content evidence.</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
-      <c r="R226" t="n">
-        <v>0</v>
-      </c>
-      <c r="S226" t="n">
-        <v>0</v>
-      </c>
-      <c r="T226" t="inlineStr"/>
-      <c r="U226" t="inlineStr"/>
-      <c r="V226" t="inlineStr"/>
+      <c r="U226" t="n">
+        <v>0</v>
+      </c>
+      <c r="V226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -13442,8 +11891,6 @@
           <t>Centro</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
       <c r="E227" t="n">
         <v>0.7725</v>
       </c>
@@ -13474,20 +11921,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
-      <c r="R227" t="n">
+      <c r="U227" t="n">
         <v>0.85</v>
       </c>
-      <c r="S227" t="n">
+      <c r="V227" t="n">
         <v>0.8</v>
       </c>
-      <c r="T227" t="inlineStr"/>
-      <c r="U227" t="inlineStr"/>
-      <c r="V227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -13498,8 +11937,6 @@
           <t>Local do desembaraço aduaneiro</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" t="n">
         <v>0.8005</v>
       </c>
@@ -13530,20 +11967,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
-      <c r="R228" t="n">
+      <c r="U228" t="n">
         <v>0.8</v>
       </c>
-      <c r="S228" t="n">
+      <c r="V228" t="n">
         <v>0.8005</v>
       </c>
-      <c r="T228" t="inlineStr"/>
-      <c r="U228" t="inlineStr"/>
-      <c r="V228" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13918,7 +12347,6 @@
       <c r="F3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -13958,7 +12386,6 @@
       <c r="F4" t="n">
         <v>250</v>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -13998,7 +12425,6 @@
       <c r="F5" t="n">
         <v>3469</v>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14038,7 +12464,6 @@
       <c r="F6" t="n">
         <v>1636</v>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14078,7 +12503,6 @@
       <c r="F7" t="n">
         <v>4318</v>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14118,7 +12542,6 @@
       <c r="F8" t="n">
         <v>1636</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14202,7 +12625,6 @@
       <c r="F10" t="n">
         <v>9</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14242,7 +12664,6 @@
       <c r="F11" t="n">
         <v>3824</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14282,7 +12703,6 @@
       <c r="F12" t="n">
         <v>4430</v>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14322,7 +12742,6 @@
       <c r="F13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14362,7 +12781,6 @@
       <c r="F14" t="n">
         <v>2</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14402,7 +12820,6 @@
       <c r="F15" t="n">
         <v>31</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14442,7 +12859,6 @@
       <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14482,7 +12898,6 @@
       <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14522,7 +12937,6 @@
       <c r="F18" t="n">
         <v>6</v>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14562,7 +12976,6 @@
       <c r="F19" t="n">
         <v>250</v>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14602,7 +13015,6 @@
       <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14642,7 +13054,6 @@
       <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>No values in this column.</t>
@@ -14682,7 +13093,6 @@
       <c r="F22" t="n">
         <v>17</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14722,7 +13132,6 @@
       <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14762,7 +13171,6 @@
       <c r="F24" t="n">
         <v>4430</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14802,7 +13210,6 @@
       <c r="F25" t="n">
         <v>75</v>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14842,7 +13249,6 @@
       <c r="F26" t="n">
         <v>49</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14882,7 +13288,6 @@
       <c r="F27" t="n">
         <v>3</v>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14922,7 +13327,6 @@
       <c r="F28" t="n">
         <v>160</v>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -14962,7 +13366,6 @@
       <c r="F29" t="n">
         <v>6</v>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -15002,7 +13405,6 @@
       <c r="F30" t="n">
         <v>2</v>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -15042,7 +13444,6 @@
       <c r="F31" t="n">
         <v>3</v>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Carries data, but no signal matched. Listed for completeness.</t>
@@ -15170,8 +13571,6 @@
       <c r="I2" t="n">
         <v>7338</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>18567 | 14488 | -2390413 | 235 | 808.5 | 2077.92</t>
@@ -15215,8 +13614,6 @@
       <c r="I3" t="n">
         <v>7334</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>999991 | 0 | 1720894 | 1882854 | 2185041 | 2595237</t>
@@ -15260,8 +13657,6 @@
       <c r="I4" t="n">
         <v>7338</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>2 | 3</t>
@@ -15305,8 +13700,6 @@
       <c r="I5" t="n">
         <v>7338</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>2 | 3</t>
@@ -15350,8 +13743,6 @@
       <c r="I6" t="n">
         <v>7338</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>2 | 3</t>
@@ -15395,8 +13786,6 @@
       <c r="I7" t="n">
         <v>7338</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>2 | 3</t>
@@ -15440,8 +13829,6 @@
       <c r="I8" t="n">
         <v>7060</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>PORT STORAGE | EMBRATEL TV | PORTABLE GAS DETECTOR FOR CALIBRATION - Serial #4000232 #4000560 #174334 | GLUCAGEN HYPOKIT INJETAVEL 1MG (1UI) REG.MS:1176600140018 | DOXICICLINA 100MG C/ 15 CPR | 19 - 9044107 - TALHA MANUAL - SWL 2,00 TON X 5,00 METROS</t>
@@ -15485,8 +13872,6 @@
       <c r="I9" t="n">
         <v>7060</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>PORT STORAGE | EMBRATEL TV | PORTABLE GAS DETECTOR FOR CALIBRATION - Serial #4000232 #4000560 #174334 | GLUCAGEN HYPOKIT INJETAVEL 1MG (1UI) REG.MS:1176600140018 | DOXICICLINA 100MG C/ 15 CPR | 19 - 9044107 - TALHA MANUAL - SWL 2,00 TON X 5,00 METROS</t>
@@ -15530,8 +13915,6 @@
       <c r="I10" t="n">
         <v>7338</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>2 | 3</t>
@@ -15580,7 +13963,6 @@
           <t>resolver scored it 0.1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>2 | 3</t>
@@ -15624,8 +14006,6 @@
       <c r="I12" t="n">
         <v>7338</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>2 | 3</t>
@@ -15669,8 +14049,6 @@
       <c r="I13" t="n">
         <v>7334</v>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>999991 | 0 | 1720894 | 1882854 | 2185041 | 2595237</t>
@@ -15714,8 +14092,6 @@
       <c r="I14" t="n">
         <v>7334</v>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>999991 | 0 | 1720894 | 1882854 | 2185041 | 2595237</t>
@@ -15759,8 +14135,6 @@
       <c r="I15" t="n">
         <v>7338</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>2025-12-03 00:00:00 | 2025-10-02 00:00:00 | 2025-10-01 00:00:00 | 2025-10-10 00:00:00 | 2025-10-22 00:00:00 | 2025-10-30 00:00:00</t>
@@ -15804,8 +14178,6 @@
       <c r="I16" t="n">
         <v>7338</v>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>' | '2318 | '2270 | '2321 | '9006 | '9015</t>
@@ -15849,8 +14221,6 @@
       <c r="I17" t="n">
         <v>7338</v>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
@@ -15894,8 +14264,6 @@
       <c r="I18" t="n">
         <v>7338</v>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>DRAGER SAFETY DO BRASIL EQUIPAMENTOS DE SEGURANCA LTDA. | ALIANCA COMERCIO IMPORTACAO E EXPORTACAO LTDA | S3 SAFETY LTDA | BOOT-TEC ELETRONICA E INFORMATICA LTDA | DISTRIBUIDORA SUED OFFSHORE LTDA (DROGARCIA) | HUMBERTO AVILA SOCIEDADE DE ADVOGADOS</t>
@@ -15939,8 +14307,6 @@
       <c r="I19" t="n">
         <v>7338</v>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>2 | 3</t>
@@ -15984,8 +14350,6 @@
       <c r="I20" t="n">
         <v>7338</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
@@ -16029,8 +14393,6 @@
       <c r="I21" t="n">
         <v>7338</v>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
@@ -16074,8 +14436,6 @@
       <c r="I22" t="n">
         <v>7338</v>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>1128 | 1999 | 1554 | 1556 | 1916 | 1949</t>
@@ -16124,7 +14484,6 @@
           <t>resolver scored it 0.0</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>2 | 3</t>
@@ -16168,8 +14527,6 @@
       <c r="I24" t="n">
         <v>7338</v>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>18567 | 395 | -164122.47 | 39.84 | 279.87 | 1080</t>
@@ -16213,8 +14570,6 @@
       <c r="I25" t="n">
         <v>7338</v>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>Ea | Piece | Hours | Inches | Kilograms | Kit</t>
@@ -16258,8 +14613,6 @@
       <c r="I26" t="n">
         <v>7338</v>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
@@ -16308,7 +14661,6 @@
           <t>resolver scored it 0.0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>55 | NFS-E | FATURA | NFSC</t>
@@ -16352,8 +14704,6 @@
       <c r="I28" t="n">
         <v>7338</v>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
@@ -16397,8 +14747,6 @@
       <c r="I29" t="n">
         <v>7338</v>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
@@ -16447,7 +14795,6 @@
           <t>resolver scored it 0.5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
@@ -16496,7 +14843,6 @@
           <t>resolver scored it 0.0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>55 | NFS-E | FATURA | NFSC</t>
@@ -16540,8 +14886,6 @@
       <c r="I32" t="n">
         <v>7338</v>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>18567 | 14488 | -2390413 | 235 | 808.5 | 2077.92</t>
@@ -16585,8 +14929,6 @@
       <c r="I33" t="n">
         <v>7338</v>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
@@ -16630,8 +14972,6 @@
       <c r="I34" t="n">
         <v>7338</v>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
@@ -16675,8 +15015,6 @@
       <c r="I35" t="n">
         <v>7338</v>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
@@ -16725,7 +15063,6 @@
           <t>resolver scored it 0.0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>18567 | 14488 | -2390413 | 235 | 808.5 | 2077.92</t>
@@ -16769,8 +15106,6 @@
       <c r="I37" t="n">
         <v>7060</v>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>PORT STORAGE | EMBRATEL TV | PORTABLE GAS DETECTOR FOR CALIBRATION - Serial #4000232 #4000560 #174334 | GLUCAGEN HYPOKIT INJETAVEL 1MG (1UI) REG.MS:1176600140018 | DOXICICLINA 100MG C/ 15 CPR | 19 - 9044107 - TALHA MANUAL - SWL 2,00 TON X 5,00 METROS</t>
@@ -16814,8 +15149,6 @@
       <c r="I38" t="n">
         <v>7338</v>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>10030 | 12289 | 3 | 1972 | 4870 | 10821</t>
